--- a/RL.xlsx
+++ b/RL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA7ABB71-593F-49CA-96C2-09B438A8E4A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67FC25D3-54A9-4893-8E41-C6546E075209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{964FB9B6-5A0B-4BED-B971-24C834B20146}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{964FB9B6-5A0B-4BED-B971-24C834B20146}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="300">
   <si>
     <t>Ralph Lauren</t>
   </si>
@@ -319,9 +319,6 @@
     <t>Tax Rate</t>
   </si>
   <si>
-    <t>Balance Sheet</t>
-  </si>
-  <si>
     <t>Cash &amp; Cash Equivalents</t>
   </si>
   <si>
@@ -409,33 +406,12 @@
     <t>Total Liabilties</t>
   </si>
   <si>
-    <t>Class A Commom Stock</t>
-  </si>
-  <si>
-    <t>Class B Commom Stock</t>
-  </si>
-  <si>
-    <t>Additional Paid in Capital</t>
-  </si>
-  <si>
-    <t>Retained Earnings</t>
-  </si>
-  <si>
-    <t>Treassury Stock</t>
-  </si>
-  <si>
-    <t>Accumalted comprehensive loss</t>
-  </si>
-  <si>
     <t xml:space="preserve">Total Equity </t>
   </si>
   <si>
     <t xml:space="preserve">Total Liabilites &amp; Equity </t>
   </si>
   <si>
-    <t>Cash Flow Statement</t>
-  </si>
-  <si>
     <t>D&amp;A</t>
   </si>
   <si>
@@ -959,6 +935,9 @@
   </si>
   <si>
     <t>Outlets</t>
+  </si>
+  <si>
+    <t>FY26</t>
   </si>
 </sst>
 </file>
@@ -971,13 +950,19 @@
     <numFmt numFmtId="166" formatCode="#,##0.0;\(#,##0.0\)"/>
     <numFmt numFmtId="167" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1055,60 +1040,62 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1521,25 +1508,25 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="H2" s="2">
-        <v>338.01</v>
+        <v>376.91</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G3" s="2" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="H3" s="3">
-        <f>38.655137+21.881276</f>
-        <v>60.536413000000003</v>
+        <f>37.63507+21.991276</f>
+        <v>59.626345999999998</v>
       </c>
       <c r="I3" s="28" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -1552,7 +1539,7 @@
       </c>
       <c r="H4" s="3">
         <f>H3*H2</f>
-        <v>20461.91295813</v>
+        <v>22473.766070860001</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -1564,11 +1551,11 @@
         <v>11</v>
       </c>
       <c r="H5" s="3">
-        <f>2031.9+218.9</f>
-        <v>2250.8000000000002</v>
+        <f>1988+77</f>
+        <v>2065</v>
       </c>
       <c r="I5" s="28" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -1582,11 +1569,11 @@
         <v>10</v>
       </c>
       <c r="H6" s="3">
-        <f>0+1238.3</f>
-        <v>1238.3</v>
+        <f>0+1238.9</f>
+        <v>1238.9000000000001</v>
       </c>
       <c r="I6" s="28" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -1595,7 +1582,7 @@
       </c>
       <c r="H7" s="3">
         <f>H4+H5-H6</f>
-        <v>21474.41295813</v>
+        <v>23299.86607086</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
@@ -1603,7 +1590,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="J9" s="7" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
@@ -1627,7 +1614,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>55</v>
@@ -1852,64 +1839,57 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DECD0C8-AF9F-4DAB-A92B-C0DC872AC0C1}">
-  <dimension ref="A1:AD135"/>
+  <dimension ref="A1:AD120"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="40.5703125" style="2" customWidth="1"/>
-    <col min="3" max="15" width="9.140625" style="2"/>
-    <col min="16" max="22" width="8.7109375" style="3"/>
-    <col min="23" max="16384" width="9.140625" style="2"/>
+    <col min="3" max="15" width="9.140625" style="12"/>
+    <col min="16" max="22" width="8.7109375" style="12"/>
+    <col min="23" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:24" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:24" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C2" s="4" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="O2" s="4"/>
       <c r="P2" s="4" t="s">
@@ -1933,10 +1913,13 @@
       <c r="V2" s="4" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W2" s="28" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -1972,10 +1955,14 @@
       <c r="V3" s="4">
         <v>223</v>
       </c>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W3" s="2">
+        <f>53+166</f>
+        <v>219</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
@@ -2011,10 +1998,14 @@
       <c r="V4" s="4">
         <v>104</v>
       </c>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W4" s="2">
+        <f>57+54</f>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
@@ -2050,10 +2041,14 @@
       <c r="V5" s="4">
         <v>237</v>
       </c>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W5" s="2">
+        <f>87+177</f>
+        <v>264</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -2094,10 +2089,13 @@
       <c r="V6" s="4">
         <v>252</v>
       </c>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="B7" s="29" t="s">
-        <v>306</v>
+      <c r="W6" s="2">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="27" t="s">
+        <v>298</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
@@ -2133,10 +2131,13 @@
       <c r="V7" s="4">
         <v>312</v>
       </c>
+      <c r="W7" s="2">
+        <v>307</v>
+      </c>
     </row>
     <row r="8" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="C8" s="11">
         <f t="shared" ref="C8:N8" si="0">+C6+C7</f>
@@ -2203,11 +2204,15 @@
         <f>+V6+V7</f>
         <v>564</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W8" s="11">
+        <f>+W6+W7</f>
+        <v>594</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
       <c r="B9" s="2" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
@@ -2241,11 +2246,14 @@
       <c r="V9" s="4">
         <v>671</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W9" s="2">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -2283,8 +2291,11 @@
       <c r="V10" s="4">
         <v>116</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W10" s="28" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
@@ -2306,9 +2317,9 @@
       <c r="U11" s="4"/>
       <c r="V11" s="4"/>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:24" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="C12" s="12"/>
       <c r="D12" s="12"/>
@@ -2341,18 +2352,25 @@
       </c>
       <c r="N12" s="12"/>
       <c r="O12" s="12"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="3"/>
+      <c r="R12" s="3"/>
+      <c r="S12" s="3"/>
+      <c r="T12" s="3"/>
       <c r="U12" s="3">
         <v>2905.5</v>
       </c>
       <c r="V12" s="3">
         <v>3050.1</v>
       </c>
-      <c r="W12" s="12"/>
+      <c r="W12" s="12">
+        <v>3329.6</v>
+      </c>
       <c r="X12" s="12"/>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:24" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="C13" s="12"/>
       <c r="D13" s="12"/>
@@ -2385,18 +2403,25 @@
       </c>
       <c r="N13" s="12"/>
       <c r="O13" s="12"/>
+      <c r="P13" s="3"/>
+      <c r="Q13" s="3"/>
+      <c r="R13" s="3"/>
+      <c r="S13" s="3"/>
+      <c r="T13" s="3"/>
       <c r="U13" s="3">
         <v>1968</v>
       </c>
       <c r="V13" s="3">
         <v>2174.9</v>
       </c>
-      <c r="W13" s="12"/>
+      <c r="W13" s="12">
+        <v>2538.9</v>
+      </c>
       <c r="X13" s="12"/>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:24" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="C14" s="12"/>
       <c r="D14" s="12"/>
@@ -2429,18 +2454,25 @@
       </c>
       <c r="N14" s="12"/>
       <c r="O14" s="12"/>
+      <c r="P14" s="3"/>
+      <c r="Q14" s="3"/>
+      <c r="R14" s="3"/>
+      <c r="S14" s="3"/>
+      <c r="T14" s="3"/>
       <c r="U14" s="3">
         <v>1566.6</v>
       </c>
       <c r="V14" s="3">
         <v>1709.4</v>
       </c>
-      <c r="W14" s="12"/>
+      <c r="W14" s="12">
+        <v>2103.5</v>
+      </c>
       <c r="X14" s="12"/>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:24" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="C15" s="12"/>
       <c r="D15" s="12"/>
@@ -2473,16 +2505,23 @@
       </c>
       <c r="N15" s="12"/>
       <c r="O15" s="12"/>
+      <c r="P15" s="3"/>
+      <c r="Q15" s="3"/>
+      <c r="R15" s="3"/>
+      <c r="S15" s="3"/>
+      <c r="T15" s="3"/>
       <c r="U15" s="3">
         <v>146.30000000000001</v>
       </c>
       <c r="V15" s="3">
         <v>144.6</v>
       </c>
-      <c r="W15" s="12"/>
+      <c r="W15" s="12">
+        <v>142.5</v>
+      </c>
       <c r="X15" s="12"/>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:24" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
         <v>41</v>
       </c>
@@ -2541,7 +2580,7 @@
       <c r="W16" s="12"/>
       <c r="X16" s="12"/>
     </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
         <v>68</v>
       </c>
@@ -2600,7 +2639,7 @@
       <c r="W17" s="12"/>
       <c r="X17" s="12"/>
     </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
         <v>69</v>
       </c>
@@ -2659,7 +2698,7 @@
       <c r="W18" s="12"/>
       <c r="X18" s="12"/>
     </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="10"/>
       <c r="B19" s="1" t="s">
         <v>72</v>
@@ -2716,7 +2755,9 @@
       <c r="V19" s="13">
         <v>7079</v>
       </c>
-      <c r="W19" s="13"/>
+      <c r="W19" s="13">
+        <v>8114.5</v>
+      </c>
       <c r="X19" s="13"/>
       <c r="Y19" s="13"/>
       <c r="Z19" s="13"/>
@@ -2725,7 +2766,7 @@
       <c r="AC19" s="1"/>
       <c r="AD19" s="1"/>
     </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
         <v>73</v>
       </c>
@@ -2781,12 +2822,14 @@
       <c r="V20" s="12">
         <v>2226.1</v>
       </c>
-      <c r="W20" s="12"/>
+      <c r="W20" s="12">
+        <v>2445.3000000000002</v>
+      </c>
       <c r="X20" s="12"/>
       <c r="Y20" s="12"/>
       <c r="Z20" s="12"/>
     </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
         <v>74</v>
       </c>
@@ -2864,12 +2907,15 @@
         <f>V19-V20</f>
         <v>4852.8999999999996</v>
       </c>
-      <c r="W21" s="12"/>
+      <c r="W21" s="12">
+        <f>W19-W20</f>
+        <v>5669.2</v>
+      </c>
       <c r="X21" s="12"/>
       <c r="Y21" s="12"/>
       <c r="Z21" s="12"/>
     </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
         <v>75</v>
       </c>
@@ -2925,12 +2971,14 @@
       <c r="V22" s="12">
         <v>3863</v>
       </c>
-      <c r="W22" s="12"/>
+      <c r="W22" s="12">
+        <v>4371.8999999999996</v>
+      </c>
       <c r="X22" s="12"/>
       <c r="Y22" s="12"/>
       <c r="Z22" s="12"/>
     </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
         <v>76</v>
       </c>
@@ -2986,12 +3034,14 @@
       <c r="V23" s="12">
         <v>0.8</v>
       </c>
-      <c r="W23" s="12"/>
+      <c r="W23" s="12">
+        <v>0</v>
+      </c>
       <c r="X23" s="12"/>
       <c r="Y23" s="12"/>
       <c r="Z23" s="12"/>
     </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
         <v>77</v>
       </c>
@@ -3047,12 +3097,14 @@
       <c r="V24" s="12">
         <v>57</v>
       </c>
-      <c r="W24" s="12"/>
+      <c r="W24" s="12">
+        <v>118.1</v>
+      </c>
       <c r="X24" s="12"/>
       <c r="Y24" s="12"/>
       <c r="Z24" s="12"/>
     </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
         <v>78</v>
       </c>
@@ -3130,12 +3182,15 @@
         <f>SUM(V22:V24)</f>
         <v>3920.8</v>
       </c>
-      <c r="W25" s="12"/>
+      <c r="W25" s="12">
+        <f>SUM(W22:W24)</f>
+        <v>4490</v>
+      </c>
       <c r="X25" s="12"/>
       <c r="Y25" s="12"/>
       <c r="Z25" s="12"/>
     </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
         <v>79</v>
       </c>
@@ -3211,12 +3266,15 @@
         <f>V21-V25</f>
         <v>932.09999999999945</v>
       </c>
-      <c r="W26" s="12"/>
+      <c r="W26" s="12">
+        <f>W21-W25</f>
+        <v>1179.1999999999998</v>
+      </c>
       <c r="X26" s="12"/>
       <c r="Y26" s="12"/>
       <c r="Z26" s="12"/>
     </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
         <v>80</v>
       </c>
@@ -3272,12 +3330,14 @@
       <c r="V27" s="12">
         <v>44.1</v>
       </c>
-      <c r="W27" s="12"/>
+      <c r="W27" s="12">
+        <v>54.2</v>
+      </c>
       <c r="X27" s="12"/>
       <c r="Y27" s="12"/>
       <c r="Z27" s="12"/>
     </row>
-    <row r="28" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
         <v>81</v>
       </c>
@@ -3333,12 +3393,14 @@
       <c r="V28" s="12">
         <v>74</v>
       </c>
-      <c r="W28" s="12"/>
+      <c r="W28" s="12">
+        <v>53.7</v>
+      </c>
       <c r="X28" s="12"/>
       <c r="Y28" s="12"/>
       <c r="Z28" s="12"/>
     </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
         <v>82</v>
       </c>
@@ -3394,12 +3456,14 @@
       <c r="V29" s="12">
         <v>-11.3</v>
       </c>
-      <c r="W29" s="12"/>
+      <c r="W29" s="12">
+        <v>-1</v>
+      </c>
       <c r="X29" s="12"/>
       <c r="Y29" s="12"/>
       <c r="Z29" s="12"/>
     </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
         <v>83</v>
       </c>
@@ -3477,12 +3541,15 @@
         <f>V26-V27+V28+V29</f>
         <v>950.69999999999948</v>
       </c>
-      <c r="W30" s="12"/>
+      <c r="W30" s="12">
+        <f>W26-W27+W28+W29</f>
+        <v>1177.6999999999998</v>
+      </c>
       <c r="X30" s="12"/>
       <c r="Y30" s="12"/>
       <c r="Z30" s="12"/>
     </row>
-    <row r="31" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B31" s="2" t="s">
         <v>84</v>
       </c>
@@ -3538,12 +3605,14 @@
       <c r="V31" s="12">
         <v>207.8</v>
       </c>
-      <c r="W31" s="12"/>
+      <c r="W31" s="12">
+        <v>236.6</v>
+      </c>
       <c r="X31" s="12"/>
       <c r="Y31" s="12"/>
       <c r="Z31" s="12"/>
     </row>
-    <row r="32" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B32" s="2" t="s">
         <v>85</v>
       </c>
@@ -3621,12 +3690,15 @@
         <f>V30-V31</f>
         <v>742.89999999999941</v>
       </c>
-      <c r="W32" s="12"/>
+      <c r="W32" s="12">
+        <f>W30-W31</f>
+        <v>941.0999999999998</v>
+      </c>
       <c r="X32" s="12"/>
       <c r="Y32" s="12"/>
       <c r="Z32" s="12"/>
     </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C33" s="12"/>
       <c r="D33" s="12"/>
       <c r="E33" s="12"/>
@@ -3652,7 +3724,7 @@
       <c r="Y33" s="12"/>
       <c r="Z33" s="12"/>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B34" s="2" t="s">
         <v>87</v>
       </c>
@@ -3703,7 +3775,7 @@
       <c r="N34" s="14"/>
       <c r="O34" s="12"/>
       <c r="P34" s="12">
-        <f t="shared" ref="P34:U34" si="15">P32/P35</f>
+        <f t="shared" ref="P34:W34" si="15">P32/P35</f>
         <v>5.5191935752436772</v>
       </c>
       <c r="Q34" s="12">
@@ -3726,13 +3798,19 @@
         <f t="shared" si="15"/>
         <v>10.669544543672828</v>
       </c>
-      <c r="V34" s="12"/>
-      <c r="W34" s="12"/>
+      <c r="V34" s="12">
+        <f t="shared" si="15"/>
+        <v>11.86741214057507</v>
+      </c>
+      <c r="W34" s="12">
+        <f t="shared" si="15"/>
+        <v>15.427868852459014</v>
+      </c>
       <c r="X34" s="12"/>
       <c r="Y34" s="12"/>
       <c r="Z34" s="12"/>
     </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B35" s="2" t="s">
         <v>86</v>
       </c>
@@ -3786,13 +3864,17 @@
       <c r="U35" s="12">
         <v>60.574281999999997</v>
       </c>
-      <c r="V35" s="12"/>
-      <c r="W35" s="12"/>
+      <c r="V35" s="12">
+        <v>62.6</v>
+      </c>
+      <c r="W35" s="12">
+        <v>61</v>
+      </c>
       <c r="X35" s="12"/>
       <c r="Y35" s="12"/>
       <c r="Z35" s="12"/>
     </row>
-    <row r="36" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C36" s="12"/>
       <c r="D36" s="12"/>
       <c r="E36" s="12"/>
@@ -3818,9 +3900,9 @@
       <c r="Y36" s="12"/>
       <c r="Z36" s="12"/>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B37" s="2" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="C37" s="12"/>
       <c r="D37" s="12"/>
@@ -3851,14 +3933,17 @@
         <f>+V8/U8-1</f>
         <v>0</v>
       </c>
-      <c r="W37" s="12"/>
+      <c r="W37" s="15">
+        <f>+W8/V8-1</f>
+        <v>5.3191489361702038E-2</v>
+      </c>
       <c r="X37" s="12"/>
       <c r="Y37" s="12"/>
       <c r="Z37" s="12"/>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B38" s="2" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="C38" s="16" t="s">
         <v>70</v>
@@ -3909,7 +3994,7 @@
         <v>70</v>
       </c>
       <c r="Q38" s="15" t="e">
-        <f t="shared" ref="Q38:V41" si="22">Q12/P12-1</f>
+        <f t="shared" ref="Q38:W41" si="22">Q12/P12-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="R38" s="15" t="e">
@@ -3932,14 +4017,17 @@
         <f t="shared" si="22"/>
         <v>4.9767681982447076E-2</v>
       </c>
-      <c r="W38" s="12"/>
+      <c r="W38" s="15">
+        <f t="shared" si="22"/>
+        <v>9.1636339792138033E-2</v>
+      </c>
       <c r="X38" s="12"/>
       <c r="Y38" s="12"/>
       <c r="Z38" s="12"/>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B39" s="2" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="C39" s="16" t="s">
         <v>70</v>
@@ -4013,14 +4101,17 @@
         <f t="shared" si="22"/>
         <v>0.1051321138211383</v>
       </c>
-      <c r="W39" s="12"/>
+      <c r="W39" s="15">
+        <f t="shared" si="22"/>
+        <v>0.16736401673640167</v>
+      </c>
       <c r="X39" s="12"/>
       <c r="Y39" s="12"/>
       <c r="Z39" s="12"/>
     </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B40" s="2" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="C40" s="16" t="s">
         <v>70</v>
@@ -4094,14 +4185,17 @@
         <f t="shared" si="22"/>
         <v>9.1152815013404886E-2</v>
       </c>
-      <c r="W40" s="12"/>
+      <c r="W40" s="15">
+        <f t="shared" si="22"/>
+        <v>0.23054873054873037</v>
+      </c>
       <c r="X40" s="12"/>
       <c r="Y40" s="12"/>
       <c r="Z40" s="12"/>
     </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B41" s="2" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="C41" s="16" t="s">
         <v>70</v>
@@ -4175,14 +4269,17 @@
         <f t="shared" si="22"/>
         <v>-1.1619958988380197E-2</v>
       </c>
-      <c r="W41" s="12"/>
+      <c r="W41" s="15">
+        <f t="shared" si="22"/>
+        <v>-1.4522821576763434E-2</v>
+      </c>
       <c r="X41" s="12"/>
       <c r="Y41" s="12"/>
       <c r="Z41" s="12"/>
     </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B42" s="2" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="C42" s="16" t="s">
         <v>70</v>
@@ -4237,7 +4334,7 @@
         <v>-1.8410801003255761E-3</v>
       </c>
       <c r="R42" s="15">
-        <f t="shared" ref="R42:V42" si="23">R16/Q16-1</f>
+        <f t="shared" ref="R42:W42" si="23">R16/Q16-1</f>
         <v>-0.25691678473094703</v>
       </c>
       <c r="S42" s="15">
@@ -4256,14 +4353,17 @@
         <f t="shared" si="23"/>
         <v>9.632268444035863E-2</v>
       </c>
-      <c r="W42" s="12"/>
+      <c r="W42" s="15">
+        <f t="shared" si="23"/>
+        <v>-1</v>
+      </c>
       <c r="X42" s="12"/>
       <c r="Y42" s="12"/>
       <c r="Z42" s="12"/>
     </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B43" s="2" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="C43" s="16" t="s">
         <v>70</v>
@@ -4318,7 +4418,7 @@
         <v>-5.9226750261232919E-2</v>
       </c>
       <c r="R43" s="15">
-        <f t="shared" ref="R43:V45" si="24">R17/Q17-1</f>
+        <f t="shared" ref="R43:W45" si="24">R17/Q17-1</f>
         <v>-0.33419228718677818</v>
       </c>
       <c r="S43" s="15">
@@ -4337,14 +4437,17 @@
         <f t="shared" si="24"/>
         <v>1.4151164425284746E-2</v>
       </c>
-      <c r="W43" s="12"/>
+      <c r="W43" s="15">
+        <f t="shared" si="24"/>
+        <v>-1</v>
+      </c>
       <c r="X43" s="12"/>
       <c r="Y43" s="12"/>
       <c r="Z43" s="12"/>
     </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B44" s="2" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="C44" s="16" t="s">
         <v>70</v>
@@ -4418,12 +4521,15 @@
         <f t="shared" si="24"/>
         <v>-1.1619958988380197E-2</v>
       </c>
-      <c r="W44" s="12"/>
+      <c r="W44" s="15">
+        <f t="shared" si="24"/>
+        <v>-1</v>
+      </c>
       <c r="X44" s="12"/>
       <c r="Y44" s="12"/>
       <c r="Z44" s="12"/>
     </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B45" s="1" t="s">
         <v>88</v>
       </c>
@@ -4499,8 +4605,12 @@
         <f t="shared" si="24"/>
         <v>6.7497059444461271E-2</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="W45" s="20">
+        <f t="shared" si="24"/>
+        <v>0.14627772284220941</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B46" s="2" t="s">
         <v>89</v>
       </c>
@@ -4577,11 +4687,15 @@
         <v>0.66830533522333135</v>
       </c>
       <c r="V46" s="15">
-        <f t="shared" ref="V46" si="28">V21/V19</f>
+        <f t="shared" ref="V46:W46" si="28">V21/V19</f>
         <v>0.68553468003955353</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="W46" s="15">
+        <f t="shared" si="28"/>
+        <v>0.69865056380553325</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B47" s="2" t="s">
         <v>90</v>
       </c>
@@ -4658,11 +4772,15 @@
         <v>0.11406339536146201</v>
       </c>
       <c r="V47" s="15">
-        <f t="shared" ref="V47" si="32">V26/V19</f>
+        <f t="shared" ref="V47:W47" si="32">V26/V19</f>
         <v>0.13167113999152416</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="W47" s="15">
+        <f t="shared" si="32"/>
+        <v>0.14532010598311662</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B48" s="2" t="s">
         <v>91</v>
       </c>
@@ -4739,12 +4857,16 @@
         <v>9.7460566396235973E-2</v>
       </c>
       <c r="V48" s="15">
-        <f t="shared" ref="V48" si="36">V32/V19</f>
+        <f t="shared" ref="V48:W48" si="36">V32/V19</f>
         <v>0.10494420115835562</v>
       </c>
+      <c r="W48" s="15">
+        <f t="shared" si="36"/>
+        <v>0.11597757101484993</v>
+      </c>
       <c r="Y48" s="21"/>
     </row>
-    <row r="49" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B49" s="2" t="s">
         <v>92</v>
       </c>
@@ -4821,1806 +4943,2099 @@
         <v>0.20284697508896823</v>
       </c>
       <c r="V49" s="15">
-        <f t="shared" ref="V49" si="40">V31/V32</f>
+        <f t="shared" ref="V49:W49" si="40">V31/V32</f>
         <v>0.27971463184816286</v>
       </c>
-    </row>
-    <row r="51" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="U51" s="17"/>
-    </row>
-    <row r="52" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A52" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B52" s="7" t="s">
+      <c r="W49" s="15">
+        <f t="shared" si="40"/>
+        <v>0.25140792689406022</v>
+      </c>
+    </row>
+    <row r="50" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P50" s="3"/>
+      <c r="Q50" s="3"/>
+      <c r="R50" s="3"/>
+      <c r="S50" s="3"/>
+      <c r="T50" s="3"/>
+      <c r="U50" s="3"/>
+      <c r="V50" s="3"/>
+    </row>
+    <row r="51" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="U51" s="30"/>
+    </row>
+    <row r="52" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="B52" s="2" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="54" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="P52" s="12">
+        <v>584.1</v>
+      </c>
+      <c r="Q52" s="12">
+        <v>1620.4</v>
+      </c>
+      <c r="R52" s="12">
+        <v>2579</v>
+      </c>
+      <c r="S52" s="12">
+        <v>1863.8</v>
+      </c>
+      <c r="T52" s="12">
+        <v>1529.3</v>
+      </c>
+      <c r="U52" s="12">
+        <v>1662.2</v>
+      </c>
+      <c r="V52" s="12">
+        <v>1922.5</v>
+      </c>
+      <c r="W52" s="12">
+        <v>1988</v>
+      </c>
+    </row>
+    <row r="53" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="B53" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="P53" s="12">
+        <v>1403.4</v>
+      </c>
+      <c r="Q53" s="12">
+        <v>495.9</v>
+      </c>
+      <c r="R53" s="12">
+        <v>197.5</v>
+      </c>
+      <c r="S53" s="12">
+        <v>734.6</v>
+      </c>
+      <c r="T53" s="12">
+        <v>36.4</v>
+      </c>
+      <c r="U53" s="12">
+        <v>121</v>
+      </c>
+      <c r="V53" s="12">
+        <v>160.5</v>
+      </c>
+      <c r="W53" s="12">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="54" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B54" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="P54" s="3">
-        <v>584.1</v>
-      </c>
-      <c r="Q54" s="3">
-        <v>1620.4</v>
-      </c>
-      <c r="R54" s="3">
-        <v>2579</v>
-      </c>
-      <c r="S54" s="3">
-        <v>1863.8</v>
-      </c>
-      <c r="T54" s="3">
-        <v>1529.3</v>
-      </c>
-      <c r="U54" s="3">
-        <v>1662.2</v>
-      </c>
-    </row>
-    <row r="55" spans="1:22" x14ac:dyDescent="0.2">
+        <v>95</v>
+      </c>
+      <c r="P54" s="12">
+        <v>398.1</v>
+      </c>
+      <c r="Q54" s="12">
+        <v>277.10000000000002</v>
+      </c>
+      <c r="R54" s="12">
+        <v>451.5</v>
+      </c>
+      <c r="S54" s="12">
+        <v>405.4</v>
+      </c>
+      <c r="T54" s="12">
+        <v>447.7</v>
+      </c>
+      <c r="U54" s="12">
+        <v>446.5</v>
+      </c>
+      <c r="V54" s="12">
+        <v>459.5</v>
+      </c>
+      <c r="W54" s="12">
+        <v>491.7</v>
+      </c>
+    </row>
+    <row r="55" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B55" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="P55" s="3">
-        <v>1403.4</v>
-      </c>
-      <c r="Q55" s="3">
-        <v>495.9</v>
-      </c>
-      <c r="R55" s="3">
-        <v>197.5</v>
-      </c>
-      <c r="S55" s="3">
-        <v>734.6</v>
-      </c>
-      <c r="T55" s="3">
-        <v>36.4</v>
-      </c>
-      <c r="U55" s="3">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="56" spans="1:22" x14ac:dyDescent="0.2">
+        <v>96</v>
+      </c>
+      <c r="P55" s="12">
+        <v>817.8</v>
+      </c>
+      <c r="Q55" s="12">
+        <v>736.2</v>
+      </c>
+      <c r="R55" s="12">
+        <v>759</v>
+      </c>
+      <c r="S55" s="12">
+        <v>977.3</v>
+      </c>
+      <c r="T55" s="12">
+        <v>1071.3</v>
+      </c>
+      <c r="U55" s="12">
+        <v>902.2</v>
+      </c>
+      <c r="V55" s="12">
+        <v>949.6</v>
+      </c>
+      <c r="W55" s="12">
+        <v>1014.3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B56" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="P56" s="3">
-        <v>398.1</v>
-      </c>
-      <c r="Q56" s="3">
-        <v>277.10000000000002</v>
-      </c>
-      <c r="R56" s="3">
-        <v>451.5</v>
-      </c>
-      <c r="S56" s="3">
-        <v>405.4</v>
-      </c>
-      <c r="T56" s="3">
-        <v>447.7</v>
-      </c>
-      <c r="U56" s="3">
-        <v>446.5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:22" x14ac:dyDescent="0.2">
+        <v>97</v>
+      </c>
+      <c r="P56" s="12">
+        <v>32.1</v>
+      </c>
+      <c r="Q56" s="12">
+        <v>84.8</v>
+      </c>
+      <c r="R56" s="12">
+        <v>54.4</v>
+      </c>
+      <c r="S56" s="12">
+        <v>63.7</v>
+      </c>
+      <c r="T56" s="12">
+        <v>50.7</v>
+      </c>
+      <c r="U56" s="12">
+        <v>56</v>
+      </c>
+      <c r="V56" s="12">
+        <v>55.4</v>
+      </c>
+      <c r="W56" s="12">
+        <v>77.8</v>
+      </c>
+    </row>
+    <row r="57" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B57" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="P57" s="3">
-        <v>817.8</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>736.2</v>
-      </c>
-      <c r="R57" s="3">
-        <v>759</v>
-      </c>
-      <c r="S57" s="3">
-        <v>977.3</v>
-      </c>
-      <c r="T57" s="3">
-        <v>1071.3</v>
-      </c>
-      <c r="U57" s="3">
-        <v>902.2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B58" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="P58" s="3">
-        <v>32.1</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>84.8</v>
-      </c>
-      <c r="R58" s="3">
-        <v>54.4</v>
-      </c>
-      <c r="S58" s="3">
-        <v>63.7</v>
-      </c>
-      <c r="T58" s="3">
-        <v>50.7</v>
-      </c>
-      <c r="U58" s="3">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="59" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B59" s="2" t="s">
+      <c r="P57" s="12">
+        <v>359.3</v>
+      </c>
+      <c r="Q57" s="12">
+        <v>160.80000000000001</v>
+      </c>
+      <c r="R57" s="12">
+        <v>166.6</v>
+      </c>
+      <c r="S57" s="12">
+        <v>172.5</v>
+      </c>
+      <c r="T57" s="12">
+        <v>188.7</v>
+      </c>
+      <c r="U57" s="12">
+        <v>171.9</v>
+      </c>
+      <c r="V57" s="12">
+        <v>242.4</v>
+      </c>
+      <c r="W57" s="12">
+        <v>238.4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:23" s="31" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="29"/>
+      <c r="B58" s="29" t="s">
         <v>99</v>
       </c>
-      <c r="P59" s="3">
-        <v>359.3</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>160.80000000000001</v>
-      </c>
-      <c r="R59" s="3">
-        <v>166.6</v>
-      </c>
-      <c r="S59" s="3">
-        <v>172.5</v>
-      </c>
-      <c r="T59" s="3">
-        <v>188.7</v>
-      </c>
-      <c r="U59" s="3">
-        <v>171.9</v>
-      </c>
-    </row>
-    <row r="60" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B60" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="P60" s="22">
-        <f t="shared" ref="P60:T60" si="41">SUM(P54:P59)</f>
+      <c r="P58" s="31">
+        <f t="shared" ref="P58:T58" si="41">SUM(P52:P57)</f>
         <v>3594.7999999999997</v>
       </c>
-      <c r="Q60" s="22">
+      <c r="Q58" s="31">
         <f t="shared" si="41"/>
         <v>3375.2000000000007</v>
       </c>
-      <c r="R60" s="22">
+      <c r="R58" s="31">
         <f t="shared" si="41"/>
         <v>4208</v>
       </c>
-      <c r="S60" s="22">
+      <c r="S58" s="31">
         <f t="shared" si="41"/>
         <v>4217.3</v>
       </c>
-      <c r="T60" s="22">
+      <c r="T58" s="31">
         <f t="shared" si="41"/>
         <v>3324.0999999999995</v>
       </c>
-      <c r="U60" s="22">
-        <f>SUM(U54:U59)</f>
+      <c r="U58" s="31">
+        <f>SUM(U52:U57)</f>
         <v>3359.7999999999997</v>
       </c>
-    </row>
-    <row r="61" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="V58" s="31">
+        <f t="shared" ref="V58:W58" si="42">SUM(V52:V57)</f>
+        <v>3789.9</v>
+      </c>
+      <c r="W58" s="31">
+        <f t="shared" si="42"/>
+        <v>3887.2000000000003</v>
+      </c>
+    </row>
+    <row r="59" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="B59" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="P59" s="12">
+        <v>1039.2</v>
+      </c>
+      <c r="Q59" s="12">
+        <v>979.5</v>
+      </c>
+      <c r="R59" s="12">
+        <v>1014</v>
+      </c>
+      <c r="S59" s="12">
+        <v>969.5</v>
+      </c>
+      <c r="T59" s="12">
+        <v>955.5</v>
+      </c>
+      <c r="U59" s="12">
+        <v>850.4</v>
+      </c>
+      <c r="V59" s="12">
+        <v>846.4</v>
+      </c>
+      <c r="W59" s="12">
+        <v>1070.5999999999999</v>
+      </c>
+    </row>
+    <row r="60" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="B60" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="P60" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="12">
+        <v>1511.6</v>
+      </c>
+      <c r="R60" s="12">
+        <v>1239.5</v>
+      </c>
+      <c r="S60" s="12">
+        <v>1111.3</v>
+      </c>
+      <c r="T60" s="12">
+        <v>1134</v>
+      </c>
+      <c r="U60" s="12">
+        <v>1014.6</v>
+      </c>
+      <c r="V60" s="12">
+        <v>1013.1</v>
+      </c>
+      <c r="W60" s="12">
+        <v>1299.5999999999999</v>
+      </c>
+    </row>
+    <row r="61" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B61" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="P61" s="3">
-        <v>1039.2</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>979.5</v>
-      </c>
-      <c r="R61" s="3">
+        <v>102</v>
+      </c>
+      <c r="P61" s="12">
+        <v>67</v>
+      </c>
+      <c r="Q61" s="12">
+        <v>245.2</v>
+      </c>
+      <c r="R61" s="12">
+        <v>283.89999999999998</v>
+      </c>
+      <c r="S61" s="12">
+        <v>303.8</v>
+      </c>
+      <c r="T61" s="12">
+        <v>255.1</v>
+      </c>
+      <c r="U61" s="12">
+        <v>288.3</v>
+      </c>
+      <c r="V61" s="12">
+        <v>335.4</v>
+      </c>
+      <c r="W61" s="12">
+        <v>345.1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="B62" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="P62" s="12">
+        <v>919.6</v>
+      </c>
+      <c r="Q62" s="12">
+        <v>915.5</v>
+      </c>
+      <c r="R62" s="12">
+        <v>934.6</v>
+      </c>
+      <c r="S62" s="12">
+        <v>908.7</v>
+      </c>
+      <c r="T62" s="12">
+        <v>898.9</v>
+      </c>
+      <c r="U62" s="12">
+        <v>888.1</v>
+      </c>
+      <c r="V62" s="12">
+        <v>888.5</v>
+      </c>
+      <c r="W62" s="12">
+        <v>904.2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="B63" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="P63" s="12">
+        <v>163.69999999999999</v>
+      </c>
+      <c r="Q63" s="12">
+        <v>141</v>
+      </c>
+      <c r="R63" s="12">
+        <v>121.1</v>
+      </c>
+      <c r="S63" s="12">
+        <v>102.9</v>
+      </c>
+      <c r="T63" s="12">
+        <v>88.9</v>
+      </c>
+      <c r="U63" s="12">
+        <v>75.7</v>
+      </c>
+      <c r="V63" s="12">
+        <v>62.8</v>
+      </c>
+      <c r="W63" s="12">
+        <v>93.3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="B64" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="P64" s="12">
+        <v>158.5</v>
+      </c>
+      <c r="Q64" s="12">
+        <v>111.9</v>
+      </c>
+      <c r="R64" s="12">
+        <v>86.4</v>
+      </c>
+      <c r="S64" s="12">
+        <v>111.2</v>
+      </c>
+      <c r="T64" s="12">
+        <v>133</v>
+      </c>
+      <c r="U64" s="12">
+        <v>125.7</v>
+      </c>
+      <c r="V64" s="12">
+        <v>111.2</v>
+      </c>
+      <c r="W64" s="12">
+        <v>139.5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:23" s="31" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="2"/>
+      <c r="B65" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="P65" s="31">
+        <f t="shared" ref="P65:T65" si="43">SUM(P59:P64)</f>
+        <v>2348</v>
+      </c>
+      <c r="Q65" s="31">
+        <f t="shared" si="43"/>
+        <v>3904.7</v>
+      </c>
+      <c r="R65" s="31">
+        <f t="shared" si="43"/>
+        <v>3679.5</v>
+      </c>
+      <c r="S65" s="31">
+        <f t="shared" si="43"/>
+        <v>3507.4</v>
+      </c>
+      <c r="T65" s="31">
+        <f t="shared" si="43"/>
+        <v>3465.4</v>
+      </c>
+      <c r="U65" s="31">
+        <f>SUM(U59:U64)</f>
+        <v>3242.7999999999997</v>
+      </c>
+      <c r="V65" s="31">
+        <f t="shared" ref="V65:W65" si="44">SUM(V59:V64)</f>
+        <v>3257.4</v>
+      </c>
+      <c r="W65" s="31">
+        <f t="shared" si="44"/>
+        <v>3852.3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="B66" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="P66" s="13">
+        <f>P58+P65</f>
+        <v>5942.7999999999993</v>
+      </c>
+      <c r="Q66" s="13">
+        <f>Q58+Q65</f>
+        <v>7279.9000000000005</v>
+      </c>
+      <c r="R66" s="13">
+        <f>R58+R65</f>
+        <v>7887.5</v>
+      </c>
+      <c r="S66" s="13">
+        <f>S58+S65</f>
+        <v>7724.7000000000007</v>
+      </c>
+      <c r="T66" s="13">
+        <f>T58+T65</f>
+        <v>6789.5</v>
+      </c>
+      <c r="U66" s="13">
+        <f>U58+U65</f>
+        <v>6602.5999999999995</v>
+      </c>
+      <c r="V66" s="13">
+        <f t="shared" ref="V66:W66" si="45">V58+V65</f>
+        <v>7047.3</v>
+      </c>
+      <c r="W66" s="13">
+        <f t="shared" si="45"/>
+        <v>7739.5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="B67" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="P67" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="12">
+        <v>774.6</v>
+      </c>
+      <c r="R67" s="12">
+        <v>0</v>
+      </c>
+      <c r="S67" s="12">
+        <v>499.8</v>
+      </c>
+      <c r="T67" s="12">
+        <v>0</v>
+      </c>
+      <c r="U67" s="12">
+        <v>0</v>
+      </c>
+      <c r="V67" s="12">
+        <v>399.7</v>
+      </c>
+      <c r="W67" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="B68" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="P68" s="12">
+        <v>202.3</v>
+      </c>
+      <c r="Q68" s="12">
+        <v>246.8</v>
+      </c>
+      <c r="R68" s="12">
+        <v>355.9</v>
+      </c>
+      <c r="S68" s="12">
+        <v>448.7</v>
+      </c>
+      <c r="T68" s="12">
+        <v>371.6</v>
+      </c>
+      <c r="U68" s="12">
+        <v>332.2</v>
+      </c>
+      <c r="V68" s="12">
+        <v>436</v>
+      </c>
+      <c r="W68" s="12">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="69" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="B69" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="P69" s="12">
+        <v>29.4</v>
+      </c>
+      <c r="Q69" s="12">
+        <v>65.099999999999994</v>
+      </c>
+      <c r="R69" s="12">
+        <v>50.6</v>
+      </c>
+      <c r="S69" s="12">
+        <v>53.8</v>
+      </c>
+      <c r="T69" s="12">
+        <v>59.7</v>
+      </c>
+      <c r="U69" s="12">
+        <v>79.8</v>
+      </c>
+      <c r="V69" s="12">
+        <v>146.5</v>
+      </c>
+      <c r="W69" s="12">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="70" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="B70" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="P70" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="12">
+        <v>288.39999999999998</v>
+      </c>
+      <c r="R70" s="12">
+        <v>302.89999999999998</v>
+      </c>
+      <c r="S70" s="12">
+        <v>262</v>
+      </c>
+      <c r="T70" s="12">
+        <v>266.7</v>
+      </c>
+      <c r="U70" s="12">
+        <v>245.5</v>
+      </c>
+      <c r="V70" s="12">
+        <v>225.4</v>
+      </c>
+      <c r="W70" s="12">
+        <v>211.7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="B71" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="P71" s="12">
+        <v>968.4</v>
+      </c>
+      <c r="Q71" s="12">
+        <v>717.1</v>
+      </c>
+      <c r="R71" s="12">
+        <v>875.4</v>
+      </c>
+      <c r="S71" s="12">
+        <v>991.4</v>
+      </c>
+      <c r="T71" s="12">
+        <v>795.5</v>
+      </c>
+      <c r="U71" s="12">
+        <v>809.7</v>
+      </c>
+      <c r="V71" s="12">
+        <v>926.1</v>
+      </c>
+      <c r="W71" s="12">
+        <v>1103.8</v>
+      </c>
+    </row>
+    <row r="72" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="B72" s="29" t="s">
+        <v>113</v>
+      </c>
+      <c r="P72" s="31">
+        <f t="shared" ref="P72:Q72" si="46">SUM(P67:P71)</f>
+        <v>1200.0999999999999</v>
+      </c>
+      <c r="Q72" s="31">
+        <f t="shared" si="46"/>
+        <v>2092</v>
+      </c>
+      <c r="R72" s="31">
+        <f>SUM(R67:R71)</f>
+        <v>1584.8</v>
+      </c>
+      <c r="S72" s="31">
+        <f t="shared" ref="S72:W72" si="47">SUM(S67:S71)</f>
+        <v>2255.6999999999998</v>
+      </c>
+      <c r="T72" s="31">
+        <f t="shared" si="47"/>
+        <v>1493.5</v>
+      </c>
+      <c r="U72" s="31">
+        <f t="shared" si="47"/>
+        <v>1467.2</v>
+      </c>
+      <c r="V72" s="31">
+        <f t="shared" si="47"/>
+        <v>2133.7000000000003</v>
+      </c>
+      <c r="W72" s="31">
+        <f t="shared" si="47"/>
+        <v>1826.5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="B73" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="P73" s="12">
+        <v>689.1</v>
+      </c>
+      <c r="Q73" s="12">
+        <v>396.4</v>
+      </c>
+      <c r="R73" s="12">
+        <v>1632.9</v>
+      </c>
+      <c r="S73" s="12">
+        <v>1136.5</v>
+      </c>
+      <c r="T73" s="12">
+        <v>1138.5</v>
+      </c>
+      <c r="U73" s="12">
+        <v>1140.5</v>
+      </c>
+      <c r="V73" s="12">
+        <v>742.9</v>
+      </c>
+      <c r="W73" s="12">
+        <v>1238.9000000000001</v>
+      </c>
+    </row>
+    <row r="74" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="B74" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="P74" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="12">
+        <v>0</v>
+      </c>
+      <c r="R74" s="12">
+        <v>0</v>
+      </c>
+      <c r="S74" s="12">
+        <v>341.6</v>
+      </c>
+      <c r="T74" s="12">
+        <v>315.3</v>
+      </c>
+      <c r="U74" s="12">
+        <v>256.10000000000002</v>
+      </c>
+      <c r="V74" s="12">
+        <v>234.8</v>
+      </c>
+      <c r="W74" s="12">
+        <v>212.3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="B75" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="P75" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="12">
+        <v>1568.3</v>
+      </c>
+      <c r="R75" s="12">
+        <v>1294.5</v>
+      </c>
+      <c r="S75" s="12">
+        <v>1132.2</v>
+      </c>
+      <c r="T75" s="12">
+        <v>1141.0999999999999</v>
+      </c>
+      <c r="U75" s="12">
         <v>1014</v>
       </c>
-      <c r="S61" s="3">
-        <v>969.5</v>
-      </c>
-      <c r="T61" s="3">
-        <v>955.5</v>
-      </c>
-      <c r="U61" s="3">
-        <v>850.4</v>
-      </c>
-    </row>
-    <row r="62" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B62" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>1511.6</v>
-      </c>
-      <c r="R62" s="3">
-        <v>1239.5</v>
-      </c>
-      <c r="S62" s="3">
-        <v>1111.3</v>
-      </c>
-      <c r="T62" s="3">
-        <v>1134</v>
-      </c>
-      <c r="U62" s="3">
-        <v>1014.6</v>
-      </c>
-    </row>
-    <row r="63" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B63" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="P63" s="3">
-        <v>67</v>
-      </c>
-      <c r="Q63" s="3">
-        <v>245.2</v>
-      </c>
-      <c r="R63" s="3">
-        <v>283.89999999999998</v>
-      </c>
-      <c r="S63" s="3">
-        <v>303.8</v>
-      </c>
-      <c r="T63" s="3">
-        <v>255.1</v>
-      </c>
-      <c r="U63" s="3">
-        <v>288.3</v>
-      </c>
-    </row>
-    <row r="64" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B64" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="P64" s="3">
-        <v>919.6</v>
-      </c>
-      <c r="Q64" s="3">
-        <v>915.5</v>
-      </c>
-      <c r="R64" s="3">
-        <v>934.6</v>
-      </c>
-      <c r="S64" s="3">
-        <v>908.7</v>
-      </c>
-      <c r="T64" s="3">
-        <v>898.9</v>
-      </c>
-      <c r="U64" s="3">
-        <v>888.1</v>
-      </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B65" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="P65" s="3">
-        <v>163.69999999999999</v>
-      </c>
-      <c r="Q65" s="3">
+      <c r="V75" s="12">
+        <v>1044.7</v>
+      </c>
+      <c r="W75" s="12">
+        <v>1325.8</v>
+      </c>
+    </row>
+    <row r="76" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="B76" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="P76" s="12">
+        <v>146.69999999999999</v>
+      </c>
+      <c r="Q76" s="12">
+        <v>132.69999999999999</v>
+      </c>
+      <c r="R76" s="12">
+        <v>118.7</v>
+      </c>
+      <c r="S76" s="12">
+        <v>98.9</v>
+      </c>
+      <c r="T76" s="12">
+        <v>75.900000000000006</v>
+      </c>
+      <c r="U76" s="12">
+        <v>42.2</v>
+      </c>
+      <c r="V76" s="12">
+        <v>193.3</v>
+      </c>
+      <c r="W76" s="12">
+        <v>168.7</v>
+      </c>
+    </row>
+    <row r="77" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="B77" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="P77" s="12">
+        <v>78.8</v>
+      </c>
+      <c r="Q77" s="12">
+        <v>88.9</v>
+      </c>
+      <c r="R77" s="12">
+        <v>91.4</v>
+      </c>
+      <c r="S77" s="12">
+        <v>91.9</v>
+      </c>
+      <c r="T77" s="12">
+        <v>93.8</v>
+      </c>
+      <c r="U77" s="12">
+        <v>118.7</v>
+      </c>
+      <c r="V77" s="12">
+        <v>0</v>
+      </c>
+      <c r="W77" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="B78" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="P78" s="12">
+        <v>540.9</v>
+      </c>
+      <c r="Q78" s="12">
+        <v>308.5</v>
+      </c>
+      <c r="R78" s="12">
+        <v>560.79999999999995</v>
+      </c>
+      <c r="S78" s="12">
+        <v>131.9</v>
+      </c>
+      <c r="T78" s="12">
+        <v>100.9</v>
+      </c>
+      <c r="U78" s="12">
+        <v>113.6</v>
+      </c>
+      <c r="V78" s="12">
+        <v>109.4</v>
+      </c>
+      <c r="W78" s="12">
+        <v>125.9</v>
+      </c>
+    </row>
+    <row r="79" spans="1:23" s="31" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="2"/>
+      <c r="B79" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="P79" s="31">
+        <f t="shared" ref="P79:T79" si="48">SUM(P73:P78)</f>
+        <v>1455.5</v>
+      </c>
+      <c r="Q79" s="31">
+        <f t="shared" si="48"/>
+        <v>2494.7999999999997</v>
+      </c>
+      <c r="R79" s="31">
+        <f>SUM(R73:R78)</f>
+        <v>3698.3</v>
+      </c>
+      <c r="S79" s="31">
+        <f t="shared" si="48"/>
+        <v>2933.0000000000005</v>
+      </c>
+      <c r="T79" s="31">
+        <f t="shared" si="48"/>
+        <v>2865.5</v>
+      </c>
+      <c r="U79" s="31">
+        <f>SUM(U73:U78)</f>
+        <v>2685.0999999999995</v>
+      </c>
+      <c r="V79" s="31">
+        <f t="shared" ref="V79:W79" si="49">SUM(V73:V78)</f>
+        <v>2325.1000000000004</v>
+      </c>
+      <c r="W79" s="31">
+        <f t="shared" si="49"/>
+        <v>3071.6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="B80" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="P80" s="13">
+        <f>P72+P79</f>
+        <v>2655.6</v>
+      </c>
+      <c r="Q80" s="13">
+        <f>Q72+Q79</f>
+        <v>4586.7999999999993</v>
+      </c>
+      <c r="R80" s="13">
+        <f>R72+R79</f>
+        <v>5283.1</v>
+      </c>
+      <c r="S80" s="13">
+        <f>S72+S79</f>
+        <v>5188.7000000000007</v>
+      </c>
+      <c r="T80" s="13">
+        <f>T72+T79</f>
+        <v>4359</v>
+      </c>
+      <c r="U80" s="13">
+        <f>U72+U79</f>
+        <v>4152.2999999999993</v>
+      </c>
+      <c r="V80" s="13">
+        <f t="shared" ref="V80:W80" si="50">V72+V79</f>
+        <v>4458.8000000000011</v>
+      </c>
+      <c r="W80" s="13">
+        <f t="shared" si="50"/>
+        <v>4898.1000000000004</v>
+      </c>
+    </row>
+    <row r="81" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B81" s="29" t="s">
+        <v>122</v>
+      </c>
+      <c r="C81" s="31"/>
+      <c r="D81" s="31"/>
+      <c r="E81" s="31"/>
+      <c r="F81" s="31"/>
+      <c r="G81" s="31"/>
+      <c r="H81" s="31"/>
+      <c r="I81" s="31"/>
+      <c r="J81" s="31"/>
+      <c r="K81" s="31"/>
+      <c r="L81" s="31"/>
+      <c r="M81" s="31"/>
+      <c r="N81" s="31"/>
+      <c r="O81" s="31"/>
+      <c r="P81" s="31">
+        <v>3287.2000000000003</v>
+      </c>
+      <c r="Q81" s="31">
+        <v>2693.1000000000013</v>
+      </c>
+      <c r="R81" s="31">
+        <v>2604.3999999999987</v>
+      </c>
+      <c r="S81" s="31">
+        <v>2536</v>
+      </c>
+      <c r="T81" s="31">
+        <v>2430.4999999999991</v>
+      </c>
+      <c r="U81" s="31">
+        <v>2450.3000000000006</v>
+      </c>
+      <c r="V81" s="12">
+        <v>2588.5</v>
+      </c>
+      <c r="W81" s="12">
+        <v>2841.4</v>
+      </c>
+    </row>
+    <row r="82" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B82" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C82" s="13"/>
+      <c r="D82" s="13"/>
+      <c r="E82" s="13"/>
+      <c r="F82" s="13"/>
+      <c r="G82" s="13"/>
+      <c r="H82" s="13"/>
+      <c r="I82" s="13"/>
+      <c r="J82" s="13"/>
+      <c r="K82" s="13"/>
+      <c r="L82" s="13"/>
+      <c r="M82" s="13"/>
+      <c r="N82" s="13"/>
+      <c r="O82" s="13"/>
+      <c r="P82" s="13">
+        <f>P81+P80</f>
+        <v>5942.8</v>
+      </c>
+      <c r="Q82" s="13">
+        <f>Q81+Q80</f>
+        <v>7279.9000000000005</v>
+      </c>
+      <c r="R82" s="13">
+        <f>R81+R80</f>
+        <v>7887.4999999999991</v>
+      </c>
+      <c r="S82" s="13">
+        <f>S81+S80</f>
+        <v>7724.7000000000007</v>
+      </c>
+      <c r="T82" s="13">
+        <f>T81+T80</f>
+        <v>6789.4999999999991</v>
+      </c>
+      <c r="U82" s="13">
+        <f>U81+U80</f>
+        <v>6602.6</v>
+      </c>
+      <c r="V82" s="13">
+        <f t="shared" ref="V82:W82" si="51">V81+V80</f>
+        <v>7047.3000000000011</v>
+      </c>
+      <c r="W82" s="13">
+        <f t="shared" si="51"/>
+        <v>7739.5</v>
+      </c>
+    </row>
+    <row r="85" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B85" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="P85" s="12">
+        <f>P32</f>
+        <v>430.89999999999964</v>
+      </c>
+      <c r="Q85" s="12">
+        <f>Q32</f>
+        <v>384.30000000000041</v>
+      </c>
+      <c r="R85" s="12">
+        <f>R32</f>
+        <v>-121.09999999999991</v>
+      </c>
+      <c r="S85" s="12">
+        <f>S32</f>
+        <v>600.10000000000014</v>
+      </c>
+      <c r="T85" s="12">
+        <f>T32</f>
+        <v>522.70000000000027</v>
+      </c>
+      <c r="U85" s="12">
+        <f>U32</f>
+        <v>646.29999999999916</v>
+      </c>
+      <c r="V85" s="12">
+        <f t="shared" ref="V85:W85" si="52">V32</f>
+        <v>742.89999999999941</v>
+      </c>
+      <c r="W85" s="12">
+        <f t="shared" si="52"/>
+        <v>941.0999999999998</v>
+      </c>
+    </row>
+    <row r="86" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B86" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="P86" s="12">
+        <v>281.3</v>
+      </c>
+      <c r="Q86" s="12">
+        <v>269.5</v>
+      </c>
+      <c r="R86" s="12">
+        <v>247.6</v>
+      </c>
+      <c r="S86" s="12">
+        <v>229.7</v>
+      </c>
+      <c r="T86" s="12">
+        <v>220.5</v>
+      </c>
+      <c r="U86" s="12">
+        <v>229</v>
+      </c>
+      <c r="V86" s="12">
+        <v>219.6</v>
+      </c>
+      <c r="W86" s="12">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="87" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B87" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="P87" s="12">
+        <v>8.5</v>
+      </c>
+      <c r="Q87" s="12">
+        <v>-168.8</v>
+      </c>
+      <c r="R87" s="12">
+        <v>35.6</v>
+      </c>
+      <c r="S87" s="12">
+        <v>-46.1</v>
+      </c>
+      <c r="T87" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="U87" s="12">
+        <v>-41.1</v>
+      </c>
+      <c r="V87" s="12">
+        <v>-50</v>
+      </c>
+      <c r="W87" s="12">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="88" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B88" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="P88" s="12">
+        <v>11.6</v>
+      </c>
+      <c r="Q88" s="12">
+        <v>0</v>
+      </c>
+      <c r="R88" s="12">
+        <v>0</v>
+      </c>
+      <c r="S88" s="12">
+        <v>0</v>
+      </c>
+      <c r="T88" s="12">
+        <v>0</v>
+      </c>
+      <c r="U88" s="12">
+        <v>0</v>
+      </c>
+      <c r="V88" s="12">
+        <v>0</v>
+      </c>
+      <c r="W88" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B89" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="P89" s="12">
+        <v>88.6</v>
+      </c>
+      <c r="Q89" s="12">
+        <v>100.6</v>
+      </c>
+      <c r="R89" s="12">
+        <v>72.7</v>
+      </c>
+      <c r="S89" s="12">
+        <v>81.7</v>
+      </c>
+      <c r="T89" s="12">
+        <v>75.5</v>
+      </c>
+      <c r="U89" s="12">
+        <v>99.5</v>
+      </c>
+      <c r="V89" s="12">
+        <v>107.9</v>
+      </c>
+      <c r="W89" s="12">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="90" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B90" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="P90" s="12">
+        <v>25.8</v>
+      </c>
+      <c r="Q90" s="12">
+        <v>38.700000000000003</v>
+      </c>
+      <c r="R90" s="12">
+        <v>96</v>
+      </c>
+      <c r="S90" s="12">
+        <v>21.3</v>
+      </c>
+      <c r="T90" s="12">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="U90" s="12">
+        <v>0</v>
+      </c>
+      <c r="V90" s="12">
+        <v>0</v>
+      </c>
+      <c r="W90" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B91" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="P91" s="12">
+        <v>0.4</v>
+      </c>
+      <c r="Q91" s="12">
+        <v>58.7</v>
+      </c>
+      <c r="R91" s="12">
+        <v>-27.6</v>
+      </c>
+      <c r="S91" s="12">
+        <v>-2.2000000000000002</v>
+      </c>
+      <c r="T91" s="12">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="U91" s="12">
+        <v>7.3</v>
+      </c>
+      <c r="V91" s="12">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="W91" s="12">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="92" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B92" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="P92" s="12">
+        <v>6.5</v>
+      </c>
+      <c r="Q92" s="12">
+        <v>-2.2999999999999998</v>
+      </c>
+      <c r="R92" s="12">
+        <v>1.8</v>
+      </c>
+      <c r="S92" s="12">
+        <v>1</v>
+      </c>
+      <c r="T92" s="12">
+        <v>1</v>
+      </c>
+      <c r="U92" s="12">
+        <v>13.7</v>
+      </c>
+      <c r="V92" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="W92" s="12">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="93" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B93" s="9" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="94" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B94" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="P94" s="12">
+        <v>10.1</v>
+      </c>
+      <c r="Q94" s="12">
+        <v>57.6</v>
+      </c>
+      <c r="R94" s="12">
+        <v>-143</v>
+      </c>
+      <c r="S94" s="12">
+        <v>32.4</v>
+      </c>
+      <c r="T94" s="12">
+        <v>-52.6</v>
+      </c>
+      <c r="U94" s="12">
+        <v>-15.3</v>
+      </c>
+      <c r="V94" s="12">
+        <v>-27.6</v>
+      </c>
+      <c r="W94" s="12">
+        <v>-35.6</v>
+      </c>
+    </row>
+    <row r="95" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B95" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="P95" s="12">
+        <v>-83.6</v>
+      </c>
+      <c r="Q95" s="12">
+        <v>72.3</v>
+      </c>
+      <c r="R95" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="S95" s="12">
+        <v>-269.3</v>
+      </c>
+      <c r="T95" s="12">
+        <v>-106.2</v>
+      </c>
+      <c r="U95" s="12">
+        <v>149.1</v>
+      </c>
+      <c r="V95" s="12">
+        <v>-52.6</v>
+      </c>
+      <c r="W95" s="12">
+        <v>-44.2</v>
+      </c>
+    </row>
+    <row r="96" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B96" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="P96" s="12">
+        <v>-40.5</v>
+      </c>
+      <c r="Q96" s="12">
+        <v>58.2</v>
+      </c>
+      <c r="R96" s="12">
+        <v>5.2</v>
+      </c>
+      <c r="S96" s="12">
+        <v>-28.3</v>
+      </c>
+      <c r="T96" s="12">
+        <v>-19.899999999999999</v>
+      </c>
+      <c r="U96" s="12">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="V96" s="12">
+        <v>-47.4</v>
+      </c>
+      <c r="W96" s="12">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="97" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B97" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="P97" s="12">
+        <v>-4.7</v>
+      </c>
+      <c r="Q97" s="12">
+        <v>-64.3</v>
+      </c>
+      <c r="R97" s="12">
+        <v>296.8</v>
+      </c>
+      <c r="S97" s="12">
+        <v>194.6</v>
+      </c>
+      <c r="T97" s="12">
+        <v>-225</v>
+      </c>
+      <c r="U97" s="12">
+        <v>15.6</v>
+      </c>
+      <c r="V97" s="12">
+        <v>226.2</v>
+      </c>
+      <c r="W97" s="12">
+        <v>142.19999999999999</v>
+      </c>
+    </row>
+    <row r="98" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B98" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="P98" s="12">
+        <v>29.7</v>
+      </c>
+      <c r="Q98" s="12">
+        <v>-42.5</v>
+      </c>
+      <c r="R98" s="12">
+        <v>-37.799999999999997</v>
+      </c>
+      <c r="S98" s="12">
+        <v>-62.3</v>
+      </c>
+      <c r="T98" s="12">
+        <v>5.7</v>
+      </c>
+      <c r="U98" s="12">
+        <v>-18.5</v>
+      </c>
+      <c r="V98" s="12">
+        <v>27.9</v>
+      </c>
+      <c r="W98" s="12">
+        <v>-94.1</v>
+      </c>
+    </row>
+    <row r="99" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B99" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="P99" s="12">
+        <v>-16.5</v>
+      </c>
+      <c r="Q99" s="12">
+        <v>0</v>
+      </c>
+      <c r="R99" s="12">
+        <v>-3.2</v>
+      </c>
+      <c r="S99" s="12">
+        <v>-61.6</v>
+      </c>
+      <c r="T99" s="12">
+        <v>-17.5</v>
+      </c>
+      <c r="U99" s="12">
+        <v>-36.299999999999997</v>
+      </c>
+      <c r="V99" s="12">
+        <v>11.7</v>
+      </c>
+      <c r="W99" s="12">
+        <v>-22.3</v>
+      </c>
+    </row>
+    <row r="100" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B100" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="P100" s="12">
+        <v>35.700000000000003</v>
+      </c>
+      <c r="Q100" s="12">
+        <v>-7.4</v>
+      </c>
+      <c r="R100" s="12">
+        <v>-45.8</v>
+      </c>
+      <c r="S100" s="12">
+        <v>24.9</v>
+      </c>
+      <c r="T100" s="12">
+        <v>-9.1</v>
+      </c>
+      <c r="U100" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="V100" s="12">
+        <v>63.7</v>
+      </c>
+      <c r="W100" s="12">
+        <v>-84.3</v>
+      </c>
+    </row>
+    <row r="101" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B101" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="P101" s="13">
+        <f t="shared" ref="P101:T101" si="53">P85+SUM(P86:P92)+SUM(P94:P100)</f>
+        <v>783.79999999999973</v>
+      </c>
+      <c r="Q101" s="13">
+        <f>Q85+SUM(Q86:Q92)+SUM(Q94:Q100)</f>
+        <v>754.60000000000036</v>
+      </c>
+      <c r="R101" s="13">
+        <f t="shared" si="53"/>
+        <v>380.90000000000003</v>
+      </c>
+      <c r="S101" s="13">
+        <f t="shared" si="53"/>
+        <v>715.90000000000032</v>
+      </c>
+      <c r="T101" s="13">
+        <f t="shared" si="53"/>
+        <v>411.00000000000017</v>
+      </c>
+      <c r="U101" s="13">
+        <f>U85+SUM(U86:U92)+SUM(U94:U100)</f>
+        <v>1069.6999999999991</v>
+      </c>
+      <c r="V101" s="13">
+        <f t="shared" ref="V101:W101" si="54">V85+SUM(V86:V92)+SUM(V94:V100)</f>
+        <v>1235.0999999999995</v>
+      </c>
+      <c r="W101" s="13">
+        <f t="shared" si="54"/>
+        <v>1154.1999999999998</v>
+      </c>
+    </row>
+    <row r="102" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B102" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="P102" s="12">
+        <v>-197.7</v>
+      </c>
+      <c r="Q102" s="12">
+        <v>-270.3</v>
+      </c>
+      <c r="R102" s="12">
+        <v>-107.8</v>
+      </c>
+      <c r="S102" s="12">
+        <v>-166.9</v>
+      </c>
+      <c r="T102" s="12">
+        <v>-217.5</v>
+      </c>
+      <c r="U102" s="12">
+        <v>-164.8</v>
+      </c>
+      <c r="V102" s="12">
+        <v>-216.2</v>
+      </c>
+      <c r="W102" s="12">
+        <v>-408.1</v>
+      </c>
+    </row>
+    <row r="103" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B103" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="P103" s="12">
+        <v>-3030.8</v>
+      </c>
+      <c r="Q103" s="12">
+        <v>-1289.7</v>
+      </c>
+      <c r="R103" s="12">
+        <v>-704.6</v>
+      </c>
+      <c r="S103" s="12">
+        <v>-1510.6</v>
+      </c>
+      <c r="T103" s="12">
+        <v>-598.6</v>
+      </c>
+      <c r="U103" s="12">
+        <v>-392.8</v>
+      </c>
+      <c r="V103" s="12">
+        <v>-781.8</v>
+      </c>
+      <c r="W103" s="12">
+        <v>-634</v>
+      </c>
+    </row>
+    <row r="104" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B104" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="R65" s="3">
-        <v>121.1</v>
-      </c>
-      <c r="S65" s="3">
-        <v>102.9</v>
-      </c>
-      <c r="T65" s="3">
-        <v>88.9</v>
-      </c>
-      <c r="U65" s="3">
-        <v>75.7</v>
-      </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B66" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="P66" s="3">
-        <v>158.5</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>111.9</v>
-      </c>
-      <c r="R66" s="3">
-        <v>86.4</v>
-      </c>
-      <c r="S66" s="3">
-        <v>111.2</v>
-      </c>
-      <c r="T66" s="3">
-        <v>133</v>
-      </c>
-      <c r="U66" s="3">
-        <v>125.7</v>
-      </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B67" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="P67" s="22">
-        <f t="shared" ref="P67:T67" si="42">SUM(P61:P66)</f>
-        <v>2348</v>
-      </c>
-      <c r="Q67" s="22">
-        <f t="shared" si="42"/>
-        <v>3904.7</v>
-      </c>
-      <c r="R67" s="22">
-        <f t="shared" si="42"/>
-        <v>3679.5</v>
-      </c>
-      <c r="S67" s="22">
-        <f t="shared" si="42"/>
-        <v>3507.4</v>
-      </c>
-      <c r="T67" s="22">
-        <f t="shared" si="42"/>
-        <v>3465.4</v>
-      </c>
-      <c r="U67" s="22">
-        <f>SUM(U61:U66)</f>
-        <v>3242.7999999999997</v>
-      </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B69" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="P69" s="22">
-        <f t="shared" ref="P69:T69" si="43">P60+P67</f>
-        <v>5942.7999999999993</v>
-      </c>
-      <c r="Q69" s="22">
-        <f t="shared" si="43"/>
-        <v>7279.9000000000005</v>
-      </c>
-      <c r="R69" s="22">
-        <f t="shared" si="43"/>
-        <v>7887.5</v>
-      </c>
-      <c r="S69" s="22">
-        <f t="shared" si="43"/>
-        <v>7724.7000000000007</v>
-      </c>
-      <c r="T69" s="22">
-        <f t="shared" si="43"/>
-        <v>6789.5</v>
-      </c>
-      <c r="U69" s="22">
-        <f>U60+U67</f>
-        <v>6602.5999999999995</v>
-      </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B71" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="P71" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q71" s="3">
-        <v>774.6</v>
-      </c>
-      <c r="R71" s="3">
-        <v>0</v>
-      </c>
-      <c r="S71" s="3">
-        <v>499.8</v>
-      </c>
-      <c r="T71" s="3">
-        <v>0</v>
-      </c>
-      <c r="U71" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B72" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="P72" s="3">
-        <v>202.3</v>
-      </c>
-      <c r="Q72" s="3">
-        <v>246.8</v>
-      </c>
-      <c r="R72" s="3">
-        <v>355.9</v>
-      </c>
-      <c r="S72" s="3">
-        <v>448.7</v>
-      </c>
-      <c r="T72" s="3">
-        <v>371.6</v>
-      </c>
-      <c r="U72" s="3">
-        <v>332.2</v>
-      </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B73" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="P73" s="3">
-        <v>29.4</v>
-      </c>
-      <c r="Q73" s="3">
-        <v>65.099999999999994</v>
-      </c>
-      <c r="R73" s="3">
-        <v>50.6</v>
-      </c>
-      <c r="S73" s="3">
-        <v>53.8</v>
-      </c>
-      <c r="T73" s="3">
-        <v>59.7</v>
-      </c>
-      <c r="U73" s="3">
-        <v>79.8</v>
-      </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B74" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="P74" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q74" s="3">
-        <v>288.39999999999998</v>
-      </c>
-      <c r="R74" s="3">
-        <v>302.89999999999998</v>
-      </c>
-      <c r="S74" s="3">
-        <v>262</v>
-      </c>
-      <c r="T74" s="3">
-        <v>266.7</v>
-      </c>
-      <c r="U74" s="3">
-        <v>245.5</v>
-      </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B75" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="P75" s="3">
-        <v>968.4</v>
-      </c>
-      <c r="Q75" s="3">
-        <v>717.1</v>
-      </c>
-      <c r="R75" s="3">
-        <v>875.4</v>
-      </c>
-      <c r="S75" s="3">
-        <v>991.4</v>
-      </c>
-      <c r="T75" s="3">
-        <v>795.5</v>
-      </c>
-      <c r="U75" s="3">
-        <v>809.7</v>
-      </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B76" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="P76" s="22">
-        <f t="shared" ref="P76:Q76" si="44">SUM(P71:P75)</f>
-        <v>1200.0999999999999</v>
-      </c>
-      <c r="Q76" s="22">
-        <f t="shared" si="44"/>
-        <v>2092</v>
-      </c>
-      <c r="R76" s="22">
-        <f>SUM(R71:R75)</f>
-        <v>1584.8</v>
-      </c>
-      <c r="S76" s="22">
-        <f t="shared" ref="S76:U76" si="45">SUM(S71:S75)</f>
-        <v>2255.6999999999998</v>
-      </c>
-      <c r="T76" s="22">
-        <f t="shared" si="45"/>
-        <v>1493.5</v>
-      </c>
-      <c r="U76" s="22">
-        <f t="shared" si="45"/>
-        <v>1467.2</v>
-      </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B77" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="P77" s="3">
-        <v>689.1</v>
-      </c>
-      <c r="Q77" s="3">
-        <v>396.4</v>
-      </c>
-      <c r="R77" s="3">
-        <v>1632.9</v>
-      </c>
-      <c r="S77" s="3">
-        <v>1136.5</v>
-      </c>
-      <c r="T77" s="3">
-        <v>1138.5</v>
-      </c>
-      <c r="U77" s="3">
-        <v>1140.5</v>
-      </c>
-      <c r="W77" s="3"/>
-    </row>
-    <row r="78" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B78" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="P78" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q78" s="3">
-        <v>0</v>
-      </c>
-      <c r="R78" s="3">
-        <v>0</v>
-      </c>
-      <c r="S78" s="3">
-        <v>341.6</v>
-      </c>
-      <c r="T78" s="3">
-        <v>315.3</v>
-      </c>
-      <c r="U78" s="3">
-        <v>256.10000000000002</v>
-      </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B79" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="P79" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q79" s="3">
-        <v>1568.3</v>
-      </c>
-      <c r="R79" s="3">
-        <v>1294.5</v>
-      </c>
-      <c r="S79" s="3">
-        <v>1132.2</v>
-      </c>
-      <c r="T79" s="3">
-        <v>1141.0999999999999</v>
-      </c>
-      <c r="U79" s="3">
-        <v>1014</v>
-      </c>
-    </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B80" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="P80" s="3">
-        <v>146.69999999999999</v>
-      </c>
-      <c r="Q80" s="3">
-        <v>132.69999999999999</v>
-      </c>
-      <c r="R80" s="3">
-        <v>118.7</v>
-      </c>
-      <c r="S80" s="3">
-        <v>98.9</v>
-      </c>
-      <c r="T80" s="3">
-        <v>75.900000000000006</v>
-      </c>
-      <c r="U80" s="3">
-        <v>42.2</v>
-      </c>
-    </row>
-    <row r="81" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B81" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="P81" s="3">
-        <v>78.8</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>88.9</v>
-      </c>
-      <c r="R81" s="3">
-        <v>91.4</v>
-      </c>
-      <c r="S81" s="3">
-        <v>91.9</v>
-      </c>
-      <c r="T81" s="3">
-        <v>93.8</v>
-      </c>
-      <c r="U81" s="3">
-        <v>118.7</v>
-      </c>
-    </row>
-    <row r="82" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B82" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="P82" s="3">
-        <v>540.9</v>
-      </c>
-      <c r="Q82" s="3">
-        <v>308.5</v>
-      </c>
-      <c r="R82" s="3">
-        <v>560.79999999999995</v>
-      </c>
-      <c r="S82" s="3">
-        <v>131.9</v>
-      </c>
-      <c r="T82" s="3">
-        <v>100.9</v>
-      </c>
-      <c r="U82" s="3">
-        <v>113.6</v>
-      </c>
-    </row>
-    <row r="83" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B83" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="P83" s="22">
-        <f t="shared" ref="P83:T83" si="46">SUM(P77:P82)</f>
-        <v>1455.5</v>
-      </c>
-      <c r="Q83" s="22">
-        <f t="shared" si="46"/>
-        <v>2494.7999999999997</v>
-      </c>
-      <c r="R83" s="22">
-        <f>SUM(R77:R82)</f>
-        <v>3698.3</v>
-      </c>
-      <c r="S83" s="22">
-        <f t="shared" si="46"/>
-        <v>2933.0000000000005</v>
-      </c>
-      <c r="T83" s="22">
-        <f t="shared" si="46"/>
-        <v>2865.5</v>
-      </c>
-      <c r="U83" s="22">
-        <f>SUM(U77:U82)</f>
-        <v>2685.0999999999995</v>
-      </c>
-    </row>
-    <row r="85" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B85" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="P85" s="22">
-        <f t="shared" ref="P85:T85" si="47">P76+P83</f>
-        <v>2655.6</v>
-      </c>
-      <c r="Q85" s="22">
-        <f t="shared" si="47"/>
-        <v>4586.7999999999993</v>
-      </c>
-      <c r="R85" s="22">
-        <f>R76+R83</f>
-        <v>5283.1</v>
-      </c>
-      <c r="S85" s="22">
-        <f t="shared" si="47"/>
-        <v>5188.7000000000007</v>
-      </c>
-      <c r="T85" s="22">
-        <f t="shared" si="47"/>
-        <v>4359</v>
-      </c>
-      <c r="U85" s="22">
-        <f>U76+U83</f>
-        <v>4152.2999999999993</v>
-      </c>
-    </row>
-    <row r="87" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B87" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="P87" s="3">
-        <v>1</v>
-      </c>
-      <c r="Q87" s="3">
-        <v>1</v>
-      </c>
-      <c r="R87" s="3">
-        <v>1</v>
-      </c>
-      <c r="S87" s="3">
-        <v>1</v>
-      </c>
-      <c r="T87" s="3">
-        <v>1</v>
-      </c>
-      <c r="U87" s="3">
-        <v>1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="88" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B88" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="P88" s="3">
-        <v>0.3</v>
-      </c>
-      <c r="Q88" s="3">
-        <v>0.3</v>
-      </c>
-      <c r="R88" s="3">
-        <v>0.3</v>
-      </c>
-      <c r="S88" s="3">
-        <v>0.3</v>
-      </c>
-      <c r="T88" s="3">
-        <v>0.3</v>
-      </c>
-      <c r="U88" s="3">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="89" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B89" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="P89" s="3">
-        <v>2493.8000000000002</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>2594.4</v>
-      </c>
-      <c r="R89" s="3">
-        <v>2667.1</v>
-      </c>
-      <c r="S89" s="3">
-        <v>2748.8</v>
-      </c>
-      <c r="T89" s="3">
-        <v>2824.3</v>
-      </c>
-      <c r="U89" s="3">
-        <v>2923.8</v>
-      </c>
-    </row>
-    <row r="90" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B90" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="P90" s="3">
-        <v>5979.1</v>
-      </c>
-      <c r="Q90" s="3">
-        <v>5994</v>
-      </c>
-      <c r="R90" s="3">
-        <v>5872.9</v>
-      </c>
-      <c r="S90" s="3">
-        <v>6274.9</v>
-      </c>
-      <c r="T90" s="3">
-        <v>6598.2</v>
-      </c>
-      <c r="U90" s="3">
-        <v>7051.6</v>
-      </c>
-    </row>
-    <row r="91" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B91" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-5083.6000000000004</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-5778.4</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-5816.1</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-6308.7</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-6797.3</v>
-      </c>
-      <c r="U91" s="3">
-        <v>-7250.3</v>
-      </c>
-    </row>
-    <row r="92" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B92" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="P92" s="3">
-        <v>-103.4</v>
-      </c>
-      <c r="Q92" s="3">
-        <v>-118.2</v>
-      </c>
-      <c r="R92" s="3">
-        <v>-120.8</v>
-      </c>
-      <c r="S92" s="3">
-        <v>-180.3</v>
-      </c>
-      <c r="T92" s="3">
-        <v>-196</v>
-      </c>
-      <c r="U92" s="3">
-        <v>-276.10000000000002</v>
-      </c>
-    </row>
-    <row r="93" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B93" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="P93" s="22">
-        <f t="shared" ref="P93:T93" si="48">SUM(P87:P92)</f>
-        <v>3287.2000000000003</v>
-      </c>
-      <c r="Q93" s="22">
-        <f t="shared" si="48"/>
-        <v>2693.1000000000013</v>
-      </c>
-      <c r="R93" s="22">
-        <f t="shared" si="48"/>
-        <v>2604.3999999999987</v>
-      </c>
-      <c r="S93" s="22">
-        <f t="shared" si="48"/>
-        <v>2536</v>
-      </c>
-      <c r="T93" s="22">
-        <f t="shared" si="48"/>
-        <v>2430.4999999999991</v>
-      </c>
-      <c r="U93" s="22">
-        <f>SUM(U87:U92)</f>
-        <v>2450.3000000000006</v>
-      </c>
-    </row>
-    <row r="95" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B95" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C95" s="1"/>
-      <c r="D95" s="1"/>
-      <c r="E95" s="1"/>
-      <c r="F95" s="1"/>
-      <c r="G95" s="1"/>
-      <c r="H95" s="1"/>
-      <c r="I95" s="1"/>
-      <c r="J95" s="1"/>
-      <c r="K95" s="1"/>
-      <c r="L95" s="1"/>
-      <c r="M95" s="1"/>
-      <c r="N95" s="1"/>
-      <c r="O95" s="1"/>
-      <c r="P95" s="22">
-        <f t="shared" ref="P95:S95" si="49">P93+P85</f>
-        <v>5942.8</v>
-      </c>
-      <c r="Q95" s="22">
-        <f t="shared" si="49"/>
-        <v>7279.9000000000005</v>
-      </c>
-      <c r="R95" s="22">
-        <f>R93+R85</f>
-        <v>7887.4999999999991</v>
-      </c>
-      <c r="S95" s="22">
-        <f t="shared" si="49"/>
-        <v>7724.7000000000007</v>
-      </c>
-      <c r="T95" s="22">
-        <f>T93+T85</f>
-        <v>6789.4999999999991</v>
-      </c>
-      <c r="U95" s="22">
-        <f>U93+U85</f>
-        <v>6602.6</v>
-      </c>
-    </row>
-    <row r="98" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A98" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B98" s="7" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="100" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="B100" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="P100" s="3">
-        <f t="shared" ref="P100:U100" si="50">P32</f>
-        <v>430.89999999999964</v>
-      </c>
-      <c r="Q100" s="3">
-        <f t="shared" si="50"/>
-        <v>384.30000000000041</v>
-      </c>
-      <c r="R100" s="3">
-        <f t="shared" si="50"/>
-        <v>-121.09999999999991</v>
-      </c>
-      <c r="S100" s="3">
-        <f t="shared" si="50"/>
-        <v>600.10000000000014</v>
-      </c>
-      <c r="T100" s="3">
-        <f t="shared" si="50"/>
-        <v>522.70000000000027</v>
-      </c>
-      <c r="U100" s="3">
-        <f t="shared" si="50"/>
-        <v>646.29999999999916</v>
-      </c>
-    </row>
-    <row r="101" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="B101" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="P101" s="3">
-        <v>281.3</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>269.5</v>
-      </c>
-      <c r="R101" s="3">
-        <v>247.6</v>
-      </c>
-      <c r="S101" s="3">
-        <v>229.7</v>
-      </c>
-      <c r="T101" s="3">
-        <v>220.5</v>
-      </c>
-      <c r="U101" s="3">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="102" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="B102" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="P102" s="3">
-        <v>8.5</v>
-      </c>
-      <c r="Q102" s="3">
-        <v>-168.8</v>
-      </c>
-      <c r="R102" s="3">
-        <v>35.6</v>
-      </c>
-      <c r="S102" s="3">
-        <v>-46.1</v>
-      </c>
-      <c r="T102" s="3">
-        <v>3.9</v>
-      </c>
-      <c r="U102" s="3">
-        <v>-41.1</v>
-      </c>
-    </row>
-    <row r="103" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="B103" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="P103" s="3">
-        <v>11.6</v>
-      </c>
-      <c r="Q103" s="3">
-        <v>0</v>
-      </c>
-      <c r="R103" s="3">
-        <v>0</v>
-      </c>
-      <c r="S103" s="3">
-        <v>0</v>
-      </c>
-      <c r="T103" s="3">
-        <v>0</v>
-      </c>
-      <c r="U103" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="B104" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="P104" s="3">
-        <v>88.6</v>
-      </c>
-      <c r="Q104" s="3">
-        <v>100.6</v>
-      </c>
-      <c r="R104" s="3">
-        <v>72.7</v>
-      </c>
-      <c r="S104" s="3">
-        <v>81.7</v>
-      </c>
-      <c r="T104" s="3">
-        <v>75.5</v>
-      </c>
-      <c r="U104" s="3">
-        <v>99.5</v>
-      </c>
-    </row>
-    <row r="105" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="P104" s="12">
+        <v>2357.5</v>
+      </c>
+      <c r="Q104" s="12">
+        <v>2240.4</v>
+      </c>
+      <c r="R104" s="12">
+        <v>1007.2</v>
+      </c>
+      <c r="S104" s="12">
+        <v>964.6</v>
+      </c>
+      <c r="T104" s="12">
+        <v>1293.4000000000001</v>
+      </c>
+      <c r="U104" s="12">
+        <v>304.3</v>
+      </c>
+      <c r="V104" s="12">
+        <v>734.3</v>
+      </c>
+      <c r="W104" s="12">
+        <v>723.6</v>
+      </c>
+    </row>
+    <row r="105" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B105" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="P105" s="3">
-        <v>25.8</v>
-      </c>
-      <c r="Q105" s="3">
-        <v>38.700000000000003</v>
-      </c>
-      <c r="R105" s="3">
-        <v>96</v>
-      </c>
-      <c r="S105" s="3">
-        <v>21.3</v>
-      </c>
-      <c r="T105" s="3">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="U105" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:21" x14ac:dyDescent="0.2">
+        <v>142</v>
+      </c>
+      <c r="P105" s="12">
+        <v>20</v>
+      </c>
+      <c r="Q105" s="12">
+        <v>20.8</v>
+      </c>
+      <c r="R105" s="12">
+        <v>0</v>
+      </c>
+      <c r="S105" s="12">
+        <v>0</v>
+      </c>
+      <c r="T105" s="12">
+        <v>0</v>
+      </c>
+      <c r="U105" s="12">
+        <v>0</v>
+      </c>
+      <c r="V105" s="12">
+        <v>0</v>
+      </c>
+      <c r="W105" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B106" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="P106" s="3">
-        <v>0.4</v>
-      </c>
-      <c r="Q106" s="3">
-        <v>58.7</v>
-      </c>
-      <c r="R106" s="3">
-        <v>-27.6</v>
-      </c>
-      <c r="S106" s="3">
-        <v>-2.2000000000000002</v>
-      </c>
-      <c r="T106" s="3">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="U106" s="3">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="107" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="B107" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="P107" s="3">
-        <v>6.5</v>
-      </c>
-      <c r="Q107" s="3">
-        <v>-2.2999999999999998</v>
-      </c>
-      <c r="R107" s="3">
-        <v>1.8</v>
-      </c>
-      <c r="S107" s="3">
-        <v>1</v>
-      </c>
-      <c r="T107" s="3">
-        <v>1</v>
-      </c>
-      <c r="U107" s="3">
-        <v>13.7</v>
-      </c>
-    </row>
-    <row r="108" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="B108" s="9" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="109" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="B109" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="P109" s="3">
-        <v>10.1</v>
-      </c>
-      <c r="Q109" s="3">
-        <v>57.6</v>
-      </c>
-      <c r="R109" s="3">
-        <v>-143</v>
-      </c>
-      <c r="S109" s="3">
-        <v>32.4</v>
-      </c>
-      <c r="T109" s="3">
-        <v>-52.6</v>
-      </c>
-      <c r="U109" s="3">
-        <v>-15.3</v>
-      </c>
-    </row>
-    <row r="110" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="B110" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="P110" s="3">
-        <v>-83.6</v>
-      </c>
-      <c r="Q110" s="3">
-        <v>72.3</v>
-      </c>
-      <c r="R110" s="3">
-        <v>3.7</v>
-      </c>
-      <c r="S110" s="3">
-        <v>-269.3</v>
-      </c>
-      <c r="T110" s="3">
-        <v>-106.2</v>
-      </c>
-      <c r="U110" s="3">
-        <v>149.1</v>
-      </c>
-    </row>
-    <row r="111" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="B111" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="P111" s="3">
-        <v>-40.5</v>
-      </c>
-      <c r="Q111" s="3">
-        <v>58.2</v>
-      </c>
-      <c r="R111" s="3">
-        <v>5.2</v>
-      </c>
-      <c r="S111" s="3">
-        <v>-28.3</v>
-      </c>
-      <c r="T111" s="3">
-        <v>-19.899999999999999</v>
-      </c>
-      <c r="U111" s="3">
-        <v>16.100000000000001</v>
-      </c>
-    </row>
-    <row r="112" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="B112" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="P112" s="3">
-        <v>-4.7</v>
-      </c>
-      <c r="Q112" s="3">
-        <v>-64.3</v>
-      </c>
-      <c r="R112" s="3">
-        <v>296.8</v>
-      </c>
-      <c r="S112" s="3">
-        <v>194.6</v>
-      </c>
-      <c r="T112" s="3">
-        <v>-225</v>
-      </c>
-      <c r="U112" s="3">
-        <v>15.6</v>
-      </c>
-    </row>
-    <row r="113" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B113" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="P113" s="3">
-        <v>29.7</v>
-      </c>
-      <c r="Q113" s="3">
-        <v>-42.5</v>
-      </c>
-      <c r="R113" s="3">
-        <v>-37.799999999999997</v>
-      </c>
-      <c r="S113" s="3">
-        <v>-62.3</v>
-      </c>
-      <c r="T113" s="3">
-        <v>5.7</v>
-      </c>
-      <c r="U113" s="3">
-        <v>-18.5</v>
-      </c>
-    </row>
-    <row r="114" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B114" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="P114" s="3">
-        <v>-16.5</v>
-      </c>
-      <c r="Q114" s="3">
-        <v>0</v>
-      </c>
-      <c r="R114" s="3">
-        <v>-3.2</v>
-      </c>
-      <c r="S114" s="3">
-        <v>-61.6</v>
-      </c>
-      <c r="T114" s="3">
-        <v>-17.5</v>
-      </c>
-      <c r="U114" s="3">
-        <v>-36.299999999999997</v>
-      </c>
-    </row>
-    <row r="115" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B115" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="P115" s="3">
-        <v>35.700000000000003</v>
-      </c>
-      <c r="Q115" s="3">
-        <v>-7.4</v>
-      </c>
-      <c r="R115" s="3">
-        <v>-45.8</v>
-      </c>
-      <c r="S115" s="3">
-        <v>24.9</v>
-      </c>
-      <c r="T115" s="3">
-        <v>-9.1</v>
-      </c>
-      <c r="U115" s="3">
-        <v>4.3</v>
-      </c>
-    </row>
-    <row r="116" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B116" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="P116" s="22">
-        <f t="shared" ref="P116:T116" si="51">P100+SUM(P101:P107)+SUM(P109:P115)</f>
-        <v>783.79999999999973</v>
-      </c>
-      <c r="Q116" s="22">
-        <f>Q100+SUM(Q101:Q107)+SUM(Q109:Q115)</f>
-        <v>754.60000000000036</v>
-      </c>
-      <c r="R116" s="22">
-        <f t="shared" si="51"/>
-        <v>380.90000000000003</v>
-      </c>
-      <c r="S116" s="22">
-        <f t="shared" si="51"/>
-        <v>715.90000000000032</v>
-      </c>
-      <c r="T116" s="22">
-        <f t="shared" si="51"/>
-        <v>411.00000000000017</v>
-      </c>
-      <c r="U116" s="22">
-        <f>U100+SUM(U101:U107)+SUM(U109:U115)</f>
-        <v>1069.6999999999991</v>
-      </c>
-    </row>
-    <row r="117" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B117" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="P117" s="3">
-        <v>-197.7</v>
-      </c>
-      <c r="Q117" s="3">
-        <v>-270.3</v>
-      </c>
-      <c r="R117" s="3">
-        <v>-107.8</v>
-      </c>
-      <c r="S117" s="3">
-        <v>-166.9</v>
-      </c>
-      <c r="T117" s="3">
-        <v>-217.5</v>
-      </c>
-      <c r="U117" s="3">
-        <v>-164.8</v>
-      </c>
-    </row>
-    <row r="118" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B118" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="P118" s="3">
-        <v>-3030.8</v>
-      </c>
-      <c r="Q118" s="3">
-        <v>-1289.7</v>
-      </c>
-      <c r="R118" s="3">
-        <v>-704.6</v>
-      </c>
-      <c r="S118" s="3">
-        <v>-1510.6</v>
-      </c>
-      <c r="T118" s="3">
-        <v>-598.6</v>
-      </c>
-      <c r="U118" s="3">
-        <v>-392.8</v>
-      </c>
-    </row>
-    <row r="119" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B119" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="P119" s="3">
-        <v>2357.5</v>
-      </c>
-      <c r="Q119" s="3">
-        <v>2240.4</v>
-      </c>
-      <c r="R119" s="3">
-        <v>1007.2</v>
-      </c>
-      <c r="S119" s="3">
-        <v>964.6</v>
-      </c>
-      <c r="T119" s="3">
-        <v>1293.4000000000001</v>
-      </c>
-      <c r="U119" s="3">
-        <v>304.3</v>
-      </c>
-    </row>
-    <row r="120" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B120" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="P120" s="3">
-        <v>20</v>
-      </c>
-      <c r="Q120" s="3">
-        <v>20.8</v>
-      </c>
-      <c r="R120" s="3">
-        <v>0</v>
-      </c>
-      <c r="S120" s="3">
-        <v>0</v>
-      </c>
-      <c r="T120" s="3">
-        <v>0</v>
-      </c>
-      <c r="U120" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B121" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="P121" s="3">
+      <c r="P106" s="12">
         <f>-23.8-4.5</f>
         <v>-28.3</v>
       </c>
-      <c r="Q121" s="3">
+      <c r="Q106" s="12">
         <v>0.9</v>
       </c>
-      <c r="R121" s="3">
+      <c r="R106" s="12">
         <v>0.2</v>
       </c>
-      <c r="S121" s="3">
+      <c r="S106" s="12">
         <v>-5</v>
       </c>
-      <c r="T121" s="3">
+      <c r="T106" s="12">
         <v>-5.8</v>
       </c>
-      <c r="U121" s="3">
+      <c r="U106" s="12">
         <v>-3.5</v>
       </c>
-    </row>
-    <row r="122" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B122" s="1" t="s">
+      <c r="V106" s="12">
+        <v>-0.4</v>
+      </c>
+      <c r="W106" s="12">
+        <f>-41.2+3.1</f>
+        <v>-38.1</v>
+      </c>
+    </row>
+    <row r="107" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B107" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="P107" s="13">
+        <f t="shared" ref="P107:T107" si="55">SUM(P102:P106)</f>
+        <v>-879.3</v>
+      </c>
+      <c r="Q107" s="13">
+        <f t="shared" si="55"/>
+        <v>702.1</v>
+      </c>
+      <c r="R107" s="13">
+        <f t="shared" si="55"/>
+        <v>195.00000000000006</v>
+      </c>
+      <c r="S107" s="13">
+        <f t="shared" si="55"/>
+        <v>-717.9</v>
+      </c>
+      <c r="T107" s="13">
+        <f t="shared" si="55"/>
+        <v>471.50000000000006</v>
+      </c>
+      <c r="U107" s="13">
+        <f>SUM(U102:U106)</f>
+        <v>-256.8</v>
+      </c>
+      <c r="V107" s="13">
+        <f t="shared" ref="V107:W107" si="56">SUM(V102:V106)</f>
+        <v>-264.10000000000002</v>
+      </c>
+      <c r="W107" s="13">
+        <f t="shared" si="56"/>
+        <v>-356.59999999999991</v>
+      </c>
+    </row>
+    <row r="108" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B108" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="P108" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q108" s="12">
+        <v>475</v>
+      </c>
+      <c r="R108" s="12">
+        <v>0</v>
+      </c>
+      <c r="S108" s="12">
+        <v>0</v>
+      </c>
+      <c r="T108" s="12">
+        <v>0</v>
+      </c>
+      <c r="U108" s="12">
+        <v>0</v>
+      </c>
+      <c r="V108" s="12">
+        <v>0</v>
+      </c>
+      <c r="W108" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B109" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P109" s="12">
+        <v>-9.9</v>
+      </c>
+      <c r="Q109" s="12">
+        <v>0</v>
+      </c>
+      <c r="R109" s="12">
+        <v>-475</v>
+      </c>
+      <c r="S109" s="12">
+        <v>0</v>
+      </c>
+      <c r="T109" s="12">
+        <v>0</v>
+      </c>
+      <c r="U109" s="12">
+        <v>0</v>
+      </c>
+      <c r="V109" s="12">
+        <v>0</v>
+      </c>
+      <c r="W109" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B110" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="P110" s="12">
+        <v>398.1</v>
+      </c>
+      <c r="Q110" s="12">
+        <v>0</v>
+      </c>
+      <c r="R110" s="12">
+        <v>1241.9000000000001</v>
+      </c>
+      <c r="S110" s="12">
+        <v>0</v>
+      </c>
+      <c r="T110" s="12">
+        <v>0</v>
+      </c>
+      <c r="U110" s="12">
+        <v>0</v>
+      </c>
+      <c r="V110" s="12">
+        <v>0</v>
+      </c>
+      <c r="W110" s="12">
+        <v>498.2</v>
+      </c>
+    </row>
+    <row r="111" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B111" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="P111" s="12">
+        <v>-300</v>
+      </c>
+      <c r="Q111" s="12">
+        <v>0</v>
+      </c>
+      <c r="R111" s="12">
+        <v>-300</v>
+      </c>
+      <c r="S111" s="12">
+        <v>0</v>
+      </c>
+      <c r="T111" s="12">
+        <v>-500</v>
+      </c>
+      <c r="U111" s="12">
+        <v>0</v>
+      </c>
+      <c r="V111" s="12">
+        <v>0</v>
+      </c>
+      <c r="W111" s="12">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="112" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B112" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="P112" s="12">
+        <v>-19.600000000000001</v>
+      </c>
+      <c r="Q112" s="12">
+        <v>-13.6</v>
+      </c>
+      <c r="R112" s="12">
+        <v>-13.9</v>
+      </c>
+      <c r="S112" s="12">
+        <v>-23.1</v>
+      </c>
+      <c r="T112" s="12">
+        <v>-21.9</v>
+      </c>
+      <c r="U112" s="12">
+        <v>-21.3</v>
+      </c>
+      <c r="V112" s="12">
+        <v>-22</v>
+      </c>
+      <c r="W112" s="12">
+        <v>-23.2</v>
+      </c>
+    </row>
+    <row r="113" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B113" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="P113" s="12">
+        <v>-190.7</v>
+      </c>
+      <c r="Q113" s="12">
+        <v>-203.9</v>
+      </c>
+      <c r="R113" s="12">
+        <v>-49.8</v>
+      </c>
+      <c r="S113" s="12">
+        <v>-150</v>
+      </c>
+      <c r="T113" s="12">
+        <v>-198.3</v>
+      </c>
+      <c r="U113" s="12">
+        <v>-194.6</v>
+      </c>
+      <c r="V113" s="12">
+        <v>-201.1</v>
+      </c>
+      <c r="W113" s="12">
+        <v>-216.5</v>
+      </c>
+    </row>
+    <row r="114" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B114" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="P114" s="12">
+        <v>-502.6</v>
+      </c>
+      <c r="Q114" s="12">
+        <v>-694.8</v>
+      </c>
+      <c r="R114" s="12">
+        <v>-37.700000000000003</v>
+      </c>
+      <c r="S114" s="12">
+        <v>-492.6</v>
+      </c>
+      <c r="T114" s="12">
+        <v>-488.6</v>
+      </c>
+      <c r="U114" s="12">
+        <v>-449.7</v>
+      </c>
+      <c r="V114" s="12">
+        <v>-480.9</v>
+      </c>
+      <c r="W114" s="12">
+        <v>-623.79999999999995</v>
+      </c>
+    </row>
+    <row r="115" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B115" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="P122" s="22">
-        <f t="shared" ref="P122:T122" si="52">SUM(P117:P121)</f>
-        <v>-879.3</v>
-      </c>
-      <c r="Q122" s="22">
-        <f t="shared" si="52"/>
-        <v>702.1</v>
-      </c>
-      <c r="R122" s="22">
-        <f t="shared" si="52"/>
-        <v>195.00000000000006</v>
-      </c>
-      <c r="S122" s="22">
-        <f t="shared" si="52"/>
-        <v>-717.9</v>
-      </c>
-      <c r="T122" s="22">
-        <f t="shared" si="52"/>
-        <v>471.50000000000006</v>
-      </c>
-      <c r="U122" s="22">
-        <f>SUM(U117:U121)</f>
-        <v>-256.8</v>
-      </c>
-    </row>
-    <row r="123" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B123" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="P123" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q123" s="3">
-        <v>475</v>
-      </c>
-      <c r="R123" s="3">
-        <v>0</v>
-      </c>
-      <c r="S123" s="3">
-        <v>0</v>
-      </c>
-      <c r="T123" s="3">
-        <v>0</v>
-      </c>
-      <c r="U123" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B124" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="P124" s="3">
-        <v>-9.9</v>
-      </c>
-      <c r="Q124" s="3">
-        <v>0</v>
-      </c>
-      <c r="R124" s="3">
-        <v>-475</v>
-      </c>
-      <c r="S124" s="3">
-        <v>0</v>
-      </c>
-      <c r="T124" s="3">
-        <v>0</v>
-      </c>
-      <c r="U124" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B125" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="P125" s="3">
-        <v>398.1</v>
-      </c>
-      <c r="Q125" s="3">
-        <v>0</v>
-      </c>
-      <c r="R125" s="3">
-        <v>1241.9000000000001</v>
-      </c>
-      <c r="S125" s="3">
-        <v>0</v>
-      </c>
-      <c r="T125" s="3">
-        <v>0</v>
-      </c>
-      <c r="U125" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B126" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="P126" s="3">
-        <v>-300</v>
-      </c>
-      <c r="Q126" s="3">
-        <v>0</v>
-      </c>
-      <c r="R126" s="3">
-        <v>-300</v>
-      </c>
-      <c r="S126" s="3">
-        <v>0</v>
-      </c>
-      <c r="T126" s="3">
-        <v>-500</v>
-      </c>
-      <c r="U126" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B127" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="P127" s="3">
-        <v>-19.600000000000001</v>
-      </c>
-      <c r="Q127" s="3">
-        <v>-13.6</v>
-      </c>
-      <c r="R127" s="3">
-        <v>-13.9</v>
-      </c>
-      <c r="S127" s="3">
-        <v>-23.1</v>
-      </c>
-      <c r="T127" s="3">
-        <v>-21.9</v>
-      </c>
-      <c r="U127" s="3">
-        <v>-21.3</v>
-      </c>
-    </row>
-    <row r="128" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B128" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="P128" s="3">
-        <v>-190.7</v>
-      </c>
-      <c r="Q128" s="3">
-        <v>-203.9</v>
-      </c>
-      <c r="R128" s="3">
-        <v>-49.8</v>
-      </c>
-      <c r="S128" s="3">
-        <v>-150</v>
-      </c>
-      <c r="T128" s="3">
-        <v>-198.3</v>
-      </c>
-      <c r="U128" s="3">
-        <v>-194.6</v>
-      </c>
-    </row>
-    <row r="129" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B129" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="P129" s="3">
-        <v>-502.6</v>
-      </c>
-      <c r="Q129" s="3">
-        <v>-694.8</v>
-      </c>
-      <c r="R129" s="3">
-        <v>-37.700000000000003</v>
-      </c>
-      <c r="S129" s="3">
-        <v>-492.6</v>
-      </c>
-      <c r="T129" s="3">
-        <v>-488.6</v>
-      </c>
-      <c r="U129" s="3">
-        <v>-449.7</v>
-      </c>
-    </row>
-    <row r="130" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B130" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="P130" s="3">
+      <c r="P115" s="12">
         <f>21.8-2.8</f>
         <v>19</v>
       </c>
-      <c r="Q130" s="3">
+      <c r="Q115" s="12">
         <v>-0.9</v>
       </c>
-      <c r="R130" s="3">
+      <c r="R115" s="12">
         <v>-8.6999999999999993</v>
       </c>
-      <c r="S130" s="3">
-        <v>0</v>
-      </c>
-      <c r="T130" s="3">
-        <v>0</v>
-      </c>
-      <c r="U130" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B131" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C131" s="1"/>
-      <c r="D131" s="1"/>
-      <c r="E131" s="1"/>
-      <c r="F131" s="1"/>
-      <c r="G131" s="1"/>
-      <c r="H131" s="1"/>
-      <c r="I131" s="1"/>
-      <c r="J131" s="1"/>
-      <c r="K131" s="1"/>
-      <c r="L131" s="1"/>
-      <c r="M131" s="1"/>
-      <c r="N131" s="1"/>
-      <c r="O131" s="1"/>
-      <c r="P131" s="22">
-        <f t="shared" ref="P131:R131" si="53">SUM(P123:P130)</f>
+      <c r="S115" s="12">
+        <v>0</v>
+      </c>
+      <c r="T115" s="12">
+        <v>0</v>
+      </c>
+      <c r="U115" s="12">
+        <v>0</v>
+      </c>
+      <c r="V115" s="12">
+        <v>0</v>
+      </c>
+      <c r="W115" s="12">
+        <v>-4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="116" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B116" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C116" s="13"/>
+      <c r="D116" s="13"/>
+      <c r="E116" s="13"/>
+      <c r="F116" s="13"/>
+      <c r="G116" s="13"/>
+      <c r="H116" s="13"/>
+      <c r="I116" s="13"/>
+      <c r="J116" s="13"/>
+      <c r="K116" s="13"/>
+      <c r="L116" s="13"/>
+      <c r="M116" s="13"/>
+      <c r="N116" s="13"/>
+      <c r="O116" s="13"/>
+      <c r="P116" s="13">
+        <f t="shared" ref="P116:R116" si="57">SUM(P108:P115)</f>
         <v>-605.69999999999993</v>
       </c>
-      <c r="Q131" s="22">
-        <f t="shared" si="53"/>
+      <c r="Q116" s="13">
+        <f t="shared" si="57"/>
         <v>-438.19999999999993</v>
       </c>
-      <c r="R131" s="22">
-        <f t="shared" si="53"/>
+      <c r="R116" s="13">
+        <f t="shared" si="57"/>
         <v>356.80000000000013</v>
       </c>
-      <c r="S131" s="22">
-        <f>SUM(S123:S130)</f>
+      <c r="S116" s="13">
+        <f>SUM(S108:S115)</f>
         <v>-665.7</v>
       </c>
-      <c r="T131" s="22">
-        <f t="shared" ref="T131:U131" si="54">SUM(T123:T130)</f>
+      <c r="T116" s="13">
+        <f t="shared" ref="T116:W116" si="58">SUM(T108:T115)</f>
         <v>-1208.8000000000002</v>
       </c>
-      <c r="U131" s="22">
-        <f t="shared" si="54"/>
+      <c r="U116" s="13">
+        <f t="shared" si="58"/>
         <v>-665.6</v>
       </c>
-    </row>
-    <row r="132" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B132" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="P132" s="3">
+      <c r="V116" s="13">
+        <f t="shared" si="58"/>
+        <v>-704</v>
+      </c>
+      <c r="W116" s="13">
+        <f t="shared" si="58"/>
+        <v>-769.69999999999993</v>
+      </c>
+    </row>
+    <row r="117" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B117" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="P117" s="12">
         <v>-27.8</v>
       </c>
-      <c r="Q132" s="3">
+      <c r="Q117" s="12">
         <v>-15.2</v>
       </c>
-      <c r="R132" s="3">
+      <c r="R117" s="12">
         <v>25.5</v>
       </c>
-      <c r="S132" s="3">
+      <c r="S117" s="12">
         <v>-48.3</v>
       </c>
-      <c r="T132" s="3">
+      <c r="T117" s="12">
         <v>-8.8000000000000007</v>
       </c>
-      <c r="U132" s="3">
+      <c r="U117" s="12">
         <v>-13.6</v>
       </c>
-    </row>
-    <row r="133" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B133" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="P133" s="22">
-        <f t="shared" ref="P133:T133" si="55">P116+P122+P131+P132</f>
+      <c r="V117" s="12">
+        <v>-8.23</v>
+      </c>
+      <c r="W117" s="12">
+        <v>37.4</v>
+      </c>
+    </row>
+    <row r="118" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B118" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="P118" s="13">
+        <f t="shared" ref="P118:T118" si="59">P101+P107+P116+P117</f>
         <v>-729.00000000000011</v>
       </c>
-      <c r="Q133" s="22">
-        <f t="shared" si="55"/>
+      <c r="Q118" s="13">
+        <f t="shared" si="59"/>
         <v>1003.3000000000003</v>
       </c>
-      <c r="R133" s="22">
-        <f t="shared" si="55"/>
+      <c r="R118" s="13">
+        <f t="shared" si="59"/>
         <v>958.20000000000027</v>
       </c>
-      <c r="S133" s="22">
-        <f t="shared" si="55"/>
+      <c r="S118" s="13">
+        <f t="shared" si="59"/>
         <v>-715.99999999999966</v>
       </c>
-      <c r="T133" s="22">
-        <f t="shared" si="55"/>
+      <c r="T118" s="13">
+        <f t="shared" si="59"/>
         <v>-335.09999999999997</v>
       </c>
-      <c r="U133" s="22">
-        <f>U116+U122+U131+U132</f>
+      <c r="U118" s="13">
+        <f>U101+U107+U116+U117</f>
         <v>133.69999999999916</v>
       </c>
-    </row>
-    <row r="134" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B134" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="P134" s="3">
-        <f>P135-P133</f>
+      <c r="V118" s="13">
+        <f t="shared" ref="V118:W118" si="60">V101+V107+V116+V117</f>
+        <v>258.76999999999941</v>
+      </c>
+      <c r="W118" s="13">
+        <f t="shared" si="60"/>
+        <v>65.299999999999983</v>
+      </c>
+    </row>
+    <row r="119" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B119" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="P119" s="12">
+        <f>P120-P118</f>
         <v>1355.4999999999991</v>
       </c>
-      <c r="Q134" s="3">
-        <f>Q135-Q133</f>
+      <c r="Q119" s="12">
+        <f>Q120-Q118</f>
         <v>626.49999999999898</v>
       </c>
-      <c r="R134" s="3">
-        <f>R135-R133</f>
+      <c r="R119" s="12">
+        <f>R120-R118</f>
         <v>1629.7999999999993</v>
       </c>
-      <c r="S134" s="3">
-        <f>S135-S133</f>
+      <c r="S119" s="12">
+        <f>S120-S118</f>
         <v>2587.9999999999995</v>
       </c>
-      <c r="T134" s="3">
-        <f>T135-T133</f>
+      <c r="T119" s="12">
+        <f>T120-T118</f>
         <v>1872</v>
       </c>
-      <c r="U134" s="3">
+      <c r="U119" s="12">
         <v>1536.9</v>
       </c>
-    </row>
-    <row r="135" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B135" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="P135" s="3">
-        <f>Q134</f>
+      <c r="V119" s="12">
+        <f>+U120</f>
+        <v>1670.5999999999992</v>
+      </c>
+      <c r="W119" s="12">
+        <f>+V120</f>
+        <v>1929.3699999999985</v>
+      </c>
+    </row>
+    <row r="120" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B120" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="P120" s="12">
+        <f>Q119</f>
         <v>626.49999999999898</v>
       </c>
-      <c r="Q135" s="3">
-        <f>R134</f>
+      <c r="Q120" s="12">
+        <f>R119</f>
         <v>1629.7999999999993</v>
       </c>
-      <c r="R135" s="3">
-        <f>S134</f>
+      <c r="R120" s="12">
+        <f>S119</f>
         <v>2587.9999999999995</v>
       </c>
-      <c r="S135" s="3">
-        <f>T134</f>
+      <c r="S120" s="12">
+        <f>T119</f>
         <v>1872</v>
       </c>
-      <c r="T135" s="3">
-        <f>U134</f>
+      <c r="T120" s="12">
+        <f>U119</f>
         <v>1536.9</v>
       </c>
-      <c r="U135" s="3">
-        <f>U134+U133</f>
+      <c r="U120" s="12">
+        <f>U119+U118</f>
         <v>1670.5999999999992</v>
+      </c>
+      <c r="V120" s="12">
+        <f>+V118+V119</f>
+        <v>1929.3699999999985</v>
+      </c>
+      <c r="W120" s="12">
+        <f>+W119+W118</f>
+        <v>1994.6699999999985</v>
       </c>
     </row>
   </sheetData>
@@ -6633,7 +7048,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A02BCB99-A63D-488B-8623-A5EEB19E3317}">
-  <dimension ref="A1:P63"/>
+  <dimension ref="A1:R63"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="2" customWidth="1"/>
@@ -6642,15 +7057,16 @@
     <col min="4" max="5" width="8.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="9" width="8.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="2"/>
+    <col min="10" max="11" width="8.85546875" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B2" s="7" t="s">
         <v>9</v>
       </c>
@@ -6672,67 +7088,81 @@
       <c r="I2" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="M2" s="4"/>
+      <c r="J2" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="K2" s="28" t="s">
+        <v>299</v>
+      </c>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4" t="s">
+        <v>158</v>
+      </c>
       <c r="N2" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+        <v>159</v>
+      </c>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B3" s="7" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="D4" s="17">
-        <f>Model!P32/Model!P93</f>
+        <f>Model!P32/Model!P81</f>
         <v>0.13108420540277427</v>
       </c>
       <c r="E4" s="17">
-        <f>Model!Q32/Model!Q93</f>
+        <f>Model!Q32/Model!Q81</f>
         <v>0.14269800601537269</v>
       </c>
       <c r="F4" s="17">
-        <f>Model!R32/Model!R93</f>
+        <f>Model!R32/Model!R81</f>
         <v>-4.649823375825525E-2</v>
       </c>
       <c r="G4" s="17">
-        <f>Model!S32/Model!S93</f>
+        <f>Model!S32/Model!S81</f>
         <v>0.23663249211356471</v>
       </c>
       <c r="H4" s="17">
-        <f>Model!T32/Model!T93</f>
+        <f>Model!T32/Model!T81</f>
         <v>0.21505862991154104</v>
       </c>
       <c r="I4" s="17">
-        <f>Model!U32/Model!U93</f>
+        <f>Model!U32/Model!U81</f>
         <v>0.26376362078112842</v>
       </c>
-      <c r="J4" s="17"/>
-      <c r="K4" s="23">
+      <c r="J4" s="17">
+        <f>Model!V32/Model!V81</f>
+        <v>0.28700019316206277</v>
+      </c>
+      <c r="K4" s="17">
+        <f>Model!W32/Model!W81</f>
+        <v>0.33120996691771654</v>
+      </c>
+      <c r="L4" s="17"/>
+      <c r="M4" s="22">
         <f>AVERAGE(G4:I4,D4)</f>
         <v>0.21163473705225211</v>
       </c>
-      <c r="L4" s="23">
+      <c r="N4" s="22">
         <f>MEDIAN(G4:I4,D4:E4)</f>
         <v>0.21505862991154104</v>
       </c>
-      <c r="N4" s="2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="P4" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="D5" s="17">
         <f>Model!P32/Model!P19</f>
@@ -6758,22 +7188,30 @@
         <f>Model!U32/Model!U19</f>
         <v>9.7460566396235973E-2</v>
       </c>
-      <c r="J5" s="17"/>
-      <c r="K5" s="23">
-        <f t="shared" ref="K5:L17" si="0">AVERAGE(G5:I5,D5)</f>
+      <c r="J5" s="17">
+        <f>Model!V32/Model!V19</f>
+        <v>0.10494420115835562</v>
+      </c>
+      <c r="K5" s="17">
+        <f>Model!W32/Model!W19</f>
+        <v>0.11597757101484993</v>
+      </c>
+      <c r="L5" s="17"/>
+      <c r="M5" s="22">
+        <f>AVERAGE(G5:I5,D5)</f>
         <v>8.583454204597514E-2</v>
       </c>
-      <c r="L5" s="23">
-        <f t="shared" ref="L5:L17" si="1">MEDIAN(G5:I5,D5:E5)</f>
+      <c r="N5" s="22">
+        <f t="shared" ref="N5:N17" si="0">MEDIAN(G5:I5,D5:E5)</f>
         <v>8.1119250108634966E-2</v>
       </c>
-      <c r="N5" s="2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="P5" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="D6" s="17">
         <f>Model!P26/Model!P19</f>
@@ -6799,667 +7237,803 @@
         <f>Model!U26/Model!U19</f>
         <v>0.11406339536146201</v>
       </c>
-      <c r="J6" s="17"/>
-      <c r="K6" s="23">
+      <c r="J6" s="17">
+        <f>Model!V26/Model!V19</f>
+        <v>0.13167113999152416</v>
+      </c>
+      <c r="K6" s="17">
+        <f>Model!W26/Model!W19</f>
+        <v>0.14532010598311662</v>
+      </c>
+      <c r="L6" s="17"/>
+      <c r="M6" s="22">
+        <f>AVERAGE(G6:I6,D6)</f>
+        <v>0.11018304789914513</v>
+      </c>
+      <c r="N6" s="22">
         <f t="shared" si="0"/>
-        <v>0.11018304789914513</v>
-      </c>
-      <c r="L6" s="23">
+        <v>0.10928673412378177</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B7" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D7" s="17">
+        <f>(Model!P26+Model!P86)/Model!P19</f>
+        <v>0.13354981783621095</v>
+      </c>
+      <c r="E7" s="17">
+        <f>(Model!Q26+Model!Q86)/Model!Q19</f>
+        <v>9.5214130328906854E-2</v>
+      </c>
+      <c r="F7" s="17">
+        <f>(Model!R26+Model!R86)/Model!R19</f>
+        <v>4.6355208143973842E-2</v>
+      </c>
+      <c r="G7" s="17">
+        <f>(Model!S26+Model!S86)/Model!S19</f>
+        <v>0.16532925946771732</v>
+      </c>
+      <c r="H7" s="17">
+        <f>(Model!T26+Model!T86)/Model!T19</f>
+        <v>0.14350673536532377</v>
+      </c>
+      <c r="I7" s="17">
+        <f>(Model!U26+Model!U86)/Model!U19</f>
+        <v>0.1485960732273727</v>
+      </c>
+      <c r="J7" s="17">
+        <f>(Model!V26+Model!V86)/Model!V19</f>
+        <v>0.16269247068795017</v>
+      </c>
+      <c r="K7" s="17">
+        <f>(Model!W26+Model!W86)/Model!W19</f>
+        <v>0.17403413642245361</v>
+      </c>
+      <c r="M7" s="22">
+        <f>AVERAGE(G7:I7,D7)</f>
+        <v>0.14774547147415618</v>
+      </c>
+      <c r="N7" s="22">
+        <f t="shared" si="0"/>
+        <v>0.14350673536532377</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B8" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D8" s="3">
+        <f>Model!P19/Model!P66</f>
+        <v>1.0622938682102714</v>
+      </c>
+      <c r="E8" s="3">
+        <f>Model!Q19/Model!Q66</f>
+        <v>0.84613799640104947</v>
+      </c>
+      <c r="F8" s="3">
+        <f>Model!R19/Model!R66</f>
+        <v>0.55794611727416799</v>
+      </c>
+      <c r="G8" s="3">
+        <f>Model!S19/Model!S66</f>
+        <v>0.80501508149183776</v>
+      </c>
+      <c r="H8" s="3">
+        <f>Model!T19/Model!T66</f>
+        <v>0.94905368583842709</v>
+      </c>
+      <c r="I8" s="3">
+        <f>Model!U19/Model!U66</f>
+        <v>1.0043619180322902</v>
+      </c>
+      <c r="J8" s="3">
+        <f>Model!V19/Model!V66</f>
+        <v>1.0044981766066436</v>
+      </c>
+      <c r="K8" s="3">
+        <f>Model!W19/Model!W66</f>
+        <v>1.0484527424252212</v>
+      </c>
+      <c r="M8" s="23">
+        <f>AVERAGE(G8:I8,D8)</f>
+        <v>0.95518113839320651</v>
+      </c>
+      <c r="N8" s="23">
+        <f>AVERAGE(H8:L8,E8)</f>
+        <v>0.9705009038607264</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B9" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D9" s="17">
+        <f>(Model!P32+Model!P27)/Model!P66</f>
+        <v>7.5991115299185522E-2</v>
+      </c>
+      <c r="E9" s="17">
+        <f>(Model!Q32+Model!Q27)/Model!Q66</f>
+        <v>5.5206802291240323E-2</v>
+      </c>
+      <c r="F9" s="17">
+        <f>(Model!R32+Model!R27)/Model!R66</f>
+        <v>-9.2044374009508604E-3</v>
+      </c>
+      <c r="G9" s="17">
+        <f>(Model!S32+Model!S27)/Model!S66</f>
+        <v>8.4676427563529985E-2</v>
+      </c>
+      <c r="H9" s="17">
+        <f>(Model!T32+Model!T27)/Model!T66</f>
+        <v>8.2936887841520035E-2</v>
+      </c>
+      <c r="I9" s="17">
+        <f>(Model!U32+Model!U27)/Model!U66</f>
+        <v>0.10427710295944011</v>
+      </c>
+      <c r="J9" s="17">
+        <f>(Model!V32+Model!V27)/Model!V66</f>
+        <v>0.11167397442992344</v>
+      </c>
+      <c r="K9" s="17">
+        <f>(Model!W32+Model!W27)/Model!W66</f>
+        <v>0.12860003876219392</v>
+      </c>
+      <c r="M9" s="22">
+        <f>AVERAGE(G9:I9,D9)</f>
+        <v>8.6970383415918909E-2</v>
+      </c>
+      <c r="N9" s="22">
+        <f t="shared" si="0"/>
+        <v>8.2936887841520035E-2</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B10" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D10" s="17">
+        <f>Model!P26/Model!P66</f>
+        <v>9.4534562832334898E-2</v>
+      </c>
+      <c r="E10" s="17">
+        <f>Model!Q26/Model!Q66</f>
+        <v>4.3544554183436647E-2</v>
+      </c>
+      <c r="F10" s="17">
+        <f>Model!R26/Model!R66</f>
+        <v>-5.5277337559429358E-3</v>
+      </c>
+      <c r="G10" s="17">
+        <f>Model!S26/Model!S66</f>
+        <v>0.1033567646639999</v>
+      </c>
+      <c r="H10" s="17">
+        <f>Model!T26/Model!T66</f>
+        <v>0.1037189778334193</v>
+      </c>
+      <c r="I10" s="17">
+        <f>Model!U26/Model!U66</f>
+        <v>0.11456093054251344</v>
+      </c>
+      <c r="J10" s="17">
+        <f>Model!V26/Model!V66</f>
+        <v>0.13226342003320413</v>
+      </c>
+      <c r="K10" s="17">
+        <f>Model!W26/Model!W66</f>
+        <v>0.15236126364752242</v>
+      </c>
+      <c r="M10" s="22">
+        <f>AVERAGE(G10:I10,D10)</f>
+        <v>0.10404280896806689</v>
+      </c>
+      <c r="N10" s="22">
+        <f t="shared" si="0"/>
+        <v>0.1033567646639999</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B11" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D11" s="17">
+        <f>Model!P26/(Model!P65+SUM(Model!P53:P57)-Model!P68)</f>
+        <v>0.10895198200294773</v>
+      </c>
+      <c r="E11" s="17">
+        <f>Model!Q26/(Model!Q65+SUM(Model!Q53:Q57)-Model!Q68)</f>
+        <v>5.8565965229922308E-2</v>
+      </c>
+      <c r="F11" s="17">
+        <f>Model!R26/(Model!R65+SUM(Model!R53:R57)-Model!R68)</f>
+        <v>-8.8034567701813001E-3</v>
+      </c>
+      <c r="G11" s="17">
+        <f>Model!S26/(Model!S65+SUM(Model!S53:S57)-Model!S68)</f>
+        <v>0.1475185691585677</v>
+      </c>
+      <c r="H11" s="17">
+        <f>Model!T26/(Model!T65+SUM(Model!T53:T57)-Model!T68)</f>
+        <v>0.1440494211021561</v>
+      </c>
+      <c r="I11" s="17">
+        <f>Model!U26/(Model!U65+SUM(Model!U53:U57)-Model!U68)</f>
+        <v>0.16414218132893521</v>
+      </c>
+      <c r="J11" s="17">
+        <f>Model!V26/(Model!V65+SUM(Model!V53:V57)-Model!V68)</f>
+        <v>0.19879286811124369</v>
+      </c>
+      <c r="K11" s="17">
+        <f>Model!W26/(Model!W65+SUM(Model!W53:W57)-Model!W68)</f>
+        <v>0.22163330514049429</v>
+      </c>
+      <c r="M11" s="22">
+        <f>AVERAGE(G11:I11,D11)</f>
+        <v>0.14116553839815169</v>
+      </c>
+      <c r="N11" s="22">
+        <f t="shared" si="0"/>
+        <v>0.1440494211021561</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B12" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D12" s="17">
+        <f>(Model!P26*(1-Model!P49))/(Model!P80+Model!P81-Model!P52)</f>
+        <v>6.7954266989665613E-2</v>
+      </c>
+      <c r="E12" s="17">
+        <f>(Model!Q26*(1-Model!Q49))/(Model!Q80+Model!Q81-Model!Q52)</f>
+        <v>6.4450983917599694E-2</v>
+      </c>
+      <c r="F12" s="17">
+        <f>(Model!R26*(1-Model!R49))/(Model!R80+Model!R81-Model!R52)</f>
+        <v>-1.1353401019989813E-2</v>
+      </c>
+      <c r="G12" s="17">
+        <f>(Model!S26*(1-Model!S49))/(Model!S80+Model!S81-Model!S52)</f>
+        <v>0.10115276816817223</v>
+      </c>
+      <c r="H12" s="17">
+        <f>(Model!T26*(1-Model!T49))/(Model!T80+Model!T81-Model!T52)</f>
+        <v>9.0537955221594135E-2</v>
+      </c>
+      <c r="I12" s="17">
+        <f>(Model!U26*(1-Model!U49))/(Model!U80+Model!U81-Model!U52)</f>
+        <v>0.12204812323753214</v>
+      </c>
+      <c r="J12" s="17">
+        <f>(Model!V26*(1-Model!V49))/(Model!V80+Model!V81-Model!V52)</f>
+        <v>0.13100569615484053</v>
+      </c>
+      <c r="K12" s="17">
+        <f>(Model!W26*(1-Model!W49))/(Model!W80+Model!W81-Model!W52)</f>
+        <v>0.1534799222127313</v>
+      </c>
+      <c r="M12" s="22">
+        <f>AVERAGE(G12:I12,D12)</f>
+        <v>9.542327840424103E-2</v>
+      </c>
+      <c r="N12" s="22">
+        <f t="shared" si="0"/>
+        <v>9.0537955221594135E-2</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B13" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D13" s="17">
+        <f>Model!P101/Model!P19</f>
+        <v>0.12415650245525102</v>
+      </c>
+      <c r="E13" s="17">
+        <f>Model!Q101/Model!Q19</f>
+        <v>0.12250397740186375</v>
+      </c>
+      <c r="F13" s="17">
+        <f>Model!R101/Model!R19</f>
+        <v>8.6552445009998188E-2</v>
+      </c>
+      <c r="G13" s="17">
+        <f>Model!S101/Model!S19</f>
+        <v>0.11512422609954175</v>
+      </c>
+      <c r="H13" s="17">
+        <f>Model!T101/Model!T19</f>
+        <v>6.3784220001241565E-2</v>
+      </c>
+      <c r="I13" s="17">
+        <f>Model!U101/Model!U19</f>
+        <v>0.1613083210181861</v>
+      </c>
+      <c r="J13" s="17">
+        <f>Model!V101/Model!V19</f>
+        <v>0.17447379573386063</v>
+      </c>
+      <c r="K13" s="17">
+        <f>Model!W101/Model!W19</f>
+        <v>0.14223920142953969</v>
+      </c>
+      <c r="M13" s="22">
+        <f>AVERAGE(G13:I13,D13)</f>
+        <v>0.11609331739355511</v>
+      </c>
+      <c r="N13" s="22">
+        <f t="shared" si="0"/>
+        <v>0.12250397740186375</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B14" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D14" s="17">
+        <f>1-(Model!P113/Model!P114)</f>
+        <v>0.62057302029446881</v>
+      </c>
+      <c r="E14" s="17">
+        <f>1-(Model!Q113/Model!Q114)</f>
+        <v>0.70653425446171558</v>
+      </c>
+      <c r="F14" s="17">
+        <f>1-(Model!R113/Model!R114)</f>
+        <v>-0.32095490716180364</v>
+      </c>
+      <c r="G14" s="17">
+        <f>1-(Model!S113/Model!S114)</f>
+        <v>0.69549330085261873</v>
+      </c>
+      <c r="H14" s="17">
+        <f>1-(Model!T113/Model!T114)</f>
+        <v>0.59414654113794518</v>
+      </c>
+      <c r="I14" s="17">
+        <f>1-(Model!U113/Model!U114)</f>
+        <v>0.56726706693351125</v>
+      </c>
+      <c r="J14" s="17">
+        <f>1-(Model!V113/Model!V114)</f>
+        <v>0.5818257433977958</v>
+      </c>
+      <c r="K14" s="17">
+        <f>1-(Model!W113/Model!W114)</f>
+        <v>0.65293363257454318</v>
+      </c>
+      <c r="M14" s="22">
+        <f>AVERAGE(G14:I14,D14)</f>
+        <v>0.61936998230463591</v>
+      </c>
+      <c r="N14" s="22">
+        <f t="shared" si="0"/>
+        <v>0.62057302029446881</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B15" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D15" s="22">
+        <f t="shared" ref="D15:H15" si="1">D14*D4</f>
+        <v>8.134732125970015E-2</v>
+      </c>
+      <c r="E15" s="22">
         <f t="shared" si="1"/>
-        <v>0.10928673412378177</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B7" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="D7" s="17">
-        <f>(Model!P26+Model!P101)/Model!P19</f>
-        <v>0.13354981783621095</v>
-      </c>
-      <c r="E7" s="17">
-        <f>(Model!Q26+Model!Q101)/Model!Q19</f>
-        <v>9.5214130328906854E-2</v>
-      </c>
-      <c r="F7" s="17">
-        <f>(Model!R26+Model!R101)/Model!R19</f>
-        <v>4.6355208143973842E-2</v>
-      </c>
-      <c r="G7" s="17">
-        <f>(Model!S26+Model!S101)/Model!S19</f>
-        <v>0.16532925946771732</v>
-      </c>
-      <c r="H7" s="17">
-        <f>(Model!T26+Model!T101)/Model!T19</f>
-        <v>0.14350673536532377</v>
-      </c>
-      <c r="I7" s="17">
-        <f>(Model!U26+Model!U101)/Model!U19</f>
-        <v>0.1485960732273727</v>
-      </c>
-      <c r="K7" s="23">
-        <f t="shared" si="0"/>
-        <v>0.14774547147415618</v>
-      </c>
-      <c r="L7" s="23">
+        <v>0.10082102929324475</v>
+      </c>
+      <c r="F15" s="22">
         <f t="shared" si="1"/>
-        <v>0.14350673536532377</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B8" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="D8" s="3">
-        <f>Model!P19/Model!P69</f>
-        <v>1.0622938682102714</v>
-      </c>
-      <c r="E8" s="3">
-        <f>Model!Q19/Model!Q69</f>
-        <v>0.84613799640104947</v>
-      </c>
-      <c r="F8" s="3">
-        <f>Model!R19/Model!R69</f>
-        <v>0.55794611727416799</v>
-      </c>
-      <c r="G8" s="3">
-        <f>Model!S19/Model!S69</f>
-        <v>0.80501508149183776</v>
-      </c>
-      <c r="H8" s="3">
-        <f>Model!T19/Model!T69</f>
-        <v>0.94905368583842709</v>
-      </c>
-      <c r="I8" s="3">
-        <f>Model!U19/Model!U69</f>
-        <v>1.0043619180322902</v>
-      </c>
-      <c r="K8" s="24">
-        <f t="shared" si="0"/>
-        <v>0.95518113839320651</v>
-      </c>
-      <c r="L8" s="24">
-        <f t="shared" si="0"/>
-        <v>0.93318453342392227</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B9" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="D9" s="17">
-        <f>(Model!P32+Model!P27)/Model!P69</f>
-        <v>7.5991115299185522E-2</v>
-      </c>
-      <c r="E9" s="17">
-        <f>(Model!Q32+Model!Q27)/Model!Q69</f>
-        <v>5.5206802291240323E-2</v>
-      </c>
-      <c r="F9" s="17">
-        <f>(Model!R32+Model!R27)/Model!R69</f>
-        <v>-9.2044374009508604E-3</v>
-      </c>
-      <c r="G9" s="17">
-        <f>(Model!S32+Model!S27)/Model!S69</f>
-        <v>8.4676427563529985E-2</v>
-      </c>
-      <c r="H9" s="17">
-        <f>(Model!T32+Model!T27)/Model!T69</f>
-        <v>8.2936887841520035E-2</v>
-      </c>
-      <c r="I9" s="17">
-        <f>(Model!U32+Model!U27)/Model!U69</f>
-        <v>0.10427710295944011</v>
-      </c>
-      <c r="K9" s="23">
-        <f t="shared" si="0"/>
-        <v>8.6970383415918909E-2</v>
-      </c>
-      <c r="L9" s="23">
+        <v>1.4923836299068658E-2</v>
+      </c>
+      <c r="G15" s="22">
         <f t="shared" si="1"/>
-        <v>8.2936887841520035E-2</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B10" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="D10" s="17">
-        <f>Model!P26/Model!P69</f>
-        <v>9.4534562832334898E-2</v>
-      </c>
-      <c r="E10" s="17">
-        <f>Model!Q26/Model!Q69</f>
-        <v>4.3544554183436647E-2</v>
-      </c>
-      <c r="F10" s="17">
-        <f>Model!R26/Model!R69</f>
-        <v>-5.5277337559429358E-3</v>
-      </c>
-      <c r="G10" s="17">
-        <f>Model!S26/Model!S69</f>
-        <v>0.1033567646639999</v>
-      </c>
-      <c r="H10" s="17">
-        <f>Model!T26/Model!T69</f>
-        <v>0.1037189778334193</v>
-      </c>
-      <c r="I10" s="17">
-        <f>Model!U26/Model!U69</f>
-        <v>0.11456093054251344</v>
-      </c>
-      <c r="K10" s="23">
-        <f t="shared" si="0"/>
-        <v>0.10404280896806689</v>
-      </c>
-      <c r="L10" s="23">
+        <v>0.16457631302904438</v>
+      </c>
+      <c r="H15" s="22">
         <f t="shared" si="1"/>
-        <v>0.1033567646639999</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B11" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="D11" s="17">
-        <f>Model!P26/(Model!P67+SUM(Model!P55:P59)-Model!P72)</f>
-        <v>0.10895198200294773</v>
-      </c>
-      <c r="E11" s="17">
-        <f>Model!Q26/(Model!Q67+SUM(Model!Q55:Q59)-Model!Q72)</f>
-        <v>5.8565965229922308E-2</v>
-      </c>
-      <c r="F11" s="17">
-        <f>Model!R26/(Model!R67+SUM(Model!R55:R59)-Model!R72)</f>
-        <v>-8.8034567701813001E-3</v>
-      </c>
-      <c r="G11" s="17">
-        <f>Model!S26/(Model!S67+SUM(Model!S55:S59)-Model!S72)</f>
-        <v>0.1475185691585677</v>
-      </c>
-      <c r="H11" s="17">
-        <f>Model!T26/(Model!T67+SUM(Model!T55:T59)-Model!T72)</f>
-        <v>0.1440494211021561</v>
-      </c>
-      <c r="I11" s="17">
-        <f>Model!U26/(Model!U67+SUM(Model!U55:U59)-Model!U72)</f>
-        <v>0.16414218132893521</v>
-      </c>
-      <c r="K11" s="23">
-        <f t="shared" si="0"/>
-        <v>0.14116553839815169</v>
-      </c>
-      <c r="L11" s="23">
-        <f t="shared" si="1"/>
-        <v>0.1440494211021561</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B12" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="D12" s="17">
-        <f>(Model!P26*(1-Model!P49))/(Model!P85+Model!P93-Model!P54)</f>
-        <v>6.7954266989665613E-2</v>
-      </c>
-      <c r="E12" s="17">
-        <f>(Model!Q26*(1-Model!Q49))/(Model!Q85+Model!Q93-Model!Q54)</f>
-        <v>6.4450983917599694E-2</v>
-      </c>
-      <c r="F12" s="17">
-        <f>(Model!R26*(1-Model!R49))/(Model!R85+Model!R93-Model!R54)</f>
-        <v>-1.1353401019989813E-2</v>
-      </c>
-      <c r="G12" s="17">
-        <f>(Model!S26*(1-Model!S49))/(Model!S85+Model!S93-Model!S54)</f>
-        <v>0.10115276816817223</v>
-      </c>
-      <c r="H12" s="17">
-        <f>(Model!T26*(1-Model!T49))/(Model!T85+Model!T93-Model!T54)</f>
-        <v>9.0537955221594135E-2</v>
-      </c>
-      <c r="I12" s="17">
-        <f>(Model!U26*(1-Model!U49))/(Model!U85+Model!U93-Model!U54)</f>
-        <v>0.12204812323753214</v>
-      </c>
-      <c r="K12" s="23">
-        <f t="shared" si="0"/>
-        <v>9.542327840424103E-2</v>
-      </c>
-      <c r="L12" s="23">
-        <f t="shared" si="1"/>
-        <v>9.0537955221594135E-2</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B13" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="D13" s="17">
-        <f>Model!P116/Model!P19</f>
-        <v>0.12415650245525102</v>
-      </c>
-      <c r="E13" s="17">
-        <f>Model!Q116/Model!Q19</f>
-        <v>0.12250397740186375</v>
-      </c>
-      <c r="F13" s="17">
-        <f>Model!R116/Model!R19</f>
-        <v>8.6552445009998188E-2</v>
-      </c>
-      <c r="G13" s="17">
-        <f>Model!S116/Model!S19</f>
-        <v>0.11512422609954175</v>
-      </c>
-      <c r="H13" s="17">
-        <f>Model!T116/Model!T19</f>
-        <v>6.3784220001241565E-2</v>
-      </c>
-      <c r="I13" s="17">
-        <f>Model!U116/Model!U19</f>
-        <v>0.1613083210181861</v>
-      </c>
-      <c r="K13" s="23">
-        <f t="shared" si="0"/>
-        <v>0.11609331739355511</v>
-      </c>
-      <c r="L13" s="23">
-        <f t="shared" si="1"/>
-        <v>0.12250397740186375</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B14" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="D14" s="17">
-        <f>1-(Model!P128/Model!P129)</f>
-        <v>0.62057302029446881</v>
-      </c>
-      <c r="E14" s="17">
-        <f>1-(Model!Q128/Model!Q129)</f>
-        <v>0.70653425446171558</v>
-      </c>
-      <c r="F14" s="17">
-        <f>1-(Model!R128/Model!R129)</f>
-        <v>-0.32095490716180364</v>
-      </c>
-      <c r="G14" s="17">
-        <f>1-(Model!S128/Model!S129)</f>
-        <v>0.69549330085261873</v>
-      </c>
-      <c r="H14" s="17">
-        <f>1-(Model!T128/Model!T129)</f>
-        <v>0.59414654113794518</v>
-      </c>
-      <c r="I14" s="17">
-        <f>1-(Model!U128/Model!U129)</f>
-        <v>0.56726706693351125</v>
-      </c>
-      <c r="K14" s="23">
-        <f t="shared" si="0"/>
-        <v>0.61936998230463591</v>
-      </c>
-      <c r="L14" s="23">
-        <f t="shared" si="1"/>
-        <v>0.62057302029446881</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B15" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="D15" s="23">
-        <f t="shared" ref="D15:H15" si="2">D14*D4</f>
-        <v>8.134732125970015E-2</v>
-      </c>
-      <c r="E15" s="23">
-        <f t="shared" si="2"/>
-        <v>0.10082102929324475</v>
-      </c>
-      <c r="F15" s="23">
-        <f t="shared" si="2"/>
-        <v>1.4923836299068658E-2</v>
-      </c>
-      <c r="G15" s="23">
-        <f t="shared" si="2"/>
-        <v>0.16457631302904438</v>
-      </c>
-      <c r="H15" s="23">
-        <f t="shared" si="2"/>
         <v>0.12777634110380753</v>
       </c>
-      <c r="I15" s="23">
+      <c r="I15" s="22">
         <f>I14*I4</f>
         <v>0.14962441552427366</v>
       </c>
-      <c r="K15" s="23">
+      <c r="J15" s="22">
+        <f t="shared" ref="J15:K15" si="2">J14*J4</f>
+        <v>0.16698410074182815</v>
+      </c>
+      <c r="K15" s="22">
+        <f t="shared" si="2"/>
+        <v>0.21625812684447893</v>
+      </c>
+      <c r="M15" s="22">
+        <f>AVERAGE(G15:I15,D15)</f>
+        <v>0.13083109772920642</v>
+      </c>
+      <c r="N15" s="22">
         <f t="shared" si="0"/>
-        <v>0.13083109772920642</v>
-      </c>
-      <c r="L15" s="23">
-        <f t="shared" si="1"/>
         <v>0.12777634110380753</v>
       </c>
-      <c r="N15" s="2" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="P15" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="D16" s="17">
-        <f>(-Model!P117+SUM(Model!P109:P115))/(Model!P26*(1-Model!P49))</f>
+        <f>(-Model!P102+SUM(Model!P94:P100))/(Model!P26*(1-Model!P49))</f>
         <v>0.35123223560095407</v>
       </c>
       <c r="E16" s="17">
-        <f>(-Model!Q117+SUM(Model!Q109:Q115))/(Model!Q26*(1-Model!Q49))</f>
+        <f>(-Model!Q102+SUM(Model!Q94:Q100))/(Model!Q26*(1-Model!Q49))</f>
         <v>0.94363328182716921</v>
       </c>
       <c r="F16" s="17">
-        <f>(-Model!R117+SUM(Model!R109:R115))/(Model!R26*(1-Model!R49))</f>
+        <f>(-Model!R102+SUM(Model!R94:R100))/(Model!R26*(1-Model!R49))</f>
         <v>-3.0479746911753476</v>
       </c>
       <c r="G16" s="17">
-        <f>(-Model!S117+SUM(Model!S109:S115))/(Model!S26*(1-Model!S49))</f>
+        <f>(-Model!S102+SUM(Model!S94:S100))/(Model!S26*(1-Model!S49))</f>
         <v>-4.5543004770761675E-3</v>
       </c>
       <c r="H16" s="17">
-        <f>(-Model!T117+SUM(Model!T109:T115))/(Model!T26*(1-Model!T49))</f>
+        <f>(-Model!T102+SUM(Model!T94:T100))/(Model!T26*(1-Model!T49))</f>
         <v>-0.43485769561254406</v>
       </c>
       <c r="I16" s="17">
-        <f>(-Model!U117+SUM(Model!U109:U115))/(Model!U26*(1-Model!U49))</f>
+        <f>(-Model!U102+SUM(Model!U94:U100))/(Model!U26*(1-Model!U49))</f>
         <v>0.46403900997204856</v>
       </c>
-      <c r="K16" s="23">
+      <c r="J16" s="17">
+        <f>(-Model!V102+SUM(Model!V94:V100))/(Model!V26*(1-Model!V49))</f>
+        <v>0.62274904032789258</v>
+      </c>
+      <c r="K16" s="17">
+        <f>(-Model!W102+SUM(Model!W94:W100))/(Model!W26*(1-Model!W49))</f>
+        <v>0.28298260455898461</v>
+      </c>
+      <c r="M16" s="22">
+        <f>AVERAGE(G16:I16,D16)</f>
+        <v>9.3964812370845599E-2</v>
+      </c>
+      <c r="N16" s="22">
         <f t="shared" si="0"/>
-        <v>9.3964812370845599E-2</v>
-      </c>
-      <c r="L16" s="23">
-        <f t="shared" si="1"/>
         <v>0.35123223560095407</v>
       </c>
-      <c r="N16" s="2" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P16" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="17" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="D17" s="23">
+        <v>184</v>
+      </c>
+      <c r="D17" s="22">
         <f t="shared" ref="D17:H17" si="3">D16*D12</f>
         <v>2.3867729113404366E-2</v>
       </c>
-      <c r="E17" s="23">
+      <c r="E17" s="22">
         <f t="shared" si="3"/>
         <v>6.0818093471154702E-2</v>
       </c>
-      <c r="F17" s="23">
+      <c r="F17" s="22">
         <f t="shared" si="3"/>
         <v>3.4604878967693327E-2</v>
       </c>
-      <c r="G17" s="23">
+      <c r="G17" s="22">
         <f t="shared" si="3"/>
         <v>-4.6068010032588176E-4</v>
       </c>
-      <c r="H17" s="23">
+      <c r="H17" s="22">
         <f t="shared" si="3"/>
         <v>-3.937112657313413E-2</v>
       </c>
-      <c r="I17" s="23">
+      <c r="I17" s="22">
         <f>I16*I12</f>
         <v>5.6635090276090989E-2</v>
       </c>
-      <c r="K17" s="23">
+      <c r="J17" s="22">
+        <f t="shared" ref="J17:K17" si="4">J16*J12</f>
+        <v>8.1583671557914433E-2</v>
+      </c>
+      <c r="K17" s="22">
+        <f t="shared" si="4"/>
+        <v>4.3432148135269057E-2</v>
+      </c>
+      <c r="M17" s="22">
+        <f>AVERAGE(G17:I17,D17)</f>
+        <v>1.0167753179008835E-2</v>
+      </c>
+      <c r="N17" s="22">
         <f t="shared" si="0"/>
-        <v>1.0167753179008835E-2</v>
-      </c>
-      <c r="L17" s="23">
-        <f t="shared" si="1"/>
         <v>2.3867729113404366E-2</v>
       </c>
-      <c r="N17" s="2" t="s">
+      <c r="P17" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="20" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B20" s="7" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="21" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B21" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D21" s="17">
+        <f>Model!P81/Model!P82</f>
+        <v>0.55313993403782735</v>
+      </c>
+      <c r="E21" s="17">
+        <f>Model!Q81/Model!Q82</f>
+        <v>0.36993640022527796</v>
+      </c>
+      <c r="F21" s="17">
+        <f>Model!R81/Model!R82</f>
+        <v>0.33019334389857358</v>
+      </c>
+      <c r="G21" s="17">
+        <f>Model!S81/Model!S82</f>
+        <v>0.32829753906300563</v>
+      </c>
+      <c r="H21" s="17">
+        <f>Model!T81/Model!T82</f>
+        <v>0.35797923263863307</v>
+      </c>
+      <c r="I21" s="17">
+        <f>Model!U81/Model!U82</f>
+        <v>0.37111138036531072</v>
+      </c>
+      <c r="J21" s="17">
+        <f>Model!V81/Model!V82</f>
+        <v>0.36730379010401143</v>
+      </c>
+      <c r="K21" s="17">
+        <f>Model!W81/Model!W82</f>
+        <v>0.36712965953872989</v>
+      </c>
+      <c r="M21" s="22">
+        <f t="shared" ref="M21:M33" si="5">AVERAGE(G21:I21,D21)</f>
+        <v>0.40263202152619421</v>
+      </c>
+      <c r="N21" s="22">
+        <f t="shared" ref="N21:N33" si="6">MEDIAN(G21:I21,D21:E21)</f>
+        <v>0.36993640022527796</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="22" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B22" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D22" s="17">
+        <f>(Model!P67+Model!P73+Model!P74+Model!P75-Model!P52-Model!P53)/Model!P81</f>
+        <v>-0.39498661474811392</v>
+      </c>
+      <c r="E22" s="17">
+        <f>(Model!Q67+Model!Q73+Model!Q74+Model!Q75-Model!Q52-Model!Q53)/Model!Q81</f>
+        <v>0.23133192232000291</v>
+      </c>
+      <c r="F22" s="17">
+        <f>(Model!R67+Model!R73+Model!R74+Model!R75-Model!R52-Model!R53)/Model!R81</f>
+        <v>5.794040853939493E-2</v>
+      </c>
+      <c r="G22" s="17">
+        <f>(Model!S67+Model!S73+Model!S74+Model!S75-Model!S52-Model!S53)/Model!S81</f>
+        <v>0.20177444794952695</v>
+      </c>
+      <c r="H22" s="17">
+        <f>(Model!T67+Model!T73+Model!T74+Model!T75-Model!T52-Model!T53)/Model!T81</f>
+        <v>0.42345196461633405</v>
+      </c>
+      <c r="I22" s="17">
+        <f>(Model!U67+Model!U73+Model!U74+Model!U75-Model!U52-Model!U53)/Model!U81</f>
+        <v>0.25605027955760506</v>
+      </c>
+      <c r="J22" s="17">
+        <f>(Model!V67+Model!V73+Model!V74+Model!V75-Model!V52-Model!V53)/Model!V81</f>
+        <v>0.1310025111068186</v>
+      </c>
+      <c r="K22" s="17">
+        <f>(Model!W67+Model!W73+Model!W74+Model!W75-Model!W52-Model!W53)/Model!W81</f>
+        <v>0.2505806996550996</v>
+      </c>
+      <c r="M22" s="22">
+        <f t="shared" si="5"/>
+        <v>0.12157251934383803</v>
+      </c>
+      <c r="N22" s="22">
+        <f t="shared" si="6"/>
+        <v>0.23133192232000291</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="23" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B23" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D23" s="17">
+        <f>(Model!P67+Model!P73+Model!P74+Model!P75-Model!P52-Model!P53)/(Model!P26*(1-Model!P49)+Model!P86+Model!P102+SUM(Model!P94:P100))</f>
+        <v>-3.4354065857466791</v>
+      </c>
+      <c r="E23" s="17">
+        <f>(Model!Q67+Model!Q73+Model!Q74+Model!Q75-Model!Q52-Model!Q53)/(Model!Q26*(1-Model!Q49)+Model!Q86+Model!Q102+SUM(Model!Q94:Q100))</f>
+        <v>1.422828098672291</v>
+      </c>
+      <c r="F23" s="17">
+        <f>(Model!R67+Model!R73+Model!R74+Model!R75-Model!R52-Model!R53)/(Model!R26*(1-Model!R49)+Model!R86+Model!R102+SUM(Model!R94:R100))</f>
+        <v>0.9708521072772508</v>
+      </c>
+      <c r="G23" s="17">
+        <f>(Model!S67+Model!S73+Model!S74+Model!S75-Model!S52-Model!S53)/(Model!S26*(1-Model!S49)+Model!S86+Model!S102+SUM(Model!S94:S100))</f>
+        <v>1.0527804515936778</v>
+      </c>
+      <c r="H23" s="17">
+        <f>(Model!T67+Model!T73+Model!T74+Model!T75-Model!T52-Model!T53)/(Model!T26*(1-Model!T49)+Model!T86+Model!T102+SUM(Model!T94:T100))</f>
+        <v>18.833345586356071</v>
+      </c>
+      <c r="I23" s="17">
+        <f>(Model!U67+Model!U73+Model!U74+Model!U75-Model!U52-Model!U53)/(Model!U26*(1-Model!U49)+Model!U86+Model!U102+SUM(Model!U94:U100))</f>
+        <v>0.80213095480752494</v>
+      </c>
+      <c r="J23" s="17">
+        <f>(Model!V67+Model!V73+Model!V74+Model!V75-Model!V52-Model!V53)/(Model!V26*(1-Model!V49)+Model!V86+Model!V102+SUM(Model!V94:V100))</f>
+        <v>0.38680108686212644</v>
+      </c>
+      <c r="K23" s="17">
+        <f>(Model!W67+Model!W73+Model!W74+Model!W75-Model!W52-Model!W53)/(Model!W26*(1-Model!W49)+Model!W86+Model!W102+SUM(Model!W94:W100))</f>
+        <v>1.2961013119834393</v>
+      </c>
+      <c r="M23" s="22">
+        <f t="shared" si="5"/>
+        <v>4.3132126017526478</v>
+      </c>
+      <c r="N23" s="22">
+        <f t="shared" si="6"/>
+        <v>1.0527804515936778</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="24" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B24" s="2" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B20" s="7" t="s">
+      <c r="D24" s="17">
+        <f>(Model!P67+Model!P73+Model!P74+Model!P75-Model!P52-Model!P53)/(Model!P26+Model!P86)</f>
+        <v>-1.5400308385719377</v>
+      </c>
+      <c r="E24" s="17">
+        <f>(Model!Q67+Model!Q73+Model!Q74+Model!Q75-Model!Q52-Model!Q53)/(Model!Q26+Model!Q86)</f>
+        <v>1.0622335890878085</v>
+      </c>
+      <c r="F24" s="17">
+        <f>(Model!R67+Model!R73+Model!R74+Model!R75-Model!R52-Model!R53)/(Model!R26+Model!R86)</f>
+        <v>0.73970588235294132</v>
+      </c>
+      <c r="G24" s="17">
+        <f>(Model!S67+Model!S73+Model!S74+Model!S75-Model!S52-Model!S53)/(Model!S26+Model!S86)</f>
+        <v>0.49771423013325583</v>
+      </c>
+      <c r="H24" s="17">
+        <f>(Model!T67+Model!T73+Model!T74+Model!T75-Model!T52-Model!T53)/(Model!T26+Model!T86)</f>
+        <v>1.1130096247431591</v>
+      </c>
+      <c r="I24" s="17">
+        <f>(Model!U67+Model!U73+Model!U74+Model!U75-Model!U52-Model!U53)/(Model!U26+Model!U86)</f>
+        <v>0.63669575806779011</v>
+      </c>
+      <c r="J24" s="17">
+        <f>(Model!V67+Model!V73+Model!V74+Model!V75-Model!V52-Model!V53)/(Model!V26+Model!V86)</f>
+        <v>0.29443431449162116</v>
+      </c>
+      <c r="K24" s="17">
+        <f>(Model!W67+Model!W73+Model!W74+Model!W75-Model!W52-Model!W53)/(Model!W26+Model!W86)</f>
+        <v>0.50417787848746642</v>
+      </c>
+      <c r="M24" s="22">
+        <f t="shared" si="5"/>
+        <v>0.17684719359306683</v>
+      </c>
+      <c r="N24" s="22">
+        <f t="shared" si="6"/>
+        <v>0.63669575806779011</v>
+      </c>
+      <c r="P24" s="2" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B21" s="2" t="s">
+    <row r="25" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B25" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="D21" s="17">
-        <f>Model!P93/Model!P95</f>
-        <v>0.55313993403782735</v>
-      </c>
-      <c r="E21" s="17">
-        <f>Model!Q93/Model!Q95</f>
-        <v>0.36993640022527796</v>
-      </c>
-      <c r="F21" s="17">
-        <f>Model!R93/Model!R95</f>
-        <v>0.33019334389857358</v>
-      </c>
-      <c r="G21" s="17">
-        <f>Model!S93/Model!S95</f>
-        <v>0.32829753906300563</v>
-      </c>
-      <c r="H21" s="17">
-        <f>Model!T93/Model!T95</f>
-        <v>0.35797923263863307</v>
-      </c>
-      <c r="I21" s="17">
-        <f>Model!U93/Model!U95</f>
-        <v>0.37111138036531072</v>
-      </c>
-      <c r="K21" s="23">
-        <f t="shared" ref="K21:K33" si="4">AVERAGE(G21:I21,D21)</f>
-        <v>0.40263202152619421</v>
-      </c>
-      <c r="L21" s="23">
-        <f t="shared" ref="L21:L33" si="5">MEDIAN(G21:I21,D21:E21)</f>
-        <v>0.36993640022527796</v>
-      </c>
-      <c r="N21" s="2" t="s">
+      <c r="D25" s="17">
+        <f>(-Model!P102/Model!P101)</f>
+        <v>0.25223271242663953</v>
+      </c>
+      <c r="E25" s="17">
+        <f>(-Model!Q102/Model!Q101)</f>
+        <v>0.35820302146832744</v>
+      </c>
+      <c r="F25" s="17">
+        <f>(-Model!R102/Model!R101)</f>
+        <v>0.28301391441323176</v>
+      </c>
+      <c r="G25" s="17">
+        <f>(-Model!S102/Model!S101)</f>
+        <v>0.23313311915071927</v>
+      </c>
+      <c r="H25" s="17">
+        <f>(-Model!T102/Model!T101)</f>
+        <v>0.52919708029197055</v>
+      </c>
+      <c r="I25" s="17">
+        <f>(-Model!U102/Model!U101)</f>
+        <v>0.15406188651023664</v>
+      </c>
+      <c r="J25" s="17">
+        <f>(-Model!V102/Model!V101)</f>
+        <v>0.17504655493482316</v>
+      </c>
+      <c r="K25" s="17">
+        <f>(-Model!W102/Model!W101)</f>
+        <v>0.35357823600762439</v>
+      </c>
+      <c r="M25" s="22">
+        <f t="shared" si="5"/>
+        <v>0.29215619959489153</v>
+      </c>
+      <c r="N25" s="22">
+        <f t="shared" si="6"/>
+        <v>0.25223271242663953</v>
+      </c>
+      <c r="P25" s="23" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B22" s="2" t="s">
+    <row r="26" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B26" s="2" t="s">
         <v>200</v>
-      </c>
-      <c r="D22" s="17">
-        <f>(Model!P71+Model!P77+Model!P78+Model!P79-Model!P54-Model!P55)/Model!P93</f>
-        <v>-0.39498661474811392</v>
-      </c>
-      <c r="E22" s="17">
-        <f>(Model!Q71+Model!Q77+Model!Q78+Model!Q79-Model!Q54-Model!Q55)/Model!Q93</f>
-        <v>0.23133192232000291</v>
-      </c>
-      <c r="F22" s="17">
-        <f>(Model!R71+Model!R77+Model!R78+Model!R79-Model!R54-Model!R55)/Model!R93</f>
-        <v>5.794040853939493E-2</v>
-      </c>
-      <c r="G22" s="17">
-        <f>(Model!S71+Model!S77+Model!S78+Model!S79-Model!S54-Model!S55)/Model!S93</f>
-        <v>0.20177444794952695</v>
-      </c>
-      <c r="H22" s="17">
-        <f>(Model!T71+Model!T77+Model!T78+Model!T79-Model!T54-Model!T55)/Model!T93</f>
-        <v>0.42345196461633405</v>
-      </c>
-      <c r="I22" s="17">
-        <f>(Model!U71+Model!U77+Model!U78+Model!U79-Model!U54-Model!U55)/Model!U93</f>
-        <v>0.25605027955760506</v>
-      </c>
-      <c r="K22" s="23">
-        <f t="shared" si="4"/>
-        <v>0.12157251934383803</v>
-      </c>
-      <c r="L22" s="23">
-        <f t="shared" si="5"/>
-        <v>0.23133192232000291</v>
-      </c>
-      <c r="N22" s="2" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B23" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="D23" s="17">
-        <f>(Model!P71+Model!P77+Model!P78+Model!P79-Model!P54-Model!P55)/(Model!P26*(1-Model!P49)+Model!P101+Model!P117+SUM(Model!P109:P115))</f>
-        <v>-3.4354065857466791</v>
-      </c>
-      <c r="E23" s="17">
-        <f>(Model!Q71+Model!Q77+Model!Q78+Model!Q79-Model!Q54-Model!Q55)/(Model!Q26*(1-Model!Q49)+Model!Q101+Model!Q117+SUM(Model!Q109:Q115))</f>
-        <v>1.422828098672291</v>
-      </c>
-      <c r="F23" s="17">
-        <f>(Model!R71+Model!R77+Model!R78+Model!R79-Model!R54-Model!R55)/(Model!R26*(1-Model!R49)+Model!R101+Model!R117+SUM(Model!R109:R115))</f>
-        <v>0.9708521072772508</v>
-      </c>
-      <c r="G23" s="17">
-        <f>(Model!S71+Model!S77+Model!S78+Model!S79-Model!S54-Model!S55)/(Model!S26*(1-Model!S49)+Model!S101+Model!S117+SUM(Model!S109:S115))</f>
-        <v>1.0527804515936778</v>
-      </c>
-      <c r="H23" s="17">
-        <f>(Model!T71+Model!T77+Model!T78+Model!T79-Model!T54-Model!T55)/(Model!T26*(1-Model!T49)+Model!T101+Model!T117+SUM(Model!T109:T115))</f>
-        <v>18.833345586356071</v>
-      </c>
-      <c r="I23" s="17">
-        <f>(Model!U71+Model!U77+Model!U78+Model!U79-Model!U54-Model!U55)/(Model!U26*(1-Model!U49)+Model!U101+Model!U117+SUM(Model!U109:U115))</f>
-        <v>0.80213095480752494</v>
-      </c>
-      <c r="K23" s="23">
-        <f t="shared" si="4"/>
-        <v>4.3132126017526478</v>
-      </c>
-      <c r="L23" s="23">
-        <f t="shared" si="5"/>
-        <v>1.0527804515936778</v>
-      </c>
-      <c r="N23" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B24" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="D24" s="17">
-        <f>(Model!P71+Model!P77+Model!P78+Model!P79-Model!P54-Model!P55)/(Model!P26+Model!P101)</f>
-        <v>-1.5400308385719377</v>
-      </c>
-      <c r="E24" s="17">
-        <f>(Model!Q71+Model!Q77+Model!Q78+Model!Q79-Model!Q54-Model!Q55)/(Model!Q26+Model!Q101)</f>
-        <v>1.0622335890878085</v>
-      </c>
-      <c r="F24" s="17">
-        <f>(Model!R71+Model!R77+Model!R78+Model!R79-Model!R54-Model!R55)/(Model!R26+Model!R101)</f>
-        <v>0.73970588235294132</v>
-      </c>
-      <c r="G24" s="17">
-        <f>(Model!S71+Model!S77+Model!S78+Model!S79-Model!S54-Model!S55)/(Model!S26+Model!S101)</f>
-        <v>0.49771423013325583</v>
-      </c>
-      <c r="H24" s="17">
-        <f>(Model!T71+Model!T77+Model!T78+Model!T79-Model!T54-Model!T55)/(Model!T26+Model!T101)</f>
-        <v>1.1130096247431591</v>
-      </c>
-      <c r="I24" s="17">
-        <f>(Model!U71+Model!U77+Model!U78+Model!U79-Model!U54-Model!U55)/(Model!U26+Model!U101)</f>
-        <v>0.63669575806779011</v>
-      </c>
-      <c r="K24" s="23">
-        <f t="shared" si="4"/>
-        <v>0.17684719359306683</v>
-      </c>
-      <c r="L24" s="23">
-        <f t="shared" si="5"/>
-        <v>0.63669575806779011</v>
-      </c>
-      <c r="N24" s="2" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B25" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="D25" s="17">
-        <f>(-Model!P117/Model!P116)</f>
-        <v>0.25223271242663953</v>
-      </c>
-      <c r="E25" s="17">
-        <f>(-Model!Q117/Model!Q116)</f>
-        <v>0.35820302146832744</v>
-      </c>
-      <c r="F25" s="17">
-        <f>(-Model!R117/Model!R116)</f>
-        <v>0.28301391441323176</v>
-      </c>
-      <c r="G25" s="17">
-        <f>(-Model!S117/Model!S116)</f>
-        <v>0.23313311915071927</v>
-      </c>
-      <c r="H25" s="17">
-        <f>(-Model!T117/Model!T116)</f>
-        <v>0.52919708029197055</v>
-      </c>
-      <c r="I25" s="17">
-        <f>(-Model!U117/Model!U116)</f>
-        <v>0.15406188651023664</v>
-      </c>
-      <c r="K25" s="23">
-        <f t="shared" si="4"/>
-        <v>0.29215619959489153</v>
-      </c>
-      <c r="L25" s="23">
-        <f t="shared" si="5"/>
-        <v>0.25223271242663953</v>
-      </c>
-      <c r="N25" s="24" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B26" s="2" t="s">
-        <v>208</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>70</v>
@@ -7479,733 +8053,877 @@
       <c r="I26" s="4" t="s">
         <v>70</v>
       </c>
+      <c r="J26" s="4" t="s">
+        <v>70</v>
+      </c>
       <c r="K26" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="L26" s="4" t="s">
+      <c r="M26" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="N26" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="N26" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="P26" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="27" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="D27" s="25">
-        <f>-Model!P117/Model!P101</f>
+        <v>202</v>
+      </c>
+      <c r="D27" s="24">
+        <f>-Model!P102/Model!P86</f>
         <v>0.70280838961962311</v>
       </c>
-      <c r="E27" s="25">
-        <f>-Model!Q117/Model!Q101</f>
+      <c r="E27" s="24">
+        <f>-Model!Q102/Model!Q86</f>
         <v>1.0029684601113174</v>
       </c>
-      <c r="F27" s="25">
-        <f>-Model!R117/Model!R101</f>
+      <c r="F27" s="24">
+        <f>-Model!R102/Model!R86</f>
         <v>0.43537964458804523</v>
       </c>
-      <c r="G27" s="25">
-        <f>-Model!S117/Model!S101</f>
+      <c r="G27" s="24">
+        <f>-Model!S102/Model!S86</f>
         <v>0.72659991292990866</v>
       </c>
-      <c r="H27" s="25">
-        <f>-Model!T117/Model!T101</f>
+      <c r="H27" s="24">
+        <f>-Model!T102/Model!T86</f>
         <v>0.98639455782312924</v>
       </c>
-      <c r="I27" s="25">
-        <f>-Model!U117/Model!U101</f>
+      <c r="I27" s="24">
+        <f>-Model!U102/Model!U86</f>
         <v>0.71965065502183412</v>
       </c>
-      <c r="K27" s="25">
+      <c r="J27" s="24">
+        <f>-Model!V102/Model!V86</f>
+        <v>0.98451730418943528</v>
+      </c>
+      <c r="K27" s="24">
+        <f>-Model!W102/Model!W86</f>
+        <v>1.7515021459227469</v>
+      </c>
+      <c r="M27" s="24">
         <f>AVERAGE(G27:I27,D27)</f>
         <v>0.78386337884862378</v>
       </c>
-      <c r="L27" s="25">
+      <c r="N27" s="24">
         <f>MEDIAN(G27:I27,D27:E27)</f>
         <v>0.72659991292990866</v>
       </c>
-      <c r="N27" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="O27" s="25"/>
-      <c r="P27" s="25"/>
-    </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P27" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q27" s="24"/>
+      <c r="R27" s="24"/>
+    </row>
+    <row r="28" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="F28" s="26">
-        <f>(Model!R93/-Model!R26)</f>
+        <v>205</v>
+      </c>
+      <c r="F28" s="25">
+        <f>(Model!R81/-Model!R26)</f>
         <v>59.733944954128539</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="K28" s="23" t="s">
-        <v>213</v>
-      </c>
-      <c r="L28" s="23" t="s">
-        <v>213</v>
-      </c>
-      <c r="N28" s="2" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.2">
+        <v>205</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="K28" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="M28" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="N28" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="P28" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="29" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="D29" s="17">
-        <f>Model!P60/Model!P69</f>
+        <f>Model!P58/Model!P66</f>
         <v>0.60490004711583767</v>
       </c>
       <c r="E29" s="17">
-        <f>Model!Q60/Model!Q69</f>
+        <f>Model!Q58/Model!Q66</f>
         <v>0.46363274220799744</v>
       </c>
       <c r="F29" s="17">
-        <f>Model!R60/Model!R69</f>
+        <f>Model!R58/Model!R66</f>
         <v>0.53350237717908078</v>
       </c>
       <c r="G29" s="17">
-        <f>Model!S60/Model!S69</f>
+        <f>Model!S58/Model!S66</f>
         <v>0.54595000453092024</v>
       </c>
       <c r="H29" s="17">
-        <f>Model!T60/Model!T69</f>
+        <f>Model!T58/Model!T66</f>
         <v>0.48959422637896743</v>
       </c>
       <c r="I29" s="17">
-        <f>Model!U60/Model!U69</f>
+        <f>Model!U58/Model!U66</f>
         <v>0.50886014600308971</v>
       </c>
-      <c r="K29" s="23">
-        <f t="shared" si="4"/>
+      <c r="J29" s="17">
+        <f>Model!V58/Model!V66</f>
+        <v>0.53778042654633684</v>
+      </c>
+      <c r="K29" s="17">
+        <f>Model!W58/Model!W66</f>
+        <v>0.50225466761418702</v>
+      </c>
+      <c r="M29" s="22">
+        <f t="shared" si="5"/>
         <v>0.53732610600720376</v>
       </c>
-      <c r="L29" s="23">
-        <f t="shared" si="5"/>
+      <c r="N29" s="22">
+        <f t="shared" si="6"/>
         <v>0.50886014600308971</v>
       </c>
-      <c r="N29" s="2" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="30" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="D30" s="23">
-        <f t="shared" ref="D30:H30" si="6">1-D29</f>
+        <v>209</v>
+      </c>
+      <c r="D30" s="22">
+        <f t="shared" ref="D30:H30" si="7">1-D29</f>
         <v>0.39509995288416233</v>
       </c>
-      <c r="E30" s="23">
-        <f t="shared" si="6"/>
+      <c r="E30" s="22">
+        <f t="shared" si="7"/>
         <v>0.53636725779200256</v>
       </c>
-      <c r="F30" s="23">
-        <f t="shared" si="6"/>
+      <c r="F30" s="22">
+        <f t="shared" si="7"/>
         <v>0.46649762282091922</v>
       </c>
-      <c r="G30" s="23">
-        <f t="shared" si="6"/>
+      <c r="G30" s="22">
+        <f t="shared" si="7"/>
         <v>0.45404999546907976</v>
       </c>
-      <c r="H30" s="23">
-        <f t="shared" si="6"/>
+      <c r="H30" s="22">
+        <f t="shared" si="7"/>
         <v>0.51040577362103257</v>
       </c>
-      <c r="I30" s="23">
+      <c r="I30" s="22">
         <f>1-I29</f>
         <v>0.49113985399691029</v>
       </c>
-      <c r="K30" s="23">
-        <f t="shared" si="4"/>
+      <c r="J30" s="22">
+        <f t="shared" ref="J30:K30" si="8">1-J29</f>
+        <v>0.46221957345366316</v>
+      </c>
+      <c r="K30" s="22">
+        <f t="shared" si="8"/>
+        <v>0.49774533238581298</v>
+      </c>
+      <c r="M30" s="22">
+        <f t="shared" si="5"/>
         <v>0.46267389399279624</v>
       </c>
-      <c r="L30" s="23">
+      <c r="N30" s="22">
+        <f t="shared" si="6"/>
+        <v>0.49113985399691029</v>
+      </c>
+      <c r="P30" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="31" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B31" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D31" s="17">
+        <f>Model!P81/Model!P65</f>
+        <v>1.4000000000000001</v>
+      </c>
+      <c r="E31" s="17">
+        <f>Model!Q81/Model!Q65</f>
+        <v>0.68970727584705649</v>
+      </c>
+      <c r="F31" s="17">
+        <f>Model!R81/Model!R65</f>
+        <v>0.70781356162522047</v>
+      </c>
+      <c r="G31" s="17">
+        <f>Model!S81/Model!S65</f>
+        <v>0.72304270969949247</v>
+      </c>
+      <c r="H31" s="17">
+        <f>Model!T81/Model!T65</f>
+        <v>0.70136203612858516</v>
+      </c>
+      <c r="I31" s="17">
+        <f>Model!U81/Model!U65</f>
+        <v>0.75561243369927245</v>
+      </c>
+      <c r="J31" s="17">
+        <f>Model!V81/Model!V65</f>
+        <v>0.7946521765825505</v>
+      </c>
+      <c r="K31" s="17">
+        <f>Model!W81/Model!W65</f>
+        <v>0.7375853386288711</v>
+      </c>
+      <c r="M31" s="22">
         <f t="shared" si="5"/>
-        <v>0.49113985399691029</v>
-      </c>
-      <c r="N30" s="2" t="s">
+        <v>0.89500429488183753</v>
+      </c>
+      <c r="N31" s="22">
+        <f t="shared" si="6"/>
+        <v>0.72304270969949247</v>
+      </c>
+      <c r="P31" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="32" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B32" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D32" s="17">
+        <f>(Model!P81+Model!P73)/Model!P81</f>
+        <v>1.2096312971525918</v>
+      </c>
+      <c r="E32" s="17">
+        <f>(Model!Q81+Model!Q73)/Model!Q81</f>
+        <v>1.1471909695146856</v>
+      </c>
+      <c r="F32" s="17">
+        <f>(Model!R81+Model!R73)/Model!R81</f>
+        <v>1.6269774228229157</v>
+      </c>
+      <c r="G32" s="17">
+        <f>(Model!S81+Model!S73)/Model!S81</f>
+        <v>1.4481466876971609</v>
+      </c>
+      <c r="H32" s="17">
+        <f>(Model!T81+Model!T73)/Model!T81</f>
+        <v>1.4684221353630942</v>
+      </c>
+      <c r="I32" s="17">
+        <f>(Model!U81+Model!U73)/Model!U81</f>
+        <v>1.4654532098110433</v>
+      </c>
+      <c r="J32" s="17">
+        <f>(Model!V81+Model!V73)/Model!V81</f>
+        <v>1.2870001931620629</v>
+      </c>
+      <c r="K32" s="17">
+        <f>(Model!W81+Model!W73)/Model!W81</f>
+        <v>1.4360174561835715</v>
+      </c>
+      <c r="M32" s="22">
+        <f t="shared" si="5"/>
+        <v>1.3979133325059725</v>
+      </c>
+      <c r="N32" s="22">
+        <f t="shared" si="6"/>
+        <v>1.4481466876971609</v>
+      </c>
+      <c r="P32" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B33" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D33" s="17">
+        <f>Model!P62/Model!P66</f>
+        <v>0.154741872518005</v>
+      </c>
+      <c r="E33" s="17">
+        <f>Model!Q62/Model!Q66</f>
+        <v>0.1257572219398618</v>
+      </c>
+      <c r="F33" s="17">
+        <f>Model!R62/Model!R66</f>
+        <v>0.11849128367670365</v>
+      </c>
+      <c r="G33" s="17">
+        <f>Model!S62/Model!S66</f>
+        <v>0.11763563633539166</v>
+      </c>
+      <c r="H33" s="17">
+        <f>Model!T62/Model!T66</f>
+        <v>0.13239561086972532</v>
+      </c>
+      <c r="I33" s="17">
+        <f>Model!U62/Model!U66</f>
+        <v>0.13450761821100779</v>
+      </c>
+      <c r="J33" s="17">
+        <f>Model!V62/Model!V66</f>
+        <v>0.12607665347012331</v>
+      </c>
+      <c r="K33" s="17">
+        <f>Model!W62/Model!W66</f>
+        <v>0.11682925253569353</v>
+      </c>
+      <c r="M33" s="22">
+        <f t="shared" si="5"/>
+        <v>0.13482018448353245</v>
+      </c>
+      <c r="N33" s="22">
+        <f t="shared" si="6"/>
+        <v>0.13239561086972532</v>
+      </c>
+      <c r="P33" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B35" s="7" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="36" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B36" s="2" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B31" s="2" t="s">
+      <c r="D36" s="23">
+        <f>Model!P54/Model!P19*360</f>
+        <v>22.701726595913193</v>
+      </c>
+      <c r="E36" s="23">
+        <f>Model!Q54/Model!Q19*360</f>
+        <v>16.19468164550797</v>
+      </c>
+      <c r="F36" s="23">
+        <f>Model!R54/Model!R19*360</f>
+        <v>36.934193782948554</v>
+      </c>
+      <c r="G36" s="23">
+        <f>Model!S54/Model!S19*360</f>
+        <v>23.469325400016082</v>
+      </c>
+      <c r="H36" s="23">
+        <f>Model!T54/Model!T19*360</f>
+        <v>25.012725805450366</v>
+      </c>
+      <c r="I36" s="23">
+        <f>Model!U54/Model!U19*360</f>
+        <v>24.239225502910397</v>
+      </c>
+      <c r="J36" s="23">
+        <f>Model!V54/Model!V19*360</f>
+        <v>23.367707303291425</v>
+      </c>
+      <c r="K36" s="23">
+        <f>Model!W54/Model!W19*360</f>
+        <v>21.814283073510381</v>
+      </c>
+      <c r="M36" s="23">
+        <f t="shared" ref="M36:M44" si="9">AVERAGE(G36:I36,D36)</f>
+        <v>23.855750826072509</v>
+      </c>
+      <c r="N36" s="23">
+        <f t="shared" ref="N36:N44" si="10">MEDIAN(G36:I36,D36:E36)</f>
+        <v>23.469325400016082</v>
+      </c>
+      <c r="P36" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="D31" s="17">
-        <f>Model!P93/Model!P67</f>
-        <v>1.4000000000000001</v>
-      </c>
-      <c r="E31" s="17">
-        <f>Model!Q93/Model!Q67</f>
-        <v>0.68970727584705649</v>
-      </c>
-      <c r="F31" s="17">
-        <f>Model!R93/Model!R67</f>
-        <v>0.70781356162522047</v>
-      </c>
-      <c r="G31" s="17">
-        <f>Model!S93/Model!S67</f>
-        <v>0.72304270969949247</v>
-      </c>
-      <c r="H31" s="17">
-        <f>Model!T93/Model!T67</f>
-        <v>0.70136203612858516</v>
-      </c>
-      <c r="I31" s="17">
-        <f>Model!U93/Model!U67</f>
-        <v>0.75561243369927245</v>
-      </c>
-      <c r="K31" s="23">
-        <f t="shared" si="4"/>
-        <v>0.89500429488183753</v>
-      </c>
-      <c r="L31" s="23">
-        <f t="shared" si="5"/>
-        <v>0.72304270969949247</v>
-      </c>
-      <c r="N31" s="2" t="s">
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B37" s="2" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="32" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B32" s="2" t="s">
+      <c r="D37" s="23">
+        <f>Model!P68/Model!P19*360</f>
+        <v>11.536195152859181</v>
+      </c>
+      <c r="E37" s="23">
+        <f>Model!Q68/Model!Q19*360</f>
+        <v>14.423844930030196</v>
+      </c>
+      <c r="F37" s="23">
+        <f>Model!R68/Model!R19*360</f>
+        <v>29.113797491365204</v>
+      </c>
+      <c r="G37" s="23">
+        <f>Model!S68/Model!S19*360</f>
+        <v>25.976039237758304</v>
+      </c>
+      <c r="H37" s="23">
+        <f>Model!T68/Model!T19*360</f>
+        <v>20.761065243031844</v>
+      </c>
+      <c r="I37" s="23">
+        <f>Model!U68/Model!U19*360</f>
+        <v>18.034200922882047</v>
+      </c>
+      <c r="J37" s="23">
+        <f>Model!V68/Model!V19*360</f>
+        <v>22.172623251871734</v>
+      </c>
+      <c r="K37" s="23">
+        <f>Model!W68/Model!W19*360</f>
+        <v>19.121326021319859</v>
+      </c>
+      <c r="M37" s="23">
+        <f t="shared" si="9"/>
+        <v>19.076875139132845</v>
+      </c>
+      <c r="N37" s="23">
+        <f t="shared" si="10"/>
+        <v>18.034200922882047</v>
+      </c>
+      <c r="P37" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="D32" s="17">
-        <f>(Model!P93+Model!P77)/Model!P93</f>
-        <v>1.2096312971525918</v>
-      </c>
-      <c r="E32" s="17">
-        <f>(Model!Q93+Model!Q77)/Model!Q93</f>
-        <v>1.1471909695146856</v>
-      </c>
-      <c r="F32" s="17">
-        <f>(Model!R93+Model!R77)/Model!R93</f>
-        <v>1.6269774228229157</v>
-      </c>
-      <c r="G32" s="17">
-        <f>(Model!S93+Model!S77)/Model!S93</f>
-        <v>1.4481466876971609</v>
-      </c>
-      <c r="H32" s="17">
-        <f>(Model!T93+Model!T77)/Model!T93</f>
-        <v>1.4684221353630942</v>
-      </c>
-      <c r="I32" s="17">
-        <f>(Model!U93+Model!U77)/Model!U93</f>
-        <v>1.4654532098110433</v>
-      </c>
-      <c r="K32" s="23">
-        <f t="shared" si="4"/>
-        <v>1.3979133325059725</v>
-      </c>
-      <c r="L32" s="23">
-        <f t="shared" si="5"/>
-        <v>1.4481466876971609</v>
-      </c>
-      <c r="N32" s="2" t="s">
+    </row>
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B38" s="2" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B33" s="2" t="s">
+      <c r="D38" s="17">
+        <f>Model!P52/Model!P72</f>
+        <v>0.48670944087992674</v>
+      </c>
+      <c r="E38" s="17">
+        <f>Model!Q52/Model!Q72</f>
+        <v>0.77456978967495227</v>
+      </c>
+      <c r="F38" s="17">
+        <f>Model!R52/Model!R72</f>
+        <v>1.6273346794548209</v>
+      </c>
+      <c r="G38" s="17">
+        <f>Model!S52/Model!S72</f>
+        <v>0.82626235758301192</v>
+      </c>
+      <c r="H38" s="17">
+        <f>Model!T52/Model!T72</f>
+        <v>1.0239705390023435</v>
+      </c>
+      <c r="I38" s="17">
+        <f>Model!U52/Model!U72</f>
+        <v>1.1329062159214831</v>
+      </c>
+      <c r="J38" s="17">
+        <f>Model!V52/Model!V72</f>
+        <v>0.90101701270094192</v>
+      </c>
+      <c r="K38" s="17">
+        <f>Model!W52/Model!W72</f>
+        <v>1.0884204763208323</v>
+      </c>
+      <c r="M38" s="22">
+        <f t="shared" si="9"/>
+        <v>0.86746213834669128</v>
+      </c>
+      <c r="N38" s="22">
+        <f t="shared" si="10"/>
+        <v>0.82626235758301192</v>
+      </c>
+      <c r="P38" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="D33" s="17">
-        <f>Model!P64/Model!P69</f>
-        <v>0.154741872518005</v>
-      </c>
-      <c r="E33" s="17">
-        <f>Model!Q64/Model!Q69</f>
-        <v>0.1257572219398618</v>
-      </c>
-      <c r="F33" s="17">
-        <f>Model!R64/Model!R69</f>
-        <v>0.11849128367670365</v>
-      </c>
-      <c r="G33" s="17">
-        <f>Model!S64/Model!S69</f>
-        <v>0.11763563633539166</v>
-      </c>
-      <c r="H33" s="17">
-        <f>Model!T64/Model!T69</f>
-        <v>0.13239561086972532</v>
-      </c>
-      <c r="I33" s="17">
-        <f>Model!U64/Model!U69</f>
-        <v>0.13450761821100779</v>
-      </c>
-      <c r="K33" s="23">
-        <f t="shared" si="4"/>
-        <v>0.13482018448353245</v>
-      </c>
-      <c r="L33" s="23">
-        <f t="shared" si="5"/>
-        <v>0.13239561086972532</v>
-      </c>
-      <c r="N33" s="2" t="s">
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B39" s="2" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B35" s="7" t="s">
+      <c r="D39" s="17">
+        <f>(Model!P52+Model!P54)/Model!P72</f>
+        <v>0.81843179735022087</v>
+      </c>
+      <c r="E39" s="17">
+        <f>(Model!Q52+Model!Q54)/Model!Q72</f>
+        <v>0.90702676864244747</v>
+      </c>
+      <c r="F39" s="17">
+        <f>(Model!R52+Model!R54)/Model!R72</f>
+        <v>1.9122286723876831</v>
+      </c>
+      <c r="G39" s="17">
+        <f>(Model!S52+Model!S54)/Model!S72</f>
+        <v>1.005984838409363</v>
+      </c>
+      <c r="H39" s="17">
+        <f>(Model!T52+Model!T54)/Model!T72</f>
+        <v>1.3237361901573486</v>
+      </c>
+      <c r="I39" s="17">
+        <f>(Model!U52+Model!U54)/Model!U72</f>
+        <v>1.4372273718647763</v>
+      </c>
+      <c r="J39" s="17">
+        <f>(Model!V52+Model!V54)/Model!V72</f>
+        <v>1.1163706237990343</v>
+      </c>
+      <c r="K39" s="17">
+        <f>(Model!W52+Model!W54)/Model!W72</f>
+        <v>1.3576238707911306</v>
+      </c>
+      <c r="M39" s="22">
+        <f t="shared" si="9"/>
+        <v>1.1463450494454273</v>
+      </c>
+      <c r="N39" s="22">
+        <f t="shared" si="10"/>
+        <v>1.005984838409363</v>
+      </c>
+      <c r="P39" s="2" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="36" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B36" s="2" t="s">
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B40" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="D36" s="24">
-        <f>Model!P56/Model!P19*360</f>
-        <v>22.701726595913193</v>
-      </c>
-      <c r="E36" s="24">
-        <f>Model!Q56/Model!Q19*360</f>
-        <v>16.19468164550797</v>
-      </c>
-      <c r="F36" s="24">
-        <f>Model!R56/Model!R19*360</f>
-        <v>36.934193782948554</v>
-      </c>
-      <c r="G36" s="24">
-        <f>Model!S56/Model!S19*360</f>
-        <v>23.469325400016082</v>
-      </c>
-      <c r="H36" s="24">
-        <f>Model!T56/Model!T19*360</f>
-        <v>25.012725805450366</v>
-      </c>
-      <c r="I36" s="24">
-        <f>Model!U56/Model!U19*360</f>
-        <v>24.239225502910397</v>
-      </c>
-      <c r="K36" s="24">
-        <f t="shared" ref="K36:K44" si="7">AVERAGE(G36:I36,D36)</f>
-        <v>23.855750826072509</v>
-      </c>
-      <c r="L36" s="24">
-        <f t="shared" ref="L36:L44" si="8">MEDIAN(G36:I36,D36:E36)</f>
-        <v>23.469325400016082</v>
-      </c>
-      <c r="N36" s="2" t="s">
+      <c r="D40" s="17">
+        <f>Model!P58/Model!P72</f>
+        <v>2.9954170485792853</v>
+      </c>
+      <c r="E40" s="17">
+        <f>Model!Q58/Model!Q72</f>
+        <v>1.6133843212237098</v>
+      </c>
+      <c r="F40" s="17">
+        <f>Model!R58/Model!R72</f>
+        <v>2.6552246340232206</v>
+      </c>
+      <c r="G40" s="17">
+        <f>Model!S58/Model!S72</f>
+        <v>1.8696191869486194</v>
+      </c>
+      <c r="H40" s="17">
+        <f>Model!T58/Model!T72</f>
+        <v>2.2257114161365914</v>
+      </c>
+      <c r="I40" s="17">
+        <f>Model!U58/Model!U72</f>
+        <v>2.2899400218102506</v>
+      </c>
+      <c r="J40" s="17">
+        <f>Model!V58/Model!V72</f>
+        <v>1.7762103388480104</v>
+      </c>
+      <c r="K40" s="17">
+        <f>Model!W58/Model!W72</f>
+        <v>2.1282233780454423</v>
+      </c>
+      <c r="M40" s="22">
+        <f t="shared" si="9"/>
+        <v>2.3451719183686865</v>
+      </c>
+      <c r="N40" s="22">
+        <f t="shared" si="10"/>
+        <v>2.2257114161365914</v>
+      </c>
+      <c r="P40" s="2" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="2" t="s">
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B41" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="D37" s="24">
-        <f>Model!P72/Model!P19*360</f>
-        <v>11.536195152859181</v>
-      </c>
-      <c r="E37" s="24">
-        <f>Model!Q72/Model!Q19*360</f>
-        <v>14.423844930030196</v>
-      </c>
-      <c r="F37" s="24">
-        <f>Model!R72/Model!R19*360</f>
-        <v>29.113797491365204</v>
-      </c>
-      <c r="G37" s="24">
-        <f>Model!S72/Model!S19*360</f>
-        <v>25.976039237758304</v>
-      </c>
-      <c r="H37" s="24">
-        <f>Model!T72/Model!T19*360</f>
-        <v>20.761065243031844</v>
-      </c>
-      <c r="I37" s="24">
-        <f>Model!U72/Model!U19*360</f>
-        <v>18.034200922882047</v>
-      </c>
-      <c r="K37" s="24">
-        <f t="shared" si="7"/>
-        <v>19.076875139132845</v>
-      </c>
-      <c r="L37" s="24">
-        <f t="shared" si="8"/>
-        <v>18.034200922882047</v>
-      </c>
-      <c r="N37" s="2" t="s">
+      <c r="D41" s="17">
+        <f>Model!P55/Model!P66</f>
+        <v>0.13761190011442417</v>
+      </c>
+      <c r="E41" s="17">
+        <f>Model!Q55/Model!Q66</f>
+        <v>0.10112776274399374</v>
+      </c>
+      <c r="F41" s="17">
+        <f>Model!R55/Model!R66</f>
+        <v>9.6228209191759118E-2</v>
+      </c>
+      <c r="G41" s="17">
+        <f>Model!S55/Model!S66</f>
+        <v>0.12651624011288462</v>
+      </c>
+      <c r="H41" s="17">
+        <f>Model!T55/Model!T66</f>
+        <v>0.15778776051255614</v>
+      </c>
+      <c r="I41" s="17">
+        <f>Model!U55/Model!U66</f>
+        <v>0.13664314058098326</v>
+      </c>
+      <c r="J41" s="17">
+        <f>Model!V55/Model!V66</f>
+        <v>0.13474664055737659</v>
+      </c>
+      <c r="K41" s="17">
+        <f>Model!W55/Model!W66</f>
+        <v>0.13105497771173849</v>
+      </c>
+      <c r="M41" s="22">
+        <f t="shared" si="9"/>
+        <v>0.13963976033021205</v>
+      </c>
+      <c r="N41" s="22">
+        <f t="shared" si="10"/>
+        <v>0.13664314058098326</v>
+      </c>
+      <c r="P41" s="2" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B38" s="2" t="s">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B42" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="D38" s="17">
-        <f>Model!P54/Model!P76</f>
-        <v>0.48670944087992674</v>
-      </c>
-      <c r="E38" s="17">
-        <f>Model!Q54/Model!Q76</f>
-        <v>0.77456978967495227</v>
-      </c>
-      <c r="F38" s="17">
-        <f>Model!R54/Model!R76</f>
-        <v>1.6273346794548209</v>
-      </c>
-      <c r="G38" s="17">
-        <f>Model!S54/Model!S76</f>
-        <v>0.82626235758301192</v>
-      </c>
-      <c r="H38" s="17">
-        <f>Model!T54/Model!T76</f>
-        <v>1.0239705390023435</v>
-      </c>
-      <c r="I38" s="17">
-        <f>Model!U54/Model!U76</f>
-        <v>1.1329062159214831</v>
-      </c>
-      <c r="K38" s="23">
-        <f t="shared" si="7"/>
-        <v>0.86746213834669128</v>
-      </c>
-      <c r="L38" s="23">
-        <f t="shared" si="8"/>
-        <v>0.82626235758301192</v>
-      </c>
-      <c r="N38" s="2" t="s">
+      <c r="D42" s="23">
+        <f>Model!P20/Model!P55</f>
+        <v>2.9677182685253118</v>
+      </c>
+      <c r="E42" s="23">
+        <f>Model!Q20/Model!Q55</f>
+        <v>3.404645476772616</v>
+      </c>
+      <c r="F42" s="23">
+        <f>Model!R20/Model!R55</f>
+        <v>2.0281949934123849</v>
+      </c>
+      <c r="G42" s="23">
+        <f>Model!S20/Model!S55</f>
+        <v>2.1191036529213139</v>
+      </c>
+      <c r="H42" s="23">
+        <f>Model!T20/Model!T55</f>
+        <v>2.1262018108839729</v>
+      </c>
+      <c r="I42" s="23">
+        <f>Model!U20/Model!U55</f>
+        <v>2.4380403458213253</v>
+      </c>
+      <c r="J42" s="23">
+        <f>Model!V20/Model!V55</f>
+        <v>2.3442502106149958</v>
+      </c>
+      <c r="K42" s="23">
+        <f>Model!W20/Model!W55</f>
+        <v>2.4108251996450756</v>
+      </c>
+      <c r="M42" s="23">
+        <f t="shared" si="9"/>
+        <v>2.412766019537981</v>
+      </c>
+      <c r="N42" s="23">
+        <f t="shared" si="10"/>
+        <v>2.4380403458213253</v>
+      </c>
+      <c r="P42" s="2" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="2" t="s">
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B43" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="D39" s="17">
-        <f>(Model!P54+Model!P56)/Model!P76</f>
-        <v>0.81843179735022087</v>
-      </c>
-      <c r="E39" s="17">
-        <f>(Model!Q54+Model!Q56)/Model!Q76</f>
-        <v>0.90702676864244747</v>
-      </c>
-      <c r="F39" s="17">
-        <f>(Model!R54+Model!R56)/Model!R76</f>
-        <v>1.9122286723876831</v>
-      </c>
-      <c r="G39" s="17">
-        <f>(Model!S54+Model!S56)/Model!S76</f>
-        <v>1.005984838409363</v>
-      </c>
-      <c r="H39" s="17">
-        <f>(Model!T54+Model!T56)/Model!T76</f>
-        <v>1.3237361901573486</v>
-      </c>
-      <c r="I39" s="17">
-        <f>(Model!U54+Model!U56)/Model!U76</f>
-        <v>1.4372273718647763</v>
-      </c>
-      <c r="K39" s="23">
-        <f t="shared" si="7"/>
-        <v>1.1463450494454273</v>
-      </c>
-      <c r="L39" s="23">
-        <f t="shared" si="8"/>
-        <v>1.005984838409363</v>
-      </c>
-      <c r="N39" s="2" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B40" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="D40" s="17">
-        <f>Model!P60/Model!P76</f>
-        <v>2.9954170485792853</v>
-      </c>
-      <c r="E40" s="17">
-        <f>Model!Q60/Model!Q76</f>
-        <v>1.6133843212237098</v>
-      </c>
-      <c r="F40" s="17">
-        <f>Model!R60/Model!R76</f>
-        <v>2.6552246340232206</v>
-      </c>
-      <c r="G40" s="17">
-        <f>Model!S60/Model!S76</f>
-        <v>1.8696191869486194</v>
-      </c>
-      <c r="H40" s="17">
-        <f>Model!T60/Model!T76</f>
-        <v>2.2257114161365914</v>
-      </c>
-      <c r="I40" s="17">
-        <f>Model!U60/Model!U76</f>
-        <v>2.2899400218102506</v>
-      </c>
-      <c r="K40" s="23">
-        <f t="shared" si="7"/>
-        <v>2.3451719183686865</v>
-      </c>
-      <c r="L40" s="23">
-        <f t="shared" si="8"/>
-        <v>2.2257114161365914</v>
-      </c>
-      <c r="N40" s="2" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B41" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="D41" s="17">
-        <f>Model!P57/Model!P69</f>
-        <v>0.13761190011442417</v>
-      </c>
-      <c r="E41" s="17">
-        <f>Model!Q57/Model!Q69</f>
-        <v>0.10112776274399374</v>
-      </c>
-      <c r="F41" s="17">
-        <f>Model!R57/Model!R69</f>
-        <v>9.6228209191759118E-2</v>
-      </c>
-      <c r="G41" s="17">
-        <f>Model!S57/Model!S69</f>
-        <v>0.12651624011288462</v>
-      </c>
-      <c r="H41" s="17">
-        <f>Model!T57/Model!T69</f>
-        <v>0.15778776051255614</v>
-      </c>
-      <c r="I41" s="17">
-        <f>Model!U57/Model!U69</f>
-        <v>0.13664314058098326</v>
-      </c>
-      <c r="K41" s="23">
-        <f t="shared" si="7"/>
-        <v>0.13963976033021205</v>
-      </c>
-      <c r="L41" s="23">
-        <f t="shared" si="8"/>
-        <v>0.13664314058098326</v>
-      </c>
-      <c r="N41" s="2" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B42" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="D42" s="24">
-        <f>Model!P20/Model!P57</f>
-        <v>2.9677182685253118</v>
-      </c>
-      <c r="E42" s="24">
-        <f>Model!Q20/Model!Q57</f>
-        <v>3.404645476772616</v>
-      </c>
-      <c r="F42" s="24">
-        <f>Model!R20/Model!R57</f>
-        <v>2.0281949934123849</v>
-      </c>
-      <c r="G42" s="24">
-        <f>Model!S20/Model!S57</f>
-        <v>2.1191036529213139</v>
-      </c>
-      <c r="H42" s="24">
-        <f>Model!T20/Model!T57</f>
-        <v>2.1262018108839729</v>
-      </c>
-      <c r="I42" s="24">
-        <f>Model!U20/Model!U57</f>
-        <v>2.4380403458213253</v>
-      </c>
-      <c r="K42" s="24">
-        <f t="shared" si="7"/>
-        <v>2.412766019537981</v>
-      </c>
-      <c r="L42" s="24">
-        <f t="shared" si="8"/>
-        <v>2.4380403458213253</v>
-      </c>
-      <c r="N42" s="2" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B43" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="D43" s="24">
-        <f t="shared" ref="D43:H43" si="9">360/D42</f>
+      <c r="D43" s="23">
+        <f t="shared" ref="D43:H43" si="11">360/D42</f>
         <v>121.3053152039555</v>
       </c>
-      <c r="E43" s="24">
-        <f t="shared" si="9"/>
+      <c r="E43" s="23">
+        <f t="shared" si="11"/>
         <v>105.737881508079</v>
       </c>
-      <c r="F43" s="24">
-        <f t="shared" si="9"/>
+      <c r="F43" s="23">
+        <f t="shared" si="11"/>
         <v>177.49772638690396</v>
       </c>
-      <c r="G43" s="24">
-        <f t="shared" si="9"/>
+      <c r="G43" s="23">
+        <f t="shared" si="11"/>
         <v>169.88314823756639</v>
       </c>
-      <c r="H43" s="24">
-        <f t="shared" si="9"/>
+      <c r="H43" s="23">
+        <f t="shared" si="11"/>
         <v>169.31600667310562</v>
       </c>
-      <c r="I43" s="24">
+      <c r="I43" s="23">
         <f>360/I42</f>
         <v>147.65957446808511</v>
       </c>
-      <c r="K43" s="24">
-        <f t="shared" si="7"/>
+      <c r="J43" s="23">
+        <f t="shared" ref="J43:K43" si="12">360/J42</f>
+        <v>153.5672251920399</v>
+      </c>
+      <c r="K43" s="23">
+        <f t="shared" si="12"/>
+        <v>149.32646301067354</v>
+      </c>
+      <c r="M43" s="23">
+        <f t="shared" si="9"/>
         <v>152.04101114567817</v>
       </c>
-      <c r="L43" s="24">
-        <f t="shared" si="8"/>
+      <c r="N43" s="23">
+        <f t="shared" si="10"/>
         <v>147.65957446808511</v>
       </c>
-      <c r="N43" s="2" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="P43" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B44" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="D44" s="24">
-        <f t="shared" ref="D44:H44" si="10">D36+D43-D37</f>
+        <v>234</v>
+      </c>
+      <c r="D44" s="23">
+        <f t="shared" ref="D44:H44" si="13">D36+D43-D37</f>
         <v>132.47084664700949</v>
       </c>
-      <c r="E44" s="24">
-        <f t="shared" si="10"/>
+      <c r="E44" s="23">
+        <f t="shared" si="13"/>
         <v>107.50871822355677</v>
       </c>
-      <c r="F44" s="24">
-        <f t="shared" si="10"/>
+      <c r="F44" s="23">
+        <f t="shared" si="13"/>
         <v>185.3181226784873</v>
       </c>
-      <c r="G44" s="24">
-        <f t="shared" si="10"/>
+      <c r="G44" s="23">
+        <f t="shared" si="13"/>
         <v>167.37643439982418</v>
       </c>
-      <c r="H44" s="24">
-        <f t="shared" si="10"/>
+      <c r="H44" s="23">
+        <f t="shared" si="13"/>
         <v>173.56766723552414</v>
       </c>
-      <c r="I44" s="24">
+      <c r="I44" s="23">
         <f>I36+I43-I37</f>
         <v>153.86459904811346</v>
       </c>
-      <c r="K44" s="24">
-        <f t="shared" si="7"/>
+      <c r="J44" s="23">
+        <f t="shared" ref="J44:K44" si="14">J36+J43-J37</f>
+        <v>154.76230924345961</v>
+      </c>
+      <c r="K44" s="23">
+        <f t="shared" si="14"/>
+        <v>152.01942006286407</v>
+      </c>
+      <c r="M44" s="23">
+        <f t="shared" si="9"/>
         <v>156.81988683261781</v>
       </c>
-      <c r="L44" s="24">
-        <f t="shared" si="8"/>
+      <c r="N44" s="23">
+        <f t="shared" si="10"/>
         <v>153.86459904811346</v>
       </c>
-      <c r="N44" s="2" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="P44" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B45" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="D45" s="27" t="s">
+        <v>236</v>
+      </c>
+      <c r="D45" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="E45" s="27" t="s">
+      <c r="E45" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="F45" s="27" t="s">
+      <c r="F45" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="G45" s="27" t="s">
+      <c r="G45" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="H45" s="27" t="s">
+      <c r="H45" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="I45" s="27" t="s">
+      <c r="I45" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="K45" s="27" t="s">
+      <c r="J45" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="L45" s="27" t="s">
+      <c r="K45" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="N45" s="2" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="M45" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="N45" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="P45" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B46" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="D46" s="27" t="s">
+        <v>238</v>
+      </c>
+      <c r="D46" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="E46" s="27" t="s">
+      <c r="E46" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="F46" s="27" t="s">
+      <c r="F46" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="G46" s="27" t="s">
+      <c r="G46" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="H46" s="27" t="s">
+      <c r="H46" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="I46" s="27" t="s">
+      <c r="I46" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="K46" s="27" t="s">
+      <c r="J46" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="L46" s="27" t="s">
+      <c r="K46" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="N46" s="2" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="M46" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="N46" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="P46" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B48" s="7" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="49" spans="2:14" x14ac:dyDescent="0.2">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="49" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B49" s="9" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="50" spans="2:14" x14ac:dyDescent="0.2">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="50" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B50" s="2" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="D50" s="3">
         <f>131.6*Model!P35</f>
@@ -8229,81 +8947,105 @@
       </c>
       <c r="I50" s="3">
         <f>Main!H4</f>
-        <v>20461.91295813</v>
-      </c>
-    </row>
-    <row r="51" spans="2:14" x14ac:dyDescent="0.2">
+        <v>22473.766070860001</v>
+      </c>
+      <c r="J50" s="3">
+        <f>Main!I4</f>
+        <v>0</v>
+      </c>
+      <c r="K50" s="3">
+        <f>Main!J4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B51" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D51" s="3">
-        <f>(Model!P71+Model!P77+Model!P78+Model!P79-Model!P54-Model!P55)+D50</f>
+        <f>(Model!P67+Model!P73+Model!P74+Model!P75-Model!P52-Model!P53)+D50</f>
         <v>8976.006800000001</v>
       </c>
       <c r="E51" s="3">
-        <f>(Model!Q71+Model!Q77+Model!Q78+Model!Q79-Model!Q54-Model!Q55)+E50</f>
+        <f>(Model!Q67+Model!Q73+Model!Q74+Model!Q75-Model!Q52-Model!Q53)+E50</f>
         <v>5985.0865999999996</v>
       </c>
       <c r="F51" s="3">
-        <f>(Model!R71+Model!R77+Model!R78+Model!R79-Model!R54-Model!R55)+F50</f>
+        <f>(Model!R67+Model!R73+Model!R74+Model!R75-Model!R52-Model!R53)+F50</f>
         <v>9899.2623000000003</v>
       </c>
       <c r="G51" s="3">
-        <f>(Model!S71+Model!S77+Model!S78+Model!S79-Model!S54-Model!S55)+G50</f>
+        <f>(Model!S67+Model!S73+Model!S74+Model!S75-Model!S52-Model!S53)+G50</f>
         <v>7988.7025000000012</v>
       </c>
       <c r="H51" s="3">
-        <f>(Model!T71+Model!T77+Model!T78+Model!T79-Model!T54-Model!T55)+H50</f>
+        <f>(Model!T67+Model!T73+Model!T74+Model!T75-Model!T52-Model!T53)+H50</f>
         <v>8465.6347999999998</v>
       </c>
       <c r="I51" s="3">
         <f>Main!H7</f>
-        <v>21474.41295813</v>
-      </c>
-    </row>
-    <row r="52" spans="2:14" x14ac:dyDescent="0.2">
+        <v>23299.86607086</v>
+      </c>
+      <c r="J51" s="3">
+        <f>Main!I7</f>
+        <v>0</v>
+      </c>
+      <c r="K51" s="3">
+        <f>Main!J7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B52" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="D52" s="24">
+        <v>243</v>
+      </c>
+      <c r="D52" s="23">
         <f>D50/Model!P32</f>
         <v>23.844063123694614</v>
       </c>
-      <c r="E52" s="24">
+      <c r="E52" s="23">
         <f>E50/Model!Q32</f>
         <v>13.952866510538627</v>
       </c>
-      <c r="F52" s="24">
+      <c r="F52" s="23">
         <f>F50/Model!R32</f>
         <v>-80.498450041288251</v>
       </c>
-      <c r="G52" s="24">
+      <c r="G52" s="23">
         <f>G50/Model!S32</f>
         <v>12.459594234294283</v>
       </c>
-      <c r="H52" s="24">
+      <c r="H52" s="23">
         <f>H50/Model!T32</f>
         <v>14.226965372106363</v>
       </c>
-      <c r="I52" s="24">
+      <c r="I52" s="23">
         <f>I50/Model!U32</f>
-        <v>31.660085035014742</v>
-      </c>
-      <c r="K52" s="24">
-        <f t="shared" ref="K52:K63" si="11">AVERAGE(G52:I52,D52)</f>
-        <v>20.547676941277501</v>
-      </c>
-      <c r="L52" s="24">
+        <v>34.77296312990876</v>
+      </c>
+      <c r="J52" s="23">
+        <f>J50/Model!V32</f>
+        <v>0</v>
+      </c>
+      <c r="K52" s="23">
+        <f>K50/Model!W32</f>
+        <v>0</v>
+      </c>
+      <c r="M52" s="23">
+        <f t="shared" ref="M52:M63" si="15">AVERAGE(G52:I52,D52)</f>
+        <v>21.325896465001005</v>
+      </c>
+      <c r="N52" s="23">
         <f>MEDIAN(G52:I52,D52:E52)</f>
         <v>14.226965372106363</v>
       </c>
-      <c r="N52" s="2" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="53" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="P52" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="53" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B53" s="2" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="D53" s="17">
         <f>D52/131.6</f>
@@ -8327,384 +9069,464 @@
       </c>
       <c r="I53" s="17">
         <f>I52/Main!H2</f>
-        <v>9.3666119449172344E-2</v>
-      </c>
-      <c r="K53" s="17">
-        <f t="shared" si="11"/>
-        <v>0.12918785952712319</v>
-      </c>
-      <c r="L53" s="17">
-        <f t="shared" ref="L53:L63" si="12">MEDIAN(G53:I53,D53:E53)</f>
+        <v>9.2258000928361561E-2</v>
+      </c>
+      <c r="J53" s="17" t="e">
+        <f>J52/Main!I2</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K53" s="17" t="e">
+        <f>K52/Main!J2</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M53" s="17">
+        <f t="shared" si="15"/>
+        <v>0.1288358298969205</v>
+      </c>
+      <c r="N53" s="17">
+        <f t="shared" ref="N53:N63" si="16">MEDIAN(G53:I53,D53:E53)</f>
         <v>0.12512722402907972</v>
       </c>
-      <c r="N53" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="54" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="P53" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="54" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B54" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="D54" s="26" t="s">
+        <v>247</v>
+      </c>
+      <c r="D54" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="E54" s="24">
+      <c r="E54" s="23">
         <f>E52/(Model!Q32/Model!P32-1)</f>
         <v>-129.01910256204266</v>
       </c>
-      <c r="F54" s="24">
+      <c r="F54" s="23">
         <f>F52/(Model!R32/Model!Q32-1)</f>
         <v>61.210040266852168</v>
       </c>
-      <c r="G54" s="24">
+      <c r="G54" s="23">
         <f>G52/(Model!S32/Model!R32-1)</f>
         <v>-2.0921476175444211</v>
       </c>
-      <c r="H54" s="24">
+      <c r="H54" s="23">
         <f>H52/(Model!T32/Model!S32-1)</f>
         <v>-110.30493436435457</v>
       </c>
-      <c r="I54" s="24">
+      <c r="I54" s="23">
         <f>I52/(Model!U32/Model!T32-1)</f>
-        <v>133.88937255503535</v>
-      </c>
-      <c r="K54" s="24">
-        <f t="shared" si="11"/>
-        <v>7.1640968577121198</v>
-      </c>
-      <c r="L54" s="24">
-        <f t="shared" si="12"/>
+        <v>147.05362320391171</v>
+      </c>
+      <c r="J54" s="23">
+        <f>J52/(Model!V32/Model!U32-1)</f>
+        <v>0</v>
+      </c>
+      <c r="K54" s="23">
+        <f>K52/(Model!W32/Model!V32-1)</f>
+        <v>0</v>
+      </c>
+      <c r="M54" s="23">
+        <f t="shared" si="15"/>
+        <v>11.552180407337573</v>
+      </c>
+      <c r="N54" s="23">
+        <f t="shared" si="16"/>
         <v>-56.198540990949496</v>
       </c>
-      <c r="N54" s="2" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="55" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="P54" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="55" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B55" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="D55" s="24">
-        <f>D50/Model!P93</f>
+        <v>249</v>
+      </c>
+      <c r="D55" s="23">
+        <f>D50/Model!P81</f>
         <v>3.1255800681431003</v>
       </c>
-      <c r="E55" s="24">
-        <f>E50/Model!Q93</f>
+      <c r="E55" s="23">
+        <f>E50/Model!Q81</f>
         <v>1.9910462292525333</v>
       </c>
-      <c r="F55" s="24">
-        <f>F50/Model!R93</f>
+      <c r="F55" s="23">
+        <f>F50/Model!R81</f>
         <v>3.7430357471970535</v>
       </c>
-      <c r="G55" s="24">
-        <f>G50/Model!S93</f>
+      <c r="G55" s="23">
+        <f>G50/Model!S81</f>
         <v>2.9483448343848582</v>
       </c>
-      <c r="H55" s="24">
-        <f>H50/Model!T93</f>
+      <c r="H55" s="23">
+        <f>H50/Model!T81</f>
         <v>3.0596316807241322</v>
       </c>
-      <c r="I55" s="24">
-        <f>I50/Model!U93</f>
-        <v>8.3507786630739069</v>
-      </c>
-      <c r="K55" s="24">
-        <f t="shared" si="11"/>
-        <v>4.3710838115814994</v>
-      </c>
-      <c r="L55" s="24">
-        <f t="shared" si="12"/>
+      <c r="I55" s="23">
+        <f>I50/Model!U81</f>
+        <v>9.1718426604334145</v>
+      </c>
+      <c r="J55" s="23">
+        <f>J50/Model!V81</f>
+        <v>0</v>
+      </c>
+      <c r="K55" s="23">
+        <f>K50/Model!W81</f>
+        <v>0</v>
+      </c>
+      <c r="M55" s="23">
+        <f t="shared" si="15"/>
+        <v>4.5763498109213767</v>
+      </c>
+      <c r="N55" s="23">
+        <f t="shared" si="16"/>
         <v>3.0596316807241322</v>
       </c>
-      <c r="N55" s="2" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="56" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="P55" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="56" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B56" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="D56" s="24">
-        <f>D50/(Model!P93-Model!P65-Model!P64)</f>
+        <v>251</v>
+      </c>
+      <c r="D56" s="23">
+        <f>D50/(Model!P81-Model!P63-Model!P62)</f>
         <v>4.6619205953083158</v>
       </c>
-      <c r="E56" s="24">
-        <f>E50/(Model!Q93-Model!Q65-Model!Q64)</f>
+      <c r="E56" s="23">
+        <f>E50/(Model!Q81-Model!Q63-Model!Q62)</f>
         <v>3.2763574483685662</v>
       </c>
-      <c r="F56" s="24">
-        <f>F50/(Model!R93-Model!R65-Model!R64)</f>
+      <c r="F56" s="23">
+        <f>F50/(Model!R81-Model!R63-Model!R62)</f>
         <v>6.2945452960547605</v>
       </c>
-      <c r="G56" s="24">
-        <f>G50/(Model!S93-Model!S65-Model!S64)</f>
+      <c r="G56" s="23">
+        <f>G50/(Model!S81-Model!S63-Model!S62)</f>
         <v>4.9048822487536086</v>
       </c>
-      <c r="H56" s="24">
-        <f>H50/(Model!T93-Model!T65-Model!T64)</f>
+      <c r="H56" s="23">
+        <f>H50/(Model!T81-Model!T63-Model!T62)</f>
         <v>5.1545260969016464</v>
       </c>
-      <c r="I56" s="24">
-        <f>I50/(Model!U93-Model!U65-Model!U64)</f>
-        <v>13.765161761271434</v>
-      </c>
-      <c r="K56" s="24">
-        <f t="shared" si="11"/>
-        <v>7.1216226755587515</v>
-      </c>
-      <c r="L56" s="24">
-        <f t="shared" si="12"/>
+      <c r="I56" s="23">
+        <f>I50/(Model!U81-Model!U63-Model!U62)</f>
+        <v>15.118577915142945</v>
+      </c>
+      <c r="J56" s="23">
+        <f>J50/(Model!V81-Model!V63-Model!V62)</f>
+        <v>0</v>
+      </c>
+      <c r="K56" s="23">
+        <f>K50/(Model!W81-Model!W63-Model!W62)</f>
+        <v>0</v>
+      </c>
+      <c r="M56" s="23">
+        <f t="shared" si="15"/>
+        <v>7.4599767140266291</v>
+      </c>
+      <c r="N56" s="23">
+        <f t="shared" si="16"/>
         <v>4.9048822487536086</v>
       </c>
-      <c r="N56" s="2" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="57" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="P56" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="57" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B57" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="D57" s="24">
-        <f>D50/Model!P116</f>
+        <v>253</v>
+      </c>
+      <c r="D57" s="23">
+        <f>D50/Model!P101</f>
         <v>13.108454707833637</v>
       </c>
-      <c r="E57" s="24">
-        <f>E50/Model!Q116</f>
+      <c r="E57" s="23">
+        <f>E50/Model!Q101</f>
         <v>7.1058661542539054</v>
       </c>
-      <c r="F57" s="24">
-        <f>F50/Model!R116</f>
+      <c r="F57" s="23">
+        <f>F50/Model!R101</f>
         <v>25.592970070884746</v>
       </c>
-      <c r="G57" s="24">
-        <f>G50/Model!S116</f>
+      <c r="G57" s="23">
+        <f>G50/Model!S101</f>
         <v>10.444199608883919</v>
       </c>
-      <c r="H57" s="24">
-        <f>H50/Model!T116</f>
+      <c r="H57" s="23">
+        <f>H50/Model!T101</f>
         <v>18.093515328467145</v>
       </c>
-      <c r="I57" s="24">
-        <f>I50/Model!U116</f>
-        <v>19.128646310301971</v>
-      </c>
-      <c r="K57" s="24">
-        <f t="shared" si="11"/>
-        <v>15.193703988871667</v>
-      </c>
-      <c r="L57" s="24">
-        <f t="shared" si="12"/>
+      <c r="I57" s="23">
+        <f>I50/Model!U101</f>
+        <v>21.0094101812284</v>
+      </c>
+      <c r="J57" s="23">
+        <f>J50/Model!V101</f>
+        <v>0</v>
+      </c>
+      <c r="K57" s="23">
+        <f>K50/Model!W101</f>
+        <v>0</v>
+      </c>
+      <c r="M57" s="23">
+        <f t="shared" si="15"/>
+        <v>15.663894956603274</v>
+      </c>
+      <c r="N57" s="23">
+        <f t="shared" si="16"/>
         <v>13.108454707833637</v>
       </c>
-      <c r="N57" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="58" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="P57" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="58" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B58" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="D58" s="24">
+        <v>255</v>
+      </c>
+      <c r="D58" s="23">
         <f>D50/Model!P19</f>
         <v>1.6274998891176937</v>
       </c>
-      <c r="E58" s="24">
+      <c r="E58" s="23">
         <f>E50/Model!Q19</f>
         <v>0.87049686678138893</v>
       </c>
-      <c r="F58" s="24">
+      <c r="F58" s="23">
         <f>F50/Model!R19</f>
         <v>2.2151341347027813</v>
       </c>
-      <c r="G58" s="24">
+      <c r="G58" s="23">
         <f>G50/Model!S19</f>
         <v>1.2023803972018976</v>
       </c>
-      <c r="H58" s="24">
+      <c r="H58" s="23">
         <f>H50/Model!T19</f>
         <v>1.154080762306785</v>
       </c>
-      <c r="I58" s="24">
+      <c r="I58" s="23">
         <f>I50/Model!U19</f>
-        <v>3.0856098196655308</v>
-      </c>
-      <c r="K58" s="24">
-        <f t="shared" si="11"/>
-        <v>1.7673927170729766</v>
-      </c>
-      <c r="L58" s="24">
-        <f t="shared" si="12"/>
+        <v>3.3889926819163376</v>
+      </c>
+      <c r="J58" s="23">
+        <f>J50/Model!V19</f>
+        <v>0</v>
+      </c>
+      <c r="K58" s="23">
+        <f>K50/Model!W19</f>
+        <v>0</v>
+      </c>
+      <c r="M58" s="23">
+        <f t="shared" si="15"/>
+        <v>1.8432384326356783</v>
+      </c>
+      <c r="N58" s="23">
+        <f t="shared" si="16"/>
         <v>1.2023803972018976</v>
       </c>
-      <c r="N58" s="2" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="59" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="P58" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="59" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B59" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="K59" s="24"/>
-      <c r="L59" s="24"/>
-    </row>
-    <row r="60" spans="2:14" x14ac:dyDescent="0.2">
+        <v>257</v>
+      </c>
+      <c r="M59" s="23"/>
+      <c r="N59" s="23"/>
+    </row>
+    <row r="60" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B60" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="D60" s="24">
-        <f>D51/(Model!P26+Model!P101)</f>
+        <v>258</v>
+      </c>
+      <c r="D60" s="23">
+        <f>D51/(Model!P26+Model!P86)</f>
         <v>10.646431977226905</v>
       </c>
-      <c r="E60" s="24">
-        <f>E51/(Model!Q26+Model!Q101)</f>
+      <c r="E60" s="23">
+        <f>E51/(Model!Q26+Model!Q86)</f>
         <v>10.204751236146624</v>
       </c>
-      <c r="F60" s="24">
-        <f>F51/(Model!R26+Model!R101)</f>
+      <c r="F60" s="23">
+        <f>F51/(Model!R26+Model!R86)</f>
         <v>48.525795588235276</v>
       </c>
-      <c r="G60" s="24">
-        <f>G51/(Model!S26+Model!S101)</f>
+      <c r="G60" s="23">
+        <f>G51/(Model!S26+Model!S86)</f>
         <v>7.7703555101643813</v>
       </c>
-      <c r="H60" s="24">
-        <f>H51/(Model!T26+Model!T101)</f>
+      <c r="H60" s="23">
+        <f>H51/(Model!T26+Model!T86)</f>
         <v>9.155006813020437</v>
       </c>
-      <c r="I60" s="24">
-        <f>I51/(Model!U26+Model!U101)</f>
-        <v>21.792584694672232</v>
-      </c>
-      <c r="K60" s="24">
-        <f t="shared" si="11"/>
-        <v>12.341094748770988</v>
-      </c>
-      <c r="L60" s="24">
-        <f t="shared" si="12"/>
+      <c r="I60" s="23">
+        <f>I51/(Model!U26+Model!U86)</f>
+        <v>23.645084301664319</v>
+      </c>
+      <c r="J60" s="23">
+        <f>J51/(Model!V26+Model!V86)</f>
+        <v>0</v>
+      </c>
+      <c r="K60" s="23">
+        <f>K51/(Model!W26+Model!W86)</f>
+        <v>0</v>
+      </c>
+      <c r="M60" s="23">
+        <f t="shared" si="15"/>
+        <v>12.804219650519011</v>
+      </c>
+      <c r="N60" s="23">
+        <f t="shared" si="16"/>
         <v>10.204751236146624</v>
       </c>
-      <c r="N60" s="2" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="61" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="P60" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="61" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B61" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="D61" s="24">
+        <v>259</v>
+      </c>
+      <c r="D61" s="23">
         <f>Ratios!D51/Model!P26</f>
         <v>15.977228195087228</v>
       </c>
-      <c r="E61" s="24">
+      <c r="E61" s="23">
         <f>Ratios!E51/Model!Q26</f>
         <v>18.880399369085143</v>
       </c>
-      <c r="F61" s="24">
+      <c r="F61" s="23">
         <f>Ratios!F51/Model!R26</f>
         <v>-227.04730045871608</v>
       </c>
-      <c r="G61" s="24">
+      <c r="G61" s="23">
         <f>Ratios!G51/Model!S26</f>
         <v>10.005889904809619</v>
       </c>
-      <c r="H61" s="24">
+      <c r="H61" s="23">
         <f>Ratios!H51/Model!T26</f>
         <v>12.021634194831009</v>
       </c>
-      <c r="I61" s="24">
+      <c r="I61" s="23">
         <f>Ratios!I51/Model!U26</f>
-        <v>28.390286829891622</v>
-      </c>
-      <c r="K61" s="24">
-        <f t="shared" si="11"/>
-        <v>16.598759781154868</v>
-      </c>
-      <c r="L61" s="24">
-        <f t="shared" si="12"/>
+        <v>30.803630447990514</v>
+      </c>
+      <c r="J61" s="23">
+        <f>Ratios!J51/Model!V26</f>
+        <v>0</v>
+      </c>
+      <c r="K61" s="23">
+        <f>Ratios!K51/Model!W26</f>
+        <v>0</v>
+      </c>
+      <c r="M61" s="23">
+        <f t="shared" si="15"/>
+        <v>17.202095685679595</v>
+      </c>
+      <c r="N61" s="23">
+        <f t="shared" si="16"/>
         <v>15.977228195087228</v>
       </c>
-      <c r="N61" s="2" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="62" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="P61" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="62" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B62" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="D62" s="24">
-        <f>D51/(Model!P26*(1-Model!P49)+Model!P101+Model!P117+SUM(Model!P109:P115))</f>
+        <v>260</v>
+      </c>
+      <c r="D62" s="23">
+        <f>D51/(Model!P26*(1-Model!P49)+Model!P86+Model!P102+SUM(Model!P94:P100))</f>
         <v>23.749409176237659</v>
       </c>
-      <c r="E62" s="24">
-        <f>E51/(Model!Q26*(1-Model!Q49)+Model!Q101+Model!Q117+SUM(Model!Q109:Q115))</f>
+      <c r="E62" s="23">
+        <f>E51/(Model!Q26*(1-Model!Q49)+Model!Q86+Model!Q102+SUM(Model!Q94:Q100))</f>
         <v>13.668939626752815</v>
       </c>
-      <c r="F62" s="24">
-        <f>F51/(Model!R26*(1-Model!R49)+Model!R101+Model!R117+SUM(Model!R109:R115))</f>
+      <c r="F62" s="23">
+        <f>F51/(Model!R26*(1-Model!R49)+Model!R86+Model!R102+SUM(Model!R94:R100))</f>
         <v>63.68932845888164</v>
       </c>
-      <c r="G62" s="24">
-        <f>G51/(Model!S26*(1-Model!S49)+Model!S101+Model!S117+SUM(Model!S109:S115))</f>
+      <c r="G62" s="23">
+        <f>G51/(Model!S26*(1-Model!S49)+Model!S86+Model!S102+SUM(Model!S94:S100))</f>
         <v>16.436095027550397</v>
       </c>
-      <c r="H62" s="24">
-        <f>H51/(Model!T26*(1-Model!T49)+Model!T101+Model!T117+SUM(Model!T109:T115))</f>
+      <c r="H62" s="23">
+        <f>H51/(Model!T26*(1-Model!T49)+Model!T86+Model!T102+SUM(Model!T94:T100))</f>
         <v>154.91277282965646</v>
       </c>
-      <c r="I62" s="24">
-        <f>I51/(Model!U26*(1-Model!U49)+Model!U101+Model!U117+SUM(Model!U109:U115))</f>
-        <v>27.455038842900713</v>
-      </c>
-      <c r="K62" s="24">
-        <f t="shared" si="11"/>
-        <v>55.638328969086309</v>
-      </c>
-      <c r="L62" s="24">
-        <f t="shared" si="12"/>
+      <c r="I62" s="23">
+        <f>I51/(Model!U26*(1-Model!U49)+Model!U86+Model!U102+SUM(Model!U94:U100))</f>
+        <v>29.788880806991376</v>
+      </c>
+      <c r="J62" s="23">
+        <f>J51/(Model!V26*(1-Model!V49)+Model!V86+Model!V102+SUM(Model!V94:V100))</f>
+        <v>0</v>
+      </c>
+      <c r="K62" s="23">
+        <f>K51/(Model!W26*(1-Model!W49)+Model!W86+Model!W102+SUM(Model!W94:W100))</f>
+        <v>0</v>
+      </c>
+      <c r="M62" s="23">
+        <f t="shared" si="15"/>
+        <v>56.22178946010898</v>
+      </c>
+      <c r="N62" s="23">
+        <f t="shared" si="16"/>
         <v>23.749409176237659</v>
       </c>
-      <c r="N62" s="2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="63" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="P62" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="63" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B63" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="D63" s="24">
+        <v>261</v>
+      </c>
+      <c r="D63" s="23">
         <f>D51/Model!P19</f>
         <v>1.4218290511642644</v>
       </c>
-      <c r="E63" s="24">
+      <c r="E63" s="23">
         <f>E51/Model!Q19</f>
         <v>0.97163651417253794</v>
       </c>
-      <c r="F63" s="24">
+      <c r="F63" s="23">
         <f>F51/Model!R19</f>
         <v>2.2494233548445739</v>
       </c>
-      <c r="G63" s="24">
+      <c r="G63" s="23">
         <f>G51/Model!S19</f>
         <v>1.2846671222963739</v>
       </c>
-      <c r="H63" s="24">
+      <c r="H63" s="23">
         <f>H51/Model!T19</f>
         <v>1.3138051399838599</v>
       </c>
-      <c r="I63" s="24">
+      <c r="I63" s="23">
         <f>I51/Model!U19</f>
-        <v>3.2382925111032361</v>
-      </c>
-      <c r="K63" s="24">
-        <f t="shared" si="11"/>
-        <v>1.8146484561369336</v>
-      </c>
-      <c r="L63" s="24">
-        <f t="shared" si="12"/>
+        <v>3.5135666783575115</v>
+      </c>
+      <c r="J63" s="23">
+        <f>J51/Model!V19</f>
+        <v>0</v>
+      </c>
+      <c r="K63" s="23">
+        <f>K51/Model!W19</f>
+        <v>0</v>
+      </c>
+      <c r="M63" s="23">
+        <f t="shared" si="15"/>
+        <v>1.8834669979505025</v>
+      </c>
+      <c r="N63" s="23">
+        <f t="shared" si="16"/>
         <v>1.3138051399838599</v>
       </c>
-      <c r="N63" s="2" t="s">
-        <v>270</v>
+      <c r="P63" s="2" t="s">
+        <v>262</v>
       </c>
     </row>
   </sheetData>

--- a/RL.xlsx
+++ b/RL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67FC25D3-54A9-4893-8E41-C6546E075209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D6354F7-6676-434E-8441-AA0741FF50A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{964FB9B6-5A0B-4BED-B971-24C834B20146}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="1" xr2:uid="{964FB9B6-5A0B-4BED-B971-24C834B20146}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="304">
   <si>
     <t>Ralph Lauren</t>
   </si>
@@ -938,6 +938,18 @@
   </si>
   <si>
     <t>FY26</t>
+  </si>
+  <si>
+    <t>Q127</t>
+  </si>
+  <si>
+    <t>Q227</t>
+  </si>
+  <si>
+    <t>Q327</t>
+  </si>
+  <si>
+    <t>Q427</t>
   </si>
 </sst>
 </file>
@@ -950,13 +962,19 @@
     <numFmt numFmtId="166" formatCode="#,##0.0;\(#,##0.0\)"/>
     <numFmt numFmtId="167" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1040,62 +1058,65 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1514,7 +1535,7 @@
         <v>7</v>
       </c>
       <c r="H2" s="2">
-        <v>376.91</v>
+        <v>389.9</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -1522,11 +1543,11 @@
         <v>292</v>
       </c>
       <c r="H3" s="3">
-        <f>37.63507+21.991276</f>
-        <v>59.626345999999998</v>
-      </c>
-      <c r="I3" s="28" t="s">
-        <v>297</v>
+        <f>37.700963+21.881276</f>
+        <v>59.582239000000001</v>
+      </c>
+      <c r="I3" s="32" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -1539,7 +1560,7 @@
       </c>
       <c r="H4" s="3">
         <f>H3*H2</f>
-        <v>22473.766070860001</v>
+        <v>23231.114986099998</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -1551,11 +1572,11 @@
         <v>11</v>
       </c>
       <c r="H5" s="3">
-        <f>1988+77</f>
-        <v>2065</v>
-      </c>
-      <c r="I5" s="28" t="s">
-        <v>297</v>
+        <f>1719+222.6</f>
+        <v>1941.6</v>
+      </c>
+      <c r="I5" s="32" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -1569,11 +1590,10 @@
         <v>10</v>
       </c>
       <c r="H6" s="3">
-        <f>0+1238.9</f>
-        <v>1238.9000000000001</v>
-      </c>
-      <c r="I6" s="28" t="s">
-        <v>297</v>
+        <v>1308.0999999999999</v>
+      </c>
+      <c r="I6" s="32" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -1582,7 +1602,7 @@
       </c>
       <c r="H7" s="3">
         <f>H4+H5-H6</f>
-        <v>23299.86607086</v>
+        <v>23864.614986099998</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
@@ -1839,22 +1859,22 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DECD0C8-AF9F-4DAB-A92B-C0DC872AC0C1}">
-  <dimension ref="A1:AD120"/>
+  <dimension ref="A1:AH120"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="40.5703125" style="2" customWidth="1"/>
-    <col min="3" max="15" width="9.140625" style="12"/>
-    <col min="16" max="22" width="8.7109375" style="12"/>
-    <col min="23" max="16384" width="9.140625" style="12"/>
+    <col min="3" max="19" width="9.140625" style="12"/>
+    <col min="20" max="26" width="8.7109375" style="12"/>
+    <col min="27" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:28" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:24" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:28" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C2" s="4" t="s">
         <v>267</v>
       </c>
@@ -1891,33 +1911,45 @@
       <c r="N2" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4" t="s">
+      <c r="O2" s="32" t="s">
+        <v>300</v>
+      </c>
+      <c r="P2" s="32" t="s">
+        <v>301</v>
+      </c>
+      <c r="Q2" s="32" t="s">
+        <v>302</v>
+      </c>
+      <c r="R2" s="32" t="s">
+        <v>303</v>
+      </c>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="U2" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="V2" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="W2" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="T2" s="4" t="s">
+      <c r="X2" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="U2" s="4" t="s">
+      <c r="Y2" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="V2" s="4" t="s">
+      <c r="Z2" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="W2" s="28" t="s">
+      <c r="AA2" s="28" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="3" spans="1:24" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:28" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
         <v>284</v>
       </c>
@@ -1942,25 +1974,31 @@
       <c r="M3" s="4">
         <v>225</v>
       </c>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="4"/>
-      <c r="R3" s="4"/>
+      <c r="N3" s="2">
+        <f>53+166</f>
+        <v>219</v>
+      </c>
+      <c r="O3" s="2">
+        <v>220</v>
+      </c>
       <c r="S3" s="4"/>
       <c r="T3" s="4"/>
-      <c r="U3" s="4">
+      <c r="U3" s="4"/>
+      <c r="V3" s="4"/>
+      <c r="W3" s="4"/>
+      <c r="X3" s="4"/>
+      <c r="Y3" s="4">
         <v>239</v>
       </c>
-      <c r="V3" s="4">
+      <c r="Z3" s="4">
         <v>223</v>
       </c>
-      <c r="W3" s="2">
+      <c r="AA3" s="2">
         <f>53+166</f>
         <v>219</v>
       </c>
     </row>
-    <row r="4" spans="1:24" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:28" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
         <v>285</v>
       </c>
@@ -1985,25 +2023,31 @@
       <c r="M4" s="4">
         <v>112</v>
       </c>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
+      <c r="N4" s="2">
+        <f>57+54</f>
+        <v>111</v>
+      </c>
+      <c r="O4" s="2">
+        <v>111</v>
+      </c>
       <c r="S4" s="4"/>
       <c r="T4" s="4"/>
-      <c r="U4" s="4">
+      <c r="U4" s="4"/>
+      <c r="V4" s="4"/>
+      <c r="W4" s="4"/>
+      <c r="X4" s="4"/>
+      <c r="Y4" s="4">
         <v>103</v>
       </c>
-      <c r="V4" s="4">
+      <c r="Z4" s="4">
         <v>104</v>
       </c>
-      <c r="W4" s="2">
+      <c r="AA4" s="2">
         <f>57+54</f>
         <v>111</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
         <v>286</v>
       </c>
@@ -2028,25 +2072,31 @@
       <c r="M5" s="4">
         <v>263</v>
       </c>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
-      <c r="P5" s="4"/>
-      <c r="Q5" s="4"/>
-      <c r="R5" s="4"/>
+      <c r="N5" s="2">
+        <f>87+177</f>
+        <v>264</v>
+      </c>
+      <c r="O5" s="2">
+        <v>269</v>
+      </c>
       <c r="S5" s="4"/>
       <c r="T5" s="4"/>
-      <c r="U5" s="4">
+      <c r="U5" s="4"/>
+      <c r="V5" s="4"/>
+      <c r="W5" s="4"/>
+      <c r="X5" s="4"/>
+      <c r="Y5" s="4">
         <v>231</v>
       </c>
-      <c r="V5" s="4">
+      <c r="Z5" s="4">
         <v>237</v>
       </c>
-      <c r="W5" s="2">
+      <c r="AA5" s="2">
         <f>87+177</f>
         <v>264</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
         <v>287</v>
       </c>
@@ -2076,24 +2126,30 @@
         <f>+SUM(M3:M5)</f>
         <v>600</v>
       </c>
-      <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="4"/>
-      <c r="Q6" s="4"/>
-      <c r="R6" s="4"/>
+      <c r="N6" s="2">
+        <v>287</v>
+      </c>
+      <c r="O6" s="2">
+        <f>+SUM(O3:O5)</f>
+        <v>600</v>
+      </c>
       <c r="S6" s="4"/>
       <c r="T6" s="4"/>
-      <c r="U6" s="4">
+      <c r="U6" s="4"/>
+      <c r="V6" s="4"/>
+      <c r="W6" s="4"/>
+      <c r="X6" s="4"/>
+      <c r="Y6" s="4">
         <v>232</v>
       </c>
-      <c r="V6" s="4">
+      <c r="Z6" s="4">
         <v>252</v>
       </c>
-      <c r="W6" s="2">
+      <c r="AA6" s="2">
         <v>287</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B7" s="27" t="s">
         <v>298</v>
       </c>
@@ -2118,29 +2174,34 @@
       <c r="M7" s="4">
         <v>0</v>
       </c>
-      <c r="N7" s="4"/>
-      <c r="O7" s="4"/>
-      <c r="P7" s="4"/>
-      <c r="Q7" s="4"/>
-      <c r="R7" s="4"/>
+      <c r="N7" s="2">
+        <v>307</v>
+      </c>
+      <c r="O7" s="2">
+        <v>0</v>
+      </c>
       <c r="S7" s="4"/>
       <c r="T7" s="4"/>
-      <c r="U7" s="4">
+      <c r="U7" s="4"/>
+      <c r="V7" s="4"/>
+      <c r="W7" s="4"/>
+      <c r="X7" s="4"/>
+      <c r="Y7" s="4">
         <v>332</v>
       </c>
-      <c r="V7" s="4">
+      <c r="Z7" s="4">
         <v>312</v>
       </c>
-      <c r="W7" s="2">
+      <c r="AA7" s="2">
         <v>307</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
         <v>288</v>
       </c>
       <c r="C8" s="11">
-        <f t="shared" ref="C8:N8" si="0">+C6+C7</f>
+        <f t="shared" ref="C8:M8" si="0">+C6+C7</f>
         <v>0</v>
       </c>
       <c r="D8" s="11">
@@ -2184,32 +2245,39 @@
         <v>600</v>
       </c>
       <c r="N8" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O8" s="11"/>
+        <f>+N6+N7</f>
+        <v>594</v>
+      </c>
+      <c r="O8" s="11">
+        <f>+O6+O7</f>
+        <v>600</v>
+      </c>
       <c r="P8" s="11"/>
       <c r="Q8" s="11"/>
       <c r="R8" s="11"/>
       <c r="S8" s="11"/>
-      <c r="T8" s="11">
-        <f t="shared" ref="T8:U8" si="1">+T6+T7</f>
-        <v>0</v>
-      </c>
-      <c r="U8" s="11">
+      <c r="T8" s="11"/>
+      <c r="U8" s="11"/>
+      <c r="V8" s="11"/>
+      <c r="W8" s="11"/>
+      <c r="X8" s="11">
+        <f t="shared" ref="X8:Y8" si="1">+X6+X7</f>
+        <v>0</v>
+      </c>
+      <c r="Y8" s="11">
         <f t="shared" si="1"/>
         <v>564</v>
       </c>
-      <c r="V8" s="11">
-        <f>+V6+V7</f>
+      <c r="Z8" s="11">
+        <f>+Z6+Z7</f>
         <v>564</v>
       </c>
-      <c r="W8" s="11">
-        <f>+W6+W7</f>
+      <c r="AA8" s="11">
+        <f>+AA6+AA7</f>
         <v>594</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
       <c r="B9" s="2" t="s">
         <v>289</v>
@@ -2233,24 +2301,29 @@
       <c r="M9" s="4">
         <v>663</v>
       </c>
-      <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
-      <c r="P9" s="4"/>
-      <c r="Q9" s="4"/>
-      <c r="R9" s="4"/>
+      <c r="N9" s="2">
+        <v>644</v>
+      </c>
+      <c r="O9" s="2">
+        <v>623</v>
+      </c>
       <c r="S9" s="4"/>
       <c r="T9" s="4"/>
-      <c r="U9" s="4">
+      <c r="U9" s="4"/>
+      <c r="V9" s="4"/>
+      <c r="W9" s="4"/>
+      <c r="X9" s="4"/>
+      <c r="Y9" s="4">
         <v>699</v>
       </c>
-      <c r="V9" s="4">
+      <c r="Z9" s="4">
         <v>671</v>
       </c>
-      <c r="W9" s="2">
+      <c r="AA9" s="2">
         <v>644</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
         <v>290</v>
@@ -2278,24 +2351,32 @@
         <f>+M8+M9</f>
         <v>1263</v>
       </c>
-      <c r="N10" s="4"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="4"/>
-      <c r="Q10" s="4"/>
-      <c r="R10" s="4"/>
+      <c r="N10" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="O10" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="P10" s="28"/>
+      <c r="Q10" s="28"/>
+      <c r="R10" s="28"/>
       <c r="S10" s="4"/>
       <c r="T10" s="4"/>
-      <c r="U10" s="4">
+      <c r="U10" s="4"/>
+      <c r="V10" s="4"/>
+      <c r="W10" s="4"/>
+      <c r="X10" s="4"/>
+      <c r="Y10" s="4">
         <v>100</v>
       </c>
-      <c r="V10" s="4">
+      <c r="Z10" s="4">
         <v>116</v>
       </c>
-      <c r="W10" s="28" t="s">
+      <c r="AA10" s="28" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:28" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
@@ -2316,8 +2397,12 @@
       <c r="T11" s="4"/>
       <c r="U11" s="4"/>
       <c r="V11" s="4"/>
-    </row>
-    <row r="12" spans="1:24" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="W11" s="4"/>
+      <c r="X11" s="4"/>
+      <c r="Y11" s="4"/>
+      <c r="Z11" s="4"/>
+    </row>
+    <row r="12" spans="1:28" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
         <v>276</v>
       </c>
@@ -2350,25 +2435,34 @@
       <c r="M12" s="12">
         <v>1078.3</v>
       </c>
-      <c r="N12" s="12"/>
-      <c r="O12" s="12"/>
-      <c r="P12" s="3"/>
-      <c r="Q12" s="3"/>
-      <c r="R12" s="3"/>
-      <c r="S12" s="3"/>
+      <c r="N12" s="12">
+        <f>+AA12-SUM(K12:M12)</f>
+        <v>762.70000000000027</v>
+      </c>
+      <c r="O12" s="12">
+        <v>740.3</v>
+      </c>
+      <c r="P12" s="12"/>
+      <c r="Q12" s="12"/>
+      <c r="R12" s="12"/>
+      <c r="S12" s="12"/>
       <c r="T12" s="3"/>
-      <c r="U12" s="3">
+      <c r="U12" s="3"/>
+      <c r="V12" s="3"/>
+      <c r="W12" s="3"/>
+      <c r="X12" s="3"/>
+      <c r="Y12" s="3">
         <v>2905.5</v>
       </c>
-      <c r="V12" s="3">
+      <c r="Z12" s="3">
         <v>3050.1</v>
       </c>
-      <c r="W12" s="12">
+      <c r="AA12" s="12">
         <v>3329.6</v>
       </c>
-      <c r="X12" s="12"/>
-    </row>
-    <row r="13" spans="1:24" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AB12" s="12"/>
+    </row>
+    <row r="13" spans="1:28" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
         <v>277</v>
       </c>
@@ -2401,25 +2495,34 @@
       <c r="M13" s="12">
         <v>676.5</v>
       </c>
-      <c r="N13" s="12"/>
-      <c r="O13" s="12"/>
-      <c r="P13" s="3"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="3"/>
-      <c r="S13" s="3"/>
+      <c r="N13" s="12">
+        <f t="shared" ref="N13:N24" si="2">+AA13-SUM(K13:M13)</f>
+        <v>619.60000000000014</v>
+      </c>
+      <c r="O13" s="12">
+        <v>594.4</v>
+      </c>
+      <c r="P13" s="12"/>
+      <c r="Q13" s="12"/>
+      <c r="R13" s="12"/>
+      <c r="S13" s="12"/>
       <c r="T13" s="3"/>
-      <c r="U13" s="3">
+      <c r="U13" s="3"/>
+      <c r="V13" s="3"/>
+      <c r="W13" s="3"/>
+      <c r="X13" s="3"/>
+      <c r="Y13" s="3">
         <v>1968</v>
       </c>
-      <c r="V13" s="3">
+      <c r="Z13" s="3">
         <v>2174.9</v>
       </c>
-      <c r="W13" s="12">
+      <c r="AA13" s="12">
         <v>2538.9</v>
       </c>
-      <c r="X13" s="12"/>
-    </row>
-    <row r="14" spans="1:24" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AB13" s="12"/>
+    </row>
+    <row r="14" spans="1:28" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
         <v>278</v>
       </c>
@@ -2452,25 +2555,34 @@
       <c r="M14" s="12">
         <v>620.29999999999995</v>
       </c>
-      <c r="N14" s="12"/>
-      <c r="O14" s="12"/>
-      <c r="P14" s="3"/>
-      <c r="Q14" s="3"/>
-      <c r="R14" s="3"/>
-      <c r="S14" s="3"/>
+      <c r="N14" s="12">
+        <f t="shared" si="2"/>
+        <v>563.59999999999991</v>
+      </c>
+      <c r="O14" s="12">
+        <v>589.29999999999995</v>
+      </c>
+      <c r="P14" s="12"/>
+      <c r="Q14" s="12"/>
+      <c r="R14" s="12"/>
+      <c r="S14" s="12"/>
       <c r="T14" s="3"/>
-      <c r="U14" s="3">
+      <c r="U14" s="3"/>
+      <c r="V14" s="3"/>
+      <c r="W14" s="3"/>
+      <c r="X14" s="3"/>
+      <c r="Y14" s="3">
         <v>1566.6</v>
       </c>
-      <c r="V14" s="3">
+      <c r="Z14" s="3">
         <v>1709.4</v>
       </c>
-      <c r="W14" s="12">
+      <c r="AA14" s="12">
         <v>2103.5</v>
       </c>
-      <c r="X14" s="12"/>
-    </row>
-    <row r="15" spans="1:24" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AB14" s="12"/>
+    </row>
+    <row r="15" spans="1:28" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
         <v>279</v>
       </c>
@@ -2503,25 +2615,34 @@
       <c r="M15" s="12">
         <v>30.9</v>
       </c>
-      <c r="N15" s="12"/>
-      <c r="O15" s="12"/>
-      <c r="P15" s="3"/>
-      <c r="Q15" s="3"/>
-      <c r="R15" s="3"/>
-      <c r="S15" s="3"/>
+      <c r="N15" s="12">
+        <f t="shared" si="2"/>
+        <v>32.800000000000011</v>
+      </c>
+      <c r="O15" s="12">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="P15" s="12"/>
+      <c r="Q15" s="12"/>
+      <c r="R15" s="12"/>
+      <c r="S15" s="12"/>
       <c r="T15" s="3"/>
-      <c r="U15" s="3">
+      <c r="U15" s="3"/>
+      <c r="V15" s="3"/>
+      <c r="W15" s="3"/>
+      <c r="X15" s="3"/>
+      <c r="Y15" s="3">
         <v>146.30000000000001</v>
       </c>
-      <c r="V15" s="3">
+      <c r="Z15" s="3">
         <v>144.6</v>
       </c>
-      <c r="W15" s="12">
+      <c r="AA15" s="12">
         <v>142.5</v>
       </c>
-      <c r="X15" s="12"/>
-    </row>
-    <row r="16" spans="1:24" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AB15" s="12"/>
+    </row>
+    <row r="16" spans="1:28" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
         <v>41</v>
       </c>
@@ -2554,33 +2675,44 @@
       <c r="M16" s="12">
         <v>1581.8</v>
       </c>
-      <c r="N16" s="12"/>
-      <c r="O16" s="3"/>
-      <c r="P16" s="3">
+      <c r="N16" s="12">
+        <f t="shared" si="2"/>
+        <v>1485.1000000000004</v>
+      </c>
+      <c r="O16" s="12">
+        <v>1201.2</v>
+      </c>
+      <c r="P16" s="12"/>
+      <c r="Q16" s="12"/>
+      <c r="R16" s="12"/>
+      <c r="S16" s="3"/>
+      <c r="T16" s="3">
         <v>3747.8</v>
       </c>
-      <c r="Q16" s="3">
+      <c r="U16" s="3">
         <v>3740.9</v>
       </c>
-      <c r="R16" s="3">
+      <c r="V16" s="3">
         <v>2779.8</v>
       </c>
-      <c r="S16" s="3">
+      <c r="W16" s="3">
         <v>3941.5</v>
       </c>
-      <c r="T16" s="3">
+      <c r="X16" s="3">
         <v>4053.1</v>
       </c>
-      <c r="U16" s="3">
+      <c r="Y16" s="3">
         <v>4351</v>
       </c>
-      <c r="V16" s="3">
+      <c r="Z16" s="3">
         <v>4770.1000000000004</v>
       </c>
-      <c r="W16" s="12"/>
-      <c r="X16" s="12"/>
-    </row>
-    <row r="17" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AA16" s="12">
+        <v>5532.6</v>
+      </c>
+      <c r="AB16" s="12"/>
+    </row>
+    <row r="17" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
         <v>68</v>
       </c>
@@ -2613,33 +2745,44 @@
       <c r="M17" s="12">
         <v>527</v>
       </c>
-      <c r="N17" s="12"/>
-      <c r="O17" s="3"/>
-      <c r="P17" s="3">
+      <c r="N17" s="12">
+        <f t="shared" si="2"/>
+        <v>727.10000000000014</v>
+      </c>
+      <c r="O17" s="12">
+        <v>483.5</v>
+      </c>
+      <c r="P17" s="12"/>
+      <c r="Q17" s="12"/>
+      <c r="R17" s="12"/>
+      <c r="S17" s="3"/>
+      <c r="T17" s="3">
         <v>2392.5</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="U17" s="3">
         <v>2250.8000000000002</v>
       </c>
-      <c r="R17" s="3">
+      <c r="V17" s="3">
         <v>1498.6</v>
       </c>
-      <c r="S17" s="3">
+      <c r="W17" s="3">
         <v>2127.3000000000002</v>
       </c>
-      <c r="T17" s="3">
+      <c r="X17" s="3">
         <v>2233.3000000000002</v>
       </c>
-      <c r="U17" s="3">
+      <c r="Y17" s="3">
         <v>2134.1</v>
       </c>
-      <c r="V17" s="3">
+      <c r="Z17" s="3">
         <v>2164.3000000000002</v>
       </c>
-      <c r="W17" s="12"/>
-      <c r="X17" s="12"/>
-    </row>
-    <row r="18" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AA17" s="12">
+        <v>2439.4</v>
+      </c>
+      <c r="AB17" s="12"/>
+    </row>
+    <row r="18" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
         <v>69</v>
       </c>
@@ -2672,33 +2815,44 @@
       <c r="M18" s="12">
         <v>34.700000000000003</v>
       </c>
-      <c r="N18" s="12"/>
-      <c r="O18" s="3"/>
-      <c r="P18" s="3">
+      <c r="N18" s="12">
+        <f t="shared" si="2"/>
+        <v>29</v>
+      </c>
+      <c r="O18" s="12">
+        <v>34.4</v>
+      </c>
+      <c r="P18" s="12"/>
+      <c r="Q18" s="12"/>
+      <c r="R18" s="12"/>
+      <c r="S18" s="3"/>
+      <c r="T18" s="3">
         <v>172.7</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="U18" s="3">
         <v>168.1</v>
       </c>
-      <c r="R18" s="3">
+      <c r="V18" s="3">
         <v>122.4</v>
       </c>
-      <c r="S18" s="3">
+      <c r="W18" s="3">
         <v>149.69999999999999</v>
       </c>
-      <c r="T18" s="3">
+      <c r="X18" s="3">
         <v>157.19999999999999</v>
       </c>
-      <c r="U18" s="3">
+      <c r="Y18" s="3">
         <v>146.30000000000001</v>
       </c>
-      <c r="V18" s="3">
+      <c r="Z18" s="3">
         <v>144.6</v>
       </c>
-      <c r="W18" s="12"/>
-      <c r="X18" s="12"/>
-    </row>
-    <row r="19" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AA18" s="12">
+        <v>142.5</v>
+      </c>
+      <c r="AB18" s="12"/>
+    </row>
+    <row r="19" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="10"/>
       <c r="B19" s="1" t="s">
         <v>72</v>
@@ -2732,41 +2886,50 @@
       <c r="M19" s="13">
         <v>2406</v>
       </c>
-      <c r="N19" s="13"/>
-      <c r="O19" s="13"/>
-      <c r="P19" s="13">
+      <c r="N19" s="13">
+        <f t="shared" si="2"/>
+        <v>1978.6999999999998</v>
+      </c>
+      <c r="O19" s="13">
+        <v>1959.8</v>
+      </c>
+      <c r="P19" s="13"/>
+      <c r="Q19" s="13"/>
+      <c r="R19" s="13"/>
+      <c r="S19" s="13"/>
+      <c r="T19" s="13">
         <v>6313</v>
       </c>
-      <c r="Q19" s="13">
+      <c r="U19" s="13">
         <v>6159.8</v>
       </c>
-      <c r="R19" s="13">
+      <c r="V19" s="13">
         <v>4400.8</v>
       </c>
-      <c r="S19" s="13">
+      <c r="W19" s="13">
         <v>6218.5</v>
       </c>
-      <c r="T19" s="13">
+      <c r="X19" s="13">
         <v>6443.6</v>
       </c>
-      <c r="U19" s="13">
+      <c r="Y19" s="13">
         <v>6631.4</v>
       </c>
-      <c r="V19" s="13">
+      <c r="Z19" s="13">
         <v>7079</v>
       </c>
-      <c r="W19" s="13">
+      <c r="AA19" s="13">
         <v>8114.5</v>
       </c>
-      <c r="X19" s="13"/>
-      <c r="Y19" s="13"/>
-      <c r="Z19" s="13"/>
-      <c r="AA19" s="1"/>
-      <c r="AB19" s="1"/>
-      <c r="AC19" s="1"/>
-      <c r="AD19" s="1"/>
-    </row>
-    <row r="20" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AB19" s="13"/>
+      <c r="AC19" s="13"/>
+      <c r="AD19" s="13"/>
+      <c r="AE19" s="1"/>
+      <c r="AF19" s="1"/>
+      <c r="AG19" s="1"/>
+      <c r="AH19" s="1"/>
+    </row>
+    <row r="20" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
         <v>73</v>
       </c>
@@ -2799,46 +2962,55 @@
       <c r="M20" s="12">
         <v>724.3</v>
       </c>
-      <c r="N20" s="12"/>
-      <c r="O20" s="12"/>
-      <c r="P20" s="12">
+      <c r="N20" s="12">
+        <f t="shared" si="2"/>
+        <v>599.90000000000032</v>
+      </c>
+      <c r="O20" s="12">
+        <v>515.6</v>
+      </c>
+      <c r="P20" s="12"/>
+      <c r="Q20" s="12"/>
+      <c r="R20" s="12"/>
+      <c r="S20" s="12"/>
+      <c r="T20" s="12">
         <v>2427</v>
       </c>
-      <c r="Q20" s="12">
+      <c r="U20" s="12">
         <v>2506.5</v>
       </c>
-      <c r="R20" s="12">
+      <c r="V20" s="12">
         <v>1539.4</v>
       </c>
-      <c r="S20" s="12">
+      <c r="W20" s="12">
         <v>2071</v>
       </c>
-      <c r="T20" s="12">
+      <c r="X20" s="12">
         <v>2277.8000000000002</v>
       </c>
-      <c r="U20" s="12">
+      <c r="Y20" s="12">
         <v>2199.6</v>
       </c>
-      <c r="V20" s="12">
+      <c r="Z20" s="12">
         <v>2226.1</v>
       </c>
-      <c r="W20" s="12">
+      <c r="AA20" s="12">
         <v>2445.3000000000002</v>
       </c>
-      <c r="X20" s="12"/>
-      <c r="Y20" s="12"/>
-      <c r="Z20" s="12"/>
-    </row>
-    <row r="21" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AB20" s="12"/>
+      <c r="AC20" s="12"/>
+      <c r="AD20" s="12"/>
+    </row>
+    <row r="21" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
         <v>74</v>
       </c>
       <c r="C21" s="12">
-        <f t="shared" ref="C21:D21" si="2">+C19-C20</f>
+        <f t="shared" ref="C21:D21" si="3">+C19-C20</f>
         <v>0</v>
       </c>
       <c r="D21" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E21" s="12">
@@ -2846,76 +3018,86 @@
         <v>1286</v>
       </c>
       <c r="F21" s="12">
-        <f t="shared" ref="F21:M21" si="3">+F19-F20</f>
+        <f t="shared" ref="F21:O21" si="4">+F19-F20</f>
         <v>1043.7</v>
       </c>
       <c r="G21" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1065.8000000000002</v>
       </c>
       <c r="H21" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1155.7</v>
       </c>
       <c r="I21" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1466.1</v>
       </c>
       <c r="J21" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1165.3</v>
       </c>
       <c r="K21" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1242.3</v>
       </c>
       <c r="L21" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1366.4</v>
       </c>
       <c r="M21" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1681.7</v>
       </c>
-      <c r="N21" s="12"/>
-      <c r="O21" s="12"/>
-      <c r="P21" s="12">
-        <f t="shared" ref="P21:T21" si="4">P19-P20</f>
+      <c r="N21" s="12">
+        <f t="shared" si="4"/>
+        <v>1378.7999999999995</v>
+      </c>
+      <c r="O21" s="12">
+        <f t="shared" si="4"/>
+        <v>1444.1999999999998</v>
+      </c>
+      <c r="P21" s="12"/>
+      <c r="Q21" s="12"/>
+      <c r="R21" s="12"/>
+      <c r="S21" s="12"/>
+      <c r="T21" s="12">
+        <f t="shared" ref="T21:X21" si="5">T19-T20</f>
         <v>3886</v>
       </c>
-      <c r="Q21" s="12">
-        <f t="shared" si="4"/>
+      <c r="U21" s="12">
+        <f t="shared" si="5"/>
         <v>3653.3</v>
       </c>
-      <c r="R21" s="12">
-        <f t="shared" si="4"/>
+      <c r="V21" s="12">
+        <f t="shared" si="5"/>
         <v>2861.4</v>
       </c>
-      <c r="S21" s="12">
-        <f t="shared" si="4"/>
+      <c r="W21" s="12">
+        <f t="shared" si="5"/>
         <v>4147.5</v>
       </c>
-      <c r="T21" s="12">
-        <f t="shared" si="4"/>
+      <c r="X21" s="12">
+        <f t="shared" si="5"/>
         <v>4165.8</v>
       </c>
-      <c r="U21" s="12">
-        <f>U19-U20</f>
+      <c r="Y21" s="12">
+        <f>Y19-Y20</f>
         <v>4431.7999999999993</v>
       </c>
-      <c r="V21" s="12">
-        <f>V19-V20</f>
+      <c r="Z21" s="12">
+        <f>Z19-Z20</f>
         <v>4852.8999999999996</v>
       </c>
-      <c r="W21" s="12">
-        <f>W19-W20</f>
+      <c r="AA21" s="12">
+        <f>AA19-AA20</f>
         <v>5669.2</v>
       </c>
-      <c r="X21" s="12"/>
-      <c r="Y21" s="12"/>
-      <c r="Z21" s="12"/>
-    </row>
-    <row r="22" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AB21" s="12"/>
+      <c r="AC21" s="12"/>
+      <c r="AD21" s="12"/>
+    </row>
+    <row r="22" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
         <v>75</v>
       </c>
@@ -2948,37 +3130,46 @@
       <c r="M22" s="12">
         <v>1178.5999999999999</v>
       </c>
-      <c r="N22" s="12"/>
-      <c r="O22" s="12"/>
-      <c r="P22" s="12">
+      <c r="N22" s="12">
+        <f t="shared" si="2"/>
+        <v>1160.4999999999995</v>
+      </c>
+      <c r="O22" s="12">
+        <v>1077</v>
+      </c>
+      <c r="P22" s="12"/>
+      <c r="Q22" s="12"/>
+      <c r="R22" s="12"/>
+      <c r="S22" s="12"/>
+      <c r="T22" s="12">
         <v>3168.3</v>
       </c>
-      <c r="Q22" s="12">
+      <c r="U22" s="12">
         <v>3237.5</v>
       </c>
-      <c r="R22" s="12">
+      <c r="V22" s="12">
         <v>2638.5</v>
       </c>
-      <c r="S22" s="12">
+      <c r="W22" s="12">
         <v>3305.6</v>
       </c>
-      <c r="T22" s="12">
+      <c r="X22" s="12">
         <v>3408.9</v>
       </c>
-      <c r="U22" s="12">
+      <c r="Y22" s="12">
         <v>3600.5</v>
       </c>
-      <c r="V22" s="12">
+      <c r="Z22" s="12">
         <v>3863</v>
       </c>
-      <c r="W22" s="12">
+      <c r="AA22" s="12">
         <v>4371.8999999999996</v>
       </c>
-      <c r="X22" s="12"/>
-      <c r="Y22" s="12"/>
-      <c r="Z22" s="12"/>
-    </row>
-    <row r="23" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AB22" s="12"/>
+      <c r="AC22" s="12"/>
+      <c r="AD22" s="12"/>
+    </row>
+    <row r="23" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
         <v>76</v>
       </c>
@@ -3011,37 +3202,46 @@
       <c r="M23" s="12">
         <v>0</v>
       </c>
-      <c r="N23" s="12"/>
-      <c r="O23" s="12"/>
-      <c r="P23" s="12">
+      <c r="N23" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O23" s="12">
+        <v>0</v>
+      </c>
+      <c r="P23" s="12"/>
+      <c r="Q23" s="12"/>
+      <c r="R23" s="12"/>
+      <c r="S23" s="12"/>
+      <c r="T23" s="12">
         <v>25.8</v>
       </c>
-      <c r="Q23" s="12">
+      <c r="U23" s="12">
         <v>31.6</v>
       </c>
-      <c r="R23" s="12">
+      <c r="V23" s="12">
         <v>96</v>
       </c>
-      <c r="S23" s="12">
+      <c r="W23" s="12">
         <v>21.3</v>
       </c>
-      <c r="T23" s="12">
+      <c r="X23" s="12">
         <v>9.6999999999999993</v>
       </c>
-      <c r="U23" s="12">
-        <v>0</v>
-      </c>
-      <c r="V23" s="12">
+      <c r="Y23" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="12">
         <v>0.8</v>
       </c>
-      <c r="W23" s="12">
-        <v>0</v>
-      </c>
-      <c r="X23" s="12"/>
-      <c r="Y23" s="12"/>
-      <c r="Z23" s="12"/>
-    </row>
-    <row r="24" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AA23" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="12"/>
+      <c r="AC23" s="12"/>
+      <c r="AD23" s="12"/>
+    </row>
+    <row r="24" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
         <v>77</v>
       </c>
@@ -3074,156 +3274,175 @@
       <c r="M24" s="12">
         <v>31.8</v>
       </c>
-      <c r="N24" s="12"/>
-      <c r="O24" s="12"/>
-      <c r="P24" s="12">
+      <c r="N24" s="12">
+        <f t="shared" si="2"/>
+        <v>29.700000000000003</v>
+      </c>
+      <c r="O24" s="12">
+        <v>24.8</v>
+      </c>
+      <c r="P24" s="12"/>
+      <c r="Q24" s="12"/>
+      <c r="R24" s="12"/>
+      <c r="S24" s="12"/>
+      <c r="T24" s="12">
         <v>130.1</v>
       </c>
-      <c r="Q24" s="12">
+      <c r="U24" s="12">
         <v>67.2</v>
       </c>
-      <c r="R24" s="12">
+      <c r="V24" s="12">
         <v>170.5</v>
       </c>
-      <c r="S24" s="12">
+      <c r="W24" s="12">
         <v>22.2</v>
       </c>
-      <c r="T24" s="12">
+      <c r="X24" s="12">
         <v>43</v>
       </c>
-      <c r="U24" s="12">
+      <c r="Y24" s="12">
         <v>74.900000000000006</v>
       </c>
-      <c r="V24" s="12">
+      <c r="Z24" s="12">
         <v>57</v>
       </c>
-      <c r="W24" s="12">
+      <c r="AA24" s="12">
         <v>118.1</v>
       </c>
-      <c r="X24" s="12"/>
-      <c r="Y24" s="12"/>
-      <c r="Z24" s="12"/>
-    </row>
-    <row r="25" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AB24" s="12"/>
+      <c r="AC24" s="12"/>
+      <c r="AD24" s="12"/>
+    </row>
+    <row r="25" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
         <v>78</v>
       </c>
       <c r="C25" s="12">
-        <f t="shared" ref="C25:M25" si="5">SUM(C22:C24)</f>
+        <f t="shared" ref="C25:O25" si="6">SUM(C22:C24)</f>
         <v>0</v>
       </c>
       <c r="D25" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E25" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>968.30000000000007</v>
       </c>
       <c r="F25" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>935.9</v>
       </c>
       <c r="G25" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>857.3</v>
       </c>
       <c r="H25" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>976.8</v>
       </c>
       <c r="I25" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1076.4000000000001</v>
       </c>
       <c r="J25" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1010.3</v>
       </c>
       <c r="K25" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>968.69999999999993</v>
       </c>
       <c r="L25" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1120.7</v>
       </c>
       <c r="M25" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1210.3999999999999</v>
       </c>
-      <c r="N25" s="12"/>
-      <c r="O25" s="12"/>
-      <c r="P25" s="12">
-        <f t="shared" ref="P25:T25" si="6">SUM(P22:P24)</f>
+      <c r="N25" s="12">
+        <f t="shared" si="6"/>
+        <v>1190.1999999999996</v>
+      </c>
+      <c r="O25" s="12">
+        <f t="shared" si="6"/>
+        <v>1101.8</v>
+      </c>
+      <c r="P25" s="12"/>
+      <c r="Q25" s="12"/>
+      <c r="R25" s="12"/>
+      <c r="S25" s="12"/>
+      <c r="T25" s="12">
+        <f t="shared" ref="T25:X25" si="7">SUM(T22:T24)</f>
         <v>3324.2000000000003</v>
       </c>
-      <c r="Q25" s="12">
-        <f t="shared" si="6"/>
+      <c r="U25" s="12">
+        <f t="shared" si="7"/>
         <v>3336.2999999999997</v>
       </c>
-      <c r="R25" s="12">
-        <f t="shared" si="6"/>
+      <c r="V25" s="12">
+        <f t="shared" si="7"/>
         <v>2905</v>
       </c>
-      <c r="S25" s="12">
-        <f t="shared" si="6"/>
+      <c r="W25" s="12">
+        <f t="shared" si="7"/>
         <v>3349.1</v>
       </c>
-      <c r="T25" s="12">
-        <f t="shared" si="6"/>
+      <c r="X25" s="12">
+        <f t="shared" si="7"/>
         <v>3461.6</v>
       </c>
-      <c r="U25" s="12">
-        <f>SUM(U22:U24)</f>
+      <c r="Y25" s="12">
+        <f>SUM(Y22:Y24)</f>
         <v>3675.4</v>
       </c>
-      <c r="V25" s="12">
-        <f>SUM(V22:V24)</f>
+      <c r="Z25" s="12">
+        <f>SUM(Z22:Z24)</f>
         <v>3920.8</v>
       </c>
-      <c r="W25" s="12">
-        <f>SUM(W22:W24)</f>
+      <c r="AA25" s="12">
+        <f>SUM(AA22:AA24)</f>
         <v>4490</v>
       </c>
-      <c r="X25" s="12"/>
-      <c r="Y25" s="12"/>
-      <c r="Z25" s="12"/>
-    </row>
-    <row r="26" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AB25" s="12"/>
+      <c r="AC25" s="12"/>
+      <c r="AD25" s="12"/>
+    </row>
+    <row r="26" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C26" s="12">
-        <f t="shared" ref="C26:J26" si="7">C21-C25</f>
+        <f t="shared" ref="C26:J26" si="8">C21-C25</f>
         <v>0</v>
       </c>
       <c r="D26" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E26" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>317.69999999999993</v>
       </c>
       <c r="F26" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>107.80000000000007</v>
       </c>
       <c r="G26" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>208.50000000000023</v>
       </c>
       <c r="H26" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>178.90000000000009</v>
       </c>
       <c r="I26" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>389.69999999999982</v>
       </c>
       <c r="J26" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>155</v>
       </c>
       <c r="K26" s="12">
@@ -3236,45 +3455,55 @@
         <f>+M21-M25</f>
         <v>471.30000000000018</v>
       </c>
-      <c r="N26" s="12"/>
-      <c r="O26" s="12"/>
-      <c r="P26" s="12">
-        <f t="shared" ref="P26:T26" si="8">P21-P25</f>
+      <c r="N26" s="12">
+        <f>+N21-N25</f>
+        <v>188.59999999999991</v>
+      </c>
+      <c r="O26" s="12">
+        <f>+O21-O25</f>
+        <v>342.39999999999986</v>
+      </c>
+      <c r="P26" s="12"/>
+      <c r="Q26" s="12"/>
+      <c r="R26" s="12"/>
+      <c r="S26" s="12"/>
+      <c r="T26" s="12">
+        <f t="shared" ref="T26:X26" si="9">T21-T25</f>
         <v>561.79999999999973</v>
       </c>
-      <c r="Q26" s="12">
-        <f t="shared" si="8"/>
+      <c r="U26" s="12">
+        <f t="shared" si="9"/>
         <v>317.00000000000045</v>
       </c>
-      <c r="R26" s="12">
-        <f t="shared" si="8"/>
+      <c r="V26" s="12">
+        <f t="shared" si="9"/>
         <v>-43.599999999999909</v>
       </c>
-      <c r="S26" s="12">
-        <f t="shared" si="8"/>
+      <c r="W26" s="12">
+        <f t="shared" si="9"/>
         <v>798.40000000000009</v>
       </c>
-      <c r="T26" s="12">
-        <f t="shared" si="8"/>
+      <c r="X26" s="12">
+        <f t="shared" si="9"/>
         <v>704.20000000000027</v>
       </c>
-      <c r="U26" s="12">
-        <f>U21-U25</f>
+      <c r="Y26" s="12">
+        <f>Y21-Y25</f>
         <v>756.39999999999918</v>
       </c>
-      <c r="V26" s="12">
-        <f>V21-V25</f>
+      <c r="Z26" s="12">
+        <f>Z21-Z25</f>
         <v>932.09999999999945</v>
       </c>
-      <c r="W26" s="12">
-        <f>W21-W25</f>
+      <c r="AA26" s="12">
+        <f>AA21-AA25</f>
         <v>1179.1999999999998</v>
       </c>
-      <c r="X26" s="12"/>
-      <c r="Y26" s="12"/>
-      <c r="Z26" s="12"/>
-    </row>
-    <row r="27" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AB26" s="12"/>
+      <c r="AC26" s="12"/>
+      <c r="AD26" s="12"/>
+    </row>
+    <row r="27" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
         <v>80</v>
       </c>
@@ -3307,37 +3536,46 @@
       <c r="M27" s="12">
         <v>13.3</v>
       </c>
-      <c r="N27" s="12"/>
-      <c r="O27" s="12"/>
-      <c r="P27" s="12">
+      <c r="N27" s="12">
+        <f t="shared" ref="N27:N31" si="10">+AA27-SUM(K27:M27)</f>
+        <v>13.5</v>
+      </c>
+      <c r="O27" s="12">
+        <v>13</v>
+      </c>
+      <c r="P27" s="12"/>
+      <c r="Q27" s="12"/>
+      <c r="R27" s="12"/>
+      <c r="S27" s="12"/>
+      <c r="T27" s="12">
         <v>20.7</v>
       </c>
-      <c r="Q27" s="12">
+      <c r="U27" s="12">
         <v>17.600000000000001</v>
       </c>
-      <c r="R27" s="12">
+      <c r="V27" s="12">
         <v>48.5</v>
       </c>
-      <c r="S27" s="12">
+      <c r="W27" s="12">
         <v>54</v>
       </c>
-      <c r="T27" s="12">
+      <c r="X27" s="12">
         <v>40.4</v>
       </c>
-      <c r="U27" s="12">
+      <c r="Y27" s="12">
         <v>42.2</v>
       </c>
-      <c r="V27" s="12">
+      <c r="Z27" s="12">
         <v>44.1</v>
       </c>
-      <c r="W27" s="12">
+      <c r="AA27" s="12">
         <v>54.2</v>
       </c>
-      <c r="X27" s="12"/>
-      <c r="Y27" s="12"/>
-      <c r="Z27" s="12"/>
-    </row>
-    <row r="28" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AB27" s="12"/>
+      <c r="AC27" s="12"/>
+      <c r="AD27" s="12"/>
+    </row>
+    <row r="28" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
         <v>81</v>
       </c>
@@ -3370,37 +3608,46 @@
       <c r="M28" s="12">
         <v>11.9</v>
       </c>
-      <c r="N28" s="12"/>
-      <c r="O28" s="12"/>
-      <c r="P28" s="12">
+      <c r="N28" s="12">
+        <f t="shared" si="10"/>
+        <v>12.400000000000006</v>
+      </c>
+      <c r="O28" s="12">
+        <v>11.6</v>
+      </c>
+      <c r="P28" s="12"/>
+      <c r="Q28" s="12"/>
+      <c r="R28" s="12"/>
+      <c r="S28" s="12"/>
+      <c r="T28" s="12">
         <v>40.799999999999997</v>
       </c>
-      <c r="Q28" s="12">
+      <c r="U28" s="12">
         <v>34.4</v>
       </c>
-      <c r="R28" s="12">
+      <c r="V28" s="12">
         <v>9.6999999999999993</v>
       </c>
-      <c r="S28" s="12">
+      <c r="W28" s="12">
         <v>5.5</v>
       </c>
-      <c r="T28" s="12">
+      <c r="X28" s="12">
         <v>32.200000000000003</v>
       </c>
-      <c r="U28" s="12">
+      <c r="Y28" s="12">
         <v>73</v>
       </c>
-      <c r="V28" s="12">
+      <c r="Z28" s="12">
         <v>74</v>
       </c>
-      <c r="W28" s="12">
+      <c r="AA28" s="12">
         <v>53.7</v>
       </c>
-      <c r="X28" s="12"/>
-      <c r="Y28" s="12"/>
-      <c r="Z28" s="12"/>
-    </row>
-    <row r="29" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AB28" s="12"/>
+      <c r="AC28" s="12"/>
+      <c r="AD28" s="12"/>
+    </row>
+    <row r="29" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
         <v>82</v>
       </c>
@@ -3433,123 +3680,142 @@
       <c r="M29" s="12">
         <v>-6.1</v>
       </c>
-      <c r="N29" s="12"/>
-      <c r="O29" s="12"/>
-      <c r="P29" s="12">
+      <c r="N29" s="12">
+        <f t="shared" si="10"/>
+        <v>5.6</v>
+      </c>
+      <c r="O29" s="12">
+        <v>1.2</v>
+      </c>
+      <c r="P29" s="12"/>
+      <c r="Q29" s="12"/>
+      <c r="R29" s="12"/>
+      <c r="S29" s="12"/>
+      <c r="T29" s="12">
         <v>0.6</v>
       </c>
-      <c r="Q29" s="12">
+      <c r="U29" s="12">
         <v>-7.4</v>
       </c>
-      <c r="R29" s="12">
+      <c r="V29" s="12">
         <v>7.6</v>
       </c>
-      <c r="S29" s="12">
+      <c r="W29" s="12">
         <v>4.7</v>
       </c>
-      <c r="T29" s="12">
+      <c r="X29" s="12">
         <v>-4.0999999999999996</v>
       </c>
-      <c r="U29" s="12">
+      <c r="Y29" s="12">
         <v>-9.8000000000000007</v>
       </c>
-      <c r="V29" s="12">
+      <c r="Z29" s="12">
         <v>-11.3</v>
       </c>
-      <c r="W29" s="12">
+      <c r="AA29" s="12">
         <v>-1</v>
       </c>
-      <c r="X29" s="12"/>
-      <c r="Y29" s="12"/>
-      <c r="Z29" s="12"/>
-    </row>
-    <row r="30" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AB29" s="12"/>
+      <c r="AC29" s="12"/>
+      <c r="AD29" s="12"/>
+    </row>
+    <row r="30" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C30" s="12">
-        <f t="shared" ref="C30:M30" si="9">C26-C27+C28+C29</f>
+        <f t="shared" ref="C30:O30" si="11">C26-C27+C28+C29</f>
         <v>0</v>
       </c>
       <c r="D30" s="12">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="E30" s="12">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>329.7999999999999</v>
       </c>
       <c r="F30" s="12">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>111.50000000000007</v>
       </c>
       <c r="G30" s="12">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>216.60000000000022</v>
       </c>
       <c r="H30" s="12">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>188.10000000000008</v>
       </c>
       <c r="I30" s="12">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>383.69999999999982</v>
       </c>
       <c r="J30" s="12">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>162.30000000000001</v>
       </c>
       <c r="K30" s="12">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>278.00000000000006</v>
       </c>
       <c r="L30" s="12">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>242.79999999999998</v>
       </c>
       <c r="M30" s="12">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>463.80000000000013</v>
       </c>
-      <c r="N30" s="12"/>
-      <c r="O30" s="12"/>
-      <c r="P30" s="12">
-        <f t="shared" ref="P30:T30" si="10">P26-P27+P28+P29</f>
+      <c r="N30" s="12">
+        <f t="shared" si="11"/>
+        <v>193.09999999999991</v>
+      </c>
+      <c r="O30" s="12">
+        <f t="shared" si="11"/>
+        <v>342.19999999999987</v>
+      </c>
+      <c r="P30" s="12"/>
+      <c r="Q30" s="12"/>
+      <c r="R30" s="12"/>
+      <c r="S30" s="12"/>
+      <c r="T30" s="12">
+        <f t="shared" ref="T30:X30" si="12">T26-T27+T28+T29</f>
         <v>582.49999999999966</v>
       </c>
-      <c r="Q30" s="12">
-        <f t="shared" si="10"/>
+      <c r="U30" s="12">
+        <f t="shared" si="12"/>
         <v>326.40000000000043</v>
       </c>
-      <c r="R30" s="12">
-        <f t="shared" si="10"/>
+      <c r="V30" s="12">
+        <f t="shared" si="12"/>
         <v>-74.799999999999912</v>
       </c>
-      <c r="S30" s="12">
-        <f t="shared" si="10"/>
+      <c r="W30" s="12">
+        <f t="shared" si="12"/>
         <v>754.60000000000014</v>
       </c>
-      <c r="T30" s="12">
-        <f t="shared" si="10"/>
+      <c r="X30" s="12">
+        <f t="shared" si="12"/>
         <v>691.90000000000032</v>
       </c>
-      <c r="U30" s="12">
-        <f>U26-U27+U28+U29</f>
+      <c r="Y30" s="12">
+        <f>Y26-Y27+Y28+Y29</f>
         <v>777.39999999999918</v>
       </c>
-      <c r="V30" s="12">
-        <f>V26-V27+V28+V29</f>
+      <c r="Z30" s="12">
+        <f>Z26-Z27+Z28+Z29</f>
         <v>950.69999999999948</v>
       </c>
-      <c r="W30" s="12">
-        <f>W26-W27+W28+W29</f>
+      <c r="AA30" s="12">
+        <f>AA26-AA27+AA28+AA29</f>
         <v>1177.6999999999998</v>
       </c>
-      <c r="X30" s="12"/>
-      <c r="Y30" s="12"/>
-      <c r="Z30" s="12"/>
-    </row>
-    <row r="31" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AB30" s="12"/>
+      <c r="AC30" s="12"/>
+      <c r="AD30" s="12"/>
+    </row>
+    <row r="31" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B31" s="2" t="s">
         <v>84</v>
       </c>
@@ -3582,123 +3848,142 @@
       <c r="M31" s="12">
         <v>102.2</v>
       </c>
-      <c r="N31" s="12"/>
-      <c r="O31" s="12"/>
-      <c r="P31" s="12">
+      <c r="N31" s="12">
+        <f t="shared" si="10"/>
+        <v>41.499999999999972</v>
+      </c>
+      <c r="O31" s="12">
+        <v>80</v>
+      </c>
+      <c r="P31" s="12"/>
+      <c r="Q31" s="12"/>
+      <c r="R31" s="12"/>
+      <c r="S31" s="12"/>
+      <c r="T31" s="12">
         <v>151.6</v>
       </c>
-      <c r="Q31" s="12">
+      <c r="U31" s="12">
         <v>-57.9</v>
       </c>
-      <c r="R31" s="12">
+      <c r="V31" s="12">
         <v>46.3</v>
       </c>
-      <c r="S31" s="12">
+      <c r="W31" s="12">
         <v>154.5</v>
       </c>
-      <c r="T31" s="12">
+      <c r="X31" s="12">
         <v>169.2</v>
       </c>
-      <c r="U31" s="12">
+      <c r="Y31" s="12">
         <v>131.1</v>
       </c>
-      <c r="V31" s="12">
+      <c r="Z31" s="12">
         <v>207.8</v>
       </c>
-      <c r="W31" s="12">
+      <c r="AA31" s="12">
         <v>236.6</v>
       </c>
-      <c r="X31" s="12"/>
-      <c r="Y31" s="12"/>
-      <c r="Z31" s="12"/>
-    </row>
-    <row r="32" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AB31" s="12"/>
+      <c r="AC31" s="12"/>
+      <c r="AD31" s="12"/>
+    </row>
+    <row r="32" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B32" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C32" s="12">
-        <f t="shared" ref="C32:M32" si="11">C30-C31</f>
+        <f t="shared" ref="C32:O32" si="13">C30-C31</f>
         <v>0</v>
       </c>
       <c r="D32" s="12">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="E32" s="12">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>276.59999999999991</v>
       </c>
       <c r="F32" s="12">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>90.700000000000074</v>
       </c>
       <c r="G32" s="12">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>168.60000000000022</v>
       </c>
       <c r="H32" s="12">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>147.90000000000009</v>
       </c>
       <c r="I32" s="12">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>297.39999999999981</v>
       </c>
       <c r="J32" s="12">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>129</v>
       </c>
       <c r="K32" s="12">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>220.40000000000006</v>
       </c>
       <c r="L32" s="12">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>207.5</v>
       </c>
       <c r="M32" s="12">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>361.60000000000014</v>
       </c>
-      <c r="N32" s="12"/>
-      <c r="O32" s="12"/>
-      <c r="P32" s="12">
-        <f t="shared" ref="P32:T32" si="12">P30-P31</f>
+      <c r="N32" s="12">
+        <f t="shared" si="13"/>
+        <v>151.59999999999994</v>
+      </c>
+      <c r="O32" s="12">
+        <f t="shared" si="13"/>
+        <v>262.19999999999987</v>
+      </c>
+      <c r="P32" s="12"/>
+      <c r="Q32" s="12"/>
+      <c r="R32" s="12"/>
+      <c r="S32" s="12"/>
+      <c r="T32" s="12">
+        <f t="shared" ref="T32:X32" si="14">T30-T31</f>
         <v>430.89999999999964</v>
       </c>
-      <c r="Q32" s="12">
-        <f t="shared" si="12"/>
+      <c r="U32" s="12">
+        <f t="shared" si="14"/>
         <v>384.30000000000041</v>
       </c>
-      <c r="R32" s="12">
-        <f t="shared" si="12"/>
+      <c r="V32" s="12">
+        <f t="shared" si="14"/>
         <v>-121.09999999999991</v>
       </c>
-      <c r="S32" s="12">
-        <f t="shared" si="12"/>
+      <c r="W32" s="12">
+        <f t="shared" si="14"/>
         <v>600.10000000000014</v>
       </c>
-      <c r="T32" s="12">
-        <f t="shared" si="12"/>
+      <c r="X32" s="12">
+        <f t="shared" si="14"/>
         <v>522.70000000000027</v>
       </c>
-      <c r="U32" s="12">
-        <f>U30-U31</f>
+      <c r="Y32" s="12">
+        <f>Y30-Y31</f>
         <v>646.29999999999916</v>
       </c>
-      <c r="V32" s="12">
-        <f>V30-V31</f>
+      <c r="Z32" s="12">
+        <f>Z30-Z31</f>
         <v>742.89999999999941</v>
       </c>
-      <c r="W32" s="12">
-        <f>W30-W31</f>
+      <c r="AA32" s="12">
+        <f>AA30-AA31</f>
         <v>941.0999999999998</v>
       </c>
-      <c r="X32" s="12"/>
-      <c r="Y32" s="12"/>
-      <c r="Z32" s="12"/>
-    </row>
-    <row r="33" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AB32" s="12"/>
+      <c r="AC32" s="12"/>
+      <c r="AD32" s="12"/>
+    </row>
+    <row r="33" spans="2:30" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C33" s="12"/>
       <c r="D33" s="12"/>
       <c r="E33" s="12"/>
@@ -3723,33 +4008,37 @@
       <c r="X33" s="12"/>
       <c r="Y33" s="12"/>
       <c r="Z33" s="12"/>
-    </row>
-    <row r="34" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AA33" s="12"/>
+      <c r="AB33" s="12"/>
+      <c r="AC33" s="12"/>
+      <c r="AD33" s="12"/>
+    </row>
+    <row r="34" spans="2:30" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B34" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C34" s="14" t="e">
-        <f t="shared" ref="C34:H34" si="13">+C32/C35</f>
+        <f t="shared" ref="C34:H34" si="15">+C32/C35</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D34" s="14" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E34" s="14">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>4.2553846153846138</v>
       </c>
       <c r="F34" s="14" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G34" s="14">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>2.6677215189873453</v>
       </c>
       <c r="H34" s="14">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>2.3626198083067105</v>
       </c>
       <c r="I34" s="14">
@@ -3757,60 +4046,70 @@
         <v>4.7583999999999973</v>
       </c>
       <c r="J34" s="14" t="e">
-        <f t="shared" ref="J34:M34" si="14">+J32/J35</f>
+        <f t="shared" ref="J34:O34" si="16">+J32/J35</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K34" s="14">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>3.6131147540983615</v>
       </c>
       <c r="L34" s="14">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>3.3960720130932898</v>
       </c>
       <c r="M34" s="14">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>5.9181669394435374</v>
       </c>
-      <c r="N34" s="14"/>
-      <c r="O34" s="12"/>
-      <c r="P34" s="12">
-        <f t="shared" ref="P34:W34" si="15">P32/P35</f>
+      <c r="N34" s="14">
+        <f t="shared" si="16"/>
+        <v>2.481178396072012</v>
+      </c>
+      <c r="O34" s="14">
+        <f t="shared" si="16"/>
+        <v>4.362728785357735</v>
+      </c>
+      <c r="P34" s="14"/>
+      <c r="Q34" s="14"/>
+      <c r="R34" s="14"/>
+      <c r="S34" s="12"/>
+      <c r="T34" s="12">
+        <f t="shared" ref="T34:AA34" si="17">T32/T35</f>
         <v>5.5191935752436772</v>
       </c>
-      <c r="Q34" s="12">
-        <f t="shared" si="15"/>
+      <c r="U34" s="12">
+        <f t="shared" si="17"/>
         <v>5.2892357240183383</v>
       </c>
-      <c r="R34" s="12">
-        <f t="shared" si="15"/>
+      <c r="V34" s="12">
+        <f t="shared" si="17"/>
         <v>-1.6559325046833751</v>
       </c>
-      <c r="S34" s="12">
-        <f t="shared" si="15"/>
+      <c r="W34" s="12">
+        <f t="shared" si="17"/>
         <v>8.5636817695326446</v>
       </c>
-      <c r="T34" s="12">
-        <f t="shared" si="15"/>
+      <c r="X34" s="12">
+        <f t="shared" si="17"/>
         <v>7.9918659409210493</v>
       </c>
-      <c r="U34" s="12">
-        <f t="shared" si="15"/>
+      <c r="Y34" s="12">
+        <f t="shared" si="17"/>
         <v>10.669544543672828</v>
       </c>
-      <c r="V34" s="12">
-        <f t="shared" si="15"/>
+      <c r="Z34" s="12">
+        <f t="shared" si="17"/>
         <v>11.86741214057507</v>
       </c>
-      <c r="W34" s="12">
-        <f t="shared" si="15"/>
+      <c r="AA34" s="12">
+        <f t="shared" si="17"/>
         <v>15.427868852459014</v>
       </c>
-      <c r="X34" s="12"/>
-      <c r="Y34" s="12"/>
-      <c r="Z34" s="12"/>
-    </row>
-    <row r="35" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AB34" s="12"/>
+      <c r="AC34" s="12"/>
+      <c r="AD34" s="12"/>
+    </row>
+    <row r="35" spans="2:30" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B35" s="2" t="s">
         <v>86</v>
       </c>
@@ -3839,42 +4138,50 @@
       <c r="M35" s="12">
         <v>61.1</v>
       </c>
-      <c r="N35" s="12"/>
-      <c r="O35" s="12"/>
-      <c r="P35" s="12">
+      <c r="N35" s="12">
+        <v>61.1</v>
+      </c>
+      <c r="O35" s="12">
+        <v>60.1</v>
+      </c>
+      <c r="P35" s="12"/>
+      <c r="Q35" s="12"/>
+      <c r="R35" s="12"/>
+      <c r="S35" s="12"/>
+      <c r="T35" s="12">
         <f>52.192+25.881</f>
         <v>78.073000000000008</v>
       </c>
-      <c r="Q35" s="12">
+      <c r="U35" s="12">
         <f>47.777+24.88^1</f>
         <v>72.656999999999996</v>
       </c>
-      <c r="R35" s="12">
+      <c r="V35" s="12">
         <f>48.25+24.881</f>
         <v>73.131</v>
       </c>
-      <c r="S35" s="12">
+      <c r="W35" s="12">
         <f>45.194+24.881</f>
         <v>70.075000000000003</v>
       </c>
-      <c r="T35" s="12">
+      <c r="X35" s="12">
         <f>40.523+24.881</f>
         <v>65.403999999999996</v>
       </c>
-      <c r="U35" s="12">
+      <c r="Y35" s="12">
         <v>60.574281999999997</v>
       </c>
-      <c r="V35" s="12">
+      <c r="Z35" s="12">
         <v>62.6</v>
       </c>
-      <c r="W35" s="12">
+      <c r="AA35" s="12">
         <v>61</v>
       </c>
-      <c r="X35" s="12"/>
-      <c r="Y35" s="12"/>
-      <c r="Z35" s="12"/>
-    </row>
-    <row r="36" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AB35" s="12"/>
+      <c r="AC35" s="12"/>
+      <c r="AD35" s="12"/>
+    </row>
+    <row r="36" spans="2:30" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C36" s="12"/>
       <c r="D36" s="12"/>
       <c r="E36" s="12"/>
@@ -3899,8 +4206,12 @@
       <c r="X36" s="12"/>
       <c r="Y36" s="12"/>
       <c r="Z36" s="12"/>
-    </row>
-    <row r="37" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AA36" s="12"/>
+      <c r="AB36" s="12"/>
+      <c r="AC36" s="12"/>
+      <c r="AD36" s="12"/>
+    </row>
+    <row r="37" spans="2:30" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B37" s="2" t="s">
         <v>291</v>
       </c>
@@ -3921,27 +4232,31 @@
       <c r="Q37" s="12"/>
       <c r="R37" s="12"/>
       <c r="S37" s="12"/>
-      <c r="T37" s="15" t="e">
-        <f t="shared" ref="T37:U37" si="16">+T8/S8-1</f>
+      <c r="T37" s="12"/>
+      <c r="U37" s="12"/>
+      <c r="V37" s="12"/>
+      <c r="W37" s="12"/>
+      <c r="X37" s="15" t="e">
+        <f t="shared" ref="X37:Y37" si="18">+X8/W8-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="U37" s="15" t="e">
-        <f t="shared" si="16"/>
+      <c r="Y37" s="15" t="e">
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V37" s="15">
-        <f>+V8/U8-1</f>
-        <v>0</v>
-      </c>
-      <c r="W37" s="15">
-        <f>+W8/V8-1</f>
+      <c r="Z37" s="15">
+        <f>+Z8/Y8-1</f>
+        <v>0</v>
+      </c>
+      <c r="AA37" s="15">
+        <f>+AA8/Z8-1</f>
         <v>5.3191489361702038E-2</v>
       </c>
-      <c r="X37" s="12"/>
-      <c r="Y37" s="12"/>
-      <c r="Z37" s="12"/>
-    </row>
-    <row r="38" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AB37" s="12"/>
+      <c r="AC37" s="12"/>
+      <c r="AD37" s="12"/>
+    </row>
+    <row r="38" spans="2:30" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B38" s="2" t="s">
         <v>280</v>
       </c>
@@ -3958,74 +4273,81 @@
         <v>70</v>
       </c>
       <c r="G38" s="17" t="e">
-        <f t="shared" ref="G38:J45" si="17">+G12/C12-1</f>
+        <f t="shared" ref="G38:J45" si="19">+G12/C12-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="H38" s="17" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I38" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>6.9002464373727701E-2</v>
       </c>
       <c r="J38" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>5.541410813239489E-2</v>
       </c>
       <c r="K38" s="17">
-        <f t="shared" ref="K38:K45" si="18">+K12/G12-1</f>
+        <f t="shared" ref="K38:K45" si="20">+K12/G12-1</f>
         <v>7.89214074317659E-2</v>
       </c>
       <c r="L38" s="17">
-        <f t="shared" ref="L38:L45" si="19">+L12/H12-1</f>
+        <f t="shared" ref="L38:L45" si="21">+L12/H12-1</f>
         <v>0.12562542258282616</v>
       </c>
       <c r="M38" s="17">
-        <f t="shared" ref="M38:M45" si="20">+M12/I12-1</f>
+        <f t="shared" ref="M38:M45" si="22">+M12/I12-1</f>
         <v>8.0785807356920758E-2</v>
       </c>
       <c r="N38" s="17">
-        <f t="shared" ref="N38:N45" si="21">+N12/J12-1</f>
-        <v>-1</v>
-      </c>
-      <c r="O38" s="12"/>
-      <c r="P38" s="16" t="s">
+        <f t="shared" ref="N38:O45" si="23">+N12/J12-1</f>
+        <v>8.2304526748971485E-2</v>
+      </c>
+      <c r="O38" s="17">
+        <f t="shared" si="23"/>
+        <v>0.12816214568729034</v>
+      </c>
+      <c r="P38" s="17"/>
+      <c r="Q38" s="17"/>
+      <c r="R38" s="17"/>
+      <c r="S38" s="12"/>
+      <c r="T38" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="Q38" s="15" t="e">
-        <f t="shared" ref="Q38:W41" si="22">Q12/P12-1</f>
+      <c r="U38" s="15" t="e">
+        <f t="shared" ref="U38:AA41" si="24">U12/T12-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="R38" s="15" t="e">
-        <f t="shared" si="22"/>
+      <c r="V38" s="15" t="e">
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S38" s="15" t="e">
-        <f t="shared" si="22"/>
+      <c r="W38" s="15" t="e">
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T38" s="15" t="e">
-        <f t="shared" si="22"/>
+      <c r="X38" s="15" t="e">
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U38" s="15" t="e">
-        <f t="shared" si="22"/>
+      <c r="Y38" s="15" t="e">
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V38" s="15">
-        <f t="shared" si="22"/>
+      <c r="Z38" s="15">
+        <f t="shared" si="24"/>
         <v>4.9767681982447076E-2</v>
       </c>
-      <c r="W38" s="15">
-        <f t="shared" si="22"/>
+      <c r="AA38" s="15">
+        <f t="shared" si="24"/>
         <v>9.1636339792138033E-2</v>
       </c>
-      <c r="X38" s="12"/>
-      <c r="Y38" s="12"/>
-      <c r="Z38" s="12"/>
-    </row>
-    <row r="39" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AB38" s="12"/>
+      <c r="AC38" s="12"/>
+      <c r="AD38" s="12"/>
+    </row>
+    <row r="39" spans="2:30" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B39" s="2" t="s">
         <v>281</v>
       </c>
@@ -4042,74 +4364,81 @@
         <v>70</v>
       </c>
       <c r="G39" s="17" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H39" s="17" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I39" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0.1589645254074783</v>
       </c>
       <c r="J39" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0.11999147485080996</v>
       </c>
       <c r="K39" s="17">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.1573784178668336</v>
       </c>
       <c r="L39" s="17">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0.21629263120692688</v>
       </c>
       <c r="M39" s="17">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.11929185969556588</v>
       </c>
       <c r="N39" s="17">
-        <f t="shared" si="21"/>
-        <v>-1</v>
-      </c>
-      <c r="O39" s="12"/>
-      <c r="P39" s="16" t="s">
+        <f t="shared" si="23"/>
+        <v>0.1790675547098004</v>
+      </c>
+      <c r="O39" s="17">
+        <f t="shared" si="23"/>
+        <v>7.195671776375101E-2</v>
+      </c>
+      <c r="P39" s="17"/>
+      <c r="Q39" s="17"/>
+      <c r="R39" s="17"/>
+      <c r="S39" s="12"/>
+      <c r="T39" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="Q39" s="15" t="e">
-        <f t="shared" si="22"/>
+      <c r="U39" s="15" t="e">
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R39" s="15" t="e">
-        <f t="shared" si="22"/>
+      <c r="V39" s="15" t="e">
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S39" s="15" t="e">
-        <f t="shared" si="22"/>
+      <c r="W39" s="15" t="e">
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T39" s="15" t="e">
-        <f t="shared" si="22"/>
+      <c r="X39" s="15" t="e">
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U39" s="15" t="e">
-        <f t="shared" si="22"/>
+      <c r="Y39" s="15" t="e">
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V39" s="15">
-        <f t="shared" si="22"/>
+      <c r="Z39" s="15">
+        <f t="shared" si="24"/>
         <v>0.1051321138211383</v>
       </c>
-      <c r="W39" s="15">
-        <f t="shared" si="22"/>
+      <c r="AA39" s="15">
+        <f t="shared" si="24"/>
         <v>0.16736401673640167</v>
       </c>
-      <c r="X39" s="12"/>
-      <c r="Y39" s="12"/>
-      <c r="Z39" s="12"/>
-    </row>
-    <row r="40" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AB39" s="12"/>
+      <c r="AC39" s="12"/>
+      <c r="AD39" s="12"/>
+    </row>
+    <row r="40" spans="2:30" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B40" s="2" t="s">
         <v>282</v>
       </c>
@@ -4126,74 +4455,81 @@
         <v>70</v>
       </c>
       <c r="G40" s="17" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H40" s="17" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I40" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0.13508064516129026</v>
       </c>
       <c r="J40" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>9.4598021810804012E-2</v>
       </c>
       <c r="K40" s="17">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.21258633921719117</v>
       </c>
       <c r="L40" s="17">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0.17201472908995274</v>
       </c>
       <c r="M40" s="17">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.22419577659364509</v>
       </c>
       <c r="N40" s="17">
-        <f t="shared" si="21"/>
-        <v>-1</v>
-      </c>
-      <c r="O40" s="12"/>
-      <c r="P40" s="16" t="s">
+        <f t="shared" si="23"/>
+        <v>0.30583873957367902</v>
+      </c>
+      <c r="O40" s="17">
+        <f t="shared" si="23"/>
+        <v>0.24324894514767914</v>
+      </c>
+      <c r="P40" s="17"/>
+      <c r="Q40" s="17"/>
+      <c r="R40" s="17"/>
+      <c r="S40" s="12"/>
+      <c r="T40" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="Q40" s="15" t="e">
-        <f t="shared" si="22"/>
+      <c r="U40" s="15" t="e">
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R40" s="15" t="e">
-        <f t="shared" si="22"/>
+      <c r="V40" s="15" t="e">
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S40" s="15" t="e">
-        <f t="shared" si="22"/>
+      <c r="W40" s="15" t="e">
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T40" s="15" t="e">
-        <f t="shared" si="22"/>
+      <c r="X40" s="15" t="e">
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U40" s="15" t="e">
-        <f t="shared" si="22"/>
+      <c r="Y40" s="15" t="e">
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V40" s="15">
-        <f t="shared" si="22"/>
+      <c r="Z40" s="15">
+        <f t="shared" si="24"/>
         <v>9.1152815013404886E-2</v>
       </c>
-      <c r="W40" s="15">
-        <f t="shared" si="22"/>
+      <c r="AA40" s="15">
+        <f t="shared" si="24"/>
         <v>0.23054873054873037</v>
       </c>
-      <c r="X40" s="12"/>
-      <c r="Y40" s="12"/>
-      <c r="Z40" s="12"/>
-    </row>
-    <row r="41" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AB40" s="12"/>
+      <c r="AC40" s="12"/>
+      <c r="AD40" s="12"/>
+    </row>
+    <row r="41" spans="2:30" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B41" s="2" t="s">
         <v>283</v>
       </c>
@@ -4210,74 +4546,81 @@
         <v>70</v>
       </c>
       <c r="G41" s="17" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H41" s="17" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I41" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>5.7926829268292845E-2</v>
       </c>
       <c r="J41" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-3.2697547683923744E-2</v>
       </c>
       <c r="K41" s="17">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>1.1764705882352899E-2</v>
       </c>
       <c r="L41" s="17">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>9.9009900990099098E-2</v>
       </c>
       <c r="M41" s="17">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>-0.10951008645533156</v>
       </c>
       <c r="N41" s="17">
-        <f t="shared" si="21"/>
-        <v>-1</v>
-      </c>
-      <c r="O41" s="12"/>
-      <c r="P41" s="16" t="s">
+        <f t="shared" si="23"/>
+        <v>-7.6056338028168691E-2</v>
+      </c>
+      <c r="O41" s="17">
+        <f t="shared" si="23"/>
+        <v>4.0697674418604501E-2</v>
+      </c>
+      <c r="P41" s="17"/>
+      <c r="Q41" s="17"/>
+      <c r="R41" s="17"/>
+      <c r="S41" s="12"/>
+      <c r="T41" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="Q41" s="15" t="e">
-        <f t="shared" si="22"/>
+      <c r="U41" s="15" t="e">
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R41" s="15" t="e">
-        <f t="shared" si="22"/>
+      <c r="V41" s="15" t="e">
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S41" s="15" t="e">
-        <f t="shared" si="22"/>
+      <c r="W41" s="15" t="e">
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T41" s="15" t="e">
-        <f t="shared" si="22"/>
+      <c r="X41" s="15" t="e">
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U41" s="15" t="e">
-        <f t="shared" si="22"/>
+      <c r="Y41" s="15" t="e">
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V41" s="15">
-        <f t="shared" si="22"/>
+      <c r="Z41" s="15">
+        <f t="shared" si="24"/>
         <v>-1.1619958988380197E-2</v>
       </c>
-      <c r="W41" s="15">
-        <f t="shared" si="22"/>
+      <c r="AA41" s="15">
+        <f t="shared" si="24"/>
         <v>-1.4522821576763434E-2</v>
       </c>
-      <c r="X41" s="12"/>
-      <c r="Y41" s="12"/>
-      <c r="Z41" s="12"/>
-    </row>
-    <row r="42" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AB41" s="12"/>
+      <c r="AC41" s="12"/>
+      <c r="AD41" s="12"/>
+    </row>
+    <row r="42" spans="2:30" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B42" s="2" t="s">
         <v>273</v>
       </c>
@@ -4294,74 +4637,81 @@
         <v>70</v>
       </c>
       <c r="G42" s="17" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H42" s="17" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I42" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0.11724819889814952</v>
       </c>
       <c r="J42" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0.58689937966565031</v>
       </c>
       <c r="K42" s="17">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.16327716443927964</v>
       </c>
       <c r="L42" s="17">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0.15331995622035755</v>
       </c>
       <c r="M42" s="17">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="N42" s="17">
-        <f t="shared" si="21"/>
-        <v>-1</v>
-      </c>
-      <c r="O42" s="12"/>
-      <c r="P42" s="16" t="s">
+        <f t="shared" si="23"/>
+        <v>-1.6033923010666973E-2</v>
+      </c>
+      <c r="O42" s="17">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="P42" s="17"/>
+      <c r="Q42" s="17"/>
+      <c r="R42" s="17"/>
+      <c r="S42" s="12"/>
+      <c r="T42" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="Q42" s="15">
-        <f>Q16/P16-1</f>
+      <c r="U42" s="15">
+        <f>U16/T16-1</f>
         <v>-1.8410801003255761E-3</v>
       </c>
-      <c r="R42" s="15">
-        <f t="shared" ref="R42:W42" si="23">R16/Q16-1</f>
+      <c r="V42" s="15">
+        <f t="shared" ref="V42:AA42" si="25">V16/U16-1</f>
         <v>-0.25691678473094703</v>
       </c>
-      <c r="S42" s="15">
-        <f t="shared" si="23"/>
+      <c r="W42" s="15">
+        <f t="shared" si="25"/>
         <v>0.41790776314842781</v>
       </c>
-      <c r="T42" s="15">
-        <f t="shared" si="23"/>
+      <c r="X42" s="15">
+        <f t="shared" si="25"/>
         <v>2.831409361918058E-2</v>
       </c>
-      <c r="U42" s="15">
-        <f t="shared" si="23"/>
+      <c r="Y42" s="15">
+        <f t="shared" si="25"/>
         <v>7.3499296834521832E-2</v>
       </c>
-      <c r="V42" s="15">
-        <f t="shared" si="23"/>
+      <c r="Z42" s="15">
+        <f t="shared" si="25"/>
         <v>9.632268444035863E-2</v>
       </c>
-      <c r="W42" s="15">
-        <f t="shared" si="23"/>
-        <v>-1</v>
-      </c>
-      <c r="X42" s="12"/>
-      <c r="Y42" s="12"/>
-      <c r="Z42" s="12"/>
-    </row>
-    <row r="43" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AA42" s="15">
+        <f t="shared" si="25"/>
+        <v>0.15984989832498275</v>
+      </c>
+      <c r="AB42" s="12"/>
+      <c r="AC42" s="12"/>
+      <c r="AD42" s="12"/>
+    </row>
+    <row r="43" spans="2:30" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B43" s="2" t="s">
         <v>274</v>
       </c>
@@ -4378,74 +4728,81 @@
         <v>70</v>
       </c>
       <c r="G43" s="17" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H43" s="17" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I43" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>8.5702513391017865E-2</v>
       </c>
       <c r="J43" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>3.8614032063437387E-2</v>
       </c>
       <c r="K43" s="17">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>8.5053859964093315E-2</v>
       </c>
       <c r="L43" s="17">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0.19110658520027135</v>
       </c>
       <c r="M43" s="17">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="N43" s="17">
-        <f t="shared" si="21"/>
-        <v>-1</v>
-      </c>
-      <c r="O43" s="12"/>
-      <c r="P43" s="16" t="s">
+        <f t="shared" si="23"/>
+        <v>0.20680497925311236</v>
+      </c>
+      <c r="O43" s="17">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="P43" s="17"/>
+      <c r="Q43" s="17"/>
+      <c r="R43" s="17"/>
+      <c r="S43" s="12"/>
+      <c r="T43" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="Q43" s="15">
-        <f>Q17/P17-1</f>
+      <c r="U43" s="15">
+        <f>U17/T17-1</f>
         <v>-5.9226750261232919E-2</v>
       </c>
-      <c r="R43" s="15">
-        <f t="shared" ref="R43:W45" si="24">R17/Q17-1</f>
+      <c r="V43" s="15">
+        <f t="shared" ref="V43:AA45" si="26">V17/U17-1</f>
         <v>-0.33419228718677818</v>
       </c>
-      <c r="S43" s="15">
-        <f t="shared" si="24"/>
+      <c r="W43" s="15">
+        <f t="shared" si="26"/>
         <v>0.41952488989723768</v>
       </c>
-      <c r="T43" s="15">
-        <f t="shared" si="24"/>
+      <c r="X43" s="15">
+        <f t="shared" si="26"/>
         <v>4.9828421003149437E-2</v>
       </c>
-      <c r="U43" s="15">
-        <f t="shared" si="24"/>
+      <c r="Y43" s="15">
+        <f t="shared" si="26"/>
         <v>-4.4418573411543538E-2</v>
       </c>
-      <c r="V43" s="15">
-        <f t="shared" si="24"/>
+      <c r="Z43" s="15">
+        <f t="shared" si="26"/>
         <v>1.4151164425284746E-2</v>
       </c>
-      <c r="W43" s="15">
-        <f t="shared" si="24"/>
-        <v>-1</v>
-      </c>
-      <c r="X43" s="12"/>
-      <c r="Y43" s="12"/>
-      <c r="Z43" s="12"/>
-    </row>
-    <row r="44" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AA43" s="15">
+        <f t="shared" si="26"/>
+        <v>0.12710807189391482</v>
+      </c>
+      <c r="AB43" s="12"/>
+      <c r="AC43" s="12"/>
+      <c r="AD43" s="12"/>
+    </row>
+    <row r="44" spans="2:30" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B44" s="2" t="s">
         <v>275</v>
       </c>
@@ -4462,74 +4819,81 @@
         <v>70</v>
       </c>
       <c r="G44" s="17" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H44" s="17" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I44" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>5.7926829268292845E-2</v>
       </c>
       <c r="J44" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-3.2697547683923744E-2</v>
       </c>
       <c r="K44" s="17">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>1.1764705882352899E-2</v>
       </c>
       <c r="L44" s="17">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>9.9009900990099098E-2</v>
       </c>
       <c r="M44" s="17">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="N44" s="17">
-        <f t="shared" si="21"/>
-        <v>-1</v>
-      </c>
-      <c r="O44" s="12"/>
-      <c r="P44" s="16" t="s">
+        <f t="shared" si="23"/>
+        <v>-0.18309859154929575</v>
+      </c>
+      <c r="O44" s="17">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="P44" s="17"/>
+      <c r="Q44" s="17"/>
+      <c r="R44" s="17"/>
+      <c r="S44" s="12"/>
+      <c r="T44" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="Q44" s="15">
-        <f>Q18/P18-1</f>
+      <c r="U44" s="15">
+        <f>U18/T18-1</f>
         <v>-2.6635784597567991E-2</v>
       </c>
-      <c r="R44" s="15">
-        <f t="shared" si="24"/>
+      <c r="V44" s="15">
+        <f t="shared" si="26"/>
         <v>-0.27186198691255203</v>
       </c>
-      <c r="S44" s="15">
-        <f t="shared" si="24"/>
+      <c r="W44" s="15">
+        <f t="shared" si="26"/>
         <v>0.22303921568627438</v>
       </c>
-      <c r="T44" s="15">
-        <f t="shared" si="24"/>
+      <c r="X44" s="15">
+        <f t="shared" si="26"/>
         <v>5.0100200400801542E-2</v>
       </c>
-      <c r="U44" s="15">
-        <f t="shared" si="24"/>
+      <c r="Y44" s="15">
+        <f t="shared" si="26"/>
         <v>-6.9338422391857391E-2</v>
       </c>
-      <c r="V44" s="15">
-        <f t="shared" si="24"/>
+      <c r="Z44" s="15">
+        <f t="shared" si="26"/>
         <v>-1.1619958988380197E-2</v>
       </c>
-      <c r="W44" s="15">
-        <f t="shared" si="24"/>
-        <v>-1</v>
-      </c>
-      <c r="X44" s="12"/>
-      <c r="Y44" s="12"/>
-      <c r="Z44" s="12"/>
-    </row>
-    <row r="45" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AA44" s="15">
+        <f t="shared" si="26"/>
+        <v>-1.4522821576763434E-2</v>
+      </c>
+      <c r="AB44" s="12"/>
+      <c r="AC44" s="12"/>
+      <c r="AD44" s="12"/>
+    </row>
+    <row r="45" spans="2:30" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B45" s="1" t="s">
         <v>88</v>
       </c>
@@ -4546,1316 +4910,1351 @@
         <v>70</v>
       </c>
       <c r="G45" s="19" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H45" s="19" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I45" s="19">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0.1083247156153051</v>
       </c>
       <c r="J45" s="19">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>8.2530773646278366E-2</v>
       </c>
       <c r="K45" s="19">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.13682052638539877</v>
       </c>
       <c r="L45" s="19">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0.16494785631517961</v>
       </c>
       <c r="M45" s="19">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.12246326102169358</v>
       </c>
       <c r="N45" s="19">
-        <f t="shared" si="21"/>
-        <v>-1</v>
-      </c>
-      <c r="O45" s="1"/>
-      <c r="P45" s="18" t="s">
+        <f t="shared" si="23"/>
+        <v>0.16579272962941127</v>
+      </c>
+      <c r="O45" s="19">
+        <f t="shared" si="23"/>
+        <v>0.14001512419289175</v>
+      </c>
+      <c r="P45" s="19"/>
+      <c r="Q45" s="19"/>
+      <c r="R45" s="19"/>
+      <c r="S45" s="1"/>
+      <c r="T45" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="Q45" s="20">
-        <f>Q19/P19-1</f>
+      <c r="U45" s="20">
+        <f>U19/T19-1</f>
         <v>-2.4267384761603061E-2</v>
       </c>
-      <c r="R45" s="20">
-        <f t="shared" si="24"/>
+      <c r="V45" s="20">
+        <f t="shared" si="26"/>
         <v>-0.28556121952011426</v>
       </c>
-      <c r="S45" s="20">
-        <f t="shared" si="24"/>
+      <c r="W45" s="20">
+        <f t="shared" si="26"/>
         <v>0.413038538447555</v>
       </c>
-      <c r="T45" s="20">
-        <f t="shared" si="24"/>
+      <c r="X45" s="20">
+        <f t="shared" si="26"/>
         <v>3.6198440138297094E-2</v>
       </c>
-      <c r="U45" s="20">
-        <f t="shared" si="24"/>
+      <c r="Y45" s="20">
+        <f t="shared" si="26"/>
         <v>2.9145198336333555E-2</v>
       </c>
-      <c r="V45" s="20">
-        <f t="shared" si="24"/>
+      <c r="Z45" s="20">
+        <f t="shared" si="26"/>
         <v>6.7497059444461271E-2</v>
       </c>
-      <c r="W45" s="20">
-        <f t="shared" si="24"/>
+      <c r="AA45" s="20">
+        <f t="shared" si="26"/>
         <v>0.14627772284220941</v>
       </c>
     </row>
-    <row r="46" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:30" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B46" s="2" t="s">
         <v>89</v>
       </c>
       <c r="C46" s="15" t="e">
-        <f t="shared" ref="C46:J46" si="25">C21/C19</f>
+        <f t="shared" ref="C46:J46" si="27">C21/C19</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D46" s="15" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E46" s="15">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0.66494312306101344</v>
       </c>
       <c r="F46" s="15">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0.66566745328145926</v>
       </c>
       <c r="G46" s="15">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0.70480095225499284</v>
       </c>
       <c r="H46" s="15">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0.66958285052143685</v>
       </c>
       <c r="I46" s="15">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0.68397480755773266</v>
       </c>
       <c r="J46" s="15">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0.68656100866081426</v>
       </c>
       <c r="K46" s="15">
-        <f t="shared" ref="K46:N46" si="26">K21/K19</f>
+        <f t="shared" ref="K46:N46" si="28">K21/K19</f>
         <v>0.72264557035658195</v>
       </c>
       <c r="L46" s="15">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0.67956433083005918</v>
       </c>
       <c r="M46" s="15">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0.6989609310058188</v>
       </c>
-      <c r="N46" s="15" t="e">
-        <f t="shared" si="26"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P46" s="15">
-        <f t="shared" ref="P46:U46" si="27">P21/P19</f>
+      <c r="N46" s="15">
+        <f t="shared" si="28"/>
+        <v>0.69682114519634086</v>
+      </c>
+      <c r="O46" s="15">
+        <f t="shared" ref="O46" si="29">O21/O19</f>
+        <v>0.73691192978875386</v>
+      </c>
+      <c r="P46" s="15"/>
+      <c r="Q46" s="15"/>
+      <c r="R46" s="15"/>
+      <c r="T46" s="15">
+        <f t="shared" ref="T46:Y46" si="30">T21/T19</f>
         <v>0.61555520354823379</v>
       </c>
-      <c r="Q46" s="15">
-        <f t="shared" si="27"/>
+      <c r="U46" s="15">
+        <f t="shared" si="30"/>
         <v>0.59308743790382801</v>
       </c>
-      <c r="R46" s="15">
-        <f t="shared" si="27"/>
+      <c r="V46" s="15">
+        <f t="shared" si="30"/>
         <v>0.65019996364297394</v>
       </c>
-      <c r="S46" s="15">
-        <f t="shared" si="27"/>
+      <c r="W46" s="15">
+        <f t="shared" si="30"/>
         <v>0.66696148588887993</v>
       </c>
-      <c r="T46" s="15">
-        <f t="shared" si="27"/>
+      <c r="X46" s="15">
+        <f t="shared" si="30"/>
         <v>0.64650195542864242</v>
       </c>
-      <c r="U46" s="15">
-        <f t="shared" si="27"/>
+      <c r="Y46" s="15">
+        <f t="shared" si="30"/>
         <v>0.66830533522333135</v>
       </c>
-      <c r="V46" s="15">
-        <f t="shared" ref="V46:W46" si="28">V21/V19</f>
+      <c r="Z46" s="15">
+        <f t="shared" ref="Z46:AA46" si="31">Z21/Z19</f>
         <v>0.68553468003955353</v>
       </c>
-      <c r="W46" s="15">
-        <f t="shared" si="28"/>
+      <c r="AA46" s="15">
+        <f t="shared" si="31"/>
         <v>0.69865056380553325</v>
       </c>
     </row>
-    <row r="47" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:30" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B47" s="2" t="s">
         <v>90</v>
       </c>
       <c r="C47" s="15" t="e">
-        <f t="shared" ref="C47:J47" si="29">C26/C19</f>
+        <f t="shared" ref="C47:J47" si="32">C26/C19</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D47" s="15" t="e">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E47" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>0.16427094105480866</v>
       </c>
       <c r="F47" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>6.8754384845972363E-2</v>
       </c>
       <c r="G47" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>0.1378785874884276</v>
       </c>
       <c r="H47" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>0.10365005793742763</v>
       </c>
       <c r="I47" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>0.18180545836249118</v>
       </c>
       <c r="J47" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>9.1321510634537209E-2</v>
       </c>
       <c r="K47" s="15">
-        <f t="shared" ref="K47:N47" si="30">K26/K19</f>
+        <f t="shared" ref="K47:N47" si="33">K26/K19</f>
         <v>0.15915304519806878</v>
       </c>
       <c r="L47" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>0.1221962500621674</v>
       </c>
       <c r="M47" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>0.19588528678304246</v>
       </c>
-      <c r="N47" s="15" t="e">
-        <f t="shared" si="30"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P47" s="15">
-        <f t="shared" ref="P47:U47" si="31">P26/P19</f>
+      <c r="N47" s="15">
+        <f t="shared" si="33"/>
+        <v>9.5315105877596368E-2</v>
+      </c>
+      <c r="O47" s="15">
+        <f t="shared" ref="O47" si="34">O26/O19</f>
+        <v>0.17471170527604851</v>
+      </c>
+      <c r="P47" s="15"/>
+      <c r="Q47" s="15"/>
+      <c r="R47" s="15"/>
+      <c r="T47" s="15">
+        <f t="shared" ref="T47:Y47" si="35">T26/T19</f>
         <v>8.8990971012197009E-2</v>
       </c>
-      <c r="Q47" s="15">
-        <f t="shared" si="31"/>
+      <c r="U47" s="15">
+        <f t="shared" si="35"/>
         <v>5.1462709828241249E-2</v>
       </c>
-      <c r="R47" s="15">
-        <f t="shared" si="31"/>
+      <c r="V47" s="15">
+        <f t="shared" si="35"/>
         <v>-9.9072895837120315E-3</v>
       </c>
-      <c r="S47" s="15">
-        <f t="shared" si="31"/>
+      <c r="W47" s="15">
+        <f t="shared" si="35"/>
         <v>0.12839109109913968</v>
       </c>
-      <c r="T47" s="15">
-        <f t="shared" si="31"/>
+      <c r="X47" s="15">
+        <f t="shared" si="35"/>
         <v>0.10928673412378177</v>
       </c>
-      <c r="U47" s="15">
-        <f t="shared" si="31"/>
+      <c r="Y47" s="15">
+        <f t="shared" si="35"/>
         <v>0.11406339536146201</v>
       </c>
-      <c r="V47" s="15">
-        <f t="shared" ref="V47:W47" si="32">V26/V19</f>
+      <c r="Z47" s="15">
+        <f t="shared" ref="Z47:AA47" si="36">Z26/Z19</f>
         <v>0.13167113999152416</v>
       </c>
-      <c r="W47" s="15">
-        <f t="shared" si="32"/>
+      <c r="AA47" s="15">
+        <f t="shared" si="36"/>
         <v>0.14532010598311662</v>
       </c>
     </row>
-    <row r="48" spans="2:26" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:30" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B48" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C48" s="15" t="e">
-        <f t="shared" ref="C48:J48" si="33">C32/C19</f>
+        <f t="shared" ref="C48:J48" si="37">C32/C19</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D48" s="15" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E48" s="15">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>0.1430196483971044</v>
       </c>
       <c r="F48" s="15">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>5.7848077045730001E-2</v>
       </c>
       <c r="G48" s="15">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>0.1114931887316494</v>
       </c>
       <c r="H48" s="15">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>8.5689455388180819E-2</v>
       </c>
       <c r="I48" s="15">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>0.13874504315372047</v>
       </c>
       <c r="J48" s="15">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>7.6003063689389028E-2</v>
       </c>
       <c r="K48" s="15">
-        <f t="shared" ref="K48:N48" si="34">K32/K19</f>
+        <f t="shared" ref="K48:N48" si="38">K32/K19</f>
         <v>0.12820661974288877</v>
       </c>
       <c r="L48" s="15">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>0.10319789128164321</v>
       </c>
       <c r="M48" s="15">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>0.15029093931837079</v>
       </c>
-      <c r="N48" s="15" t="e">
-        <f t="shared" si="34"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P48" s="15">
-        <f t="shared" ref="P48:U48" si="35">P32/P19</f>
+      <c r="N48" s="15">
+        <f t="shared" si="38"/>
+        <v>7.6615959973720088E-2</v>
+      </c>
+      <c r="O48" s="15">
+        <f t="shared" ref="O48" si="39">O32/O19</f>
+        <v>0.13378916215940395</v>
+      </c>
+      <c r="P48" s="15"/>
+      <c r="Q48" s="15"/>
+      <c r="R48" s="15"/>
+      <c r="T48" s="15">
+        <f t="shared" ref="T48:Y48" si="40">T32/T19</f>
         <v>6.8255979724378205E-2</v>
       </c>
-      <c r="Q48" s="15">
-        <f t="shared" si="35"/>
+      <c r="U48" s="15">
+        <f t="shared" si="40"/>
         <v>6.2388389233416733E-2</v>
       </c>
-      <c r="R48" s="15">
-        <f t="shared" si="35"/>
+      <c r="V48" s="15">
+        <f t="shared" si="40"/>
         <v>-2.7517724050172675E-2</v>
       </c>
-      <c r="S48" s="15">
-        <f t="shared" si="35"/>
+      <c r="W48" s="15">
+        <f t="shared" si="40"/>
         <v>9.6502371954651459E-2</v>
       </c>
-      <c r="T48" s="15">
-        <f t="shared" si="35"/>
+      <c r="X48" s="15">
+        <f t="shared" si="40"/>
         <v>8.1119250108634966E-2</v>
       </c>
-      <c r="U48" s="15">
-        <f t="shared" si="35"/>
+      <c r="Y48" s="15">
+        <f t="shared" si="40"/>
         <v>9.7460566396235973E-2</v>
       </c>
-      <c r="V48" s="15">
-        <f t="shared" ref="V48:W48" si="36">V32/V19</f>
+      <c r="Z48" s="15">
+        <f t="shared" ref="Z48:AA48" si="41">Z32/Z19</f>
         <v>0.10494420115835562</v>
       </c>
-      <c r="W48" s="15">
-        <f t="shared" si="36"/>
+      <c r="AA48" s="15">
+        <f t="shared" si="41"/>
         <v>0.11597757101484993</v>
       </c>
-      <c r="Y48" s="21"/>
-    </row>
-    <row r="49" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AC48" s="21"/>
+    </row>
+    <row r="49" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B49" s="2" t="s">
         <v>92</v>
       </c>
       <c r="C49" s="15" t="e">
-        <f t="shared" ref="C49:J49" si="37">C31/C32</f>
+        <f t="shared" ref="C49:J49" si="42">C31/C32</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D49" s="15" t="e">
-        <f t="shared" si="37"/>
+        <f t="shared" si="42"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E49" s="15">
-        <f t="shared" si="37"/>
+        <f t="shared" si="42"/>
         <v>0.19233550253073037</v>
       </c>
       <c r="F49" s="15">
-        <f t="shared" si="37"/>
+        <f t="shared" si="42"/>
         <v>0.22932745314222694</v>
       </c>
       <c r="G49" s="15">
-        <f t="shared" si="37"/>
+        <f t="shared" si="42"/>
         <v>0.28469750889679679</v>
       </c>
       <c r="H49" s="15">
-        <f t="shared" si="37"/>
+        <f t="shared" si="42"/>
         <v>0.27180527383367126</v>
       </c>
       <c r="I49" s="15">
-        <f t="shared" si="37"/>
+        <f t="shared" si="42"/>
         <v>0.29018157363819791</v>
       </c>
       <c r="J49" s="15">
-        <f t="shared" si="37"/>
+        <f t="shared" si="42"/>
         <v>0.25813953488372093</v>
       </c>
       <c r="K49" s="15">
-        <f t="shared" ref="K49:N49" si="38">K31/K32</f>
+        <f t="shared" ref="K49:N49" si="43">K31/K32</f>
         <v>0.26134301270417415</v>
       </c>
       <c r="L49" s="15">
-        <f t="shared" si="38"/>
+        <f t="shared" si="43"/>
         <v>0.17012048192771084</v>
       </c>
       <c r="M49" s="15">
-        <f t="shared" si="38"/>
+        <f t="shared" si="43"/>
         <v>0.28263274336283178</v>
       </c>
-      <c r="N49" s="15" t="e">
-        <f t="shared" si="38"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P49" s="15">
-        <f t="shared" ref="P49:U49" si="39">P31/P32</f>
+      <c r="N49" s="15">
+        <f t="shared" si="43"/>
+        <v>0.27374670184696565</v>
+      </c>
+      <c r="O49" s="15">
+        <f t="shared" ref="O49" si="44">O31/O32</f>
+        <v>0.30511060259344025</v>
+      </c>
+      <c r="P49" s="15"/>
+      <c r="Q49" s="15"/>
+      <c r="R49" s="15"/>
+      <c r="T49" s="15">
+        <f t="shared" ref="T49:Y49" si="45">T31/T32</f>
         <v>0.35182176839173851</v>
       </c>
-      <c r="Q49" s="15">
-        <f t="shared" si="39"/>
+      <c r="U49" s="15">
+        <f t="shared" si="45"/>
         <v>-0.15066354410616689</v>
       </c>
-      <c r="R49" s="15">
-        <f t="shared" si="39"/>
+      <c r="V49" s="15">
+        <f t="shared" si="45"/>
         <v>-0.38232865400495486</v>
       </c>
-      <c r="S49" s="15">
-        <f t="shared" si="39"/>
+      <c r="W49" s="15">
+        <f t="shared" si="45"/>
         <v>0.2574570904849191</v>
       </c>
-      <c r="T49" s="15">
-        <f t="shared" si="39"/>
+      <c r="X49" s="15">
+        <f t="shared" si="45"/>
         <v>0.32370384541802161</v>
       </c>
-      <c r="U49" s="15">
-        <f t="shared" si="39"/>
+      <c r="Y49" s="15">
+        <f t="shared" si="45"/>
         <v>0.20284697508896823</v>
       </c>
-      <c r="V49" s="15">
-        <f t="shared" ref="V49:W49" si="40">V31/V32</f>
+      <c r="Z49" s="15">
+        <f t="shared" ref="Z49:AA49" si="46">Z31/Z32</f>
         <v>0.27971463184816286</v>
       </c>
-      <c r="W49" s="15">
-        <f t="shared" si="40"/>
+      <c r="AA49" s="15">
+        <f t="shared" si="46"/>
         <v>0.25140792689406022</v>
       </c>
     </row>
-    <row r="50" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="P50" s="3"/>
-      <c r="Q50" s="3"/>
-      <c r="R50" s="3"/>
-      <c r="S50" s="3"/>
+    <row r="50" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="T50" s="3"/>
       <c r="U50" s="3"/>
       <c r="V50" s="3"/>
-    </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="U51" s="30"/>
-    </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="W50" s="3"/>
+      <c r="X50" s="3"/>
+      <c r="Y50" s="3"/>
+      <c r="Z50" s="3"/>
+    </row>
+    <row r="51" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="Y51" s="30"/>
+    </row>
+    <row r="52" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B52" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="P52" s="12">
+      <c r="T52" s="12">
         <v>584.1</v>
       </c>
-      <c r="Q52" s="12">
+      <c r="U52" s="12">
         <v>1620.4</v>
       </c>
-      <c r="R52" s="12">
+      <c r="V52" s="12">
         <v>2579</v>
       </c>
-      <c r="S52" s="12">
+      <c r="W52" s="12">
         <v>1863.8</v>
       </c>
-      <c r="T52" s="12">
+      <c r="X52" s="12">
         <v>1529.3</v>
       </c>
-      <c r="U52" s="12">
+      <c r="Y52" s="12">
         <v>1662.2</v>
       </c>
-      <c r="V52" s="12">
+      <c r="Z52" s="12">
         <v>1922.5</v>
       </c>
-      <c r="W52" s="12">
+      <c r="AA52" s="12">
         <v>1988</v>
       </c>
     </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B53" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="P53" s="12">
+      <c r="T53" s="12">
         <v>1403.4</v>
       </c>
-      <c r="Q53" s="12">
+      <c r="U53" s="12">
         <v>495.9</v>
       </c>
-      <c r="R53" s="12">
+      <c r="V53" s="12">
         <v>197.5</v>
       </c>
-      <c r="S53" s="12">
+      <c r="W53" s="12">
         <v>734.6</v>
       </c>
-      <c r="T53" s="12">
+      <c r="X53" s="12">
         <v>36.4</v>
       </c>
-      <c r="U53" s="12">
+      <c r="Y53" s="12">
         <v>121</v>
       </c>
-      <c r="V53" s="12">
+      <c r="Z53" s="12">
         <v>160.5</v>
       </c>
-      <c r="W53" s="12">
+      <c r="AA53" s="12">
         <v>77</v>
       </c>
     </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B54" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="P54" s="12">
+      <c r="T54" s="12">
         <v>398.1</v>
       </c>
-      <c r="Q54" s="12">
+      <c r="U54" s="12">
         <v>277.10000000000002</v>
       </c>
-      <c r="R54" s="12">
+      <c r="V54" s="12">
         <v>451.5</v>
       </c>
-      <c r="S54" s="12">
+      <c r="W54" s="12">
         <v>405.4</v>
       </c>
-      <c r="T54" s="12">
+      <c r="X54" s="12">
         <v>447.7</v>
       </c>
-      <c r="U54" s="12">
+      <c r="Y54" s="12">
         <v>446.5</v>
       </c>
-      <c r="V54" s="12">
+      <c r="Z54" s="12">
         <v>459.5</v>
       </c>
-      <c r="W54" s="12">
+      <c r="AA54" s="12">
         <v>491.7</v>
       </c>
     </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B55" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="P55" s="12">
+      <c r="T55" s="12">
         <v>817.8</v>
       </c>
-      <c r="Q55" s="12">
+      <c r="U55" s="12">
         <v>736.2</v>
       </c>
-      <c r="R55" s="12">
+      <c r="V55" s="12">
         <v>759</v>
       </c>
-      <c r="S55" s="12">
+      <c r="W55" s="12">
         <v>977.3</v>
       </c>
-      <c r="T55" s="12">
+      <c r="X55" s="12">
         <v>1071.3</v>
       </c>
-      <c r="U55" s="12">
+      <c r="Y55" s="12">
         <v>902.2</v>
       </c>
-      <c r="V55" s="12">
+      <c r="Z55" s="12">
         <v>949.6</v>
       </c>
-      <c r="W55" s="12">
+      <c r="AA55" s="12">
         <v>1014.3</v>
       </c>
     </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B56" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="P56" s="12">
+      <c r="T56" s="12">
         <v>32.1</v>
       </c>
-      <c r="Q56" s="12">
+      <c r="U56" s="12">
         <v>84.8</v>
       </c>
-      <c r="R56" s="12">
+      <c r="V56" s="12">
         <v>54.4</v>
       </c>
-      <c r="S56" s="12">
+      <c r="W56" s="12">
         <v>63.7</v>
       </c>
-      <c r="T56" s="12">
+      <c r="X56" s="12">
         <v>50.7</v>
       </c>
-      <c r="U56" s="12">
+      <c r="Y56" s="12">
         <v>56</v>
       </c>
-      <c r="V56" s="12">
+      <c r="Z56" s="12">
         <v>55.4</v>
       </c>
-      <c r="W56" s="12">
+      <c r="AA56" s="12">
         <v>77.8</v>
       </c>
     </row>
-    <row r="57" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B57" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="P57" s="12">
+      <c r="T57" s="12">
         <v>359.3</v>
       </c>
-      <c r="Q57" s="12">
+      <c r="U57" s="12">
         <v>160.80000000000001</v>
       </c>
-      <c r="R57" s="12">
+      <c r="V57" s="12">
         <v>166.6</v>
       </c>
-      <c r="S57" s="12">
+      <c r="W57" s="12">
         <v>172.5</v>
       </c>
-      <c r="T57" s="12">
+      <c r="X57" s="12">
         <v>188.7</v>
       </c>
-      <c r="U57" s="12">
+      <c r="Y57" s="12">
         <v>171.9</v>
       </c>
-      <c r="V57" s="12">
+      <c r="Z57" s="12">
         <v>242.4</v>
       </c>
-      <c r="W57" s="12">
+      <c r="AA57" s="12">
         <v>238.4</v>
       </c>
     </row>
-    <row r="58" spans="1:23" s="31" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:27" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A58" s="29"/>
       <c r="B58" s="29" t="s">
         <v>99</v>
       </c>
-      <c r="P58" s="31">
-        <f t="shared" ref="P58:T58" si="41">SUM(P52:P57)</f>
+      <c r="T58" s="31">
+        <f t="shared" ref="T58:X58" si="47">SUM(T52:T57)</f>
         <v>3594.7999999999997</v>
       </c>
-      <c r="Q58" s="31">
-        <f t="shared" si="41"/>
+      <c r="U58" s="31">
+        <f t="shared" si="47"/>
         <v>3375.2000000000007</v>
       </c>
-      <c r="R58" s="31">
-        <f t="shared" si="41"/>
+      <c r="V58" s="31">
+        <f t="shared" si="47"/>
         <v>4208</v>
       </c>
-      <c r="S58" s="31">
-        <f t="shared" si="41"/>
+      <c r="W58" s="31">
+        <f t="shared" si="47"/>
         <v>4217.3</v>
       </c>
-      <c r="T58" s="31">
-        <f t="shared" si="41"/>
+      <c r="X58" s="31">
+        <f t="shared" si="47"/>
         <v>3324.0999999999995</v>
       </c>
-      <c r="U58" s="31">
-        <f>SUM(U52:U57)</f>
+      <c r="Y58" s="31">
+        <f>SUM(Y52:Y57)</f>
         <v>3359.7999999999997</v>
       </c>
-      <c r="V58" s="31">
-        <f t="shared" ref="V58:W58" si="42">SUM(V52:V57)</f>
+      <c r="Z58" s="31">
+        <f t="shared" ref="Z58:AA58" si="48">SUM(Z52:Z57)</f>
         <v>3789.9</v>
       </c>
-      <c r="W58" s="31">
-        <f t="shared" si="42"/>
+      <c r="AA58" s="31">
+        <f t="shared" si="48"/>
         <v>3887.2000000000003</v>
       </c>
     </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B59" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="P59" s="12">
+      <c r="T59" s="12">
         <v>1039.2</v>
       </c>
-      <c r="Q59" s="12">
+      <c r="U59" s="12">
         <v>979.5</v>
       </c>
-      <c r="R59" s="12">
+      <c r="V59" s="12">
         <v>1014</v>
       </c>
-      <c r="S59" s="12">
+      <c r="W59" s="12">
         <v>969.5</v>
       </c>
-      <c r="T59" s="12">
+      <c r="X59" s="12">
         <v>955.5</v>
       </c>
-      <c r="U59" s="12">
+      <c r="Y59" s="12">
         <v>850.4</v>
       </c>
-      <c r="V59" s="12">
+      <c r="Z59" s="12">
         <v>846.4</v>
       </c>
-      <c r="W59" s="12">
+      <c r="AA59" s="12">
         <v>1070.5999999999999</v>
       </c>
     </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B60" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="P60" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="12">
+      <c r="T60" s="12">
+        <v>0</v>
+      </c>
+      <c r="U60" s="12">
         <v>1511.6</v>
       </c>
-      <c r="R60" s="12">
+      <c r="V60" s="12">
         <v>1239.5</v>
       </c>
-      <c r="S60" s="12">
+      <c r="W60" s="12">
         <v>1111.3</v>
       </c>
-      <c r="T60" s="12">
+      <c r="X60" s="12">
         <v>1134</v>
       </c>
-      <c r="U60" s="12">
+      <c r="Y60" s="12">
         <v>1014.6</v>
       </c>
-      <c r="V60" s="12">
+      <c r="Z60" s="12">
         <v>1013.1</v>
       </c>
-      <c r="W60" s="12">
+      <c r="AA60" s="12">
         <v>1299.5999999999999</v>
       </c>
     </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B61" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="P61" s="12">
+      <c r="T61" s="12">
         <v>67</v>
       </c>
-      <c r="Q61" s="12">
+      <c r="U61" s="12">
         <v>245.2</v>
       </c>
-      <c r="R61" s="12">
+      <c r="V61" s="12">
         <v>283.89999999999998</v>
       </c>
-      <c r="S61" s="12">
+      <c r="W61" s="12">
         <v>303.8</v>
       </c>
-      <c r="T61" s="12">
+      <c r="X61" s="12">
         <v>255.1</v>
       </c>
-      <c r="U61" s="12">
+      <c r="Y61" s="12">
         <v>288.3</v>
       </c>
-      <c r="V61" s="12">
+      <c r="Z61" s="12">
         <v>335.4</v>
       </c>
-      <c r="W61" s="12">
+      <c r="AA61" s="12">
         <v>345.1</v>
       </c>
     </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B62" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="P62" s="12">
+      <c r="T62" s="12">
         <v>919.6</v>
       </c>
-      <c r="Q62" s="12">
+      <c r="U62" s="12">
         <v>915.5</v>
       </c>
-      <c r="R62" s="12">
+      <c r="V62" s="12">
         <v>934.6</v>
       </c>
-      <c r="S62" s="12">
+      <c r="W62" s="12">
         <v>908.7</v>
       </c>
-      <c r="T62" s="12">
+      <c r="X62" s="12">
         <v>898.9</v>
       </c>
-      <c r="U62" s="12">
+      <c r="Y62" s="12">
         <v>888.1</v>
       </c>
-      <c r="V62" s="12">
+      <c r="Z62" s="12">
         <v>888.5</v>
       </c>
-      <c r="W62" s="12">
+      <c r="AA62" s="12">
         <v>904.2</v>
       </c>
     </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B63" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="P63" s="12">
+      <c r="T63" s="12">
         <v>163.69999999999999</v>
       </c>
-      <c r="Q63" s="12">
+      <c r="U63" s="12">
         <v>141</v>
       </c>
-      <c r="R63" s="12">
+      <c r="V63" s="12">
         <v>121.1</v>
       </c>
-      <c r="S63" s="12">
+      <c r="W63" s="12">
         <v>102.9</v>
       </c>
-      <c r="T63" s="12">
+      <c r="X63" s="12">
         <v>88.9</v>
       </c>
-      <c r="U63" s="12">
+      <c r="Y63" s="12">
         <v>75.7</v>
       </c>
-      <c r="V63" s="12">
+      <c r="Z63" s="12">
         <v>62.8</v>
       </c>
-      <c r="W63" s="12">
+      <c r="AA63" s="12">
         <v>93.3</v>
       </c>
     </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B64" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="P64" s="12">
+      <c r="T64" s="12">
         <v>158.5</v>
       </c>
-      <c r="Q64" s="12">
+      <c r="U64" s="12">
         <v>111.9</v>
       </c>
-      <c r="R64" s="12">
+      <c r="V64" s="12">
         <v>86.4</v>
       </c>
-      <c r="S64" s="12">
+      <c r="W64" s="12">
         <v>111.2</v>
       </c>
-      <c r="T64" s="12">
+      <c r="X64" s="12">
         <v>133</v>
       </c>
-      <c r="U64" s="12">
+      <c r="Y64" s="12">
         <v>125.7</v>
       </c>
-      <c r="V64" s="12">
+      <c r="Z64" s="12">
         <v>111.2</v>
       </c>
-      <c r="W64" s="12">
+      <c r="AA64" s="12">
         <v>139.5</v>
       </c>
     </row>
-    <row r="65" spans="1:23" s="31" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:27" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2"/>
       <c r="B65" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="P65" s="31">
-        <f t="shared" ref="P65:T65" si="43">SUM(P59:P64)</f>
+      <c r="T65" s="31">
+        <f t="shared" ref="T65:X65" si="49">SUM(T59:T64)</f>
         <v>2348</v>
       </c>
-      <c r="Q65" s="31">
-        <f t="shared" si="43"/>
+      <c r="U65" s="31">
+        <f t="shared" si="49"/>
         <v>3904.7</v>
       </c>
-      <c r="R65" s="31">
-        <f t="shared" si="43"/>
+      <c r="V65" s="31">
+        <f t="shared" si="49"/>
         <v>3679.5</v>
       </c>
-      <c r="S65" s="31">
-        <f t="shared" si="43"/>
+      <c r="W65" s="31">
+        <f t="shared" si="49"/>
         <v>3507.4</v>
       </c>
-      <c r="T65" s="31">
-        <f t="shared" si="43"/>
+      <c r="X65" s="31">
+        <f t="shared" si="49"/>
         <v>3465.4</v>
       </c>
-      <c r="U65" s="31">
-        <f>SUM(U59:U64)</f>
+      <c r="Y65" s="31">
+        <f>SUM(Y59:Y64)</f>
         <v>3242.7999999999997</v>
       </c>
-      <c r="V65" s="31">
-        <f t="shared" ref="V65:W65" si="44">SUM(V59:V64)</f>
+      <c r="Z65" s="31">
+        <f t="shared" ref="Z65:AA65" si="50">SUM(Z59:Z64)</f>
         <v>3257.4</v>
       </c>
-      <c r="W65" s="31">
-        <f t="shared" si="44"/>
+      <c r="AA65" s="31">
+        <f t="shared" si="50"/>
         <v>3852.3</v>
       </c>
     </row>
-    <row r="66" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B66" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="P66" s="13">
-        <f>P58+P65</f>
+      <c r="T66" s="13">
+        <f t="shared" ref="T66:Y66" si="51">T58+T65</f>
         <v>5942.7999999999993</v>
       </c>
-      <c r="Q66" s="13">
-        <f>Q58+Q65</f>
+      <c r="U66" s="13">
+        <f t="shared" si="51"/>
         <v>7279.9000000000005</v>
       </c>
-      <c r="R66" s="13">
-        <f>R58+R65</f>
+      <c r="V66" s="13">
+        <f t="shared" si="51"/>
         <v>7887.5</v>
       </c>
-      <c r="S66" s="13">
-        <f>S58+S65</f>
+      <c r="W66" s="13">
+        <f t="shared" si="51"/>
         <v>7724.7000000000007</v>
       </c>
-      <c r="T66" s="13">
-        <f>T58+T65</f>
+      <c r="X66" s="13">
+        <f t="shared" si="51"/>
         <v>6789.5</v>
       </c>
-      <c r="U66" s="13">
-        <f>U58+U65</f>
+      <c r="Y66" s="13">
+        <f t="shared" si="51"/>
         <v>6602.5999999999995</v>
       </c>
-      <c r="V66" s="13">
-        <f t="shared" ref="V66:W66" si="45">V58+V65</f>
+      <c r="Z66" s="13">
+        <f t="shared" ref="Z66:AA66" si="52">Z58+Z65</f>
         <v>7047.3</v>
       </c>
-      <c r="W66" s="13">
-        <f t="shared" si="45"/>
+      <c r="AA66" s="13">
+        <f t="shared" si="52"/>
         <v>7739.5</v>
       </c>
     </row>
-    <row r="67" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B67" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="P67" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q67" s="12">
+      <c r="T67" s="12">
+        <v>0</v>
+      </c>
+      <c r="U67" s="12">
         <v>774.6</v>
       </c>
-      <c r="R67" s="12">
-        <v>0</v>
-      </c>
-      <c r="S67" s="12">
+      <c r="V67" s="12">
+        <v>0</v>
+      </c>
+      <c r="W67" s="12">
         <v>499.8</v>
       </c>
-      <c r="T67" s="12">
-        <v>0</v>
-      </c>
-      <c r="U67" s="12">
-        <v>0</v>
-      </c>
-      <c r="V67" s="12">
+      <c r="X67" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y67" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z67" s="12">
         <v>399.7</v>
       </c>
-      <c r="W67" s="31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AA67" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B68" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="P68" s="12">
+      <c r="T68" s="12">
         <v>202.3</v>
       </c>
-      <c r="Q68" s="12">
+      <c r="U68" s="12">
         <v>246.8</v>
       </c>
-      <c r="R68" s="12">
+      <c r="V68" s="12">
         <v>355.9</v>
       </c>
-      <c r="S68" s="12">
+      <c r="W68" s="12">
         <v>448.7</v>
       </c>
-      <c r="T68" s="12">
+      <c r="X68" s="12">
         <v>371.6</v>
       </c>
-      <c r="U68" s="12">
+      <c r="Y68" s="12">
         <v>332.2</v>
       </c>
-      <c r="V68" s="12">
+      <c r="Z68" s="12">
         <v>436</v>
       </c>
-      <c r="W68" s="12">
+      <c r="AA68" s="12">
         <v>431</v>
       </c>
     </row>
-    <row r="69" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B69" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="P69" s="12">
+      <c r="T69" s="12">
         <v>29.4</v>
       </c>
-      <c r="Q69" s="12">
+      <c r="U69" s="12">
         <v>65.099999999999994</v>
       </c>
-      <c r="R69" s="12">
+      <c r="V69" s="12">
         <v>50.6</v>
       </c>
-      <c r="S69" s="12">
+      <c r="W69" s="12">
         <v>53.8</v>
       </c>
-      <c r="T69" s="12">
+      <c r="X69" s="12">
         <v>59.7</v>
       </c>
-      <c r="U69" s="12">
+      <c r="Y69" s="12">
         <v>79.8</v>
       </c>
-      <c r="V69" s="12">
+      <c r="Z69" s="12">
         <v>146.5</v>
       </c>
-      <c r="W69" s="12">
+      <c r="AA69" s="12">
         <v>80</v>
       </c>
     </row>
-    <row r="70" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B70" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="P70" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q70" s="12">
+      <c r="T70" s="12">
+        <v>0</v>
+      </c>
+      <c r="U70" s="12">
         <v>288.39999999999998</v>
       </c>
-      <c r="R70" s="12">
+      <c r="V70" s="12">
         <v>302.89999999999998</v>
       </c>
-      <c r="S70" s="12">
+      <c r="W70" s="12">
         <v>262</v>
       </c>
-      <c r="T70" s="12">
+      <c r="X70" s="12">
         <v>266.7</v>
       </c>
-      <c r="U70" s="12">
+      <c r="Y70" s="12">
         <v>245.5</v>
       </c>
-      <c r="V70" s="12">
+      <c r="Z70" s="12">
         <v>225.4</v>
       </c>
-      <c r="W70" s="12">
+      <c r="AA70" s="12">
         <v>211.7</v>
       </c>
     </row>
-    <row r="71" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B71" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="P71" s="12">
+      <c r="T71" s="12">
         <v>968.4</v>
       </c>
-      <c r="Q71" s="12">
+      <c r="U71" s="12">
         <v>717.1</v>
       </c>
-      <c r="R71" s="12">
+      <c r="V71" s="12">
         <v>875.4</v>
       </c>
-      <c r="S71" s="12">
+      <c r="W71" s="12">
         <v>991.4</v>
       </c>
-      <c r="T71" s="12">
+      <c r="X71" s="12">
         <v>795.5</v>
       </c>
-      <c r="U71" s="12">
+      <c r="Y71" s="12">
         <v>809.7</v>
       </c>
-      <c r="V71" s="12">
+      <c r="Z71" s="12">
         <v>926.1</v>
       </c>
-      <c r="W71" s="12">
+      <c r="AA71" s="12">
         <v>1103.8</v>
       </c>
     </row>
-    <row r="72" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B72" s="29" t="s">
         <v>113</v>
       </c>
-      <c r="P72" s="31">
-        <f t="shared" ref="P72:Q72" si="46">SUM(P67:P71)</f>
+      <c r="T72" s="31">
+        <f t="shared" ref="T72:U72" si="53">SUM(T67:T71)</f>
         <v>1200.0999999999999</v>
       </c>
-      <c r="Q72" s="31">
-        <f t="shared" si="46"/>
+      <c r="U72" s="31">
+        <f t="shared" si="53"/>
         <v>2092</v>
       </c>
-      <c r="R72" s="31">
-        <f>SUM(R67:R71)</f>
+      <c r="V72" s="31">
+        <f>SUM(V67:V71)</f>
         <v>1584.8</v>
       </c>
-      <c r="S72" s="31">
-        <f t="shared" ref="S72:W72" si="47">SUM(S67:S71)</f>
+      <c r="W72" s="31">
+        <f t="shared" ref="W72:AA72" si="54">SUM(W67:W71)</f>
         <v>2255.6999999999998</v>
       </c>
-      <c r="T72" s="31">
-        <f t="shared" si="47"/>
+      <c r="X72" s="31">
+        <f t="shared" si="54"/>
         <v>1493.5</v>
       </c>
-      <c r="U72" s="31">
-        <f t="shared" si="47"/>
+      <c r="Y72" s="31">
+        <f t="shared" si="54"/>
         <v>1467.2</v>
       </c>
-      <c r="V72" s="31">
-        <f t="shared" si="47"/>
+      <c r="Z72" s="31">
+        <f t="shared" si="54"/>
         <v>2133.7000000000003</v>
       </c>
-      <c r="W72" s="31">
-        <f t="shared" si="47"/>
+      <c r="AA72" s="31">
+        <f t="shared" si="54"/>
         <v>1826.5</v>
       </c>
     </row>
-    <row r="73" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B73" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="P73" s="12">
+      <c r="T73" s="12">
         <v>689.1</v>
       </c>
-      <c r="Q73" s="12">
+      <c r="U73" s="12">
         <v>396.4</v>
       </c>
-      <c r="R73" s="12">
+      <c r="V73" s="12">
         <v>1632.9</v>
       </c>
-      <c r="S73" s="12">
+      <c r="W73" s="12">
         <v>1136.5</v>
       </c>
-      <c r="T73" s="12">
+      <c r="X73" s="12">
         <v>1138.5</v>
       </c>
-      <c r="U73" s="12">
+      <c r="Y73" s="12">
         <v>1140.5</v>
       </c>
-      <c r="V73" s="12">
+      <c r="Z73" s="12">
         <v>742.9</v>
       </c>
-      <c r="W73" s="12">
+      <c r="AA73" s="12">
         <v>1238.9000000000001</v>
       </c>
     </row>
-    <row r="74" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B74" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="P74" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q74" s="12">
-        <v>0</v>
-      </c>
-      <c r="R74" s="12">
-        <v>0</v>
-      </c>
-      <c r="S74" s="12">
+      <c r="T74" s="12">
+        <v>0</v>
+      </c>
+      <c r="U74" s="12">
+        <v>0</v>
+      </c>
+      <c r="V74" s="12">
+        <v>0</v>
+      </c>
+      <c r="W74" s="12">
         <v>341.6</v>
       </c>
-      <c r="T74" s="12">
+      <c r="X74" s="12">
         <v>315.3</v>
       </c>
-      <c r="U74" s="12">
+      <c r="Y74" s="12">
         <v>256.10000000000002</v>
       </c>
-      <c r="V74" s="12">
+      <c r="Z74" s="12">
         <v>234.8</v>
       </c>
-      <c r="W74" s="12">
+      <c r="AA74" s="12">
         <v>212.3</v>
       </c>
     </row>
-    <row r="75" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B75" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="P75" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q75" s="12">
+      <c r="T75" s="12">
+        <v>0</v>
+      </c>
+      <c r="U75" s="12">
         <v>1568.3</v>
       </c>
-      <c r="R75" s="12">
+      <c r="V75" s="12">
         <v>1294.5</v>
       </c>
-      <c r="S75" s="12">
+      <c r="W75" s="12">
         <v>1132.2</v>
       </c>
-      <c r="T75" s="12">
+      <c r="X75" s="12">
         <v>1141.0999999999999</v>
       </c>
-      <c r="U75" s="12">
+      <c r="Y75" s="12">
         <v>1014</v>
       </c>
-      <c r="V75" s="12">
+      <c r="Z75" s="12">
         <v>1044.7</v>
       </c>
-      <c r="W75" s="12">
+      <c r="AA75" s="12">
         <v>1325.8</v>
       </c>
     </row>
-    <row r="76" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B76" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="P76" s="12">
+      <c r="T76" s="12">
         <v>146.69999999999999</v>
       </c>
-      <c r="Q76" s="12">
+      <c r="U76" s="12">
         <v>132.69999999999999</v>
       </c>
-      <c r="R76" s="12">
+      <c r="V76" s="12">
         <v>118.7</v>
       </c>
-      <c r="S76" s="12">
+      <c r="W76" s="12">
         <v>98.9</v>
       </c>
-      <c r="T76" s="12">
+      <c r="X76" s="12">
         <v>75.900000000000006</v>
       </c>
-      <c r="U76" s="12">
+      <c r="Y76" s="12">
         <v>42.2</v>
       </c>
-      <c r="V76" s="12">
+      <c r="Z76" s="12">
         <v>193.3</v>
       </c>
-      <c r="W76" s="12">
+      <c r="AA76" s="12">
         <v>168.7</v>
       </c>
     </row>
-    <row r="77" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B77" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="P77" s="12">
+      <c r="T77" s="12">
         <v>78.8</v>
       </c>
-      <c r="Q77" s="12">
+      <c r="U77" s="12">
         <v>88.9</v>
       </c>
-      <c r="R77" s="12">
+      <c r="V77" s="12">
         <v>91.4</v>
       </c>
-      <c r="S77" s="12">
+      <c r="W77" s="12">
         <v>91.9</v>
       </c>
-      <c r="T77" s="12">
+      <c r="X77" s="12">
         <v>93.8</v>
       </c>
-      <c r="U77" s="12">
+      <c r="Y77" s="12">
         <v>118.7</v>
       </c>
-      <c r="V77" s="12">
-        <v>0</v>
-      </c>
-      <c r="W77" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="Z77" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B78" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="P78" s="12">
+      <c r="T78" s="12">
         <v>540.9</v>
       </c>
-      <c r="Q78" s="12">
+      <c r="U78" s="12">
         <v>308.5</v>
       </c>
-      <c r="R78" s="12">
+      <c r="V78" s="12">
         <v>560.79999999999995</v>
       </c>
-      <c r="S78" s="12">
+      <c r="W78" s="12">
         <v>131.9</v>
       </c>
-      <c r="T78" s="12">
+      <c r="X78" s="12">
         <v>100.9</v>
       </c>
-      <c r="U78" s="12">
+      <c r="Y78" s="12">
         <v>113.6</v>
       </c>
-      <c r="V78" s="12">
+      <c r="Z78" s="12">
         <v>109.4</v>
       </c>
-      <c r="W78" s="12">
+      <c r="AA78" s="12">
         <v>125.9</v>
       </c>
     </row>
-    <row r="79" spans="1:23" s="31" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:27" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A79" s="2"/>
       <c r="B79" s="29" t="s">
         <v>120</v>
       </c>
-      <c r="P79" s="31">
-        <f t="shared" ref="P79:T79" si="48">SUM(P73:P78)</f>
+      <c r="T79" s="31">
+        <f t="shared" ref="T79:X79" si="55">SUM(T73:T78)</f>
         <v>1455.5</v>
       </c>
-      <c r="Q79" s="31">
-        <f t="shared" si="48"/>
+      <c r="U79" s="31">
+        <f t="shared" si="55"/>
         <v>2494.7999999999997</v>
       </c>
-      <c r="R79" s="31">
-        <f>SUM(R73:R78)</f>
+      <c r="V79" s="31">
+        <f>SUM(V73:V78)</f>
         <v>3698.3</v>
       </c>
-      <c r="S79" s="31">
-        <f t="shared" si="48"/>
+      <c r="W79" s="31">
+        <f t="shared" si="55"/>
         <v>2933.0000000000005</v>
       </c>
-      <c r="T79" s="31">
-        <f t="shared" si="48"/>
+      <c r="X79" s="31">
+        <f t="shared" si="55"/>
         <v>2865.5</v>
       </c>
-      <c r="U79" s="31">
-        <f>SUM(U73:U78)</f>
+      <c r="Y79" s="31">
+        <f>SUM(Y73:Y78)</f>
         <v>2685.0999999999995</v>
       </c>
-      <c r="V79" s="31">
-        <f t="shared" ref="V79:W79" si="49">SUM(V73:V78)</f>
+      <c r="Z79" s="31">
+        <f t="shared" ref="Z79:AA79" si="56">SUM(Z73:Z78)</f>
         <v>2325.1000000000004</v>
       </c>
-      <c r="W79" s="31">
-        <f t="shared" si="49"/>
+      <c r="AA79" s="31">
+        <f t="shared" si="56"/>
         <v>3071.6</v>
       </c>
     </row>
-    <row r="80" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B80" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="P80" s="13">
-        <f>P72+P79</f>
+      <c r="T80" s="13">
+        <f t="shared" ref="T80:Y80" si="57">T72+T79</f>
         <v>2655.6</v>
       </c>
-      <c r="Q80" s="13">
-        <f>Q72+Q79</f>
+      <c r="U80" s="13">
+        <f t="shared" si="57"/>
         <v>4586.7999999999993</v>
       </c>
-      <c r="R80" s="13">
-        <f>R72+R79</f>
+      <c r="V80" s="13">
+        <f t="shared" si="57"/>
         <v>5283.1</v>
       </c>
-      <c r="S80" s="13">
-        <f>S72+S79</f>
+      <c r="W80" s="13">
+        <f t="shared" si="57"/>
         <v>5188.7000000000007</v>
       </c>
-      <c r="T80" s="13">
-        <f>T72+T79</f>
+      <c r="X80" s="13">
+        <f t="shared" si="57"/>
         <v>4359</v>
       </c>
-      <c r="U80" s="13">
-        <f>U72+U79</f>
+      <c r="Y80" s="13">
+        <f t="shared" si="57"/>
         <v>4152.2999999999993</v>
       </c>
-      <c r="V80" s="13">
-        <f t="shared" ref="V80:W80" si="50">V72+V79</f>
+      <c r="Z80" s="13">
+        <f t="shared" ref="Z80:AA80" si="58">Z72+Z79</f>
         <v>4458.8000000000011</v>
       </c>
-      <c r="W80" s="13">
-        <f t="shared" si="50"/>
+      <c r="AA80" s="13">
+        <f t="shared" si="58"/>
         <v>4898.1000000000004</v>
       </c>
     </row>
-    <row r="81" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B81" s="29" t="s">
         <v>122</v>
       </c>
@@ -5872,32 +6271,36 @@
       <c r="M81" s="31"/>
       <c r="N81" s="31"/>
       <c r="O81" s="31"/>
-      <c r="P81" s="31">
+      <c r="P81" s="31"/>
+      <c r="Q81" s="31"/>
+      <c r="R81" s="31"/>
+      <c r="S81" s="31"/>
+      <c r="T81" s="31">
         <v>3287.2000000000003</v>
       </c>
-      <c r="Q81" s="31">
+      <c r="U81" s="31">
         <v>2693.1000000000013</v>
       </c>
-      <c r="R81" s="31">
+      <c r="V81" s="31">
         <v>2604.3999999999987</v>
       </c>
-      <c r="S81" s="31">
+      <c r="W81" s="31">
         <v>2536</v>
       </c>
-      <c r="T81" s="31">
+      <c r="X81" s="31">
         <v>2430.4999999999991</v>
       </c>
-      <c r="U81" s="31">
+      <c r="Y81" s="31">
         <v>2450.3000000000006</v>
       </c>
-      <c r="V81" s="12">
+      <c r="Z81" s="12">
         <v>2588.5</v>
       </c>
-      <c r="W81" s="12">
+      <c r="AA81" s="12">
         <v>2841.4</v>
       </c>
     </row>
-    <row r="82" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B82" s="1" t="s">
         <v>123</v>
       </c>
@@ -5914,153 +6317,145 @@
       <c r="M82" s="13"/>
       <c r="N82" s="13"/>
       <c r="O82" s="13"/>
-      <c r="P82" s="13">
-        <f>P81+P80</f>
+      <c r="P82" s="13"/>
+      <c r="Q82" s="13"/>
+      <c r="R82" s="13"/>
+      <c r="S82" s="13"/>
+      <c r="T82" s="13">
+        <f t="shared" ref="T82:Y82" si="59">T81+T80</f>
         <v>5942.8</v>
       </c>
-      <c r="Q82" s="13">
-        <f>Q81+Q80</f>
+      <c r="U82" s="13">
+        <f t="shared" si="59"/>
         <v>7279.9000000000005</v>
       </c>
-      <c r="R82" s="13">
-        <f>R81+R80</f>
+      <c r="V82" s="13">
+        <f t="shared" si="59"/>
         <v>7887.4999999999991</v>
       </c>
-      <c r="S82" s="13">
-        <f>S81+S80</f>
+      <c r="W82" s="13">
+        <f t="shared" si="59"/>
         <v>7724.7000000000007</v>
       </c>
-      <c r="T82" s="13">
-        <f>T81+T80</f>
+      <c r="X82" s="13">
+        <f t="shared" si="59"/>
         <v>6789.4999999999991</v>
       </c>
-      <c r="U82" s="13">
-        <f>U81+U80</f>
+      <c r="Y82" s="13">
+        <f t="shared" si="59"/>
         <v>6602.6</v>
       </c>
-      <c r="V82" s="13">
-        <f t="shared" ref="V82:W82" si="51">V81+V80</f>
+      <c r="Z82" s="13">
+        <f t="shared" ref="Z82:AA82" si="60">Z81+Z80</f>
         <v>7047.3000000000011</v>
       </c>
-      <c r="W82" s="13">
-        <f t="shared" si="51"/>
+      <c r="AA82" s="13">
+        <f t="shared" si="60"/>
         <v>7739.5</v>
       </c>
     </row>
-    <row r="85" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="85" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B85" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="P85" s="12">
-        <f>P32</f>
+      <c r="T85" s="12">
+        <f t="shared" ref="T85:Y85" si="61">T32</f>
         <v>430.89999999999964</v>
       </c>
-      <c r="Q85" s="12">
-        <f>Q32</f>
+      <c r="U85" s="12">
+        <f t="shared" si="61"/>
         <v>384.30000000000041</v>
       </c>
-      <c r="R85" s="12">
-        <f>R32</f>
+      <c r="V85" s="12">
+        <f t="shared" si="61"/>
         <v>-121.09999999999991</v>
       </c>
-      <c r="S85" s="12">
-        <f>S32</f>
+      <c r="W85" s="12">
+        <f t="shared" si="61"/>
         <v>600.10000000000014</v>
       </c>
-      <c r="T85" s="12">
-        <f>T32</f>
+      <c r="X85" s="12">
+        <f t="shared" si="61"/>
         <v>522.70000000000027</v>
       </c>
-      <c r="U85" s="12">
-        <f>U32</f>
+      <c r="Y85" s="12">
+        <f t="shared" si="61"/>
         <v>646.29999999999916</v>
       </c>
-      <c r="V85" s="12">
-        <f t="shared" ref="V85:W85" si="52">V32</f>
+      <c r="Z85" s="12">
+        <f t="shared" ref="Z85:AA85" si="62">Z32</f>
         <v>742.89999999999941</v>
       </c>
-      <c r="W85" s="12">
-        <f t="shared" si="52"/>
+      <c r="AA85" s="12">
+        <f t="shared" si="62"/>
         <v>941.0999999999998</v>
       </c>
     </row>
-    <row r="86" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="86" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B86" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="P86" s="12">
+      <c r="T86" s="12">
         <v>281.3</v>
       </c>
-      <c r="Q86" s="12">
+      <c r="U86" s="12">
         <v>269.5</v>
       </c>
-      <c r="R86" s="12">
+      <c r="V86" s="12">
         <v>247.6</v>
       </c>
-      <c r="S86" s="12">
+      <c r="W86" s="12">
         <v>229.7</v>
       </c>
-      <c r="T86" s="12">
+      <c r="X86" s="12">
         <v>220.5</v>
       </c>
-      <c r="U86" s="12">
+      <c r="Y86" s="12">
         <v>229</v>
       </c>
-      <c r="V86" s="12">
+      <c r="Z86" s="12">
         <v>219.6</v>
       </c>
-      <c r="W86" s="12">
+      <c r="AA86" s="12">
         <v>233</v>
       </c>
     </row>
-    <row r="87" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="87" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B87" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="P87" s="12">
+      <c r="T87" s="12">
         <v>8.5</v>
       </c>
-      <c r="Q87" s="12">
+      <c r="U87" s="12">
         <v>-168.8</v>
       </c>
-      <c r="R87" s="12">
+      <c r="V87" s="12">
         <v>35.6</v>
       </c>
-      <c r="S87" s="12">
+      <c r="W87" s="12">
         <v>-46.1</v>
       </c>
-      <c r="T87" s="12">
+      <c r="X87" s="12">
         <v>3.9</v>
       </c>
-      <c r="U87" s="12">
+      <c r="Y87" s="12">
         <v>-41.1</v>
       </c>
-      <c r="V87" s="12">
+      <c r="Z87" s="12">
         <v>-50</v>
       </c>
-      <c r="W87" s="12">
+      <c r="AA87" s="12">
         <v>8.4</v>
       </c>
     </row>
-    <row r="88" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="88" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B88" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="P88" s="12">
+      <c r="T88" s="12">
         <v>11.6</v>
       </c>
-      <c r="Q88" s="12">
-        <v>0</v>
-      </c>
-      <c r="R88" s="12">
-        <v>0</v>
-      </c>
-      <c r="S88" s="12">
-        <v>0</v>
-      </c>
-      <c r="T88" s="12">
-        <v>0</v>
-      </c>
       <c r="U88" s="12">
         <v>0</v>
       </c>
@@ -6070,786 +6465,798 @@
       <c r="W88" s="12">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z88" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA88" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B89" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="P89" s="12">
+      <c r="T89" s="12">
         <v>88.6</v>
       </c>
-      <c r="Q89" s="12">
+      <c r="U89" s="12">
         <v>100.6</v>
       </c>
-      <c r="R89" s="12">
+      <c r="V89" s="12">
         <v>72.7</v>
       </c>
-      <c r="S89" s="12">
+      <c r="W89" s="12">
         <v>81.7</v>
       </c>
-      <c r="T89" s="12">
+      <c r="X89" s="12">
         <v>75.5</v>
       </c>
-      <c r="U89" s="12">
+      <c r="Y89" s="12">
         <v>99.5</v>
       </c>
-      <c r="V89" s="12">
+      <c r="Z89" s="12">
         <v>107.9</v>
       </c>
-      <c r="W89" s="12">
+      <c r="AA89" s="12">
         <v>111</v>
       </c>
     </row>
-    <row r="90" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="90" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B90" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="P90" s="12">
+      <c r="T90" s="12">
         <v>25.8</v>
       </c>
-      <c r="Q90" s="12">
+      <c r="U90" s="12">
         <v>38.700000000000003</v>
       </c>
-      <c r="R90" s="12">
+      <c r="V90" s="12">
         <v>96</v>
       </c>
-      <c r="S90" s="12">
+      <c r="W90" s="12">
         <v>21.3</v>
       </c>
-      <c r="T90" s="12">
+      <c r="X90" s="12">
         <v>9.6999999999999993</v>
       </c>
-      <c r="U90" s="12">
-        <v>0</v>
-      </c>
-      <c r="V90" s="12">
-        <v>0</v>
-      </c>
-      <c r="W90" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="Y90" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z90" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA90" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B91" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="P91" s="12">
+      <c r="T91" s="12">
         <v>0.4</v>
       </c>
-      <c r="Q91" s="12">
+      <c r="U91" s="12">
         <v>58.7</v>
       </c>
-      <c r="R91" s="12">
+      <c r="V91" s="12">
         <v>-27.6</v>
       </c>
-      <c r="S91" s="12">
+      <c r="W91" s="12">
         <v>-2.2000000000000002</v>
       </c>
-      <c r="T91" s="12">
+      <c r="X91" s="12">
         <v>2.2999999999999998</v>
       </c>
-      <c r="U91" s="12">
+      <c r="Y91" s="12">
         <v>7.3</v>
       </c>
-      <c r="V91" s="12">
+      <c r="Z91" s="12">
         <v>9.1999999999999993</v>
       </c>
-      <c r="W91" s="12">
+      <c r="AA91" s="12">
         <v>13.6</v>
       </c>
     </row>
-    <row r="92" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="92" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B92" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="P92" s="12">
+      <c r="T92" s="12">
         <v>6.5</v>
       </c>
-      <c r="Q92" s="12">
+      <c r="U92" s="12">
         <v>-2.2999999999999998</v>
       </c>
-      <c r="R92" s="12">
+      <c r="V92" s="12">
         <v>1.8</v>
       </c>
-      <c r="S92" s="12">
+      <c r="W92" s="12">
         <v>1</v>
       </c>
-      <c r="T92" s="12">
+      <c r="X92" s="12">
         <v>1</v>
       </c>
-      <c r="U92" s="12">
+      <c r="Y92" s="12">
         <v>13.7</v>
       </c>
-      <c r="V92" s="12">
+      <c r="Z92" s="12">
         <v>3.6</v>
       </c>
-      <c r="W92" s="12">
+      <c r="AA92" s="12">
         <v>5.4</v>
       </c>
     </row>
-    <row r="93" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="93" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B93" s="9" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="94" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="94" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B94" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="P94" s="12">
+      <c r="T94" s="12">
         <v>10.1</v>
       </c>
-      <c r="Q94" s="12">
+      <c r="U94" s="12">
         <v>57.6</v>
       </c>
-      <c r="R94" s="12">
+      <c r="V94" s="12">
         <v>-143</v>
       </c>
-      <c r="S94" s="12">
+      <c r="W94" s="12">
         <v>32.4</v>
       </c>
-      <c r="T94" s="12">
+      <c r="X94" s="12">
         <v>-52.6</v>
       </c>
-      <c r="U94" s="12">
+      <c r="Y94" s="12">
         <v>-15.3</v>
       </c>
-      <c r="V94" s="12">
+      <c r="Z94" s="12">
         <v>-27.6</v>
       </c>
-      <c r="W94" s="12">
+      <c r="AA94" s="12">
         <v>-35.6</v>
       </c>
     </row>
-    <row r="95" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="95" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B95" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="P95" s="12">
+      <c r="T95" s="12">
         <v>-83.6</v>
       </c>
-      <c r="Q95" s="12">
+      <c r="U95" s="12">
         <v>72.3</v>
       </c>
-      <c r="R95" s="12">
+      <c r="V95" s="12">
         <v>3.7</v>
       </c>
-      <c r="S95" s="12">
+      <c r="W95" s="12">
         <v>-269.3</v>
       </c>
-      <c r="T95" s="12">
+      <c r="X95" s="12">
         <v>-106.2</v>
       </c>
-      <c r="U95" s="12">
+      <c r="Y95" s="12">
         <v>149.1</v>
       </c>
-      <c r="V95" s="12">
+      <c r="Z95" s="12">
         <v>-52.6</v>
       </c>
-      <c r="W95" s="12">
+      <c r="AA95" s="12">
         <v>-44.2</v>
       </c>
     </row>
-    <row r="96" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="96" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B96" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="P96" s="12">
+      <c r="T96" s="12">
         <v>-40.5</v>
       </c>
-      <c r="Q96" s="12">
+      <c r="U96" s="12">
         <v>58.2</v>
       </c>
-      <c r="R96" s="12">
+      <c r="V96" s="12">
         <v>5.2</v>
       </c>
-      <c r="S96" s="12">
+      <c r="W96" s="12">
         <v>-28.3</v>
       </c>
-      <c r="T96" s="12">
+      <c r="X96" s="12">
         <v>-19.899999999999999</v>
       </c>
-      <c r="U96" s="12">
+      <c r="Y96" s="12">
         <v>16.100000000000001</v>
       </c>
-      <c r="V96" s="12">
+      <c r="Z96" s="12">
         <v>-47.4</v>
       </c>
-      <c r="W96" s="12">
+      <c r="AA96" s="12">
         <v>-20</v>
       </c>
     </row>
-    <row r="97" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="97" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B97" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="P97" s="12">
+      <c r="T97" s="12">
         <v>-4.7</v>
       </c>
-      <c r="Q97" s="12">
+      <c r="U97" s="12">
         <v>-64.3</v>
       </c>
-      <c r="R97" s="12">
+      <c r="V97" s="12">
         <v>296.8</v>
       </c>
-      <c r="S97" s="12">
+      <c r="W97" s="12">
         <v>194.6</v>
       </c>
-      <c r="T97" s="12">
+      <c r="X97" s="12">
         <v>-225</v>
       </c>
-      <c r="U97" s="12">
+      <c r="Y97" s="12">
         <v>15.6</v>
       </c>
-      <c r="V97" s="12">
+      <c r="Z97" s="12">
         <v>226.2</v>
       </c>
-      <c r="W97" s="12">
+      <c r="AA97" s="12">
         <v>142.19999999999999</v>
       </c>
     </row>
-    <row r="98" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="98" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B98" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="P98" s="12">
+      <c r="T98" s="12">
         <v>29.7</v>
       </c>
-      <c r="Q98" s="12">
+      <c r="U98" s="12">
         <v>-42.5</v>
       </c>
-      <c r="R98" s="12">
+      <c r="V98" s="12">
         <v>-37.799999999999997</v>
       </c>
-      <c r="S98" s="12">
+      <c r="W98" s="12">
         <v>-62.3</v>
       </c>
-      <c r="T98" s="12">
+      <c r="X98" s="12">
         <v>5.7</v>
       </c>
-      <c r="U98" s="12">
+      <c r="Y98" s="12">
         <v>-18.5</v>
       </c>
-      <c r="V98" s="12">
+      <c r="Z98" s="12">
         <v>27.9</v>
       </c>
-      <c r="W98" s="12">
+      <c r="AA98" s="12">
         <v>-94.1</v>
       </c>
     </row>
-    <row r="99" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="99" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B99" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="P99" s="12">
+      <c r="T99" s="12">
         <v>-16.5</v>
       </c>
-      <c r="Q99" s="12">
-        <v>0</v>
-      </c>
-      <c r="R99" s="12">
+      <c r="U99" s="12">
+        <v>0</v>
+      </c>
+      <c r="V99" s="12">
         <v>-3.2</v>
       </c>
-      <c r="S99" s="12">
+      <c r="W99" s="12">
         <v>-61.6</v>
       </c>
-      <c r="T99" s="12">
+      <c r="X99" s="12">
         <v>-17.5</v>
       </c>
-      <c r="U99" s="12">
+      <c r="Y99" s="12">
         <v>-36.299999999999997</v>
       </c>
-      <c r="V99" s="12">
+      <c r="Z99" s="12">
         <v>11.7</v>
       </c>
-      <c r="W99" s="12">
+      <c r="AA99" s="12">
         <v>-22.3</v>
       </c>
     </row>
-    <row r="100" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="100" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B100" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="P100" s="12">
+      <c r="T100" s="12">
         <v>35.700000000000003</v>
       </c>
-      <c r="Q100" s="12">
+      <c r="U100" s="12">
         <v>-7.4</v>
       </c>
-      <c r="R100" s="12">
+      <c r="V100" s="12">
         <v>-45.8</v>
       </c>
-      <c r="S100" s="12">
+      <c r="W100" s="12">
         <v>24.9</v>
       </c>
-      <c r="T100" s="12">
+      <c r="X100" s="12">
         <v>-9.1</v>
       </c>
-      <c r="U100" s="12">
+      <c r="Y100" s="12">
         <v>4.3</v>
       </c>
-      <c r="V100" s="12">
+      <c r="Z100" s="12">
         <v>63.7</v>
       </c>
-      <c r="W100" s="12">
+      <c r="AA100" s="12">
         <v>-84.3</v>
       </c>
     </row>
-    <row r="101" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="101" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B101" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="P101" s="13">
-        <f t="shared" ref="P101:T101" si="53">P85+SUM(P86:P92)+SUM(P94:P100)</f>
+      <c r="T101" s="13">
+        <f t="shared" ref="T101:X101" si="63">T85+SUM(T86:T92)+SUM(T94:T100)</f>
         <v>783.79999999999973</v>
-      </c>
-      <c r="Q101" s="13">
-        <f>Q85+SUM(Q86:Q92)+SUM(Q94:Q100)</f>
-        <v>754.60000000000036</v>
-      </c>
-      <c r="R101" s="13">
-        <f t="shared" si="53"/>
-        <v>380.90000000000003</v>
-      </c>
-      <c r="S101" s="13">
-        <f t="shared" si="53"/>
-        <v>715.90000000000032</v>
-      </c>
-      <c r="T101" s="13">
-        <f t="shared" si="53"/>
-        <v>411.00000000000017</v>
       </c>
       <c r="U101" s="13">
         <f>U85+SUM(U86:U92)+SUM(U94:U100)</f>
+        <v>754.60000000000036</v>
+      </c>
+      <c r="V101" s="13">
+        <f t="shared" si="63"/>
+        <v>380.90000000000003</v>
+      </c>
+      <c r="W101" s="13">
+        <f t="shared" si="63"/>
+        <v>715.90000000000032</v>
+      </c>
+      <c r="X101" s="13">
+        <f t="shared" si="63"/>
+        <v>411.00000000000017</v>
+      </c>
+      <c r="Y101" s="13">
+        <f>Y85+SUM(Y86:Y92)+SUM(Y94:Y100)</f>
         <v>1069.6999999999991</v>
       </c>
-      <c r="V101" s="13">
-        <f t="shared" ref="V101:W101" si="54">V85+SUM(V86:V92)+SUM(V94:V100)</f>
+      <c r="Z101" s="13">
+        <f t="shared" ref="Z101:AA101" si="64">Z85+SUM(Z86:Z92)+SUM(Z94:Z100)</f>
         <v>1235.0999999999995</v>
       </c>
-      <c r="W101" s="13">
-        <f t="shared" si="54"/>
+      <c r="AA101" s="13">
+        <f t="shared" si="64"/>
         <v>1154.1999999999998</v>
       </c>
     </row>
-    <row r="102" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="102" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B102" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="P102" s="12">
+      <c r="T102" s="12">
         <v>-197.7</v>
       </c>
-      <c r="Q102" s="12">
+      <c r="U102" s="12">
         <v>-270.3</v>
       </c>
-      <c r="R102" s="12">
+      <c r="V102" s="12">
         <v>-107.8</v>
       </c>
-      <c r="S102" s="12">
+      <c r="W102" s="12">
         <v>-166.9</v>
       </c>
-      <c r="T102" s="12">
+      <c r="X102" s="12">
         <v>-217.5</v>
       </c>
-      <c r="U102" s="12">
+      <c r="Y102" s="12">
         <v>-164.8</v>
       </c>
-      <c r="V102" s="12">
+      <c r="Z102" s="12">
         <v>-216.2</v>
       </c>
-      <c r="W102" s="12">
+      <c r="AA102" s="12">
         <v>-408.1</v>
       </c>
     </row>
-    <row r="103" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="103" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B103" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="P103" s="12">
+      <c r="T103" s="12">
         <v>-3030.8</v>
       </c>
-      <c r="Q103" s="12">
+      <c r="U103" s="12">
         <v>-1289.7</v>
       </c>
-      <c r="R103" s="12">
+      <c r="V103" s="12">
         <v>-704.6</v>
       </c>
-      <c r="S103" s="12">
+      <c r="W103" s="12">
         <v>-1510.6</v>
       </c>
-      <c r="T103" s="12">
+      <c r="X103" s="12">
         <v>-598.6</v>
       </c>
-      <c r="U103" s="12">
+      <c r="Y103" s="12">
         <v>-392.8</v>
       </c>
-      <c r="V103" s="12">
+      <c r="Z103" s="12">
         <v>-781.8</v>
       </c>
-      <c r="W103" s="12">
+      <c r="AA103" s="12">
         <v>-634</v>
       </c>
     </row>
-    <row r="104" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="104" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B104" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="P104" s="12">
+      <c r="T104" s="12">
         <v>2357.5</v>
       </c>
-      <c r="Q104" s="12">
+      <c r="U104" s="12">
         <v>2240.4</v>
       </c>
-      <c r="R104" s="12">
+      <c r="V104" s="12">
         <v>1007.2</v>
       </c>
-      <c r="S104" s="12">
+      <c r="W104" s="12">
         <v>964.6</v>
       </c>
-      <c r="T104" s="12">
+      <c r="X104" s="12">
         <v>1293.4000000000001</v>
       </c>
-      <c r="U104" s="12">
+      <c r="Y104" s="12">
         <v>304.3</v>
       </c>
-      <c r="V104" s="12">
+      <c r="Z104" s="12">
         <v>734.3</v>
       </c>
-      <c r="W104" s="12">
+      <c r="AA104" s="12">
         <v>723.6</v>
       </c>
     </row>
-    <row r="105" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="105" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B105" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="P105" s="12">
+      <c r="T105" s="12">
         <v>20</v>
       </c>
-      <c r="Q105" s="12">
+      <c r="U105" s="12">
         <v>20.8</v>
       </c>
-      <c r="R105" s="12">
-        <v>0</v>
-      </c>
-      <c r="S105" s="12">
-        <v>0</v>
-      </c>
-      <c r="T105" s="12">
-        <v>0</v>
-      </c>
-      <c r="U105" s="12">
-        <v>0</v>
-      </c>
       <c r="V105" s="12">
         <v>0</v>
       </c>
       <c r="W105" s="12">
         <v>0</v>
       </c>
-    </row>
-    <row r="106" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X105" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y105" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z105" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA105" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B106" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="P106" s="12">
+      <c r="T106" s="12">
         <f>-23.8-4.5</f>
         <v>-28.3</v>
       </c>
-      <c r="Q106" s="12">
+      <c r="U106" s="12">
         <v>0.9</v>
       </c>
-      <c r="R106" s="12">
+      <c r="V106" s="12">
         <v>0.2</v>
       </c>
-      <c r="S106" s="12">
+      <c r="W106" s="12">
         <v>-5</v>
       </c>
-      <c r="T106" s="12">
+      <c r="X106" s="12">
         <v>-5.8</v>
       </c>
-      <c r="U106" s="12">
+      <c r="Y106" s="12">
         <v>-3.5</v>
       </c>
-      <c r="V106" s="12">
+      <c r="Z106" s="12">
         <v>-0.4</v>
       </c>
-      <c r="W106" s="12">
+      <c r="AA106" s="12">
         <f>-41.2+3.1</f>
         <v>-38.1</v>
       </c>
     </row>
-    <row r="107" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="107" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B107" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="P107" s="13">
-        <f t="shared" ref="P107:T107" si="55">SUM(P102:P106)</f>
+      <c r="T107" s="13">
+        <f t="shared" ref="T107:X107" si="65">SUM(T102:T106)</f>
         <v>-879.3</v>
       </c>
-      <c r="Q107" s="13">
-        <f t="shared" si="55"/>
+      <c r="U107" s="13">
+        <f t="shared" si="65"/>
         <v>702.1</v>
       </c>
-      <c r="R107" s="13">
-        <f t="shared" si="55"/>
+      <c r="V107" s="13">
+        <f t="shared" si="65"/>
         <v>195.00000000000006</v>
       </c>
-      <c r="S107" s="13">
-        <f t="shared" si="55"/>
+      <c r="W107" s="13">
+        <f t="shared" si="65"/>
         <v>-717.9</v>
       </c>
-      <c r="T107" s="13">
-        <f t="shared" si="55"/>
+      <c r="X107" s="13">
+        <f t="shared" si="65"/>
         <v>471.50000000000006</v>
       </c>
-      <c r="U107" s="13">
-        <f>SUM(U102:U106)</f>
+      <c r="Y107" s="13">
+        <f>SUM(Y102:Y106)</f>
         <v>-256.8</v>
       </c>
-      <c r="V107" s="13">
-        <f t="shared" ref="V107:W107" si="56">SUM(V102:V106)</f>
+      <c r="Z107" s="13">
+        <f t="shared" ref="Z107:AA107" si="66">SUM(Z102:Z106)</f>
         <v>-264.10000000000002</v>
       </c>
-      <c r="W107" s="13">
-        <f t="shared" si="56"/>
+      <c r="AA107" s="13">
+        <f t="shared" si="66"/>
         <v>-356.59999999999991</v>
       </c>
     </row>
-    <row r="108" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="108" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B108" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="P108" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q108" s="12">
+      <c r="T108" s="12">
+        <v>0</v>
+      </c>
+      <c r="U108" s="12">
         <v>475</v>
       </c>
-      <c r="R108" s="12">
-        <v>0</v>
-      </c>
-      <c r="S108" s="12">
-        <v>0</v>
-      </c>
-      <c r="T108" s="12">
-        <v>0</v>
-      </c>
-      <c r="U108" s="12">
-        <v>0</v>
-      </c>
       <c r="V108" s="12">
         <v>0</v>
       </c>
       <c r="W108" s="12">
         <v>0</v>
       </c>
-    </row>
-    <row r="109" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X108" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y108" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z108" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA108" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B109" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="P109" s="12">
+      <c r="T109" s="12">
         <v>-9.9</v>
       </c>
-      <c r="Q109" s="12">
-        <v>0</v>
-      </c>
-      <c r="R109" s="12">
+      <c r="U109" s="12">
+        <v>0</v>
+      </c>
+      <c r="V109" s="12">
         <v>-475</v>
       </c>
-      <c r="S109" s="12">
-        <v>0</v>
-      </c>
-      <c r="T109" s="12">
-        <v>0</v>
-      </c>
-      <c r="U109" s="12">
-        <v>0</v>
-      </c>
-      <c r="V109" s="12">
-        <v>0</v>
-      </c>
       <c r="W109" s="12">
         <v>0</v>
       </c>
-    </row>
-    <row r="110" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X109" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y109" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z109" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA109" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B110" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="P110" s="12">
+      <c r="T110" s="12">
         <v>398.1</v>
       </c>
-      <c r="Q110" s="12">
-        <v>0</v>
-      </c>
-      <c r="R110" s="12">
+      <c r="U110" s="12">
+        <v>0</v>
+      </c>
+      <c r="V110" s="12">
         <v>1241.9000000000001</v>
       </c>
-      <c r="S110" s="12">
-        <v>0</v>
-      </c>
-      <c r="T110" s="12">
-        <v>0</v>
-      </c>
-      <c r="U110" s="12">
-        <v>0</v>
-      </c>
-      <c r="V110" s="12">
-        <v>0</v>
-      </c>
       <c r="W110" s="12">
+        <v>0</v>
+      </c>
+      <c r="X110" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y110" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z110" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA110" s="12">
         <v>498.2</v>
       </c>
     </row>
-    <row r="111" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="111" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B111" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="P111" s="12">
+      <c r="T111" s="12">
         <v>-300</v>
       </c>
-      <c r="Q111" s="12">
-        <v>0</v>
-      </c>
-      <c r="R111" s="12">
+      <c r="U111" s="12">
+        <v>0</v>
+      </c>
+      <c r="V111" s="12">
         <v>-300</v>
       </c>
-      <c r="S111" s="12">
-        <v>0</v>
-      </c>
-      <c r="T111" s="12">
+      <c r="W111" s="12">
+        <v>0</v>
+      </c>
+      <c r="X111" s="12">
         <v>-500</v>
       </c>
-      <c r="U111" s="12">
-        <v>0</v>
-      </c>
-      <c r="V111" s="12">
-        <v>0</v>
-      </c>
-      <c r="W111" s="12">
+      <c r="Y111" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z111" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA111" s="12">
         <v>-400</v>
       </c>
     </row>
-    <row r="112" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="112" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B112" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="P112" s="12">
+      <c r="T112" s="12">
         <v>-19.600000000000001</v>
       </c>
-      <c r="Q112" s="12">
+      <c r="U112" s="12">
         <v>-13.6</v>
       </c>
-      <c r="R112" s="12">
+      <c r="V112" s="12">
         <v>-13.9</v>
       </c>
-      <c r="S112" s="12">
+      <c r="W112" s="12">
         <v>-23.1</v>
       </c>
-      <c r="T112" s="12">
+      <c r="X112" s="12">
         <v>-21.9</v>
       </c>
-      <c r="U112" s="12">
+      <c r="Y112" s="12">
         <v>-21.3</v>
       </c>
-      <c r="V112" s="12">
+      <c r="Z112" s="12">
         <v>-22</v>
       </c>
-      <c r="W112" s="12">
+      <c r="AA112" s="12">
         <v>-23.2</v>
       </c>
     </row>
-    <row r="113" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="113" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B113" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="P113" s="12">
+      <c r="T113" s="12">
         <v>-190.7</v>
       </c>
-      <c r="Q113" s="12">
+      <c r="U113" s="12">
         <v>-203.9</v>
       </c>
-      <c r="R113" s="12">
+      <c r="V113" s="12">
         <v>-49.8</v>
       </c>
-      <c r="S113" s="12">
+      <c r="W113" s="12">
         <v>-150</v>
       </c>
-      <c r="T113" s="12">
+      <c r="X113" s="12">
         <v>-198.3</v>
       </c>
-      <c r="U113" s="12">
+      <c r="Y113" s="12">
         <v>-194.6</v>
       </c>
-      <c r="V113" s="12">
+      <c r="Z113" s="12">
         <v>-201.1</v>
       </c>
-      <c r="W113" s="12">
+      <c r="AA113" s="12">
         <v>-216.5</v>
       </c>
     </row>
-    <row r="114" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="114" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B114" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="P114" s="12">
+      <c r="T114" s="12">
         <v>-502.6</v>
       </c>
-      <c r="Q114" s="12">
+      <c r="U114" s="12">
         <v>-694.8</v>
       </c>
-      <c r="R114" s="12">
+      <c r="V114" s="12">
         <v>-37.700000000000003</v>
       </c>
-      <c r="S114" s="12">
+      <c r="W114" s="12">
         <v>-492.6</v>
       </c>
-      <c r="T114" s="12">
+      <c r="X114" s="12">
         <v>-488.6</v>
       </c>
-      <c r="U114" s="12">
+      <c r="Y114" s="12">
         <v>-449.7</v>
       </c>
-      <c r="V114" s="12">
+      <c r="Z114" s="12">
         <v>-480.9</v>
       </c>
-      <c r="W114" s="12">
+      <c r="AA114" s="12">
         <v>-623.79999999999995</v>
       </c>
     </row>
-    <row r="115" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="115" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B115" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="P115" s="12">
+      <c r="T115" s="12">
         <f>21.8-2.8</f>
         <v>19</v>
       </c>
-      <c r="Q115" s="12">
+      <c r="U115" s="12">
         <v>-0.9</v>
       </c>
-      <c r="R115" s="12">
+      <c r="V115" s="12">
         <v>-8.6999999999999993</v>
       </c>
-      <c r="S115" s="12">
-        <v>0</v>
-      </c>
-      <c r="T115" s="12">
-        <v>0</v>
-      </c>
-      <c r="U115" s="12">
-        <v>0</v>
-      </c>
-      <c r="V115" s="12">
-        <v>0</v>
-      </c>
       <c r="W115" s="12">
+        <v>0</v>
+      </c>
+      <c r="X115" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y115" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z115" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA115" s="12">
         <v>-4.4000000000000004</v>
       </c>
     </row>
-    <row r="116" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="116" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B116" s="1" t="s">
         <v>153</v>
       </c>
@@ -6866,175 +7273,179 @@
       <c r="M116" s="13"/>
       <c r="N116" s="13"/>
       <c r="O116" s="13"/>
-      <c r="P116" s="13">
-        <f t="shared" ref="P116:R116" si="57">SUM(P108:P115)</f>
+      <c r="P116" s="13"/>
+      <c r="Q116" s="13"/>
+      <c r="R116" s="13"/>
+      <c r="S116" s="13"/>
+      <c r="T116" s="13">
+        <f t="shared" ref="T116:V116" si="67">SUM(T108:T115)</f>
         <v>-605.69999999999993</v>
       </c>
-      <c r="Q116" s="13">
-        <f t="shared" si="57"/>
+      <c r="U116" s="13">
+        <f t="shared" si="67"/>
         <v>-438.19999999999993</v>
       </c>
-      <c r="R116" s="13">
-        <f t="shared" si="57"/>
+      <c r="V116" s="13">
+        <f t="shared" si="67"/>
         <v>356.80000000000013</v>
       </c>
-      <c r="S116" s="13">
-        <f>SUM(S108:S115)</f>
+      <c r="W116" s="13">
+        <f>SUM(W108:W115)</f>
         <v>-665.7</v>
       </c>
-      <c r="T116" s="13">
-        <f t="shared" ref="T116:W116" si="58">SUM(T108:T115)</f>
+      <c r="X116" s="13">
+        <f t="shared" ref="X116:AA116" si="68">SUM(X108:X115)</f>
         <v>-1208.8000000000002</v>
       </c>
-      <c r="U116" s="13">
-        <f t="shared" si="58"/>
+      <c r="Y116" s="13">
+        <f t="shared" si="68"/>
         <v>-665.6</v>
       </c>
-      <c r="V116" s="13">
-        <f t="shared" si="58"/>
+      <c r="Z116" s="13">
+        <f t="shared" si="68"/>
         <v>-704</v>
       </c>
-      <c r="W116" s="13">
-        <f t="shared" si="58"/>
+      <c r="AA116" s="13">
+        <f t="shared" si="68"/>
         <v>-769.69999999999993</v>
       </c>
     </row>
-    <row r="117" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="117" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B117" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="P117" s="12">
+      <c r="T117" s="12">
         <v>-27.8</v>
       </c>
-      <c r="Q117" s="12">
+      <c r="U117" s="12">
         <v>-15.2</v>
       </c>
-      <c r="R117" s="12">
+      <c r="V117" s="12">
         <v>25.5</v>
       </c>
-      <c r="S117" s="12">
+      <c r="W117" s="12">
         <v>-48.3</v>
       </c>
-      <c r="T117" s="12">
+      <c r="X117" s="12">
         <v>-8.8000000000000007</v>
       </c>
-      <c r="U117" s="12">
+      <c r="Y117" s="12">
         <v>-13.6</v>
       </c>
-      <c r="V117" s="12">
+      <c r="Z117" s="12">
         <v>-8.23</v>
       </c>
-      <c r="W117" s="12">
+      <c r="AA117" s="12">
         <v>37.4</v>
       </c>
     </row>
-    <row r="118" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="118" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B118" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="P118" s="13">
-        <f t="shared" ref="P118:T118" si="59">P101+P107+P116+P117</f>
+      <c r="T118" s="13">
+        <f t="shared" ref="T118:X118" si="69">T101+T107+T116+T117</f>
         <v>-729.00000000000011</v>
       </c>
-      <c r="Q118" s="13">
-        <f t="shared" si="59"/>
+      <c r="U118" s="13">
+        <f t="shared" si="69"/>
         <v>1003.3000000000003</v>
       </c>
-      <c r="R118" s="13">
-        <f t="shared" si="59"/>
+      <c r="V118" s="13">
+        <f t="shared" si="69"/>
         <v>958.20000000000027</v>
       </c>
-      <c r="S118" s="13">
-        <f t="shared" si="59"/>
+      <c r="W118" s="13">
+        <f t="shared" si="69"/>
         <v>-715.99999999999966</v>
       </c>
-      <c r="T118" s="13">
-        <f t="shared" si="59"/>
+      <c r="X118" s="13">
+        <f t="shared" si="69"/>
         <v>-335.09999999999997</v>
       </c>
-      <c r="U118" s="13">
-        <f>U101+U107+U116+U117</f>
+      <c r="Y118" s="13">
+        <f>Y101+Y107+Y116+Y117</f>
         <v>133.69999999999916</v>
       </c>
-      <c r="V118" s="13">
-        <f t="shared" ref="V118:W118" si="60">V101+V107+V116+V117</f>
+      <c r="Z118" s="13">
+        <f t="shared" ref="Z118:AA118" si="70">Z101+Z107+Z116+Z117</f>
         <v>258.76999999999941</v>
       </c>
-      <c r="W118" s="13">
-        <f t="shared" si="60"/>
+      <c r="AA118" s="13">
+        <f t="shared" si="70"/>
         <v>65.299999999999983</v>
       </c>
     </row>
-    <row r="119" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="119" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B119" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="P119" s="12">
-        <f>P120-P118</f>
-        <v>1355.4999999999991</v>
-      </c>
-      <c r="Q119" s="12">
-        <f>Q120-Q118</f>
-        <v>626.49999999999898</v>
-      </c>
-      <c r="R119" s="12">
-        <f>R120-R118</f>
-        <v>1629.7999999999993</v>
-      </c>
-      <c r="S119" s="12">
-        <f>S120-S118</f>
-        <v>2587.9999999999995</v>
-      </c>
       <c r="T119" s="12">
         <f>T120-T118</f>
+        <v>1355.4999999999991</v>
+      </c>
+      <c r="U119" s="12">
+        <f>U120-U118</f>
+        <v>626.49999999999898</v>
+      </c>
+      <c r="V119" s="12">
+        <f>V120-V118</f>
+        <v>1629.7999999999993</v>
+      </c>
+      <c r="W119" s="12">
+        <f>W120-W118</f>
+        <v>2587.9999999999995</v>
+      </c>
+      <c r="X119" s="12">
+        <f>X120-X118</f>
         <v>1872</v>
       </c>
-      <c r="U119" s="12">
+      <c r="Y119" s="12">
         <v>1536.9</v>
       </c>
-      <c r="V119" s="12">
-        <f>+U120</f>
+      <c r="Z119" s="12">
+        <f>+Y120</f>
         <v>1670.5999999999992</v>
       </c>
-      <c r="W119" s="12">
-        <f>+V120</f>
+      <c r="AA119" s="12">
+        <f>+Z120</f>
         <v>1929.3699999999985</v>
       </c>
     </row>
-    <row r="120" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="120" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B120" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="P120" s="12">
-        <f>Q119</f>
-        <v>626.49999999999898</v>
-      </c>
-      <c r="Q120" s="12">
-        <f>R119</f>
-        <v>1629.7999999999993</v>
-      </c>
-      <c r="R120" s="12">
-        <f>S119</f>
-        <v>2587.9999999999995</v>
-      </c>
-      <c r="S120" s="12">
-        <f>T119</f>
-        <v>1872</v>
-      </c>
       <c r="T120" s="12">
         <f>U119</f>
+        <v>626.49999999999898</v>
+      </c>
+      <c r="U120" s="12">
+        <f>V119</f>
+        <v>1629.7999999999993</v>
+      </c>
+      <c r="V120" s="12">
+        <f>W119</f>
+        <v>2587.9999999999995</v>
+      </c>
+      <c r="W120" s="12">
+        <f>X119</f>
+        <v>1872</v>
+      </c>
+      <c r="X120" s="12">
+        <f>Y119</f>
         <v>1536.9</v>
       </c>
-      <c r="U120" s="12">
-        <f>U119+U118</f>
+      <c r="Y120" s="12">
+        <f>Y119+Y118</f>
         <v>1670.5999999999992</v>
       </c>
-      <c r="V120" s="12">
-        <f>+V118+V119</f>
+      <c r="Z120" s="12">
+        <f>+Z118+Z119</f>
         <v>1929.3699999999985</v>
       </c>
-      <c r="W120" s="12">
-        <f>+W119+W118</f>
+      <c r="AA120" s="12">
+        <f>+AA119+AA118</f>
         <v>1994.6699999999985</v>
       </c>
     </row>
@@ -7116,40 +7527,40 @@
         <v>162</v>
       </c>
       <c r="D4" s="17">
-        <f>Model!P32/Model!P81</f>
+        <f>Model!T32/Model!T81</f>
         <v>0.13108420540277427</v>
       </c>
       <c r="E4" s="17">
-        <f>Model!Q32/Model!Q81</f>
+        <f>Model!U32/Model!U81</f>
         <v>0.14269800601537269</v>
       </c>
       <c r="F4" s="17">
-        <f>Model!R32/Model!R81</f>
+        <f>Model!V32/Model!V81</f>
         <v>-4.649823375825525E-2</v>
       </c>
       <c r="G4" s="17">
-        <f>Model!S32/Model!S81</f>
+        <f>Model!W32/Model!W81</f>
         <v>0.23663249211356471</v>
       </c>
       <c r="H4" s="17">
-        <f>Model!T32/Model!T81</f>
+        <f>Model!X32/Model!X81</f>
         <v>0.21505862991154104</v>
       </c>
       <c r="I4" s="17">
-        <f>Model!U32/Model!U81</f>
+        <f>Model!Y32/Model!Y81</f>
         <v>0.26376362078112842</v>
       </c>
       <c r="J4" s="17">
-        <f>Model!V32/Model!V81</f>
+        <f>Model!Z32/Model!Z81</f>
         <v>0.28700019316206277</v>
       </c>
       <c r="K4" s="17">
-        <f>Model!W32/Model!W81</f>
+        <f>Model!AA32/Model!AA81</f>
         <v>0.33120996691771654</v>
       </c>
       <c r="L4" s="17"/>
       <c r="M4" s="22">
-        <f>AVERAGE(G4:I4,D4)</f>
+        <f t="shared" ref="M4:M17" si="0">AVERAGE(G4:I4,D4)</f>
         <v>0.21163473705225211</v>
       </c>
       <c r="N4" s="22">
@@ -7165,44 +7576,44 @@
         <v>164</v>
       </c>
       <c r="D5" s="17">
-        <f>Model!P32/Model!P19</f>
+        <f>Model!T32/Model!T19</f>
         <v>6.8255979724378205E-2</v>
       </c>
       <c r="E5" s="17">
-        <f>Model!Q32/Model!Q19</f>
+        <f>Model!U32/Model!U19</f>
         <v>6.2388389233416733E-2</v>
       </c>
       <c r="F5" s="17">
-        <f>Model!R32/Model!R19</f>
+        <f>Model!V32/Model!V19</f>
         <v>-2.7517724050172675E-2</v>
       </c>
       <c r="G5" s="17">
-        <f>Model!S32/Model!S19</f>
+        <f>Model!W32/Model!W19</f>
         <v>9.6502371954651459E-2</v>
       </c>
       <c r="H5" s="17">
-        <f>Model!T32/Model!T19</f>
+        <f>Model!X32/Model!X19</f>
         <v>8.1119250108634966E-2</v>
       </c>
       <c r="I5" s="17">
-        <f>Model!U32/Model!U19</f>
+        <f>Model!Y32/Model!Y19</f>
         <v>9.7460566396235973E-2</v>
       </c>
       <c r="J5" s="17">
-        <f>Model!V32/Model!V19</f>
+        <f>Model!Z32/Model!Z19</f>
         <v>0.10494420115835562</v>
       </c>
       <c r="K5" s="17">
-        <f>Model!W32/Model!W19</f>
+        <f>Model!AA32/Model!AA19</f>
         <v>0.11597757101484993</v>
       </c>
       <c r="L5" s="17"/>
       <c r="M5" s="22">
-        <f>AVERAGE(G5:I5,D5)</f>
+        <f t="shared" si="0"/>
         <v>8.583454204597514E-2</v>
       </c>
       <c r="N5" s="22">
-        <f t="shared" ref="N5:N17" si="0">MEDIAN(G5:I5,D5:E5)</f>
+        <f t="shared" ref="N5:N17" si="1">MEDIAN(G5:I5,D5:E5)</f>
         <v>8.1119250108634966E-2</v>
       </c>
       <c r="P5" s="2" t="s">
@@ -7214,44 +7625,44 @@
         <v>166</v>
       </c>
       <c r="D6" s="17">
-        <f>Model!P26/Model!P19</f>
+        <f>Model!T26/Model!T19</f>
         <v>8.8990971012197009E-2</v>
       </c>
       <c r="E6" s="17">
-        <f>Model!Q26/Model!Q19</f>
+        <f>Model!U26/Model!U19</f>
         <v>5.1462709828241249E-2</v>
       </c>
       <c r="F6" s="17">
-        <f>Model!R26/Model!R19</f>
+        <f>Model!V26/Model!V19</f>
         <v>-9.9072895837120315E-3</v>
       </c>
       <c r="G6" s="17">
-        <f>Model!S26/Model!S19</f>
+        <f>Model!W26/Model!W19</f>
         <v>0.12839109109913968</v>
       </c>
       <c r="H6" s="17">
-        <f>Model!T26/Model!T19</f>
+        <f>Model!X26/Model!X19</f>
         <v>0.10928673412378177</v>
       </c>
       <c r="I6" s="17">
-        <f>Model!U26/Model!U19</f>
+        <f>Model!Y26/Model!Y19</f>
         <v>0.11406339536146201</v>
       </c>
       <c r="J6" s="17">
-        <f>Model!V26/Model!V19</f>
+        <f>Model!Z26/Model!Z19</f>
         <v>0.13167113999152416</v>
       </c>
       <c r="K6" s="17">
-        <f>Model!W26/Model!W19</f>
+        <f>Model!AA26/Model!AA19</f>
         <v>0.14532010598311662</v>
       </c>
       <c r="L6" s="17"/>
       <c r="M6" s="22">
-        <f>AVERAGE(G6:I6,D6)</f>
+        <f t="shared" si="0"/>
         <v>0.11018304789914513</v>
       </c>
       <c r="N6" s="22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.10928673412378177</v>
       </c>
       <c r="P6" s="2" t="s">
@@ -7263,43 +7674,43 @@
         <v>168</v>
       </c>
       <c r="D7" s="17">
-        <f>(Model!P26+Model!P86)/Model!P19</f>
+        <f>(Model!T26+Model!T86)/Model!T19</f>
         <v>0.13354981783621095</v>
       </c>
       <c r="E7" s="17">
-        <f>(Model!Q26+Model!Q86)/Model!Q19</f>
+        <f>(Model!U26+Model!U86)/Model!U19</f>
         <v>9.5214130328906854E-2</v>
       </c>
       <c r="F7" s="17">
-        <f>(Model!R26+Model!R86)/Model!R19</f>
+        <f>(Model!V26+Model!V86)/Model!V19</f>
         <v>4.6355208143973842E-2</v>
       </c>
       <c r="G7" s="17">
-        <f>(Model!S26+Model!S86)/Model!S19</f>
+        <f>(Model!W26+Model!W86)/Model!W19</f>
         <v>0.16532925946771732</v>
       </c>
       <c r="H7" s="17">
-        <f>(Model!T26+Model!T86)/Model!T19</f>
+        <f>(Model!X26+Model!X86)/Model!X19</f>
         <v>0.14350673536532377</v>
       </c>
       <c r="I7" s="17">
-        <f>(Model!U26+Model!U86)/Model!U19</f>
+        <f>(Model!Y26+Model!Y86)/Model!Y19</f>
         <v>0.1485960732273727</v>
       </c>
       <c r="J7" s="17">
-        <f>(Model!V26+Model!V86)/Model!V19</f>
+        <f>(Model!Z26+Model!Z86)/Model!Z19</f>
         <v>0.16269247068795017</v>
       </c>
       <c r="K7" s="17">
-        <f>(Model!W26+Model!W86)/Model!W19</f>
+        <f>(Model!AA26+Model!AA86)/Model!AA19</f>
         <v>0.17403413642245361</v>
       </c>
       <c r="M7" s="22">
-        <f>AVERAGE(G7:I7,D7)</f>
+        <f t="shared" si="0"/>
         <v>0.14774547147415618</v>
       </c>
       <c r="N7" s="22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.14350673536532377</v>
       </c>
       <c r="P7" s="2" t="s">
@@ -7311,39 +7722,39 @@
         <v>170</v>
       </c>
       <c r="D8" s="3">
-        <f>Model!P19/Model!P66</f>
+        <f>Model!T19/Model!T66</f>
         <v>1.0622938682102714</v>
       </c>
       <c r="E8" s="3">
-        <f>Model!Q19/Model!Q66</f>
+        <f>Model!U19/Model!U66</f>
         <v>0.84613799640104947</v>
       </c>
       <c r="F8" s="3">
-        <f>Model!R19/Model!R66</f>
+        <f>Model!V19/Model!V66</f>
         <v>0.55794611727416799</v>
       </c>
       <c r="G8" s="3">
-        <f>Model!S19/Model!S66</f>
+        <f>Model!W19/Model!W66</f>
         <v>0.80501508149183776</v>
       </c>
       <c r="H8" s="3">
-        <f>Model!T19/Model!T66</f>
+        <f>Model!X19/Model!X66</f>
         <v>0.94905368583842709</v>
       </c>
       <c r="I8" s="3">
-        <f>Model!U19/Model!U66</f>
+        <f>Model!Y19/Model!Y66</f>
         <v>1.0043619180322902</v>
       </c>
       <c r="J8" s="3">
-        <f>Model!V19/Model!V66</f>
+        <f>Model!Z19/Model!Z66</f>
         <v>1.0044981766066436</v>
       </c>
       <c r="K8" s="3">
-        <f>Model!W19/Model!W66</f>
+        <f>Model!AA19/Model!AA66</f>
         <v>1.0484527424252212</v>
       </c>
       <c r="M8" s="23">
-        <f>AVERAGE(G8:I8,D8)</f>
+        <f t="shared" si="0"/>
         <v>0.95518113839320651</v>
       </c>
       <c r="N8" s="23">
@@ -7359,43 +7770,43 @@
         <v>172</v>
       </c>
       <c r="D9" s="17">
-        <f>(Model!P32+Model!P27)/Model!P66</f>
+        <f>(Model!T32+Model!T27)/Model!T66</f>
         <v>7.5991115299185522E-2</v>
       </c>
       <c r="E9" s="17">
-        <f>(Model!Q32+Model!Q27)/Model!Q66</f>
+        <f>(Model!U32+Model!U27)/Model!U66</f>
         <v>5.5206802291240323E-2</v>
       </c>
       <c r="F9" s="17">
-        <f>(Model!R32+Model!R27)/Model!R66</f>
+        <f>(Model!V32+Model!V27)/Model!V66</f>
         <v>-9.2044374009508604E-3</v>
       </c>
       <c r="G9" s="17">
-        <f>(Model!S32+Model!S27)/Model!S66</f>
+        <f>(Model!W32+Model!W27)/Model!W66</f>
         <v>8.4676427563529985E-2</v>
       </c>
       <c r="H9" s="17">
-        <f>(Model!T32+Model!T27)/Model!T66</f>
+        <f>(Model!X32+Model!X27)/Model!X66</f>
         <v>8.2936887841520035E-2</v>
       </c>
       <c r="I9" s="17">
-        <f>(Model!U32+Model!U27)/Model!U66</f>
+        <f>(Model!Y32+Model!Y27)/Model!Y66</f>
         <v>0.10427710295944011</v>
       </c>
       <c r="J9" s="17">
-        <f>(Model!V32+Model!V27)/Model!V66</f>
+        <f>(Model!Z32+Model!Z27)/Model!Z66</f>
         <v>0.11167397442992344</v>
       </c>
       <c r="K9" s="17">
-        <f>(Model!W32+Model!W27)/Model!W66</f>
+        <f>(Model!AA32+Model!AA27)/Model!AA66</f>
         <v>0.12860003876219392</v>
       </c>
       <c r="M9" s="22">
-        <f>AVERAGE(G9:I9,D9)</f>
+        <f t="shared" si="0"/>
         <v>8.6970383415918909E-2</v>
       </c>
       <c r="N9" s="22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8.2936887841520035E-2</v>
       </c>
       <c r="P9" s="2" t="s">
@@ -7407,43 +7818,43 @@
         <v>174</v>
       </c>
       <c r="D10" s="17">
-        <f>Model!P26/Model!P66</f>
+        <f>Model!T26/Model!T66</f>
         <v>9.4534562832334898E-2</v>
       </c>
       <c r="E10" s="17">
-        <f>Model!Q26/Model!Q66</f>
+        <f>Model!U26/Model!U66</f>
         <v>4.3544554183436647E-2</v>
       </c>
       <c r="F10" s="17">
-        <f>Model!R26/Model!R66</f>
+        <f>Model!V26/Model!V66</f>
         <v>-5.5277337559429358E-3</v>
       </c>
       <c r="G10" s="17">
-        <f>Model!S26/Model!S66</f>
+        <f>Model!W26/Model!W66</f>
         <v>0.1033567646639999</v>
       </c>
       <c r="H10" s="17">
-        <f>Model!T26/Model!T66</f>
+        <f>Model!X26/Model!X66</f>
         <v>0.1037189778334193</v>
       </c>
       <c r="I10" s="17">
-        <f>Model!U26/Model!U66</f>
+        <f>Model!Y26/Model!Y66</f>
         <v>0.11456093054251344</v>
       </c>
       <c r="J10" s="17">
-        <f>Model!V26/Model!V66</f>
+        <f>Model!Z26/Model!Z66</f>
         <v>0.13226342003320413</v>
       </c>
       <c r="K10" s="17">
-        <f>Model!W26/Model!W66</f>
+        <f>Model!AA26/Model!AA66</f>
         <v>0.15236126364752242</v>
       </c>
       <c r="M10" s="22">
-        <f>AVERAGE(G10:I10,D10)</f>
+        <f t="shared" si="0"/>
         <v>0.10404280896806689</v>
       </c>
       <c r="N10" s="22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.1033567646639999</v>
       </c>
       <c r="P10" s="2" t="s">
@@ -7455,43 +7866,43 @@
         <v>176</v>
       </c>
       <c r="D11" s="17">
-        <f>Model!P26/(Model!P65+SUM(Model!P53:P57)-Model!P68)</f>
+        <f>Model!T26/(Model!T65+SUM(Model!T53:T57)-Model!T68)</f>
         <v>0.10895198200294773</v>
       </c>
       <c r="E11" s="17">
-        <f>Model!Q26/(Model!Q65+SUM(Model!Q53:Q57)-Model!Q68)</f>
+        <f>Model!U26/(Model!U65+SUM(Model!U53:U57)-Model!U68)</f>
         <v>5.8565965229922308E-2</v>
       </c>
       <c r="F11" s="17">
-        <f>Model!R26/(Model!R65+SUM(Model!R53:R57)-Model!R68)</f>
+        <f>Model!V26/(Model!V65+SUM(Model!V53:V57)-Model!V68)</f>
         <v>-8.8034567701813001E-3</v>
       </c>
       <c r="G11" s="17">
-        <f>Model!S26/(Model!S65+SUM(Model!S53:S57)-Model!S68)</f>
+        <f>Model!W26/(Model!W65+SUM(Model!W53:W57)-Model!W68)</f>
         <v>0.1475185691585677</v>
       </c>
       <c r="H11" s="17">
-        <f>Model!T26/(Model!T65+SUM(Model!T53:T57)-Model!T68)</f>
+        <f>Model!X26/(Model!X65+SUM(Model!X53:X57)-Model!X68)</f>
         <v>0.1440494211021561</v>
       </c>
       <c r="I11" s="17">
-        <f>Model!U26/(Model!U65+SUM(Model!U53:U57)-Model!U68)</f>
+        <f>Model!Y26/(Model!Y65+SUM(Model!Y53:Y57)-Model!Y68)</f>
         <v>0.16414218132893521</v>
       </c>
       <c r="J11" s="17">
-        <f>Model!V26/(Model!V65+SUM(Model!V53:V57)-Model!V68)</f>
+        <f>Model!Z26/(Model!Z65+SUM(Model!Z53:Z57)-Model!Z68)</f>
         <v>0.19879286811124369</v>
       </c>
       <c r="K11" s="17">
-        <f>Model!W26/(Model!W65+SUM(Model!W53:W57)-Model!W68)</f>
+        <f>Model!AA26/(Model!AA65+SUM(Model!AA53:AA57)-Model!AA68)</f>
         <v>0.22163330514049429</v>
       </c>
       <c r="M11" s="22">
-        <f>AVERAGE(G11:I11,D11)</f>
+        <f t="shared" si="0"/>
         <v>0.14116553839815169</v>
       </c>
       <c r="N11" s="22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.1440494211021561</v>
       </c>
       <c r="P11" s="2" t="s">
@@ -7503,43 +7914,43 @@
         <v>178</v>
       </c>
       <c r="D12" s="17">
-        <f>(Model!P26*(1-Model!P49))/(Model!P80+Model!P81-Model!P52)</f>
+        <f>(Model!T26*(1-Model!T49))/(Model!T80+Model!T81-Model!T52)</f>
         <v>6.7954266989665613E-2</v>
       </c>
       <c r="E12" s="17">
-        <f>(Model!Q26*(1-Model!Q49))/(Model!Q80+Model!Q81-Model!Q52)</f>
+        <f>(Model!U26*(1-Model!U49))/(Model!U80+Model!U81-Model!U52)</f>
         <v>6.4450983917599694E-2</v>
       </c>
       <c r="F12" s="17">
-        <f>(Model!R26*(1-Model!R49))/(Model!R80+Model!R81-Model!R52)</f>
+        <f>(Model!V26*(1-Model!V49))/(Model!V80+Model!V81-Model!V52)</f>
         <v>-1.1353401019989813E-2</v>
       </c>
       <c r="G12" s="17">
-        <f>(Model!S26*(1-Model!S49))/(Model!S80+Model!S81-Model!S52)</f>
+        <f>(Model!W26*(1-Model!W49))/(Model!W80+Model!W81-Model!W52)</f>
         <v>0.10115276816817223</v>
       </c>
       <c r="H12" s="17">
-        <f>(Model!T26*(1-Model!T49))/(Model!T80+Model!T81-Model!T52)</f>
+        <f>(Model!X26*(1-Model!X49))/(Model!X80+Model!X81-Model!X52)</f>
         <v>9.0537955221594135E-2</v>
       </c>
       <c r="I12" s="17">
-        <f>(Model!U26*(1-Model!U49))/(Model!U80+Model!U81-Model!U52)</f>
+        <f>(Model!Y26*(1-Model!Y49))/(Model!Y80+Model!Y81-Model!Y52)</f>
         <v>0.12204812323753214</v>
       </c>
       <c r="J12" s="17">
-        <f>(Model!V26*(1-Model!V49))/(Model!V80+Model!V81-Model!V52)</f>
+        <f>(Model!Z26*(1-Model!Z49))/(Model!Z80+Model!Z81-Model!Z52)</f>
         <v>0.13100569615484053</v>
       </c>
       <c r="K12" s="17">
-        <f>(Model!W26*(1-Model!W49))/(Model!W80+Model!W81-Model!W52)</f>
+        <f>(Model!AA26*(1-Model!AA49))/(Model!AA80+Model!AA81-Model!AA52)</f>
         <v>0.1534799222127313</v>
       </c>
       <c r="M12" s="22">
-        <f>AVERAGE(G12:I12,D12)</f>
+        <f t="shared" si="0"/>
         <v>9.542327840424103E-2</v>
       </c>
       <c r="N12" s="22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9.0537955221594135E-2</v>
       </c>
       <c r="P12" s="2" t="s">
@@ -7551,43 +7962,43 @@
         <v>180</v>
       </c>
       <c r="D13" s="17">
-        <f>Model!P101/Model!P19</f>
+        <f>Model!T101/Model!T19</f>
         <v>0.12415650245525102</v>
       </c>
       <c r="E13" s="17">
-        <f>Model!Q101/Model!Q19</f>
+        <f>Model!U101/Model!U19</f>
         <v>0.12250397740186375</v>
       </c>
       <c r="F13" s="17">
-        <f>Model!R101/Model!R19</f>
+        <f>Model!V101/Model!V19</f>
         <v>8.6552445009998188E-2</v>
       </c>
       <c r="G13" s="17">
-        <f>Model!S101/Model!S19</f>
+        <f>Model!W101/Model!W19</f>
         <v>0.11512422609954175</v>
       </c>
       <c r="H13" s="17">
-        <f>Model!T101/Model!T19</f>
+        <f>Model!X101/Model!X19</f>
         <v>6.3784220001241565E-2</v>
       </c>
       <c r="I13" s="17">
-        <f>Model!U101/Model!U19</f>
+        <f>Model!Y101/Model!Y19</f>
         <v>0.1613083210181861</v>
       </c>
       <c r="J13" s="17">
-        <f>Model!V101/Model!V19</f>
+        <f>Model!Z101/Model!Z19</f>
         <v>0.17447379573386063</v>
       </c>
       <c r="K13" s="17">
-        <f>Model!W101/Model!W19</f>
+        <f>Model!AA101/Model!AA19</f>
         <v>0.14223920142953969</v>
       </c>
       <c r="M13" s="22">
-        <f>AVERAGE(G13:I13,D13)</f>
+        <f t="shared" si="0"/>
         <v>0.11609331739355511</v>
       </c>
       <c r="N13" s="22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.12250397740186375</v>
       </c>
       <c r="P13" s="2" t="s">
@@ -7599,43 +8010,43 @@
         <v>182</v>
       </c>
       <c r="D14" s="17">
-        <f>1-(Model!P113/Model!P114)</f>
+        <f>1-(Model!T113/Model!T114)</f>
         <v>0.62057302029446881</v>
       </c>
       <c r="E14" s="17">
-        <f>1-(Model!Q113/Model!Q114)</f>
+        <f>1-(Model!U113/Model!U114)</f>
         <v>0.70653425446171558</v>
       </c>
       <c r="F14" s="17">
-        <f>1-(Model!R113/Model!R114)</f>
+        <f>1-(Model!V113/Model!V114)</f>
         <v>-0.32095490716180364</v>
       </c>
       <c r="G14" s="17">
-        <f>1-(Model!S113/Model!S114)</f>
+        <f>1-(Model!W113/Model!W114)</f>
         <v>0.69549330085261873</v>
       </c>
       <c r="H14" s="17">
-        <f>1-(Model!T113/Model!T114)</f>
+        <f>1-(Model!X113/Model!X114)</f>
         <v>0.59414654113794518</v>
       </c>
       <c r="I14" s="17">
-        <f>1-(Model!U113/Model!U114)</f>
+        <f>1-(Model!Y113/Model!Y114)</f>
         <v>0.56726706693351125</v>
       </c>
       <c r="J14" s="17">
-        <f>1-(Model!V113/Model!V114)</f>
+        <f>1-(Model!Z113/Model!Z114)</f>
         <v>0.5818257433977958</v>
       </c>
       <c r="K14" s="17">
-        <f>1-(Model!W113/Model!W114)</f>
+        <f>1-(Model!AA113/Model!AA114)</f>
         <v>0.65293363257454318</v>
       </c>
       <c r="M14" s="22">
-        <f>AVERAGE(G14:I14,D14)</f>
+        <f t="shared" si="0"/>
         <v>0.61936998230463591</v>
       </c>
       <c r="N14" s="22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.62057302029446881</v>
       </c>
       <c r="P14" s="2" t="s">
@@ -7647,23 +8058,23 @@
         <v>184</v>
       </c>
       <c r="D15" s="22">
-        <f t="shared" ref="D15:H15" si="1">D14*D4</f>
+        <f t="shared" ref="D15:H15" si="2">D14*D4</f>
         <v>8.134732125970015E-2</v>
       </c>
       <c r="E15" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.10082102929324475</v>
       </c>
       <c r="F15" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.4923836299068658E-2</v>
       </c>
       <c r="G15" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.16457631302904438</v>
       </c>
       <c r="H15" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.12777634110380753</v>
       </c>
       <c r="I15" s="22">
@@ -7671,19 +8082,19 @@
         <v>0.14962441552427366</v>
       </c>
       <c r="J15" s="22">
-        <f t="shared" ref="J15:K15" si="2">J14*J4</f>
+        <f t="shared" ref="J15:K15" si="3">J14*J4</f>
         <v>0.16698410074182815</v>
       </c>
       <c r="K15" s="22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.21625812684447893</v>
       </c>
       <c r="M15" s="22">
-        <f>AVERAGE(G15:I15,D15)</f>
+        <f t="shared" si="0"/>
         <v>0.13083109772920642</v>
       </c>
       <c r="N15" s="22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.12777634110380753</v>
       </c>
       <c r="P15" s="2" t="s">
@@ -7695,43 +8106,43 @@
         <v>186</v>
       </c>
       <c r="D16" s="17">
-        <f>(-Model!P102+SUM(Model!P94:P100))/(Model!P26*(1-Model!P49))</f>
+        <f>(-Model!T102+SUM(Model!T94:T100))/(Model!T26*(1-Model!T49))</f>
         <v>0.35123223560095407</v>
       </c>
       <c r="E16" s="17">
-        <f>(-Model!Q102+SUM(Model!Q94:Q100))/(Model!Q26*(1-Model!Q49))</f>
+        <f>(-Model!U102+SUM(Model!U94:U100))/(Model!U26*(1-Model!U49))</f>
         <v>0.94363328182716921</v>
       </c>
       <c r="F16" s="17">
-        <f>(-Model!R102+SUM(Model!R94:R100))/(Model!R26*(1-Model!R49))</f>
+        <f>(-Model!V102+SUM(Model!V94:V100))/(Model!V26*(1-Model!V49))</f>
         <v>-3.0479746911753476</v>
       </c>
       <c r="G16" s="17">
-        <f>(-Model!S102+SUM(Model!S94:S100))/(Model!S26*(1-Model!S49))</f>
+        <f>(-Model!W102+SUM(Model!W94:W100))/(Model!W26*(1-Model!W49))</f>
         <v>-4.5543004770761675E-3</v>
       </c>
       <c r="H16" s="17">
-        <f>(-Model!T102+SUM(Model!T94:T100))/(Model!T26*(1-Model!T49))</f>
+        <f>(-Model!X102+SUM(Model!X94:X100))/(Model!X26*(1-Model!X49))</f>
         <v>-0.43485769561254406</v>
       </c>
       <c r="I16" s="17">
-        <f>(-Model!U102+SUM(Model!U94:U100))/(Model!U26*(1-Model!U49))</f>
+        <f>(-Model!Y102+SUM(Model!Y94:Y100))/(Model!Y26*(1-Model!Y49))</f>
         <v>0.46403900997204856</v>
       </c>
       <c r="J16" s="17">
-        <f>(-Model!V102+SUM(Model!V94:V100))/(Model!V26*(1-Model!V49))</f>
+        <f>(-Model!Z102+SUM(Model!Z94:Z100))/(Model!Z26*(1-Model!Z49))</f>
         <v>0.62274904032789258</v>
       </c>
       <c r="K16" s="17">
-        <f>(-Model!W102+SUM(Model!W94:W100))/(Model!W26*(1-Model!W49))</f>
+        <f>(-Model!AA102+SUM(Model!AA94:AA100))/(Model!AA26*(1-Model!AA49))</f>
         <v>0.28298260455898461</v>
       </c>
       <c r="M16" s="22">
-        <f>AVERAGE(G16:I16,D16)</f>
+        <f t="shared" si="0"/>
         <v>9.3964812370845599E-2</v>
       </c>
       <c r="N16" s="22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.35123223560095407</v>
       </c>
       <c r="P16" s="2" t="s">
@@ -7743,23 +8154,23 @@
         <v>184</v>
       </c>
       <c r="D17" s="22">
-        <f t="shared" ref="D17:H17" si="3">D16*D12</f>
+        <f t="shared" ref="D17:H17" si="4">D16*D12</f>
         <v>2.3867729113404366E-2</v>
       </c>
       <c r="E17" s="22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6.0818093471154702E-2</v>
       </c>
       <c r="F17" s="22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.4604878967693327E-2</v>
       </c>
       <c r="G17" s="22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-4.6068010032588176E-4</v>
       </c>
       <c r="H17" s="22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-3.937112657313413E-2</v>
       </c>
       <c r="I17" s="22">
@@ -7767,19 +8178,19 @@
         <v>5.6635090276090989E-2</v>
       </c>
       <c r="J17" s="22">
-        <f t="shared" ref="J17:K17" si="4">J16*J12</f>
+        <f t="shared" ref="J17:K17" si="5">J16*J12</f>
         <v>8.1583671557914433E-2</v>
       </c>
       <c r="K17" s="22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4.3432148135269057E-2</v>
       </c>
       <c r="M17" s="22">
-        <f>AVERAGE(G17:I17,D17)</f>
+        <f t="shared" si="0"/>
         <v>1.0167753179008835E-2</v>
       </c>
       <c r="N17" s="22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.3867729113404366E-2</v>
       </c>
       <c r="P17" s="2" t="s">
@@ -7796,43 +8207,43 @@
         <v>190</v>
       </c>
       <c r="D21" s="17">
-        <f>Model!P81/Model!P82</f>
+        <f>Model!T81/Model!T82</f>
         <v>0.55313993403782735</v>
       </c>
       <c r="E21" s="17">
-        <f>Model!Q81/Model!Q82</f>
+        <f>Model!U81/Model!U82</f>
         <v>0.36993640022527796</v>
       </c>
       <c r="F21" s="17">
-        <f>Model!R81/Model!R82</f>
+        <f>Model!V81/Model!V82</f>
         <v>0.33019334389857358</v>
       </c>
       <c r="G21" s="17">
-        <f>Model!S81/Model!S82</f>
+        <f>Model!W81/Model!W82</f>
         <v>0.32829753906300563</v>
       </c>
       <c r="H21" s="17">
-        <f>Model!T81/Model!T82</f>
+        <f>Model!X81/Model!X82</f>
         <v>0.35797923263863307</v>
       </c>
       <c r="I21" s="17">
-        <f>Model!U81/Model!U82</f>
+        <f>Model!Y81/Model!Y82</f>
         <v>0.37111138036531072</v>
       </c>
       <c r="J21" s="17">
-        <f>Model!V81/Model!V82</f>
+        <f>Model!Z81/Model!Z82</f>
         <v>0.36730379010401143</v>
       </c>
       <c r="K21" s="17">
-        <f>Model!W81/Model!W82</f>
+        <f>Model!AA81/Model!AA82</f>
         <v>0.36712965953872989</v>
       </c>
       <c r="M21" s="22">
-        <f t="shared" ref="M21:M33" si="5">AVERAGE(G21:I21,D21)</f>
+        <f t="shared" ref="M21:M33" si="6">AVERAGE(G21:I21,D21)</f>
         <v>0.40263202152619421</v>
       </c>
       <c r="N21" s="22">
-        <f t="shared" ref="N21:N33" si="6">MEDIAN(G21:I21,D21:E21)</f>
+        <f t="shared" ref="N21:N33" si="7">MEDIAN(G21:I21,D21:E21)</f>
         <v>0.36993640022527796</v>
       </c>
       <c r="P21" s="2" t="s">
@@ -7844,43 +8255,43 @@
         <v>192</v>
       </c>
       <c r="D22" s="17">
-        <f>(Model!P67+Model!P73+Model!P74+Model!P75-Model!P52-Model!P53)/Model!P81</f>
+        <f>(Model!T67+Model!T73+Model!T74+Model!T75-Model!T52-Model!T53)/Model!T81</f>
         <v>-0.39498661474811392</v>
       </c>
       <c r="E22" s="17">
-        <f>(Model!Q67+Model!Q73+Model!Q74+Model!Q75-Model!Q52-Model!Q53)/Model!Q81</f>
+        <f>(Model!U67+Model!U73+Model!U74+Model!U75-Model!U52-Model!U53)/Model!U81</f>
         <v>0.23133192232000291</v>
       </c>
       <c r="F22" s="17">
-        <f>(Model!R67+Model!R73+Model!R74+Model!R75-Model!R52-Model!R53)/Model!R81</f>
+        <f>(Model!V67+Model!V73+Model!V74+Model!V75-Model!V52-Model!V53)/Model!V81</f>
         <v>5.794040853939493E-2</v>
       </c>
       <c r="G22" s="17">
-        <f>(Model!S67+Model!S73+Model!S74+Model!S75-Model!S52-Model!S53)/Model!S81</f>
+        <f>(Model!W67+Model!W73+Model!W74+Model!W75-Model!W52-Model!W53)/Model!W81</f>
         <v>0.20177444794952695</v>
       </c>
       <c r="H22" s="17">
-        <f>(Model!T67+Model!T73+Model!T74+Model!T75-Model!T52-Model!T53)/Model!T81</f>
+        <f>(Model!X67+Model!X73+Model!X74+Model!X75-Model!X52-Model!X53)/Model!X81</f>
         <v>0.42345196461633405</v>
       </c>
       <c r="I22" s="17">
-        <f>(Model!U67+Model!U73+Model!U74+Model!U75-Model!U52-Model!U53)/Model!U81</f>
+        <f>(Model!Y67+Model!Y73+Model!Y74+Model!Y75-Model!Y52-Model!Y53)/Model!Y81</f>
         <v>0.25605027955760506</v>
       </c>
       <c r="J22" s="17">
-        <f>(Model!V67+Model!V73+Model!V74+Model!V75-Model!V52-Model!V53)/Model!V81</f>
+        <f>(Model!Z67+Model!Z73+Model!Z74+Model!Z75-Model!Z52-Model!Z53)/Model!Z81</f>
         <v>0.1310025111068186</v>
       </c>
       <c r="K22" s="17">
-        <f>(Model!W67+Model!W73+Model!W74+Model!W75-Model!W52-Model!W53)/Model!W81</f>
+        <f>(Model!AA67+Model!AA73+Model!AA74+Model!AA75-Model!AA52-Model!AA53)/Model!AA81</f>
         <v>0.2505806996550996</v>
       </c>
       <c r="M22" s="22">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.12157251934383803</v>
       </c>
       <c r="N22" s="22">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.23133192232000291</v>
       </c>
       <c r="P22" s="2" t="s">
@@ -7892,43 +8303,43 @@
         <v>194</v>
       </c>
       <c r="D23" s="17">
-        <f>(Model!P67+Model!P73+Model!P74+Model!P75-Model!P52-Model!P53)/(Model!P26*(1-Model!P49)+Model!P86+Model!P102+SUM(Model!P94:P100))</f>
+        <f>(Model!T67+Model!T73+Model!T74+Model!T75-Model!T52-Model!T53)/(Model!T26*(1-Model!T49)+Model!T86+Model!T102+SUM(Model!T94:T100))</f>
         <v>-3.4354065857466791</v>
       </c>
       <c r="E23" s="17">
-        <f>(Model!Q67+Model!Q73+Model!Q74+Model!Q75-Model!Q52-Model!Q53)/(Model!Q26*(1-Model!Q49)+Model!Q86+Model!Q102+SUM(Model!Q94:Q100))</f>
+        <f>(Model!U67+Model!U73+Model!U74+Model!U75-Model!U52-Model!U53)/(Model!U26*(1-Model!U49)+Model!U86+Model!U102+SUM(Model!U94:U100))</f>
         <v>1.422828098672291</v>
       </c>
       <c r="F23" s="17">
-        <f>(Model!R67+Model!R73+Model!R74+Model!R75-Model!R52-Model!R53)/(Model!R26*(1-Model!R49)+Model!R86+Model!R102+SUM(Model!R94:R100))</f>
+        <f>(Model!V67+Model!V73+Model!V74+Model!V75-Model!V52-Model!V53)/(Model!V26*(1-Model!V49)+Model!V86+Model!V102+SUM(Model!V94:V100))</f>
         <v>0.9708521072772508</v>
       </c>
       <c r="G23" s="17">
-        <f>(Model!S67+Model!S73+Model!S74+Model!S75-Model!S52-Model!S53)/(Model!S26*(1-Model!S49)+Model!S86+Model!S102+SUM(Model!S94:S100))</f>
+        <f>(Model!W67+Model!W73+Model!W74+Model!W75-Model!W52-Model!W53)/(Model!W26*(1-Model!W49)+Model!W86+Model!W102+SUM(Model!W94:W100))</f>
         <v>1.0527804515936778</v>
       </c>
       <c r="H23" s="17">
-        <f>(Model!T67+Model!T73+Model!T74+Model!T75-Model!T52-Model!T53)/(Model!T26*(1-Model!T49)+Model!T86+Model!T102+SUM(Model!T94:T100))</f>
+        <f>(Model!X67+Model!X73+Model!X74+Model!X75-Model!X52-Model!X53)/(Model!X26*(1-Model!X49)+Model!X86+Model!X102+SUM(Model!X94:X100))</f>
         <v>18.833345586356071</v>
       </c>
       <c r="I23" s="17">
-        <f>(Model!U67+Model!U73+Model!U74+Model!U75-Model!U52-Model!U53)/(Model!U26*(1-Model!U49)+Model!U86+Model!U102+SUM(Model!U94:U100))</f>
+        <f>(Model!Y67+Model!Y73+Model!Y74+Model!Y75-Model!Y52-Model!Y53)/(Model!Y26*(1-Model!Y49)+Model!Y86+Model!Y102+SUM(Model!Y94:Y100))</f>
         <v>0.80213095480752494</v>
       </c>
       <c r="J23" s="17">
-        <f>(Model!V67+Model!V73+Model!V74+Model!V75-Model!V52-Model!V53)/(Model!V26*(1-Model!V49)+Model!V86+Model!V102+SUM(Model!V94:V100))</f>
+        <f>(Model!Z67+Model!Z73+Model!Z74+Model!Z75-Model!Z52-Model!Z53)/(Model!Z26*(1-Model!Z49)+Model!Z86+Model!Z102+SUM(Model!Z94:Z100))</f>
         <v>0.38680108686212644</v>
       </c>
       <c r="K23" s="17">
-        <f>(Model!W67+Model!W73+Model!W74+Model!W75-Model!W52-Model!W53)/(Model!W26*(1-Model!W49)+Model!W86+Model!W102+SUM(Model!W94:W100))</f>
+        <f>(Model!AA67+Model!AA73+Model!AA74+Model!AA75-Model!AA52-Model!AA53)/(Model!AA26*(1-Model!AA49)+Model!AA86+Model!AA102+SUM(Model!AA94:AA100))</f>
         <v>1.2961013119834393</v>
       </c>
       <c r="M23" s="22">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4.3132126017526478</v>
       </c>
       <c r="N23" s="22">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1.0527804515936778</v>
       </c>
       <c r="P23" s="2" t="s">
@@ -7940,43 +8351,43 @@
         <v>196</v>
       </c>
       <c r="D24" s="17">
-        <f>(Model!P67+Model!P73+Model!P74+Model!P75-Model!P52-Model!P53)/(Model!P26+Model!P86)</f>
+        <f>(Model!T67+Model!T73+Model!T74+Model!T75-Model!T52-Model!T53)/(Model!T26+Model!T86)</f>
         <v>-1.5400308385719377</v>
       </c>
       <c r="E24" s="17">
-        <f>(Model!Q67+Model!Q73+Model!Q74+Model!Q75-Model!Q52-Model!Q53)/(Model!Q26+Model!Q86)</f>
+        <f>(Model!U67+Model!U73+Model!U74+Model!U75-Model!U52-Model!U53)/(Model!U26+Model!U86)</f>
         <v>1.0622335890878085</v>
       </c>
       <c r="F24" s="17">
-        <f>(Model!R67+Model!R73+Model!R74+Model!R75-Model!R52-Model!R53)/(Model!R26+Model!R86)</f>
+        <f>(Model!V67+Model!V73+Model!V74+Model!V75-Model!V52-Model!V53)/(Model!V26+Model!V86)</f>
         <v>0.73970588235294132</v>
       </c>
       <c r="G24" s="17">
-        <f>(Model!S67+Model!S73+Model!S74+Model!S75-Model!S52-Model!S53)/(Model!S26+Model!S86)</f>
+        <f>(Model!W67+Model!W73+Model!W74+Model!W75-Model!W52-Model!W53)/(Model!W26+Model!W86)</f>
         <v>0.49771423013325583</v>
       </c>
       <c r="H24" s="17">
-        <f>(Model!T67+Model!T73+Model!T74+Model!T75-Model!T52-Model!T53)/(Model!T26+Model!T86)</f>
+        <f>(Model!X67+Model!X73+Model!X74+Model!X75-Model!X52-Model!X53)/(Model!X26+Model!X86)</f>
         <v>1.1130096247431591</v>
       </c>
       <c r="I24" s="17">
-        <f>(Model!U67+Model!U73+Model!U74+Model!U75-Model!U52-Model!U53)/(Model!U26+Model!U86)</f>
+        <f>(Model!Y67+Model!Y73+Model!Y74+Model!Y75-Model!Y52-Model!Y53)/(Model!Y26+Model!Y86)</f>
         <v>0.63669575806779011</v>
       </c>
       <c r="J24" s="17">
-        <f>(Model!V67+Model!V73+Model!V74+Model!V75-Model!V52-Model!V53)/(Model!V26+Model!V86)</f>
+        <f>(Model!Z67+Model!Z73+Model!Z74+Model!Z75-Model!Z52-Model!Z53)/(Model!Z26+Model!Z86)</f>
         <v>0.29443431449162116</v>
       </c>
       <c r="K24" s="17">
-        <f>(Model!W67+Model!W73+Model!W74+Model!W75-Model!W52-Model!W53)/(Model!W26+Model!W86)</f>
+        <f>(Model!AA67+Model!AA73+Model!AA74+Model!AA75-Model!AA52-Model!AA53)/(Model!AA26+Model!AA86)</f>
         <v>0.50417787848746642</v>
       </c>
       <c r="M24" s="22">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.17684719359306683</v>
       </c>
       <c r="N24" s="22">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.63669575806779011</v>
       </c>
       <c r="P24" s="2" t="s">
@@ -7988,43 +8399,43 @@
         <v>198</v>
       </c>
       <c r="D25" s="17">
-        <f>(-Model!P102/Model!P101)</f>
+        <f>(-Model!T102/Model!T101)</f>
         <v>0.25223271242663953</v>
       </c>
       <c r="E25" s="17">
-        <f>(-Model!Q102/Model!Q101)</f>
+        <f>(-Model!U102/Model!U101)</f>
         <v>0.35820302146832744</v>
       </c>
       <c r="F25" s="17">
-        <f>(-Model!R102/Model!R101)</f>
+        <f>(-Model!V102/Model!V101)</f>
         <v>0.28301391441323176</v>
       </c>
       <c r="G25" s="17">
-        <f>(-Model!S102/Model!S101)</f>
+        <f>(-Model!W102/Model!W101)</f>
         <v>0.23313311915071927</v>
       </c>
       <c r="H25" s="17">
-        <f>(-Model!T102/Model!T101)</f>
+        <f>(-Model!X102/Model!X101)</f>
         <v>0.52919708029197055</v>
       </c>
       <c r="I25" s="17">
-        <f>(-Model!U102/Model!U101)</f>
+        <f>(-Model!Y102/Model!Y101)</f>
         <v>0.15406188651023664</v>
       </c>
       <c r="J25" s="17">
-        <f>(-Model!V102/Model!V101)</f>
+        <f>(-Model!Z102/Model!Z101)</f>
         <v>0.17504655493482316</v>
       </c>
       <c r="K25" s="17">
-        <f>(-Model!W102/Model!W101)</f>
+        <f>(-Model!AA102/Model!AA101)</f>
         <v>0.35357823600762439</v>
       </c>
       <c r="M25" s="22">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.29215619959489153</v>
       </c>
       <c r="N25" s="22">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.25223271242663953</v>
       </c>
       <c r="P25" s="23" t="s">
@@ -8074,35 +8485,35 @@
         <v>202</v>
       </c>
       <c r="D27" s="24">
-        <f>-Model!P102/Model!P86</f>
+        <f>-Model!T102/Model!T86</f>
         <v>0.70280838961962311</v>
       </c>
       <c r="E27" s="24">
-        <f>-Model!Q102/Model!Q86</f>
+        <f>-Model!U102/Model!U86</f>
         <v>1.0029684601113174</v>
       </c>
       <c r="F27" s="24">
-        <f>-Model!R102/Model!R86</f>
+        <f>-Model!V102/Model!V86</f>
         <v>0.43537964458804523</v>
       </c>
       <c r="G27" s="24">
-        <f>-Model!S102/Model!S86</f>
+        <f>-Model!W102/Model!W86</f>
         <v>0.72659991292990866</v>
       </c>
       <c r="H27" s="24">
-        <f>-Model!T102/Model!T86</f>
+        <f>-Model!X102/Model!X86</f>
         <v>0.98639455782312924</v>
       </c>
       <c r="I27" s="24">
-        <f>-Model!U102/Model!U86</f>
+        <f>-Model!Y102/Model!Y86</f>
         <v>0.71965065502183412</v>
       </c>
       <c r="J27" s="24">
-        <f>-Model!V102/Model!V86</f>
+        <f>-Model!Z102/Model!Z86</f>
         <v>0.98451730418943528</v>
       </c>
       <c r="K27" s="24">
-        <f>-Model!W102/Model!W86</f>
+        <f>-Model!AA102/Model!AA86</f>
         <v>1.7515021459227469</v>
       </c>
       <c r="M27" s="24">
@@ -8130,7 +8541,7 @@
         <v>205</v>
       </c>
       <c r="F28" s="25">
-        <f>(Model!R81/-Model!R26)</f>
+        <f>(Model!V81/-Model!V26)</f>
         <v>59.733944954128539</v>
       </c>
       <c r="G28" s="4" t="s">
@@ -8163,43 +8574,43 @@
         <v>207</v>
       </c>
       <c r="D29" s="17">
-        <f>Model!P58/Model!P66</f>
+        <f>Model!T58/Model!T66</f>
         <v>0.60490004711583767</v>
       </c>
       <c r="E29" s="17">
-        <f>Model!Q58/Model!Q66</f>
+        <f>Model!U58/Model!U66</f>
         <v>0.46363274220799744</v>
       </c>
       <c r="F29" s="17">
-        <f>Model!R58/Model!R66</f>
+        <f>Model!V58/Model!V66</f>
         <v>0.53350237717908078</v>
       </c>
       <c r="G29" s="17">
-        <f>Model!S58/Model!S66</f>
+        <f>Model!W58/Model!W66</f>
         <v>0.54595000453092024</v>
       </c>
       <c r="H29" s="17">
-        <f>Model!T58/Model!T66</f>
+        <f>Model!X58/Model!X66</f>
         <v>0.48959422637896743</v>
       </c>
       <c r="I29" s="17">
-        <f>Model!U58/Model!U66</f>
+        <f>Model!Y58/Model!Y66</f>
         <v>0.50886014600308971</v>
       </c>
       <c r="J29" s="17">
-        <f>Model!V58/Model!V66</f>
+        <f>Model!Z58/Model!Z66</f>
         <v>0.53778042654633684</v>
       </c>
       <c r="K29" s="17">
-        <f>Model!W58/Model!W66</f>
+        <f>Model!AA58/Model!AA66</f>
         <v>0.50225466761418702</v>
       </c>
       <c r="M29" s="22">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.53732610600720376</v>
       </c>
       <c r="N29" s="22">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.50886014600308971</v>
       </c>
       <c r="P29" s="2" t="s">
@@ -8211,23 +8622,23 @@
         <v>209</v>
       </c>
       <c r="D30" s="22">
-        <f t="shared" ref="D30:H30" si="7">1-D29</f>
+        <f t="shared" ref="D30:H30" si="8">1-D29</f>
         <v>0.39509995288416233</v>
       </c>
       <c r="E30" s="22">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.53636725779200256</v>
       </c>
       <c r="F30" s="22">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.46649762282091922</v>
       </c>
       <c r="G30" s="22">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.45404999546907976</v>
       </c>
       <c r="H30" s="22">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.51040577362103257</v>
       </c>
       <c r="I30" s="22">
@@ -8235,19 +8646,19 @@
         <v>0.49113985399691029</v>
       </c>
       <c r="J30" s="22">
-        <f t="shared" ref="J30:K30" si="8">1-J29</f>
+        <f t="shared" ref="J30:K30" si="9">1-J29</f>
         <v>0.46221957345366316</v>
       </c>
       <c r="K30" s="22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.49774533238581298</v>
       </c>
       <c r="M30" s="22">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.46267389399279624</v>
       </c>
       <c r="N30" s="22">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.49113985399691029</v>
       </c>
       <c r="P30" s="2" t="s">
@@ -8259,43 +8670,43 @@
         <v>211</v>
       </c>
       <c r="D31" s="17">
-        <f>Model!P81/Model!P65</f>
+        <f>Model!T81/Model!T65</f>
         <v>1.4000000000000001</v>
       </c>
       <c r="E31" s="17">
-        <f>Model!Q81/Model!Q65</f>
+        <f>Model!U81/Model!U65</f>
         <v>0.68970727584705649</v>
       </c>
       <c r="F31" s="17">
-        <f>Model!R81/Model!R65</f>
+        <f>Model!V81/Model!V65</f>
         <v>0.70781356162522047</v>
       </c>
       <c r="G31" s="17">
-        <f>Model!S81/Model!S65</f>
+        <f>Model!W81/Model!W65</f>
         <v>0.72304270969949247</v>
       </c>
       <c r="H31" s="17">
-        <f>Model!T81/Model!T65</f>
+        <f>Model!X81/Model!X65</f>
         <v>0.70136203612858516</v>
       </c>
       <c r="I31" s="17">
-        <f>Model!U81/Model!U65</f>
+        <f>Model!Y81/Model!Y65</f>
         <v>0.75561243369927245</v>
       </c>
       <c r="J31" s="17">
-        <f>Model!V81/Model!V65</f>
+        <f>Model!Z81/Model!Z65</f>
         <v>0.7946521765825505</v>
       </c>
       <c r="K31" s="17">
-        <f>Model!W81/Model!W65</f>
+        <f>Model!AA81/Model!AA65</f>
         <v>0.7375853386288711</v>
       </c>
       <c r="M31" s="22">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.89500429488183753</v>
       </c>
       <c r="N31" s="22">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.72304270969949247</v>
       </c>
       <c r="P31" s="2" t="s">
@@ -8307,43 +8718,43 @@
         <v>213</v>
       </c>
       <c r="D32" s="17">
-        <f>(Model!P81+Model!P73)/Model!P81</f>
+        <f>(Model!T81+Model!T73)/Model!T81</f>
         <v>1.2096312971525918</v>
       </c>
       <c r="E32" s="17">
-        <f>(Model!Q81+Model!Q73)/Model!Q81</f>
+        <f>(Model!U81+Model!U73)/Model!U81</f>
         <v>1.1471909695146856</v>
       </c>
       <c r="F32" s="17">
-        <f>(Model!R81+Model!R73)/Model!R81</f>
+        <f>(Model!V81+Model!V73)/Model!V81</f>
         <v>1.6269774228229157</v>
       </c>
       <c r="G32" s="17">
-        <f>(Model!S81+Model!S73)/Model!S81</f>
+        <f>(Model!W81+Model!W73)/Model!W81</f>
         <v>1.4481466876971609</v>
       </c>
       <c r="H32" s="17">
-        <f>(Model!T81+Model!T73)/Model!T81</f>
+        <f>(Model!X81+Model!X73)/Model!X81</f>
         <v>1.4684221353630942</v>
       </c>
       <c r="I32" s="17">
-        <f>(Model!U81+Model!U73)/Model!U81</f>
+        <f>(Model!Y81+Model!Y73)/Model!Y81</f>
         <v>1.4654532098110433</v>
       </c>
       <c r="J32" s="17">
-        <f>(Model!V81+Model!V73)/Model!V81</f>
+        <f>(Model!Z81+Model!Z73)/Model!Z81</f>
         <v>1.2870001931620629</v>
       </c>
       <c r="K32" s="17">
-        <f>(Model!W81+Model!W73)/Model!W81</f>
+        <f>(Model!AA81+Model!AA73)/Model!AA81</f>
         <v>1.4360174561835715</v>
       </c>
       <c r="M32" s="22">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.3979133325059725</v>
       </c>
       <c r="N32" s="22">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1.4481466876971609</v>
       </c>
       <c r="P32" s="2" t="s">
@@ -8355,43 +8766,43 @@
         <v>215</v>
       </c>
       <c r="D33" s="17">
-        <f>Model!P62/Model!P66</f>
+        <f>Model!T62/Model!T66</f>
         <v>0.154741872518005</v>
       </c>
       <c r="E33" s="17">
-        <f>Model!Q62/Model!Q66</f>
+        <f>Model!U62/Model!U66</f>
         <v>0.1257572219398618</v>
       </c>
       <c r="F33" s="17">
-        <f>Model!R62/Model!R66</f>
+        <f>Model!V62/Model!V66</f>
         <v>0.11849128367670365</v>
       </c>
       <c r="G33" s="17">
-        <f>Model!S62/Model!S66</f>
+        <f>Model!W62/Model!W66</f>
         <v>0.11763563633539166</v>
       </c>
       <c r="H33" s="17">
-        <f>Model!T62/Model!T66</f>
+        <f>Model!X62/Model!X66</f>
         <v>0.13239561086972532</v>
       </c>
       <c r="I33" s="17">
-        <f>Model!U62/Model!U66</f>
+        <f>Model!Y62/Model!Y66</f>
         <v>0.13450761821100779</v>
       </c>
       <c r="J33" s="17">
-        <f>Model!V62/Model!V66</f>
+        <f>Model!Z62/Model!Z66</f>
         <v>0.12607665347012331</v>
       </c>
       <c r="K33" s="17">
-        <f>Model!W62/Model!W66</f>
+        <f>Model!AA62/Model!AA66</f>
         <v>0.11682925253569353</v>
       </c>
       <c r="M33" s="22">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.13482018448353245</v>
       </c>
       <c r="N33" s="22">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.13239561086972532</v>
       </c>
       <c r="P33" s="2" t="s">
@@ -8408,43 +8819,43 @@
         <v>218</v>
       </c>
       <c r="D36" s="23">
-        <f>Model!P54/Model!P19*360</f>
+        <f>Model!T54/Model!T19*360</f>
         <v>22.701726595913193</v>
       </c>
       <c r="E36" s="23">
-        <f>Model!Q54/Model!Q19*360</f>
+        <f>Model!U54/Model!U19*360</f>
         <v>16.19468164550797</v>
       </c>
       <c r="F36" s="23">
-        <f>Model!R54/Model!R19*360</f>
+        <f>Model!V54/Model!V19*360</f>
         <v>36.934193782948554</v>
       </c>
       <c r="G36" s="23">
-        <f>Model!S54/Model!S19*360</f>
+        <f>Model!W54/Model!W19*360</f>
         <v>23.469325400016082</v>
       </c>
       <c r="H36" s="23">
-        <f>Model!T54/Model!T19*360</f>
+        <f>Model!X54/Model!X19*360</f>
         <v>25.012725805450366</v>
       </c>
       <c r="I36" s="23">
-        <f>Model!U54/Model!U19*360</f>
+        <f>Model!Y54/Model!Y19*360</f>
         <v>24.239225502910397</v>
       </c>
       <c r="J36" s="23">
-        <f>Model!V54/Model!V19*360</f>
+        <f>Model!Z54/Model!Z19*360</f>
         <v>23.367707303291425</v>
       </c>
       <c r="K36" s="23">
-        <f>Model!W54/Model!W19*360</f>
+        <f>Model!AA54/Model!AA19*360</f>
         <v>21.814283073510381</v>
       </c>
       <c r="M36" s="23">
-        <f t="shared" ref="M36:M44" si="9">AVERAGE(G36:I36,D36)</f>
+        <f t="shared" ref="M36:M44" si="10">AVERAGE(G36:I36,D36)</f>
         <v>23.855750826072509</v>
       </c>
       <c r="N36" s="23">
-        <f t="shared" ref="N36:N44" si="10">MEDIAN(G36:I36,D36:E36)</f>
+        <f t="shared" ref="N36:N44" si="11">MEDIAN(G36:I36,D36:E36)</f>
         <v>23.469325400016082</v>
       </c>
       <c r="P36" s="2" t="s">
@@ -8456,43 +8867,43 @@
         <v>220</v>
       </c>
       <c r="D37" s="23">
-        <f>Model!P68/Model!P19*360</f>
+        <f>Model!T68/Model!T19*360</f>
         <v>11.536195152859181</v>
       </c>
       <c r="E37" s="23">
-        <f>Model!Q68/Model!Q19*360</f>
+        <f>Model!U68/Model!U19*360</f>
         <v>14.423844930030196</v>
       </c>
       <c r="F37" s="23">
-        <f>Model!R68/Model!R19*360</f>
+        <f>Model!V68/Model!V19*360</f>
         <v>29.113797491365204</v>
       </c>
       <c r="G37" s="23">
-        <f>Model!S68/Model!S19*360</f>
+        <f>Model!W68/Model!W19*360</f>
         <v>25.976039237758304</v>
       </c>
       <c r="H37" s="23">
-        <f>Model!T68/Model!T19*360</f>
+        <f>Model!X68/Model!X19*360</f>
         <v>20.761065243031844</v>
       </c>
       <c r="I37" s="23">
-        <f>Model!U68/Model!U19*360</f>
+        <f>Model!Y68/Model!Y19*360</f>
         <v>18.034200922882047</v>
       </c>
       <c r="J37" s="23">
-        <f>Model!V68/Model!V19*360</f>
+        <f>Model!Z68/Model!Z19*360</f>
         <v>22.172623251871734</v>
       </c>
       <c r="K37" s="23">
-        <f>Model!W68/Model!W19*360</f>
+        <f>Model!AA68/Model!AA19*360</f>
         <v>19.121326021319859</v>
       </c>
       <c r="M37" s="23">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>19.076875139132845</v>
       </c>
       <c r="N37" s="23">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>18.034200922882047</v>
       </c>
       <c r="P37" s="2" t="s">
@@ -8504,43 +8915,43 @@
         <v>222</v>
       </c>
       <c r="D38" s="17">
-        <f>Model!P52/Model!P72</f>
+        <f>Model!T52/Model!T72</f>
         <v>0.48670944087992674</v>
       </c>
       <c r="E38" s="17">
-        <f>Model!Q52/Model!Q72</f>
+        <f>Model!U52/Model!U72</f>
         <v>0.77456978967495227</v>
       </c>
       <c r="F38" s="17">
-        <f>Model!R52/Model!R72</f>
+        <f>Model!V52/Model!V72</f>
         <v>1.6273346794548209</v>
       </c>
       <c r="G38" s="17">
-        <f>Model!S52/Model!S72</f>
+        <f>Model!W52/Model!W72</f>
         <v>0.82626235758301192</v>
       </c>
       <c r="H38" s="17">
-        <f>Model!T52/Model!T72</f>
+        <f>Model!X52/Model!X72</f>
         <v>1.0239705390023435</v>
       </c>
       <c r="I38" s="17">
-        <f>Model!U52/Model!U72</f>
+        <f>Model!Y52/Model!Y72</f>
         <v>1.1329062159214831</v>
       </c>
       <c r="J38" s="17">
-        <f>Model!V52/Model!V72</f>
+        <f>Model!Z52/Model!Z72</f>
         <v>0.90101701270094192</v>
       </c>
       <c r="K38" s="17">
-        <f>Model!W52/Model!W72</f>
+        <f>Model!AA52/Model!AA72</f>
         <v>1.0884204763208323</v>
       </c>
       <c r="M38" s="22">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.86746213834669128</v>
       </c>
       <c r="N38" s="22">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.82626235758301192</v>
       </c>
       <c r="P38" s="2" t="s">
@@ -8552,43 +8963,43 @@
         <v>224</v>
       </c>
       <c r="D39" s="17">
-        <f>(Model!P52+Model!P54)/Model!P72</f>
+        <f>(Model!T52+Model!T54)/Model!T72</f>
         <v>0.81843179735022087</v>
       </c>
       <c r="E39" s="17">
-        <f>(Model!Q52+Model!Q54)/Model!Q72</f>
+        <f>(Model!U52+Model!U54)/Model!U72</f>
         <v>0.90702676864244747</v>
       </c>
       <c r="F39" s="17">
-        <f>(Model!R52+Model!R54)/Model!R72</f>
+        <f>(Model!V52+Model!V54)/Model!V72</f>
         <v>1.9122286723876831</v>
       </c>
       <c r="G39" s="17">
-        <f>(Model!S52+Model!S54)/Model!S72</f>
+        <f>(Model!W52+Model!W54)/Model!W72</f>
         <v>1.005984838409363</v>
       </c>
       <c r="H39" s="17">
-        <f>(Model!T52+Model!T54)/Model!T72</f>
+        <f>(Model!X52+Model!X54)/Model!X72</f>
         <v>1.3237361901573486</v>
       </c>
       <c r="I39" s="17">
-        <f>(Model!U52+Model!U54)/Model!U72</f>
+        <f>(Model!Y52+Model!Y54)/Model!Y72</f>
         <v>1.4372273718647763</v>
       </c>
       <c r="J39" s="17">
-        <f>(Model!V52+Model!V54)/Model!V72</f>
+        <f>(Model!Z52+Model!Z54)/Model!Z72</f>
         <v>1.1163706237990343</v>
       </c>
       <c r="K39" s="17">
-        <f>(Model!W52+Model!W54)/Model!W72</f>
+        <f>(Model!AA52+Model!AA54)/Model!AA72</f>
         <v>1.3576238707911306</v>
       </c>
       <c r="M39" s="22">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.1463450494454273</v>
       </c>
       <c r="N39" s="22">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.005984838409363</v>
       </c>
       <c r="P39" s="2" t="s">
@@ -8600,43 +9011,43 @@
         <v>226</v>
       </c>
       <c r="D40" s="17">
-        <f>Model!P58/Model!P72</f>
+        <f>Model!T58/Model!T72</f>
         <v>2.9954170485792853</v>
       </c>
       <c r="E40" s="17">
-        <f>Model!Q58/Model!Q72</f>
+        <f>Model!U58/Model!U72</f>
         <v>1.6133843212237098</v>
       </c>
       <c r="F40" s="17">
-        <f>Model!R58/Model!R72</f>
+        <f>Model!V58/Model!V72</f>
         <v>2.6552246340232206</v>
       </c>
       <c r="G40" s="17">
-        <f>Model!S58/Model!S72</f>
+        <f>Model!W58/Model!W72</f>
         <v>1.8696191869486194</v>
       </c>
       <c r="H40" s="17">
-        <f>Model!T58/Model!T72</f>
+        <f>Model!X58/Model!X72</f>
         <v>2.2257114161365914</v>
       </c>
       <c r="I40" s="17">
-        <f>Model!U58/Model!U72</f>
+        <f>Model!Y58/Model!Y72</f>
         <v>2.2899400218102506</v>
       </c>
       <c r="J40" s="17">
-        <f>Model!V58/Model!V72</f>
+        <f>Model!Z58/Model!Z72</f>
         <v>1.7762103388480104</v>
       </c>
       <c r="K40" s="17">
-        <f>Model!W58/Model!W72</f>
+        <f>Model!AA58/Model!AA72</f>
         <v>2.1282233780454423</v>
       </c>
       <c r="M40" s="22">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2.3451719183686865</v>
       </c>
       <c r="N40" s="22">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.2257114161365914</v>
       </c>
       <c r="P40" s="2" t="s">
@@ -8648,43 +9059,43 @@
         <v>228</v>
       </c>
       <c r="D41" s="17">
-        <f>Model!P55/Model!P66</f>
+        <f>Model!T55/Model!T66</f>
         <v>0.13761190011442417</v>
       </c>
       <c r="E41" s="17">
-        <f>Model!Q55/Model!Q66</f>
+        <f>Model!U55/Model!U66</f>
         <v>0.10112776274399374</v>
       </c>
       <c r="F41" s="17">
-        <f>Model!R55/Model!R66</f>
+        <f>Model!V55/Model!V66</f>
         <v>9.6228209191759118E-2</v>
       </c>
       <c r="G41" s="17">
-        <f>Model!S55/Model!S66</f>
+        <f>Model!W55/Model!W66</f>
         <v>0.12651624011288462</v>
       </c>
       <c r="H41" s="17">
-        <f>Model!T55/Model!T66</f>
+        <f>Model!X55/Model!X66</f>
         <v>0.15778776051255614</v>
       </c>
       <c r="I41" s="17">
-        <f>Model!U55/Model!U66</f>
+        <f>Model!Y55/Model!Y66</f>
         <v>0.13664314058098326</v>
       </c>
       <c r="J41" s="17">
-        <f>Model!V55/Model!V66</f>
+        <f>Model!Z55/Model!Z66</f>
         <v>0.13474664055737659</v>
       </c>
       <c r="K41" s="17">
-        <f>Model!W55/Model!W66</f>
+        <f>Model!AA55/Model!AA66</f>
         <v>0.13105497771173849</v>
       </c>
       <c r="M41" s="22">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.13963976033021205</v>
       </c>
       <c r="N41" s="22">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.13664314058098326</v>
       </c>
       <c r="P41" s="2" t="s">
@@ -8696,43 +9107,43 @@
         <v>230</v>
       </c>
       <c r="D42" s="23">
-        <f>Model!P20/Model!P55</f>
+        <f>Model!T20/Model!T55</f>
         <v>2.9677182685253118</v>
       </c>
       <c r="E42" s="23">
-        <f>Model!Q20/Model!Q55</f>
+        <f>Model!U20/Model!U55</f>
         <v>3.404645476772616</v>
       </c>
       <c r="F42" s="23">
-        <f>Model!R20/Model!R55</f>
+        <f>Model!V20/Model!V55</f>
         <v>2.0281949934123849</v>
       </c>
       <c r="G42" s="23">
-        <f>Model!S20/Model!S55</f>
+        <f>Model!W20/Model!W55</f>
         <v>2.1191036529213139</v>
       </c>
       <c r="H42" s="23">
-        <f>Model!T20/Model!T55</f>
+        <f>Model!X20/Model!X55</f>
         <v>2.1262018108839729</v>
       </c>
       <c r="I42" s="23">
-        <f>Model!U20/Model!U55</f>
+        <f>Model!Y20/Model!Y55</f>
         <v>2.4380403458213253</v>
       </c>
       <c r="J42" s="23">
-        <f>Model!V20/Model!V55</f>
+        <f>Model!Z20/Model!Z55</f>
         <v>2.3442502106149958</v>
       </c>
       <c r="K42" s="23">
-        <f>Model!W20/Model!W55</f>
+        <f>Model!AA20/Model!AA55</f>
         <v>2.4108251996450756</v>
       </c>
       <c r="M42" s="23">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2.412766019537981</v>
       </c>
       <c r="N42" s="23">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.4380403458213253</v>
       </c>
       <c r="P42" s="2" t="s">
@@ -8744,23 +9155,23 @@
         <v>232</v>
       </c>
       <c r="D43" s="23">
-        <f t="shared" ref="D43:H43" si="11">360/D42</f>
+        <f t="shared" ref="D43:H43" si="12">360/D42</f>
         <v>121.3053152039555</v>
       </c>
       <c r="E43" s="23">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>105.737881508079</v>
       </c>
       <c r="F43" s="23">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>177.49772638690396</v>
       </c>
       <c r="G43" s="23">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>169.88314823756639</v>
       </c>
       <c r="H43" s="23">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>169.31600667310562</v>
       </c>
       <c r="I43" s="23">
@@ -8768,19 +9179,19 @@
         <v>147.65957446808511</v>
       </c>
       <c r="J43" s="23">
-        <f t="shared" ref="J43:K43" si="12">360/J42</f>
+        <f t="shared" ref="J43:K43" si="13">360/J42</f>
         <v>153.5672251920399</v>
       </c>
       <c r="K43" s="23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>149.32646301067354</v>
       </c>
       <c r="M43" s="23">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>152.04101114567817</v>
       </c>
       <c r="N43" s="23">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>147.65957446808511</v>
       </c>
       <c r="P43" s="2" t="s">
@@ -8792,23 +9203,23 @@
         <v>234</v>
       </c>
       <c r="D44" s="23">
-        <f t="shared" ref="D44:H44" si="13">D36+D43-D37</f>
+        <f t="shared" ref="D44:H44" si="14">D36+D43-D37</f>
         <v>132.47084664700949</v>
       </c>
       <c r="E44" s="23">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>107.50871822355677</v>
       </c>
       <c r="F44" s="23">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>185.3181226784873</v>
       </c>
       <c r="G44" s="23">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>167.37643439982418</v>
       </c>
       <c r="H44" s="23">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>173.56766723552414</v>
       </c>
       <c r="I44" s="23">
@@ -8816,19 +9227,19 @@
         <v>153.86459904811346</v>
       </c>
       <c r="J44" s="23">
-        <f t="shared" ref="J44:K44" si="14">J36+J43-J37</f>
+        <f t="shared" ref="J44:K44" si="15">J36+J43-J37</f>
         <v>154.76230924345961</v>
       </c>
       <c r="K44" s="23">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>152.01942006286407</v>
       </c>
       <c r="M44" s="23">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>156.81988683261781</v>
       </c>
       <c r="N44" s="23">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>153.86459904811346</v>
       </c>
       <c r="P44" s="2" t="s">
@@ -8926,28 +9337,28 @@
         <v>242</v>
       </c>
       <c r="D50" s="3">
-        <f>131.6*Model!P35</f>
+        <f>131.6*Model!T35</f>
         <v>10274.406800000001</v>
       </c>
       <c r="E50" s="3">
-        <f>73.8*Model!Q35</f>
+        <f>73.8*Model!U35</f>
         <v>5362.0865999999996</v>
       </c>
       <c r="F50" s="3">
-        <f>133.3*Model!R35</f>
+        <f>133.3*Model!V35</f>
         <v>9748.3623000000007</v>
       </c>
       <c r="G50" s="3">
-        <f>106.7*Model!S35</f>
+        <f>106.7*Model!W35</f>
         <v>7477.0025000000005</v>
       </c>
       <c r="H50" s="3">
-        <f>113.7*Model!T35</f>
+        <f>113.7*Model!X35</f>
         <v>7436.4348</v>
       </c>
       <c r="I50" s="3">
         <f>Main!H4</f>
-        <v>22473.766070860001</v>
+        <v>23231.114986099998</v>
       </c>
       <c r="J50" s="3">
         <f>Main!I4</f>
@@ -8963,28 +9374,28 @@
         <v>12</v>
       </c>
       <c r="D51" s="3">
-        <f>(Model!P67+Model!P73+Model!P74+Model!P75-Model!P52-Model!P53)+D50</f>
+        <f>(Model!T67+Model!T73+Model!T74+Model!T75-Model!T52-Model!T53)+D50</f>
         <v>8976.006800000001</v>
       </c>
       <c r="E51" s="3">
-        <f>(Model!Q67+Model!Q73+Model!Q74+Model!Q75-Model!Q52-Model!Q53)+E50</f>
+        <f>(Model!U67+Model!U73+Model!U74+Model!U75-Model!U52-Model!U53)+E50</f>
         <v>5985.0865999999996</v>
       </c>
       <c r="F51" s="3">
-        <f>(Model!R67+Model!R73+Model!R74+Model!R75-Model!R52-Model!R53)+F50</f>
+        <f>(Model!V67+Model!V73+Model!V74+Model!V75-Model!V52-Model!V53)+F50</f>
         <v>9899.2623000000003</v>
       </c>
       <c r="G51" s="3">
-        <f>(Model!S67+Model!S73+Model!S74+Model!S75-Model!S52-Model!S53)+G50</f>
+        <f>(Model!W67+Model!W73+Model!W74+Model!W75-Model!W52-Model!W53)+G50</f>
         <v>7988.7025000000012</v>
       </c>
       <c r="H51" s="3">
-        <f>(Model!T67+Model!T73+Model!T74+Model!T75-Model!T52-Model!T53)+H50</f>
+        <f>(Model!X67+Model!X73+Model!X74+Model!X75-Model!X52-Model!X53)+H50</f>
         <v>8465.6347999999998</v>
       </c>
       <c r="I51" s="3">
         <f>Main!H7</f>
-        <v>23299.86607086</v>
+        <v>23864.614986099998</v>
       </c>
       <c r="J51" s="3">
         <f>Main!I7</f>
@@ -9000,40 +9411,40 @@
         <v>243</v>
       </c>
       <c r="D52" s="23">
-        <f>D50/Model!P32</f>
+        <f>D50/Model!T32</f>
         <v>23.844063123694614</v>
       </c>
       <c r="E52" s="23">
-        <f>E50/Model!Q32</f>
+        <f>E50/Model!U32</f>
         <v>13.952866510538627</v>
       </c>
       <c r="F52" s="23">
-        <f>F50/Model!R32</f>
+        <f>F50/Model!V32</f>
         <v>-80.498450041288251</v>
       </c>
       <c r="G52" s="23">
-        <f>G50/Model!S32</f>
+        <f>G50/Model!W32</f>
         <v>12.459594234294283</v>
       </c>
       <c r="H52" s="23">
-        <f>H50/Model!T32</f>
+        <f>H50/Model!X32</f>
         <v>14.226965372106363</v>
       </c>
       <c r="I52" s="23">
-        <f>I50/Model!U32</f>
-        <v>34.77296312990876</v>
+        <f>I50/Model!Y32</f>
+        <v>35.944785681726792</v>
       </c>
       <c r="J52" s="23">
-        <f>J50/Model!V32</f>
+        <f>J50/Model!Z32</f>
         <v>0</v>
       </c>
       <c r="K52" s="23">
-        <f>K50/Model!W32</f>
+        <f>K50/Model!AA32</f>
         <v>0</v>
       </c>
       <c r="M52" s="23">
-        <f t="shared" ref="M52:M63" si="15">AVERAGE(G52:I52,D52)</f>
-        <v>21.325896465001005</v>
+        <f t="shared" ref="M52:M63" si="16">AVERAGE(G52:I52,D52)</f>
+        <v>21.618852102955511</v>
       </c>
       <c r="N52" s="23">
         <f>MEDIAN(G52:I52,D52:E52)</f>
@@ -9069,7 +9480,7 @@
       </c>
       <c r="I53" s="17">
         <f>I52/Main!H2</f>
-        <v>9.2258000928361561E-2</v>
+        <v>9.2189755531487033E-2</v>
       </c>
       <c r="J53" s="17" t="e">
         <f>J52/Main!I2</f>
@@ -9080,11 +9491,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="M53" s="17">
-        <f t="shared" si="15"/>
-        <v>0.1288358298969205</v>
+        <f t="shared" si="16"/>
+        <v>0.12881876854770186</v>
       </c>
       <c r="N53" s="17">
-        <f t="shared" ref="N53:N63" si="16">MEDIAN(G53:I53,D53:E53)</f>
+        <f t="shared" ref="N53:N63" si="17">MEDIAN(G53:I53,D53:E53)</f>
         <v>0.12512722402907972</v>
       </c>
       <c r="P53" s="2" t="s">
@@ -9099,39 +9510,39 @@
         <v>70</v>
       </c>
       <c r="E54" s="23">
-        <f>E52/(Model!Q32/Model!P32-1)</f>
+        <f>E52/(Model!U32/Model!T32-1)</f>
         <v>-129.01910256204266</v>
       </c>
       <c r="F54" s="23">
-        <f>F52/(Model!R32/Model!Q32-1)</f>
+        <f>F52/(Model!V32/Model!U32-1)</f>
         <v>61.210040266852168</v>
       </c>
       <c r="G54" s="23">
-        <f>G52/(Model!S32/Model!R32-1)</f>
+        <f>G52/(Model!W32/Model!V32-1)</f>
         <v>-2.0921476175444211</v>
       </c>
       <c r="H54" s="23">
-        <f>H52/(Model!T32/Model!S32-1)</f>
+        <f>H52/(Model!X32/Model!W32-1)</f>
         <v>-110.30493436435457</v>
       </c>
       <c r="I54" s="23">
-        <f>I52/(Model!U32/Model!T32-1)</f>
-        <v>147.05362320391171</v>
+        <f>I52/(Model!Y32/Model!X32-1)</f>
+        <v>152.00921906018431</v>
       </c>
       <c r="J54" s="23">
-        <f>J52/(Model!V32/Model!U32-1)</f>
+        <f>J52/(Model!Z32/Model!Y32-1)</f>
         <v>0</v>
       </c>
       <c r="K54" s="23">
-        <f>K52/(Model!W32/Model!V32-1)</f>
+        <f>K52/(Model!AA32/Model!Z32-1)</f>
         <v>0</v>
       </c>
       <c r="M54" s="23">
-        <f t="shared" si="15"/>
-        <v>11.552180407337573</v>
+        <f t="shared" si="16"/>
+        <v>13.204045692761772</v>
       </c>
       <c r="N54" s="23">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-56.198540990949496</v>
       </c>
       <c r="P54" s="2" t="s">
@@ -9143,43 +9554,43 @@
         <v>249</v>
       </c>
       <c r="D55" s="23">
-        <f>D50/Model!P81</f>
+        <f>D50/Model!T81</f>
         <v>3.1255800681431003</v>
       </c>
       <c r="E55" s="23">
-        <f>E50/Model!Q81</f>
+        <f>E50/Model!U81</f>
         <v>1.9910462292525333</v>
       </c>
       <c r="F55" s="23">
-        <f>F50/Model!R81</f>
+        <f>F50/Model!V81</f>
         <v>3.7430357471970535</v>
       </c>
       <c r="G55" s="23">
-        <f>G50/Model!S81</f>
+        <f>G50/Model!W81</f>
         <v>2.9483448343848582</v>
       </c>
       <c r="H55" s="23">
-        <f>H50/Model!T81</f>
+        <f>H50/Model!X81</f>
         <v>3.0596316807241322</v>
       </c>
       <c r="I55" s="23">
-        <f>I50/Model!U81</f>
-        <v>9.1718426604334145</v>
+        <f>I50/Model!Y81</f>
+        <v>9.4809268196139218</v>
       </c>
       <c r="J55" s="23">
-        <f>J50/Model!V81</f>
+        <f>J50/Model!Z81</f>
         <v>0</v>
       </c>
       <c r="K55" s="23">
-        <f>K50/Model!W81</f>
+        <f>K50/Model!AA81</f>
         <v>0</v>
       </c>
       <c r="M55" s="23">
-        <f t="shared" si="15"/>
-        <v>4.5763498109213767</v>
+        <f t="shared" si="16"/>
+        <v>4.6536208507165036</v>
       </c>
       <c r="N55" s="23">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>3.0596316807241322</v>
       </c>
       <c r="P55" s="2" t="s">
@@ -9191,43 +9602,43 @@
         <v>251</v>
       </c>
       <c r="D56" s="23">
-        <f>D50/(Model!P81-Model!P63-Model!P62)</f>
+        <f>D50/(Model!T81-Model!T63-Model!T62)</f>
         <v>4.6619205953083158</v>
       </c>
       <c r="E56" s="23">
-        <f>E50/(Model!Q81-Model!Q63-Model!Q62)</f>
+        <f>E50/(Model!U81-Model!U63-Model!U62)</f>
         <v>3.2763574483685662</v>
       </c>
       <c r="F56" s="23">
-        <f>F50/(Model!R81-Model!R63-Model!R62)</f>
+        <f>F50/(Model!V81-Model!V63-Model!V62)</f>
         <v>6.2945452960547605</v>
       </c>
       <c r="G56" s="23">
-        <f>G50/(Model!S81-Model!S63-Model!S62)</f>
+        <f>G50/(Model!W81-Model!W63-Model!W62)</f>
         <v>4.9048822487536086</v>
       </c>
       <c r="H56" s="23">
-        <f>H50/(Model!T81-Model!T63-Model!T62)</f>
+        <f>H50/(Model!X81-Model!X63-Model!X62)</f>
         <v>5.1545260969016464</v>
       </c>
       <c r="I56" s="23">
-        <f>I50/(Model!U81-Model!U63-Model!U62)</f>
-        <v>15.118577915142945</v>
+        <f>I50/(Model!Y81-Model!Y63-Model!Y62)</f>
+        <v>15.628062553716774</v>
       </c>
       <c r="J56" s="23">
-        <f>J50/(Model!V81-Model!V63-Model!V62)</f>
+        <f>J50/(Model!Z81-Model!Z63-Model!Z62)</f>
         <v>0</v>
       </c>
       <c r="K56" s="23">
-        <f>K50/(Model!W81-Model!W63-Model!W62)</f>
+        <f>K50/(Model!AA81-Model!AA63-Model!AA62)</f>
         <v>0</v>
       </c>
       <c r="M56" s="23">
-        <f t="shared" si="15"/>
-        <v>7.4599767140266291</v>
+        <f t="shared" si="16"/>
+        <v>7.5873478736700868</v>
       </c>
       <c r="N56" s="23">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>4.9048822487536086</v>
       </c>
       <c r="P56" s="2" t="s">
@@ -9239,43 +9650,43 @@
         <v>253</v>
       </c>
       <c r="D57" s="23">
-        <f>D50/Model!P101</f>
+        <f>D50/Model!T101</f>
         <v>13.108454707833637</v>
       </c>
       <c r="E57" s="23">
-        <f>E50/Model!Q101</f>
+        <f>E50/Model!U101</f>
         <v>7.1058661542539054</v>
       </c>
       <c r="F57" s="23">
-        <f>F50/Model!R101</f>
+        <f>F50/Model!V101</f>
         <v>25.592970070884746</v>
       </c>
       <c r="G57" s="23">
-        <f>G50/Model!S101</f>
+        <f>G50/Model!W101</f>
         <v>10.444199608883919</v>
       </c>
       <c r="H57" s="23">
-        <f>H50/Model!T101</f>
+        <f>H50/Model!X101</f>
         <v>18.093515328467145</v>
       </c>
       <c r="I57" s="23">
-        <f>I50/Model!U101</f>
-        <v>21.0094101812284</v>
+        <f>I50/Model!Y101</f>
+        <v>21.71741141076939</v>
       </c>
       <c r="J57" s="23">
-        <f>J50/Model!V101</f>
+        <f>J50/Model!Z101</f>
         <v>0</v>
       </c>
       <c r="K57" s="23">
-        <f>K50/Model!W101</f>
+        <f>K50/Model!AA101</f>
         <v>0</v>
       </c>
       <c r="M57" s="23">
-        <f t="shared" si="15"/>
-        <v>15.663894956603274</v>
+        <f t="shared" si="16"/>
+        <v>15.840895263988523</v>
       </c>
       <c r="N57" s="23">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>13.108454707833637</v>
       </c>
       <c r="P57" s="2" t="s">
@@ -9287,43 +9698,43 @@
         <v>255</v>
       </c>
       <c r="D58" s="23">
-        <f>D50/Model!P19</f>
+        <f>D50/Model!T19</f>
         <v>1.6274998891176937</v>
       </c>
       <c r="E58" s="23">
-        <f>E50/Model!Q19</f>
+        <f>E50/Model!U19</f>
         <v>0.87049686678138893</v>
       </c>
       <c r="F58" s="23">
-        <f>F50/Model!R19</f>
+        <f>F50/Model!V19</f>
         <v>2.2151341347027813</v>
       </c>
       <c r="G58" s="23">
-        <f>G50/Model!S19</f>
+        <f>G50/Model!W19</f>
         <v>1.2023803972018976</v>
       </c>
       <c r="H58" s="23">
-        <f>H50/Model!T19</f>
+        <f>H50/Model!X19</f>
         <v>1.154080762306785</v>
       </c>
       <c r="I58" s="23">
-        <f>I50/Model!U19</f>
-        <v>3.3889926819163376</v>
+        <f>I50/Model!Y19</f>
+        <v>3.5031991715324065</v>
       </c>
       <c r="J58" s="23">
-        <f>J50/Model!V19</f>
+        <f>J50/Model!Z19</f>
         <v>0</v>
       </c>
       <c r="K58" s="23">
-        <f>K50/Model!W19</f>
+        <f>K50/Model!AA19</f>
         <v>0</v>
       </c>
       <c r="M58" s="23">
-        <f t="shared" si="15"/>
-        <v>1.8432384326356783</v>
+        <f t="shared" si="16"/>
+        <v>1.8717900550396958</v>
       </c>
       <c r="N58" s="23">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1.2023803972018976</v>
       </c>
       <c r="P58" s="2" t="s">
@@ -9342,43 +9753,43 @@
         <v>258</v>
       </c>
       <c r="D60" s="23">
-        <f>D51/(Model!P26+Model!P86)</f>
+        <f>D51/(Model!T26+Model!T86)</f>
         <v>10.646431977226905</v>
       </c>
       <c r="E60" s="23">
-        <f>E51/(Model!Q26+Model!Q86)</f>
+        <f>E51/(Model!U26+Model!U86)</f>
         <v>10.204751236146624</v>
       </c>
       <c r="F60" s="23">
-        <f>F51/(Model!R26+Model!R86)</f>
+        <f>F51/(Model!V26+Model!V86)</f>
         <v>48.525795588235276</v>
       </c>
       <c r="G60" s="23">
-        <f>G51/(Model!S26+Model!S86)</f>
+        <f>G51/(Model!W26+Model!W86)</f>
         <v>7.7703555101643813</v>
       </c>
       <c r="H60" s="23">
-        <f>H51/(Model!T26+Model!T86)</f>
+        <f>H51/(Model!X26+Model!X86)</f>
         <v>9.155006813020437</v>
       </c>
       <c r="I60" s="23">
-        <f>I51/(Model!U26+Model!U86)</f>
-        <v>23.645084301664319</v>
+        <f>I51/(Model!Y26+Model!Y86)</f>
+        <v>24.218200716561821</v>
       </c>
       <c r="J60" s="23">
-        <f>J51/(Model!V26+Model!V86)</f>
+        <f>J51/(Model!Z26+Model!Z86)</f>
         <v>0</v>
       </c>
       <c r="K60" s="23">
-        <f>K51/(Model!W26+Model!W86)</f>
+        <f>K51/(Model!AA26+Model!AA86)</f>
         <v>0</v>
       </c>
       <c r="M60" s="23">
-        <f t="shared" si="15"/>
-        <v>12.804219650519011</v>
+        <f t="shared" si="16"/>
+        <v>12.947498754243385</v>
       </c>
       <c r="N60" s="23">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>10.204751236146624</v>
       </c>
       <c r="P60" s="2" t="s">
@@ -9390,43 +9801,43 @@
         <v>259</v>
       </c>
       <c r="D61" s="23">
-        <f>Ratios!D51/Model!P26</f>
+        <f>Ratios!D51/Model!T26</f>
         <v>15.977228195087228</v>
       </c>
       <c r="E61" s="23">
-        <f>Ratios!E51/Model!Q26</f>
+        <f>Ratios!E51/Model!U26</f>
         <v>18.880399369085143</v>
       </c>
       <c r="F61" s="23">
-        <f>Ratios!F51/Model!R26</f>
+        <f>Ratios!F51/Model!V26</f>
         <v>-227.04730045871608</v>
       </c>
       <c r="G61" s="23">
-        <f>Ratios!G51/Model!S26</f>
+        <f>Ratios!G51/Model!W26</f>
         <v>10.005889904809619</v>
       </c>
       <c r="H61" s="23">
-        <f>Ratios!H51/Model!T26</f>
+        <f>Ratios!H51/Model!X26</f>
         <v>12.021634194831009</v>
       </c>
       <c r="I61" s="23">
-        <f>Ratios!I51/Model!U26</f>
-        <v>30.803630447990514</v>
+        <f>Ratios!I51/Model!Y26</f>
+        <v>31.550257781729275</v>
       </c>
       <c r="J61" s="23">
-        <f>Ratios!J51/Model!V26</f>
+        <f>Ratios!J51/Model!Z26</f>
         <v>0</v>
       </c>
       <c r="K61" s="23">
-        <f>Ratios!K51/Model!W26</f>
+        <f>Ratios!K51/Model!AA26</f>
         <v>0</v>
       </c>
       <c r="M61" s="23">
-        <f t="shared" si="15"/>
-        <v>17.202095685679595</v>
+        <f t="shared" si="16"/>
+        <v>17.388752519114284</v>
       </c>
       <c r="N61" s="23">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>15.977228195087228</v>
       </c>
       <c r="P61" s="2" t="s">
@@ -9438,43 +9849,43 @@
         <v>260</v>
       </c>
       <c r="D62" s="23">
-        <f>D51/(Model!P26*(1-Model!P49)+Model!P86+Model!P102+SUM(Model!P94:P100))</f>
+        <f>D51/(Model!T26*(1-Model!T49)+Model!T86+Model!T102+SUM(Model!T94:T100))</f>
         <v>23.749409176237659</v>
       </c>
       <c r="E62" s="23">
-        <f>E51/(Model!Q26*(1-Model!Q49)+Model!Q86+Model!Q102+SUM(Model!Q94:Q100))</f>
+        <f>E51/(Model!U26*(1-Model!U49)+Model!U86+Model!U102+SUM(Model!U94:U100))</f>
         <v>13.668939626752815</v>
       </c>
       <c r="F62" s="23">
-        <f>F51/(Model!R26*(1-Model!R49)+Model!R86+Model!R102+SUM(Model!R94:R100))</f>
+        <f>F51/(Model!V26*(1-Model!V49)+Model!V86+Model!V102+SUM(Model!V94:V100))</f>
         <v>63.68932845888164</v>
       </c>
       <c r="G62" s="23">
-        <f>G51/(Model!S26*(1-Model!S49)+Model!S86+Model!S102+SUM(Model!S94:S100))</f>
+        <f>G51/(Model!W26*(1-Model!W49)+Model!W86+Model!W102+SUM(Model!W94:W100))</f>
         <v>16.436095027550397</v>
       </c>
       <c r="H62" s="23">
-        <f>H51/(Model!T26*(1-Model!T49)+Model!T86+Model!T102+SUM(Model!T94:T100))</f>
+        <f>H51/(Model!X26*(1-Model!X49)+Model!X86+Model!X102+SUM(Model!X94:X100))</f>
         <v>154.91277282965646</v>
       </c>
       <c r="I62" s="23">
-        <f>I51/(Model!U26*(1-Model!U49)+Model!U86+Model!U102+SUM(Model!U94:U100))</f>
-        <v>29.788880806991376</v>
+        <f>I51/(Model!Y26*(1-Model!Y49)+Model!Y86+Model!Y102+SUM(Model!Y94:Y100))</f>
+        <v>30.510912344460252</v>
       </c>
       <c r="J62" s="23">
-        <f>J51/(Model!V26*(1-Model!V49)+Model!V86+Model!V102+SUM(Model!V94:V100))</f>
+        <f>J51/(Model!Z26*(1-Model!Z49)+Model!Z86+Model!Z102+SUM(Model!Z94:Z100))</f>
         <v>0</v>
       </c>
       <c r="K62" s="23">
-        <f>K51/(Model!W26*(1-Model!W49)+Model!W86+Model!W102+SUM(Model!W94:W100))</f>
+        <f>K51/(Model!AA26*(1-Model!AA49)+Model!AA86+Model!AA102+SUM(Model!AA94:AA100))</f>
         <v>0</v>
       </c>
       <c r="M62" s="23">
-        <f t="shared" si="15"/>
-        <v>56.22178946010898</v>
+        <f t="shared" si="16"/>
+        <v>56.402297344476196</v>
       </c>
       <c r="N62" s="23">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>23.749409176237659</v>
       </c>
       <c r="P62" s="2" t="s">
@@ -9486,43 +9897,43 @@
         <v>261</v>
       </c>
       <c r="D63" s="23">
-        <f>D51/Model!P19</f>
+        <f>D51/Model!T19</f>
         <v>1.4218290511642644</v>
       </c>
       <c r="E63" s="23">
-        <f>E51/Model!Q19</f>
+        <f>E51/Model!U19</f>
         <v>0.97163651417253794</v>
       </c>
       <c r="F63" s="23">
-        <f>F51/Model!R19</f>
+        <f>F51/Model!V19</f>
         <v>2.2494233548445739</v>
       </c>
       <c r="G63" s="23">
-        <f>G51/Model!S19</f>
+        <f>G51/Model!W19</f>
         <v>1.2846671222963739</v>
       </c>
       <c r="H63" s="23">
-        <f>H51/Model!T19</f>
+        <f>H51/Model!X19</f>
         <v>1.3138051399838599</v>
       </c>
       <c r="I63" s="23">
-        <f>I51/Model!U19</f>
-        <v>3.5135666783575115</v>
+        <f>I51/Model!Y19</f>
+        <v>3.5987295271134299</v>
       </c>
       <c r="J63" s="23">
-        <f>J51/Model!V19</f>
+        <f>J51/Model!Z19</f>
         <v>0</v>
       </c>
       <c r="K63" s="23">
-        <f>K51/Model!W19</f>
+        <f>K51/Model!AA19</f>
         <v>0</v>
       </c>
       <c r="M63" s="23">
-        <f t="shared" si="15"/>
-        <v>1.8834669979505025</v>
+        <f t="shared" si="16"/>
+        <v>1.9047577101394821</v>
       </c>
       <c r="N63" s="23">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1.3138051399838599</v>
       </c>
       <c r="P63" s="2" t="s">
